--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A0C30BD-B245-472B-ADA2-B2CCDF169E1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAAF84B-7B37-4842-9C06-9CE1CCE32940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="630">
   <si>
     <t>id</t>
   </si>
@@ -320,9 +320,6 @@
     <t>الصنف</t>
   </si>
   <si>
-    <t>الشارات (|)</t>
-  </si>
-  <si>
     <t>فيديوهات (|)</t>
   </si>
   <si>
@@ -2193,6 +2190,12 @@
   </si>
   <si>
     <t>custom_label_1</t>
+  </si>
+  <si>
+    <t>custom_label_0</t>
+  </si>
+  <si>
+    <t>end</t>
   </si>
 </sst>
 </file>
@@ -2200,7 +2203,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -2252,7 +2255,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -2618,46 +2621,49 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>616</v>
+      </c>
+      <c r="C1" t="s">
         <v>617</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>618</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>619</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>620</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>621</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>622</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>623</v>
       </c>
-      <c r="I1" t="s">
-        <v>624</v>
-      </c>
       <c r="J1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K1" t="s">
+        <v>628</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="M1" t="s">
+        <v>629</v>
+      </c>
+      <c r="N1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
-      </c>
-      <c r="P1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -2665,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1">
         <v>350</v>
@@ -2674,34 +2680,34 @@
         <v>450</v>
       </c>
       <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
-        <v>15</v>
-      </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O2">
         <v>4</v>
@@ -2715,7 +2721,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1">
         <v>200</v>
@@ -2724,34 +2730,34 @@
         <v>280</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" t="s">
         <v>23</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>24</v>
       </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
       <c r="N3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O3">
         <v>4</v>
@@ -2765,7 +2771,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1">
         <v>600</v>
@@ -2774,34 +2780,34 @@
         <v>800</v>
       </c>
       <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" t="s">
+        <v>624</v>
+      </c>
+      <c r="J4" t="s">
+        <v>626</v>
+      </c>
+      <c r="K4" t="s">
         <v>29</v>
       </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" t="s">
-        <v>625</v>
-      </c>
-      <c r="J4" t="s">
-        <v>627</v>
-      </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>30</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>31</v>
       </c>
-      <c r="M4" t="s">
-        <v>32</v>
-      </c>
       <c r="N4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -2815,7 +2821,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1">
         <v>250</v>
@@ -2824,34 +2830,34 @@
         <v>320</v>
       </c>
       <c r="E5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>624</v>
+      </c>
+      <c r="J5" t="s">
+        <v>626</v>
+      </c>
+      <c r="K5" t="s">
         <v>36</v>
       </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" t="s">
-        <v>625</v>
-      </c>
-      <c r="J5" t="s">
-        <v>627</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
         <v>37</v>
       </c>
-      <c r="L5" t="s">
+      <c r="M5" t="s">
         <v>38</v>
       </c>
-      <c r="M5" t="s">
-        <v>39</v>
-      </c>
       <c r="N5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O5">
         <v>4</v>
@@ -2865,7 +2871,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" s="1">
         <v>800</v>
@@ -2874,34 +2880,34 @@
         <v>1000</v>
       </c>
       <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" t="s">
         <v>41</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>42</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" t="s">
+        <v>624</v>
+      </c>
+      <c r="J6" t="s">
+        <v>626</v>
+      </c>
+      <c r="K6" t="s">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6" t="s">
-        <v>625</v>
-      </c>
-      <c r="J6" t="s">
-        <v>627</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
         <v>44</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>45</v>
       </c>
-      <c r="M6" t="s">
-        <v>46</v>
-      </c>
       <c r="N6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O6">
         <v>5</v>
@@ -2915,7 +2921,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1">
         <v>1250</v>
@@ -2924,34 +2930,34 @@
         <v>1800</v>
       </c>
       <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>49</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" t="s">
+        <v>624</v>
+      </c>
+      <c r="J7" t="s">
+        <v>626</v>
+      </c>
+      <c r="K7" t="s">
         <v>50</v>
       </c>
-      <c r="H7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I7" t="s">
-        <v>625</v>
-      </c>
-      <c r="J7" t="s">
-        <v>627</v>
-      </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>51</v>
       </c>
-      <c r="L7" t="s">
+      <c r="M7" t="s">
         <v>52</v>
       </c>
-      <c r="M7" t="s">
-        <v>53</v>
-      </c>
       <c r="N7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O7">
         <v>5</v>
@@ -2965,7 +2971,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1">
         <v>5200</v>
@@ -2974,34 +2980,34 @@
         <v>5800</v>
       </c>
       <c r="E8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
         <v>55</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>56</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" t="s">
+        <v>624</v>
+      </c>
+      <c r="J8" t="s">
+        <v>626</v>
+      </c>
+      <c r="K8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
-        <v>625</v>
-      </c>
-      <c r="J8" t="s">
-        <v>627</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>58</v>
       </c>
-      <c r="L8" t="s">
+      <c r="M8" t="s">
         <v>59</v>
       </c>
-      <c r="M8" t="s">
-        <v>60</v>
-      </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O8">
         <v>5</v>
@@ -3015,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1">
         <v>400</v>
@@ -3024,34 +3030,34 @@
         <v>520</v>
       </c>
       <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
         <v>62</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>63</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>64</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
+        <v>624</v>
+      </c>
+      <c r="J9" t="s">
+        <v>626</v>
+      </c>
+      <c r="K9" t="s">
         <v>65</v>
       </c>
-      <c r="I9" t="s">
-        <v>625</v>
-      </c>
-      <c r="J9" t="s">
-        <v>627</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="L9" t="s">
         <v>66</v>
       </c>
-      <c r="L9" t="s">
+      <c r="M9" t="s">
         <v>67</v>
       </c>
-      <c r="M9" t="s">
-        <v>68</v>
-      </c>
       <c r="N9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O9">
         <v>4</v>
@@ -3065,7 +3071,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1">
         <v>100</v>
@@ -3074,34 +3080,34 @@
         <v>150</v>
       </c>
       <c r="E10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F10" t="s">
         <v>70</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>71</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>624</v>
+      </c>
+      <c r="J10" t="s">
+        <v>626</v>
+      </c>
+      <c r="K10" t="s">
         <v>72</v>
       </c>
-      <c r="H10" t="s">
-        <v>65</v>
-      </c>
-      <c r="I10" t="s">
-        <v>625</v>
-      </c>
-      <c r="J10" t="s">
-        <v>627</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="L10" t="s">
         <v>73</v>
       </c>
-      <c r="L10" t="s">
-        <v>74</v>
-      </c>
       <c r="M10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O10">
         <v>4</v>
@@ -3115,7 +3121,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C11" s="1">
         <v>80</v>
@@ -3124,34 +3130,34 @@
         <v>120</v>
       </c>
       <c r="E11" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" t="s">
         <v>76</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>77</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" t="s">
+        <v>624</v>
+      </c>
+      <c r="J11" t="s">
+        <v>626</v>
+      </c>
+      <c r="K11" t="s">
         <v>78</v>
       </c>
-      <c r="H11" t="s">
-        <v>65</v>
-      </c>
-      <c r="I11" t="s">
-        <v>625</v>
-      </c>
-      <c r="J11" t="s">
-        <v>627</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="L11" t="s">
         <v>79</v>
       </c>
-      <c r="L11" t="s">
-        <v>80</v>
-      </c>
       <c r="M11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O11">
         <v>4</v>
@@ -3165,7 +3171,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C12" s="1">
         <v>3500</v>
@@ -3174,34 +3180,34 @@
         <v>4200</v>
       </c>
       <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
         <v>82</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>83</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>84</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
+        <v>624</v>
+      </c>
+      <c r="J12" t="s">
+        <v>626</v>
+      </c>
+      <c r="K12" t="s">
+        <v>12</v>
+      </c>
+      <c r="L12" t="s">
         <v>85</v>
       </c>
-      <c r="I12" t="s">
-        <v>625</v>
-      </c>
-      <c r="J12" t="s">
-        <v>627</v>
-      </c>
-      <c r="K12" t="s">
-        <v>13</v>
-      </c>
-      <c r="L12" t="s">
-        <v>86</v>
-      </c>
       <c r="M12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O12">
         <v>4.0999999999999996</v>
@@ -3215,7 +3221,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="1">
         <v>2999</v>
@@ -3224,34 +3230,34 @@
         <v>3400</v>
       </c>
       <c r="E13" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" t="s">
         <v>88</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>89</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" t="s">
+        <v>624</v>
+      </c>
+      <c r="J13" t="s">
+        <v>626</v>
+      </c>
+      <c r="K13" t="s">
         <v>90</v>
       </c>
-      <c r="H13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" t="s">
-        <v>625</v>
-      </c>
-      <c r="J13" t="s">
-        <v>627</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="L13" t="s">
         <v>91</v>
       </c>
-      <c r="L13" t="s">
-        <v>92</v>
-      </c>
       <c r="M13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O13">
         <v>4.2</v>
@@ -3265,7 +3271,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1">
         <v>800</v>
@@ -3274,34 +3280,34 @@
         <v>1100</v>
       </c>
       <c r="E14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" t="s">
         <v>94</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>95</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" t="s">
+        <v>624</v>
+      </c>
+      <c r="J14" t="s">
+        <v>626</v>
+      </c>
+      <c r="K14" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" t="s">
         <v>96</v>
       </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>625</v>
-      </c>
-      <c r="J14" t="s">
-        <v>627</v>
-      </c>
-      <c r="K14" t="s">
-        <v>13</v>
-      </c>
-      <c r="L14" t="s">
-        <v>97</v>
-      </c>
       <c r="M14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O14">
         <v>4.3</v>
@@ -3315,7 +3321,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="1">
         <v>5500</v>
@@ -3324,34 +3330,34 @@
         <v>6200</v>
       </c>
       <c r="E15" t="s">
+        <v>98</v>
+      </c>
+      <c r="F15" t="s">
         <v>99</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>100</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" t="s">
+        <v>624</v>
+      </c>
+      <c r="J15" t="s">
+        <v>626</v>
+      </c>
+      <c r="K15" t="s">
+        <v>90</v>
+      </c>
+      <c r="L15" t="s">
         <v>101</v>
       </c>
-      <c r="H15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" t="s">
-        <v>625</v>
-      </c>
-      <c r="J15" t="s">
-        <v>627</v>
-      </c>
-      <c r="K15" t="s">
-        <v>91</v>
-      </c>
-      <c r="L15" t="s">
-        <v>102</v>
-      </c>
       <c r="M15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O15">
         <v>4.4000000000000004</v>
@@ -3365,7 +3371,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1">
         <v>3200</v>
@@ -3374,34 +3380,34 @@
         <v>3800</v>
       </c>
       <c r="E16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" t="s">
         <v>104</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>105</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" t="s">
+        <v>624</v>
+      </c>
+      <c r="J16" t="s">
+        <v>626</v>
+      </c>
+      <c r="K16" t="s">
+        <v>12</v>
+      </c>
+      <c r="L16" t="s">
         <v>106</v>
       </c>
-      <c r="H16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" t="s">
-        <v>625</v>
-      </c>
-      <c r="J16" t="s">
-        <v>627</v>
-      </c>
-      <c r="K16" t="s">
-        <v>13</v>
-      </c>
-      <c r="L16" t="s">
-        <v>107</v>
-      </c>
       <c r="M16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O16">
         <v>4.5</v>
@@ -3415,7 +3421,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="1">
         <v>2200</v>
@@ -3424,34 +3430,34 @@
         <v>2600</v>
       </c>
       <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
         <v>109</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>110</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" t="s">
+        <v>624</v>
+      </c>
+      <c r="J17" t="s">
+        <v>626</v>
+      </c>
+      <c r="K17" t="s">
+        <v>90</v>
+      </c>
+      <c r="L17" t="s">
         <v>111</v>
       </c>
-      <c r="H17" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" t="s">
-        <v>625</v>
-      </c>
-      <c r="J17" t="s">
-        <v>627</v>
-      </c>
-      <c r="K17" t="s">
-        <v>91</v>
-      </c>
-      <c r="L17" t="s">
-        <v>112</v>
-      </c>
       <c r="M17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O17">
         <v>4.5999999999999996</v>
@@ -3465,7 +3471,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C18" s="1">
         <v>1500</v>
@@ -3474,34 +3480,34 @@
         <v>1800</v>
       </c>
       <c r="E18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" t="s">
         <v>114</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>115</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
+        <v>84</v>
+      </c>
+      <c r="I18" t="s">
+        <v>624</v>
+      </c>
+      <c r="J18" t="s">
+        <v>626</v>
+      </c>
+      <c r="K18" t="s">
+        <v>12</v>
+      </c>
+      <c r="L18" t="s">
         <v>116</v>
       </c>
-      <c r="H18" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" t="s">
-        <v>625</v>
-      </c>
-      <c r="J18" t="s">
-        <v>627</v>
-      </c>
-      <c r="K18" t="s">
-        <v>13</v>
-      </c>
-      <c r="L18" t="s">
-        <v>117</v>
-      </c>
       <c r="M18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O18">
         <v>4.7</v>
@@ -3515,7 +3521,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C19" s="1">
         <v>1200</v>
@@ -3524,34 +3530,34 @@
         <v>1450</v>
       </c>
       <c r="E19" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" t="s">
         <v>119</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>120</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" t="s">
+        <v>624</v>
+      </c>
+      <c r="J19" t="s">
+        <v>626</v>
+      </c>
+      <c r="K19" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" t="s">
         <v>121</v>
       </c>
-      <c r="H19" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" t="s">
-        <v>625</v>
-      </c>
-      <c r="J19" t="s">
-        <v>627</v>
-      </c>
-      <c r="K19" t="s">
-        <v>91</v>
-      </c>
-      <c r="L19" t="s">
-        <v>122</v>
-      </c>
       <c r="M19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O19">
         <v>4.8</v>
@@ -3565,7 +3571,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="1">
         <v>1700</v>
@@ -3574,34 +3580,34 @@
         <v>2000</v>
       </c>
       <c r="E20" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" t="s">
         <v>124</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>125</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" t="s">
+        <v>624</v>
+      </c>
+      <c r="J20" t="s">
+        <v>626</v>
+      </c>
+      <c r="K20" t="s">
+        <v>12</v>
+      </c>
+      <c r="L20" t="s">
         <v>126</v>
       </c>
-      <c r="H20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" t="s">
-        <v>625</v>
-      </c>
-      <c r="J20" t="s">
-        <v>627</v>
-      </c>
-      <c r="K20" t="s">
-        <v>13</v>
-      </c>
-      <c r="L20" t="s">
-        <v>127</v>
-      </c>
       <c r="M20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O20">
         <v>4.9000000000000004</v>
@@ -3615,7 +3621,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C21" s="1">
         <v>950</v>
@@ -3624,34 +3630,34 @@
         <v>1200</v>
       </c>
       <c r="E21" t="s">
+        <v>128</v>
+      </c>
+      <c r="F21" t="s">
         <v>129</v>
       </c>
-      <c r="F21" t="s">
+      <c r="G21" t="s">
         <v>130</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" t="s">
+        <v>624</v>
+      </c>
+      <c r="J21" t="s">
+        <v>626</v>
+      </c>
+      <c r="K21" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" t="s">
         <v>131</v>
       </c>
-      <c r="H21" t="s">
-        <v>85</v>
-      </c>
-      <c r="I21" t="s">
-        <v>625</v>
-      </c>
-      <c r="J21" t="s">
-        <v>627</v>
-      </c>
-      <c r="K21" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" t="s">
-        <v>132</v>
-      </c>
       <c r="M21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O21">
         <v>4</v>
@@ -3665,7 +3671,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C22" s="1">
         <v>4500</v>
@@ -3674,34 +3680,34 @@
         <v>5100</v>
       </c>
       <c r="E22" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" t="s">
         <v>134</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>135</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>136</v>
       </c>
-      <c r="H22" t="s">
+      <c r="I22" t="s">
+        <v>624</v>
+      </c>
+      <c r="J22" t="s">
+        <v>626</v>
+      </c>
+      <c r="K22" t="s">
+        <v>12</v>
+      </c>
+      <c r="L22" t="s">
         <v>137</v>
       </c>
-      <c r="I22" t="s">
-        <v>625</v>
-      </c>
-      <c r="J22" t="s">
-        <v>627</v>
-      </c>
-      <c r="K22" t="s">
-        <v>13</v>
-      </c>
-      <c r="L22" t="s">
-        <v>138</v>
-      </c>
       <c r="M22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O22">
         <v>4.0999999999999996</v>
@@ -3715,7 +3721,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C23" s="1">
         <v>6500</v>
@@ -3724,34 +3730,34 @@
         <v>7500</v>
       </c>
       <c r="E23" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" t="s">
         <v>140</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>141</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
+        <v>136</v>
+      </c>
+      <c r="I23" t="s">
+        <v>624</v>
+      </c>
+      <c r="J23" t="s">
+        <v>626</v>
+      </c>
+      <c r="K23" t="s">
+        <v>90</v>
+      </c>
+      <c r="L23" t="s">
         <v>142</v>
       </c>
-      <c r="H23" t="s">
-        <v>137</v>
-      </c>
-      <c r="I23" t="s">
-        <v>625</v>
-      </c>
-      <c r="J23" t="s">
-        <v>627</v>
-      </c>
-      <c r="K23" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" t="s">
-        <v>143</v>
-      </c>
       <c r="M23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O23">
         <v>4.2</v>
@@ -3765,7 +3771,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C24" s="1">
         <v>2100</v>
@@ -3774,34 +3780,34 @@
         <v>2500</v>
       </c>
       <c r="E24" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" t="s">
         <v>145</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>146</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
+        <v>624</v>
+      </c>
+      <c r="J24" t="s">
+        <v>626</v>
+      </c>
+      <c r="K24" t="s">
+        <v>12</v>
+      </c>
+      <c r="L24" t="s">
         <v>147</v>
       </c>
-      <c r="H24" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" t="s">
-        <v>625</v>
-      </c>
-      <c r="J24" t="s">
-        <v>627</v>
-      </c>
-      <c r="K24" t="s">
-        <v>13</v>
-      </c>
-      <c r="L24" t="s">
-        <v>148</v>
-      </c>
       <c r="M24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O24">
         <v>4.3</v>
@@ -3815,7 +3821,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" s="1">
         <v>3800</v>
@@ -3824,34 +3830,34 @@
         <v>4400</v>
       </c>
       <c r="E25" t="s">
+        <v>149</v>
+      </c>
+      <c r="F25" t="s">
         <v>150</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>151</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" t="s">
+        <v>624</v>
+      </c>
+      <c r="J25" t="s">
+        <v>626</v>
+      </c>
+      <c r="K25" t="s">
+        <v>90</v>
+      </c>
+      <c r="L25" t="s">
         <v>152</v>
       </c>
-      <c r="H25" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" t="s">
-        <v>625</v>
-      </c>
-      <c r="J25" t="s">
-        <v>627</v>
-      </c>
-      <c r="K25" t="s">
-        <v>91</v>
-      </c>
-      <c r="L25" t="s">
-        <v>153</v>
-      </c>
       <c r="M25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O25">
         <v>4.4000000000000004</v>
@@ -3865,7 +3871,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C26" s="1">
         <v>8500</v>
@@ -3874,34 +3880,34 @@
         <v>9800</v>
       </c>
       <c r="E26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" t="s">
         <v>155</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>156</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
+        <v>136</v>
+      </c>
+      <c r="I26" t="s">
+        <v>624</v>
+      </c>
+      <c r="J26" t="s">
+        <v>626</v>
+      </c>
+      <c r="K26" t="s">
+        <v>12</v>
+      </c>
+      <c r="L26" t="s">
         <v>157</v>
       </c>
-      <c r="H26" t="s">
-        <v>137</v>
-      </c>
-      <c r="I26" t="s">
-        <v>625</v>
-      </c>
-      <c r="J26" t="s">
-        <v>627</v>
-      </c>
-      <c r="K26" t="s">
-        <v>13</v>
-      </c>
-      <c r="L26" t="s">
-        <v>158</v>
-      </c>
       <c r="M26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O26">
         <v>4.5</v>
@@ -3915,7 +3921,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C27" s="1">
         <v>3300</v>
@@ -3924,34 +3930,34 @@
         <v>3900</v>
       </c>
       <c r="E27" t="s">
+        <v>159</v>
+      </c>
+      <c r="F27" t="s">
         <v>160</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>161</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
+        <v>136</v>
+      </c>
+      <c r="I27" t="s">
+        <v>624</v>
+      </c>
+      <c r="J27" t="s">
+        <v>626</v>
+      </c>
+      <c r="K27" t="s">
+        <v>90</v>
+      </c>
+      <c r="L27" t="s">
         <v>162</v>
       </c>
-      <c r="H27" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" t="s">
-        <v>625</v>
-      </c>
-      <c r="J27" t="s">
-        <v>627</v>
-      </c>
-      <c r="K27" t="s">
-        <v>91</v>
-      </c>
-      <c r="L27" t="s">
-        <v>163</v>
-      </c>
       <c r="M27" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O27">
         <v>4.5999999999999996</v>
@@ -3965,7 +3971,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C28" s="1">
         <v>1600</v>
@@ -3974,34 +3980,34 @@
         <v>1950</v>
       </c>
       <c r="E28" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" t="s">
         <v>165</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>166</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
+        <v>136</v>
+      </c>
+      <c r="I28" t="s">
+        <v>624</v>
+      </c>
+      <c r="J28" t="s">
+        <v>626</v>
+      </c>
+      <c r="K28" t="s">
+        <v>12</v>
+      </c>
+      <c r="L28" t="s">
         <v>167</v>
       </c>
-      <c r="H28" t="s">
-        <v>137</v>
-      </c>
-      <c r="I28" t="s">
-        <v>625</v>
-      </c>
-      <c r="J28" t="s">
-        <v>627</v>
-      </c>
-      <c r="K28" t="s">
-        <v>13</v>
-      </c>
-      <c r="L28" t="s">
-        <v>168</v>
-      </c>
       <c r="M28" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O28">
         <v>4.7</v>
@@ -4015,7 +4021,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="1">
         <v>1400</v>
@@ -4024,34 +4030,34 @@
         <v>1700</v>
       </c>
       <c r="E29" t="s">
+        <v>169</v>
+      </c>
+      <c r="F29" t="s">
         <v>170</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>171</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
+        <v>136</v>
+      </c>
+      <c r="I29" t="s">
+        <v>624</v>
+      </c>
+      <c r="J29" t="s">
+        <v>626</v>
+      </c>
+      <c r="K29" t="s">
+        <v>90</v>
+      </c>
+      <c r="L29" t="s">
         <v>172</v>
       </c>
-      <c r="H29" t="s">
-        <v>137</v>
-      </c>
-      <c r="I29" t="s">
-        <v>625</v>
-      </c>
-      <c r="J29" t="s">
-        <v>627</v>
-      </c>
-      <c r="K29" t="s">
-        <v>91</v>
-      </c>
-      <c r="L29" t="s">
-        <v>173</v>
-      </c>
       <c r="M29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O29">
         <v>4.8</v>
@@ -4065,7 +4071,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C30" s="1">
         <v>5800</v>
@@ -4074,34 +4080,34 @@
         <v>6600</v>
       </c>
       <c r="E30" t="s">
+        <v>174</v>
+      </c>
+      <c r="F30" t="s">
         <v>175</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>176</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s">
+        <v>624</v>
+      </c>
+      <c r="J30" t="s">
+        <v>626</v>
+      </c>
+      <c r="K30" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" t="s">
         <v>177</v>
       </c>
-      <c r="H30" t="s">
-        <v>137</v>
-      </c>
-      <c r="I30" t="s">
-        <v>625</v>
-      </c>
-      <c r="J30" t="s">
-        <v>627</v>
-      </c>
-      <c r="K30" t="s">
-        <v>13</v>
-      </c>
-      <c r="L30" t="s">
-        <v>178</v>
-      </c>
       <c r="M30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O30">
         <v>4.9000000000000004</v>
@@ -4115,7 +4121,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C31" s="1">
         <v>4900</v>
@@ -4124,34 +4130,34 @@
         <v>5600</v>
       </c>
       <c r="E31" t="s">
+        <v>179</v>
+      </c>
+      <c r="F31" t="s">
         <v>180</v>
       </c>
-      <c r="F31" t="s">
+      <c r="G31" t="s">
         <v>181</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" t="s">
+        <v>624</v>
+      </c>
+      <c r="J31" t="s">
+        <v>626</v>
+      </c>
+      <c r="K31" t="s">
+        <v>90</v>
+      </c>
+      <c r="L31" t="s">
         <v>182</v>
       </c>
-      <c r="H31" t="s">
-        <v>137</v>
-      </c>
-      <c r="I31" t="s">
-        <v>625</v>
-      </c>
-      <c r="J31" t="s">
-        <v>627</v>
-      </c>
-      <c r="K31" t="s">
-        <v>91</v>
-      </c>
-      <c r="L31" t="s">
-        <v>183</v>
-      </c>
       <c r="M31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O31">
         <v>4</v>
@@ -4165,7 +4171,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="1">
         <v>1200</v>
@@ -4174,34 +4180,34 @@
         <v>1500</v>
       </c>
       <c r="E32" t="s">
+        <v>184</v>
+      </c>
+      <c r="F32" t="s">
         <v>185</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>186</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>187</v>
       </c>
-      <c r="H32" t="s">
+      <c r="I32" t="s">
+        <v>624</v>
+      </c>
+      <c r="J32" t="s">
+        <v>626</v>
+      </c>
+      <c r="K32" t="s">
+        <v>12</v>
+      </c>
+      <c r="L32" t="s">
         <v>188</v>
       </c>
-      <c r="I32" t="s">
-        <v>625</v>
-      </c>
-      <c r="J32" t="s">
-        <v>627</v>
-      </c>
-      <c r="K32" t="s">
-        <v>13</v>
-      </c>
-      <c r="L32" t="s">
-        <v>189</v>
-      </c>
       <c r="M32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O32">
         <v>4.0999999999999996</v>
@@ -4215,7 +4221,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C33" s="1">
         <v>1600</v>
@@ -4224,34 +4230,34 @@
         <v>1900</v>
       </c>
       <c r="E33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" t="s">
         <v>191</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>192</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
+        <v>187</v>
+      </c>
+      <c r="I33" t="s">
+        <v>624</v>
+      </c>
+      <c r="J33" t="s">
+        <v>626</v>
+      </c>
+      <c r="K33" t="s">
+        <v>90</v>
+      </c>
+      <c r="L33" t="s">
         <v>193</v>
       </c>
-      <c r="H33" t="s">
-        <v>188</v>
-      </c>
-      <c r="I33" t="s">
-        <v>625</v>
-      </c>
-      <c r="J33" t="s">
-        <v>627</v>
-      </c>
-      <c r="K33" t="s">
-        <v>91</v>
-      </c>
-      <c r="L33" t="s">
-        <v>194</v>
-      </c>
       <c r="M33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O33">
         <v>4.2</v>
@@ -4265,7 +4271,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C34" s="1">
         <v>3999</v>
@@ -4274,34 +4280,34 @@
         <v>4600</v>
       </c>
       <c r="E34" t="s">
+        <v>195</v>
+      </c>
+      <c r="F34" t="s">
         <v>196</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>197</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
+        <v>187</v>
+      </c>
+      <c r="I34" t="s">
+        <v>624</v>
+      </c>
+      <c r="J34" t="s">
+        <v>626</v>
+      </c>
+      <c r="K34" t="s">
+        <v>12</v>
+      </c>
+      <c r="L34" t="s">
         <v>198</v>
       </c>
-      <c r="H34" t="s">
-        <v>188</v>
-      </c>
-      <c r="I34" t="s">
-        <v>625</v>
-      </c>
-      <c r="J34" t="s">
-        <v>627</v>
-      </c>
-      <c r="K34" t="s">
-        <v>13</v>
-      </c>
-      <c r="L34" t="s">
-        <v>199</v>
-      </c>
       <c r="M34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O34">
         <v>4.3</v>
@@ -4315,7 +4321,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C35" s="1">
         <v>450</v>
@@ -4324,34 +4330,34 @@
         <v>550</v>
       </c>
       <c r="E35" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" t="s">
         <v>201</v>
       </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>202</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
+        <v>187</v>
+      </c>
+      <c r="I35" t="s">
+        <v>624</v>
+      </c>
+      <c r="J35" t="s">
+        <v>626</v>
+      </c>
+      <c r="K35" t="s">
+        <v>90</v>
+      </c>
+      <c r="L35" t="s">
         <v>203</v>
       </c>
-      <c r="H35" t="s">
-        <v>188</v>
-      </c>
-      <c r="I35" t="s">
-        <v>625</v>
-      </c>
-      <c r="J35" t="s">
-        <v>627</v>
-      </c>
-      <c r="K35" t="s">
-        <v>91</v>
-      </c>
-      <c r="L35" t="s">
-        <v>204</v>
-      </c>
       <c r="M35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O35">
         <v>4.4000000000000004</v>
@@ -4365,7 +4371,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C36" s="1">
         <v>2700</v>
@@ -4374,34 +4380,34 @@
         <v>3200</v>
       </c>
       <c r="E36" t="s">
+        <v>205</v>
+      </c>
+      <c r="F36" t="s">
         <v>206</v>
       </c>
-      <c r="F36" t="s">
+      <c r="G36" t="s">
         <v>207</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
+        <v>187</v>
+      </c>
+      <c r="I36" t="s">
+        <v>624</v>
+      </c>
+      <c r="J36" t="s">
+        <v>626</v>
+      </c>
+      <c r="K36" t="s">
+        <v>12</v>
+      </c>
+      <c r="L36" t="s">
         <v>208</v>
       </c>
-      <c r="H36" t="s">
-        <v>188</v>
-      </c>
-      <c r="I36" t="s">
-        <v>625</v>
-      </c>
-      <c r="J36" t="s">
-        <v>627</v>
-      </c>
-      <c r="K36" t="s">
-        <v>13</v>
-      </c>
-      <c r="L36" t="s">
-        <v>209</v>
-      </c>
       <c r="M36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O36">
         <v>4.5</v>
@@ -4415,7 +4421,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C37" s="1">
         <v>2200</v>
@@ -4424,34 +4430,34 @@
         <v>2550</v>
       </c>
       <c r="E37" t="s">
+        <v>210</v>
+      </c>
+      <c r="F37" t="s">
         <v>211</v>
       </c>
-      <c r="F37" t="s">
+      <c r="G37" t="s">
         <v>212</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
+        <v>187</v>
+      </c>
+      <c r="I37" t="s">
+        <v>624</v>
+      </c>
+      <c r="J37" t="s">
+        <v>626</v>
+      </c>
+      <c r="K37" t="s">
+        <v>90</v>
+      </c>
+      <c r="L37" t="s">
         <v>213</v>
       </c>
-      <c r="H37" t="s">
-        <v>188</v>
-      </c>
-      <c r="I37" t="s">
-        <v>625</v>
-      </c>
-      <c r="J37" t="s">
-        <v>627</v>
-      </c>
-      <c r="K37" t="s">
-        <v>91</v>
-      </c>
-      <c r="L37" t="s">
-        <v>214</v>
-      </c>
       <c r="M37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O37">
         <v>4.5999999999999996</v>
@@ -4465,7 +4471,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C38" s="1">
         <v>750</v>
@@ -4474,34 +4480,34 @@
         <v>900</v>
       </c>
       <c r="E38" t="s">
+        <v>215</v>
+      </c>
+      <c r="F38" t="s">
         <v>216</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>217</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
+        <v>187</v>
+      </c>
+      <c r="I38" t="s">
+        <v>624</v>
+      </c>
+      <c r="J38" t="s">
+        <v>626</v>
+      </c>
+      <c r="K38" t="s">
+        <v>12</v>
+      </c>
+      <c r="L38" t="s">
         <v>218</v>
       </c>
-      <c r="H38" t="s">
-        <v>188</v>
-      </c>
-      <c r="I38" t="s">
-        <v>625</v>
-      </c>
-      <c r="J38" t="s">
-        <v>627</v>
-      </c>
-      <c r="K38" t="s">
-        <v>13</v>
-      </c>
-      <c r="L38" t="s">
-        <v>219</v>
-      </c>
       <c r="M38" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O38">
         <v>4.7</v>
@@ -4515,7 +4521,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C39" s="1">
         <v>4200</v>
@@ -4524,34 +4530,34 @@
         <v>4800</v>
       </c>
       <c r="E39" t="s">
+        <v>220</v>
+      </c>
+      <c r="F39" t="s">
         <v>221</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>222</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
+        <v>187</v>
+      </c>
+      <c r="I39" t="s">
+        <v>624</v>
+      </c>
+      <c r="J39" t="s">
+        <v>626</v>
+      </c>
+      <c r="K39" t="s">
+        <v>90</v>
+      </c>
+      <c r="L39" t="s">
         <v>223</v>
       </c>
-      <c r="H39" t="s">
-        <v>188</v>
-      </c>
-      <c r="I39" t="s">
-        <v>625</v>
-      </c>
-      <c r="J39" t="s">
-        <v>627</v>
-      </c>
-      <c r="K39" t="s">
-        <v>91</v>
-      </c>
-      <c r="L39" t="s">
-        <v>224</v>
-      </c>
       <c r="M39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N39" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O39">
         <v>4.8</v>
@@ -4565,7 +4571,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C40" s="1">
         <v>1100</v>
@@ -4574,34 +4580,34 @@
         <v>1350</v>
       </c>
       <c r="E40" t="s">
+        <v>225</v>
+      </c>
+      <c r="F40" t="s">
         <v>226</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>227</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
+        <v>187</v>
+      </c>
+      <c r="I40" t="s">
+        <v>624</v>
+      </c>
+      <c r="J40" t="s">
+        <v>626</v>
+      </c>
+      <c r="K40" t="s">
+        <v>12</v>
+      </c>
+      <c r="L40" t="s">
         <v>228</v>
       </c>
-      <c r="H40" t="s">
-        <v>188</v>
-      </c>
-      <c r="I40" t="s">
-        <v>625</v>
-      </c>
-      <c r="J40" t="s">
-        <v>627</v>
-      </c>
-      <c r="K40" t="s">
-        <v>13</v>
-      </c>
-      <c r="L40" t="s">
-        <v>229</v>
-      </c>
       <c r="M40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N40" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O40">
         <v>4.9000000000000004</v>
@@ -4615,7 +4621,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C41" s="1">
         <v>3400</v>
@@ -4624,34 +4630,34 @@
         <v>3950</v>
       </c>
       <c r="E41" t="s">
+        <v>230</v>
+      </c>
+      <c r="F41" t="s">
         <v>231</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>232</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
+        <v>187</v>
+      </c>
+      <c r="I41" t="s">
+        <v>624</v>
+      </c>
+      <c r="J41" t="s">
+        <v>626</v>
+      </c>
+      <c r="K41" t="s">
+        <v>90</v>
+      </c>
+      <c r="L41" t="s">
         <v>233</v>
       </c>
-      <c r="H41" t="s">
-        <v>188</v>
-      </c>
-      <c r="I41" t="s">
-        <v>625</v>
-      </c>
-      <c r="J41" t="s">
-        <v>627</v>
-      </c>
-      <c r="K41" t="s">
-        <v>91</v>
-      </c>
-      <c r="L41" t="s">
-        <v>234</v>
-      </c>
       <c r="M41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O41">
         <v>4</v>
@@ -4665,7 +4671,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C42" s="1">
         <v>350</v>
@@ -4674,34 +4680,34 @@
         <v>450</v>
       </c>
       <c r="E42" t="s">
+        <v>234</v>
+      </c>
+      <c r="F42" t="s">
         <v>235</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>236</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>237</v>
       </c>
-      <c r="H42" t="s">
-        <v>238</v>
-      </c>
       <c r="I42" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="J42" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L42" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M42" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O42">
         <v>4.0999999999999996</v>
@@ -4715,7 +4721,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C43" s="1">
         <v>280</v>
@@ -4724,34 +4730,34 @@
         <v>360</v>
       </c>
       <c r="E43" t="s">
+        <v>239</v>
+      </c>
+      <c r="F43" t="s">
         <v>240</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>241</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
+        <v>237</v>
+      </c>
+      <c r="I43" t="s">
+        <v>624</v>
+      </c>
+      <c r="J43" t="s">
+        <v>626</v>
+      </c>
+      <c r="K43" t="s">
+        <v>90</v>
+      </c>
+      <c r="L43" t="s">
         <v>242</v>
       </c>
-      <c r="H43" t="s">
-        <v>238</v>
-      </c>
-      <c r="I43" t="s">
-        <v>625</v>
-      </c>
-      <c r="J43" t="s">
-        <v>627</v>
-      </c>
-      <c r="K43" t="s">
-        <v>91</v>
-      </c>
-      <c r="L43" t="s">
-        <v>243</v>
-      </c>
       <c r="M43" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N43" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O43">
         <v>4.2</v>
@@ -4765,7 +4771,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C44" s="1">
         <v>190</v>
@@ -4774,34 +4780,34 @@
         <v>240</v>
       </c>
       <c r="E44" t="s">
+        <v>244</v>
+      </c>
+      <c r="F44" t="s">
         <v>245</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>246</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
+        <v>237</v>
+      </c>
+      <c r="I44" t="s">
+        <v>624</v>
+      </c>
+      <c r="J44" t="s">
+        <v>626</v>
+      </c>
+      <c r="K44" t="s">
+        <v>12</v>
+      </c>
+      <c r="L44" t="s">
         <v>247</v>
       </c>
-      <c r="H44" t="s">
-        <v>238</v>
-      </c>
-      <c r="I44" t="s">
-        <v>625</v>
-      </c>
-      <c r="J44" t="s">
-        <v>627</v>
-      </c>
-      <c r="K44" t="s">
-        <v>13</v>
-      </c>
-      <c r="L44" t="s">
-        <v>248</v>
-      </c>
       <c r="M44" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N44" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O44">
         <v>4.3</v>
@@ -4815,7 +4821,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C45" s="1">
         <v>150</v>
@@ -4824,34 +4830,34 @@
         <v>200</v>
       </c>
       <c r="E45" t="s">
+        <v>249</v>
+      </c>
+      <c r="F45" t="s">
         <v>250</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>251</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
+        <v>237</v>
+      </c>
+      <c r="I45" t="s">
+        <v>624</v>
+      </c>
+      <c r="J45" t="s">
+        <v>626</v>
+      </c>
+      <c r="K45" t="s">
+        <v>90</v>
+      </c>
+      <c r="L45" t="s">
         <v>252</v>
       </c>
-      <c r="H45" t="s">
-        <v>238</v>
-      </c>
-      <c r="I45" t="s">
-        <v>625</v>
-      </c>
-      <c r="J45" t="s">
-        <v>627</v>
-      </c>
-      <c r="K45" t="s">
-        <v>91</v>
-      </c>
-      <c r="L45" t="s">
-        <v>253</v>
-      </c>
       <c r="M45" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O45">
         <v>4.4000000000000004</v>
@@ -4865,7 +4871,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C46" s="1">
         <v>680</v>
@@ -4874,34 +4880,34 @@
         <v>800</v>
       </c>
       <c r="E46" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46" t="s">
         <v>255</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>256</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
+        <v>237</v>
+      </c>
+      <c r="I46" t="s">
+        <v>624</v>
+      </c>
+      <c r="J46" t="s">
+        <v>626</v>
+      </c>
+      <c r="K46" t="s">
+        <v>12</v>
+      </c>
+      <c r="L46" t="s">
         <v>257</v>
       </c>
-      <c r="H46" t="s">
-        <v>238</v>
-      </c>
-      <c r="I46" t="s">
-        <v>625</v>
-      </c>
-      <c r="J46" t="s">
-        <v>627</v>
-      </c>
-      <c r="K46" t="s">
-        <v>13</v>
-      </c>
-      <c r="L46" t="s">
-        <v>258</v>
-      </c>
       <c r="M46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O46">
         <v>4.5</v>
@@ -4915,7 +4921,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C47" s="1">
         <v>400</v>
@@ -4924,34 +4930,34 @@
         <v>490</v>
       </c>
       <c r="E47" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" t="s">
         <v>260</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>261</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
+        <v>237</v>
+      </c>
+      <c r="I47" t="s">
+        <v>624</v>
+      </c>
+      <c r="J47" t="s">
+        <v>626</v>
+      </c>
+      <c r="K47" t="s">
+        <v>90</v>
+      </c>
+      <c r="L47" t="s">
         <v>262</v>
       </c>
-      <c r="H47" t="s">
-        <v>238</v>
-      </c>
-      <c r="I47" t="s">
-        <v>625</v>
-      </c>
-      <c r="J47" t="s">
-        <v>627</v>
-      </c>
-      <c r="K47" t="s">
-        <v>91</v>
-      </c>
-      <c r="L47" t="s">
-        <v>263</v>
-      </c>
       <c r="M47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N47" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O47">
         <v>4.5999999999999996</v>
@@ -4965,7 +4971,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C48" s="1">
         <v>850</v>
@@ -4974,34 +4980,34 @@
         <v>1100</v>
       </c>
       <c r="E48" t="s">
+        <v>264</v>
+      </c>
+      <c r="F48" t="s">
         <v>265</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>266</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
+        <v>237</v>
+      </c>
+      <c r="I48" t="s">
+        <v>624</v>
+      </c>
+      <c r="J48" t="s">
+        <v>626</v>
+      </c>
+      <c r="K48" t="s">
+        <v>12</v>
+      </c>
+      <c r="L48" t="s">
         <v>267</v>
       </c>
-      <c r="H48" t="s">
-        <v>238</v>
-      </c>
-      <c r="I48" t="s">
-        <v>625</v>
-      </c>
-      <c r="J48" t="s">
-        <v>627</v>
-      </c>
-      <c r="K48" t="s">
-        <v>13</v>
-      </c>
-      <c r="L48" t="s">
-        <v>268</v>
-      </c>
       <c r="M48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N48" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O48">
         <v>4.7</v>
@@ -5015,7 +5021,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C49" s="1">
         <v>1900</v>
@@ -5024,34 +5030,34 @@
         <v>2300</v>
       </c>
       <c r="E49" t="s">
+        <v>269</v>
+      </c>
+      <c r="F49" t="s">
         <v>270</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>271</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
+        <v>237</v>
+      </c>
+      <c r="I49" t="s">
+        <v>624</v>
+      </c>
+      <c r="J49" t="s">
+        <v>626</v>
+      </c>
+      <c r="K49" t="s">
+        <v>90</v>
+      </c>
+      <c r="L49" t="s">
         <v>272</v>
       </c>
-      <c r="H49" t="s">
-        <v>238</v>
-      </c>
-      <c r="I49" t="s">
-        <v>625</v>
-      </c>
-      <c r="J49" t="s">
-        <v>627</v>
-      </c>
-      <c r="K49" t="s">
-        <v>91</v>
-      </c>
-      <c r="L49" t="s">
-        <v>273</v>
-      </c>
       <c r="M49" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N49" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O49">
         <v>4.8</v>
@@ -5065,7 +5071,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C50" s="1">
         <v>450</v>
@@ -5074,34 +5080,34 @@
         <v>520</v>
       </c>
       <c r="E50" t="s">
+        <v>274</v>
+      </c>
+      <c r="F50" t="s">
         <v>275</v>
       </c>
-      <c r="F50" t="s">
+      <c r="G50" t="s">
         <v>276</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
+        <v>237</v>
+      </c>
+      <c r="I50" t="s">
+        <v>624</v>
+      </c>
+      <c r="J50" t="s">
+        <v>626</v>
+      </c>
+      <c r="K50" t="s">
+        <v>12</v>
+      </c>
+      <c r="L50" t="s">
         <v>277</v>
       </c>
-      <c r="H50" t="s">
-        <v>238</v>
-      </c>
-      <c r="I50" t="s">
-        <v>625</v>
-      </c>
-      <c r="J50" t="s">
-        <v>627</v>
-      </c>
-      <c r="K50" t="s">
-        <v>13</v>
-      </c>
-      <c r="L50" t="s">
-        <v>278</v>
-      </c>
       <c r="M50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N50" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O50">
         <v>4.9000000000000004</v>
@@ -5115,7 +5121,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C51" s="1">
         <v>300</v>
@@ -5124,34 +5130,34 @@
         <v>380</v>
       </c>
       <c r="E51" t="s">
+        <v>279</v>
+      </c>
+      <c r="F51" t="s">
         <v>280</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>281</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
+        <v>237</v>
+      </c>
+      <c r="I51" t="s">
+        <v>624</v>
+      </c>
+      <c r="J51" t="s">
+        <v>626</v>
+      </c>
+      <c r="K51" t="s">
+        <v>90</v>
+      </c>
+      <c r="L51" t="s">
         <v>282</v>
       </c>
-      <c r="H51" t="s">
-        <v>238</v>
-      </c>
-      <c r="I51" t="s">
-        <v>625</v>
-      </c>
-      <c r="J51" t="s">
-        <v>627</v>
-      </c>
-      <c r="K51" t="s">
-        <v>91</v>
-      </c>
-      <c r="L51" t="s">
-        <v>283</v>
-      </c>
       <c r="M51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N51" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O51">
         <v>4</v>
@@ -5165,7 +5171,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C52" s="1">
         <v>180</v>
@@ -5174,34 +5180,34 @@
         <v>250</v>
       </c>
       <c r="E52" t="s">
+        <v>284</v>
+      </c>
+      <c r="F52" t="s">
         <v>285</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>286</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>287</v>
       </c>
-      <c r="H52" t="s">
+      <c r="I52" t="s">
+        <v>624</v>
+      </c>
+      <c r="J52" t="s">
+        <v>626</v>
+      </c>
+      <c r="K52" t="s">
+        <v>12</v>
+      </c>
+      <c r="L52" t="s">
         <v>288</v>
       </c>
-      <c r="I52" t="s">
-        <v>625</v>
-      </c>
-      <c r="J52" t="s">
-        <v>627</v>
-      </c>
-      <c r="K52" t="s">
-        <v>13</v>
-      </c>
-      <c r="L52" t="s">
-        <v>289</v>
-      </c>
       <c r="M52" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O52">
         <v>4.0999999999999996</v>
@@ -5215,7 +5221,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C53" s="1">
         <v>900</v>
@@ -5224,34 +5230,34 @@
         <v>1150</v>
       </c>
       <c r="E53" t="s">
+        <v>290</v>
+      </c>
+      <c r="F53" t="s">
         <v>291</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>292</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
+        <v>287</v>
+      </c>
+      <c r="I53" t="s">
+        <v>624</v>
+      </c>
+      <c r="J53" t="s">
+        <v>626</v>
+      </c>
+      <c r="K53" t="s">
+        <v>90</v>
+      </c>
+      <c r="L53" t="s">
         <v>293</v>
       </c>
-      <c r="H53" t="s">
-        <v>288</v>
-      </c>
-      <c r="I53" t="s">
-        <v>625</v>
-      </c>
-      <c r="J53" t="s">
-        <v>627</v>
-      </c>
-      <c r="K53" t="s">
-        <v>91</v>
-      </c>
-      <c r="L53" t="s">
-        <v>294</v>
-      </c>
       <c r="M53" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O53">
         <v>4.2</v>
@@ -5265,7 +5271,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C54" s="1">
         <v>85</v>
@@ -5274,34 +5280,34 @@
         <v>120</v>
       </c>
       <c r="E54" t="s">
+        <v>295</v>
+      </c>
+      <c r="F54" t="s">
         <v>296</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>297</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
+        <v>287</v>
+      </c>
+      <c r="I54" t="s">
+        <v>624</v>
+      </c>
+      <c r="J54" t="s">
+        <v>626</v>
+      </c>
+      <c r="K54" t="s">
+        <v>12</v>
+      </c>
+      <c r="L54" t="s">
         <v>298</v>
       </c>
-      <c r="H54" t="s">
-        <v>288</v>
-      </c>
-      <c r="I54" t="s">
-        <v>625</v>
-      </c>
-      <c r="J54" t="s">
-        <v>627</v>
-      </c>
-      <c r="K54" t="s">
-        <v>13</v>
-      </c>
-      <c r="L54" t="s">
-        <v>299</v>
-      </c>
       <c r="M54" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N54" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O54">
         <v>4.3</v>
@@ -5315,7 +5321,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C55" s="1">
         <v>400</v>
@@ -5324,34 +5330,34 @@
         <v>490</v>
       </c>
       <c r="E55" t="s">
+        <v>300</v>
+      </c>
+      <c r="F55" t="s">
         <v>301</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>302</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
+        <v>287</v>
+      </c>
+      <c r="I55" t="s">
+        <v>624</v>
+      </c>
+      <c r="J55" t="s">
+        <v>626</v>
+      </c>
+      <c r="K55" t="s">
+        <v>90</v>
+      </c>
+      <c r="L55" t="s">
         <v>303</v>
       </c>
-      <c r="H55" t="s">
-        <v>288</v>
-      </c>
-      <c r="I55" t="s">
-        <v>625</v>
-      </c>
-      <c r="J55" t="s">
-        <v>627</v>
-      </c>
-      <c r="K55" t="s">
-        <v>91</v>
-      </c>
-      <c r="L55" t="s">
-        <v>304</v>
-      </c>
       <c r="M55" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O55">
         <v>4.4000000000000004</v>
@@ -5365,7 +5371,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C56" s="1">
         <v>160</v>
@@ -5374,34 +5380,34 @@
         <v>210</v>
       </c>
       <c r="E56" t="s">
+        <v>305</v>
+      </c>
+      <c r="F56" t="s">
         <v>306</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>307</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
+        <v>287</v>
+      </c>
+      <c r="I56" t="s">
+        <v>624</v>
+      </c>
+      <c r="J56" t="s">
+        <v>626</v>
+      </c>
+      <c r="K56" t="s">
+        <v>12</v>
+      </c>
+      <c r="L56" t="s">
         <v>308</v>
       </c>
-      <c r="H56" t="s">
-        <v>288</v>
-      </c>
-      <c r="I56" t="s">
-        <v>625</v>
-      </c>
-      <c r="J56" t="s">
-        <v>627</v>
-      </c>
-      <c r="K56" t="s">
-        <v>13</v>
-      </c>
-      <c r="L56" t="s">
-        <v>309</v>
-      </c>
       <c r="M56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N56" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O56">
         <v>4.5</v>
@@ -5415,7 +5421,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C57" s="1">
         <v>380</v>
@@ -5424,34 +5430,34 @@
         <v>450</v>
       </c>
       <c r="E57" t="s">
+        <v>310</v>
+      </c>
+      <c r="F57" t="s">
         <v>311</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>312</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
+        <v>287</v>
+      </c>
+      <c r="I57" t="s">
+        <v>624</v>
+      </c>
+      <c r="J57" t="s">
+        <v>626</v>
+      </c>
+      <c r="K57" t="s">
+        <v>90</v>
+      </c>
+      <c r="L57" t="s">
         <v>313</v>
       </c>
-      <c r="H57" t="s">
-        <v>288</v>
-      </c>
-      <c r="I57" t="s">
-        <v>625</v>
-      </c>
-      <c r="J57" t="s">
-        <v>627</v>
-      </c>
-      <c r="K57" t="s">
-        <v>91</v>
-      </c>
-      <c r="L57" t="s">
-        <v>314</v>
-      </c>
       <c r="M57" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N57" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O57">
         <v>4.5999999999999996</v>
@@ -5465,7 +5471,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C58" s="1">
         <v>550</v>
@@ -5474,34 +5480,34 @@
         <v>680</v>
       </c>
       <c r="E58" t="s">
+        <v>315</v>
+      </c>
+      <c r="F58" t="s">
         <v>316</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>317</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
+        <v>287</v>
+      </c>
+      <c r="I58" t="s">
+        <v>624</v>
+      </c>
+      <c r="J58" t="s">
+        <v>626</v>
+      </c>
+      <c r="K58" t="s">
+        <v>12</v>
+      </c>
+      <c r="L58" t="s">
         <v>318</v>
       </c>
-      <c r="H58" t="s">
-        <v>288</v>
-      </c>
-      <c r="I58" t="s">
-        <v>625</v>
-      </c>
-      <c r="J58" t="s">
-        <v>627</v>
-      </c>
-      <c r="K58" t="s">
-        <v>13</v>
-      </c>
-      <c r="L58" t="s">
-        <v>319</v>
-      </c>
       <c r="M58" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N58" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O58">
         <v>4.7</v>
@@ -5515,7 +5521,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C59" s="1">
         <v>700</v>
@@ -5524,34 +5530,34 @@
         <v>820</v>
       </c>
       <c r="E59" t="s">
+        <v>320</v>
+      </c>
+      <c r="F59" t="s">
         <v>321</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>322</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
+        <v>287</v>
+      </c>
+      <c r="I59" t="s">
+        <v>624</v>
+      </c>
+      <c r="J59" t="s">
+        <v>626</v>
+      </c>
+      <c r="K59" t="s">
+        <v>90</v>
+      </c>
+      <c r="L59" t="s">
         <v>323</v>
       </c>
-      <c r="H59" t="s">
-        <v>288</v>
-      </c>
-      <c r="I59" t="s">
-        <v>625</v>
-      </c>
-      <c r="J59" t="s">
-        <v>627</v>
-      </c>
-      <c r="K59" t="s">
-        <v>91</v>
-      </c>
-      <c r="L59" t="s">
-        <v>324</v>
-      </c>
       <c r="M59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O59">
         <v>4.8</v>
@@ -5565,7 +5571,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C60" s="1">
         <v>290</v>
@@ -5574,34 +5580,34 @@
         <v>350</v>
       </c>
       <c r="E60" t="s">
+        <v>325</v>
+      </c>
+      <c r="F60" t="s">
         <v>326</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>327</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
+        <v>287</v>
+      </c>
+      <c r="I60" t="s">
+        <v>624</v>
+      </c>
+      <c r="J60" t="s">
+        <v>626</v>
+      </c>
+      <c r="K60" t="s">
+        <v>12</v>
+      </c>
+      <c r="L60" t="s">
         <v>328</v>
       </c>
-      <c r="H60" t="s">
-        <v>288</v>
-      </c>
-      <c r="I60" t="s">
-        <v>625</v>
-      </c>
-      <c r="J60" t="s">
-        <v>627</v>
-      </c>
-      <c r="K60" t="s">
-        <v>13</v>
-      </c>
-      <c r="L60" t="s">
-        <v>329</v>
-      </c>
       <c r="M60" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N60" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O60">
         <v>4.9000000000000004</v>
@@ -5615,7 +5621,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C61" s="1">
         <v>220</v>
@@ -5624,34 +5630,34 @@
         <v>280</v>
       </c>
       <c r="E61" t="s">
+        <v>330</v>
+      </c>
+      <c r="F61" t="s">
         <v>331</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>332</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
+        <v>287</v>
+      </c>
+      <c r="I61" t="s">
+        <v>624</v>
+      </c>
+      <c r="J61" t="s">
+        <v>626</v>
+      </c>
+      <c r="K61" t="s">
+        <v>90</v>
+      </c>
+      <c r="L61" t="s">
         <v>333</v>
       </c>
-      <c r="H61" t="s">
-        <v>288</v>
-      </c>
-      <c r="I61" t="s">
-        <v>625</v>
-      </c>
-      <c r="J61" t="s">
-        <v>627</v>
-      </c>
-      <c r="K61" t="s">
-        <v>91</v>
-      </c>
-      <c r="L61" t="s">
-        <v>334</v>
-      </c>
       <c r="M61" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N61" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O61">
         <v>4</v>
@@ -5665,7 +5671,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C62" s="1">
         <v>200</v>
@@ -5674,34 +5680,34 @@
         <v>280</v>
       </c>
       <c r="E62" t="s">
+        <v>335</v>
+      </c>
+      <c r="F62" t="s">
         <v>336</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>337</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>338</v>
       </c>
-      <c r="H62" t="s">
+      <c r="I62" t="s">
+        <v>624</v>
+      </c>
+      <c r="J62" t="s">
+        <v>626</v>
+      </c>
+      <c r="K62" t="s">
+        <v>12</v>
+      </c>
+      <c r="L62" t="s">
         <v>339</v>
       </c>
-      <c r="I62" t="s">
-        <v>625</v>
-      </c>
-      <c r="J62" t="s">
-        <v>627</v>
-      </c>
-      <c r="K62" t="s">
-        <v>13</v>
-      </c>
-      <c r="L62" t="s">
-        <v>340</v>
-      </c>
       <c r="M62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N62" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O62">
         <v>4.0999999999999996</v>
@@ -5715,7 +5721,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C63" s="1">
         <v>350</v>
@@ -5724,34 +5730,34 @@
         <v>440</v>
       </c>
       <c r="E63" t="s">
+        <v>341</v>
+      </c>
+      <c r="F63" t="s">
         <v>342</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>343</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
+        <v>338</v>
+      </c>
+      <c r="I63" t="s">
+        <v>624</v>
+      </c>
+      <c r="J63" t="s">
+        <v>626</v>
+      </c>
+      <c r="K63" t="s">
+        <v>90</v>
+      </c>
+      <c r="L63" t="s">
         <v>344</v>
       </c>
-      <c r="H63" t="s">
-        <v>339</v>
-      </c>
-      <c r="I63" t="s">
-        <v>625</v>
-      </c>
-      <c r="J63" t="s">
-        <v>627</v>
-      </c>
-      <c r="K63" t="s">
-        <v>91</v>
-      </c>
-      <c r="L63" t="s">
-        <v>345</v>
-      </c>
       <c r="M63" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N63" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O63">
         <v>4.2</v>
@@ -5765,7 +5771,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C64" s="1">
         <v>2200</v>
@@ -5774,34 +5780,34 @@
         <v>2500</v>
       </c>
       <c r="E64" t="s">
+        <v>346</v>
+      </c>
+      <c r="F64" t="s">
         <v>347</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>348</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
+        <v>338</v>
+      </c>
+      <c r="I64" t="s">
+        <v>624</v>
+      </c>
+      <c r="J64" t="s">
+        <v>626</v>
+      </c>
+      <c r="K64" t="s">
+        <v>12</v>
+      </c>
+      <c r="L64" t="s">
         <v>349</v>
       </c>
-      <c r="H64" t="s">
-        <v>339</v>
-      </c>
-      <c r="I64" t="s">
-        <v>625</v>
-      </c>
-      <c r="J64" t="s">
-        <v>627</v>
-      </c>
-      <c r="K64" t="s">
-        <v>13</v>
-      </c>
-      <c r="L64" t="s">
-        <v>350</v>
-      </c>
       <c r="M64" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N64" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O64">
         <v>4.3</v>
@@ -5815,7 +5821,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C65" s="1">
         <v>800</v>
@@ -5824,34 +5830,34 @@
         <v>950</v>
       </c>
       <c r="E65" t="s">
+        <v>351</v>
+      </c>
+      <c r="F65" t="s">
         <v>352</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>353</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
+        <v>338</v>
+      </c>
+      <c r="I65" t="s">
+        <v>624</v>
+      </c>
+      <c r="J65" t="s">
+        <v>626</v>
+      </c>
+      <c r="K65" t="s">
+        <v>90</v>
+      </c>
+      <c r="L65" t="s">
         <v>354</v>
       </c>
-      <c r="H65" t="s">
-        <v>339</v>
-      </c>
-      <c r="I65" t="s">
-        <v>625</v>
-      </c>
-      <c r="J65" t="s">
-        <v>627</v>
-      </c>
-      <c r="K65" t="s">
-        <v>91</v>
-      </c>
-      <c r="L65" t="s">
-        <v>355</v>
-      </c>
       <c r="M65" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O65">
         <v>4.4000000000000004</v>
@@ -5865,7 +5871,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C66" s="1">
         <v>140</v>
@@ -5874,34 +5880,34 @@
         <v>185</v>
       </c>
       <c r="E66" t="s">
+        <v>356</v>
+      </c>
+      <c r="F66" t="s">
         <v>357</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>358</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
+        <v>338</v>
+      </c>
+      <c r="I66" t="s">
+        <v>624</v>
+      </c>
+      <c r="J66" t="s">
+        <v>626</v>
+      </c>
+      <c r="K66" t="s">
+        <v>12</v>
+      </c>
+      <c r="L66" t="s">
         <v>359</v>
       </c>
-      <c r="H66" t="s">
-        <v>339</v>
-      </c>
-      <c r="I66" t="s">
-        <v>625</v>
-      </c>
-      <c r="J66" t="s">
-        <v>627</v>
-      </c>
-      <c r="K66" t="s">
-        <v>13</v>
-      </c>
-      <c r="L66" t="s">
-        <v>360</v>
-      </c>
       <c r="M66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N66" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O66">
         <v>4.5</v>
@@ -5915,7 +5921,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C67" s="1">
         <v>1800</v>
@@ -5924,34 +5930,34 @@
         <v>2100</v>
       </c>
       <c r="E67" t="s">
+        <v>361</v>
+      </c>
+      <c r="F67" t="s">
         <v>362</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>363</v>
       </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
+        <v>338</v>
+      </c>
+      <c r="I67" t="s">
+        <v>624</v>
+      </c>
+      <c r="J67" t="s">
+        <v>626</v>
+      </c>
+      <c r="K67" t="s">
+        <v>90</v>
+      </c>
+      <c r="L67" t="s">
         <v>364</v>
       </c>
-      <c r="H67" t="s">
-        <v>339</v>
-      </c>
-      <c r="I67" t="s">
-        <v>625</v>
-      </c>
-      <c r="J67" t="s">
-        <v>627</v>
-      </c>
-      <c r="K67" t="s">
-        <v>91</v>
-      </c>
-      <c r="L67" t="s">
-        <v>365</v>
-      </c>
       <c r="M67" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O67">
         <v>4.5999999999999996</v>
@@ -5965,7 +5971,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C68" s="1">
         <v>490</v>
@@ -5974,34 +5980,34 @@
         <v>580</v>
       </c>
       <c r="E68" t="s">
+        <v>366</v>
+      </c>
+      <c r="F68" t="s">
         <v>367</v>
       </c>
-      <c r="F68" t="s">
+      <c r="G68" t="s">
         <v>368</v>
       </c>
-      <c r="G68" t="s">
+      <c r="H68" t="s">
+        <v>338</v>
+      </c>
+      <c r="I68" t="s">
+        <v>624</v>
+      </c>
+      <c r="J68" t="s">
+        <v>626</v>
+      </c>
+      <c r="K68" t="s">
+        <v>12</v>
+      </c>
+      <c r="L68" t="s">
         <v>369</v>
       </c>
-      <c r="H68" t="s">
-        <v>339</v>
-      </c>
-      <c r="I68" t="s">
-        <v>625</v>
-      </c>
-      <c r="J68" t="s">
-        <v>627</v>
-      </c>
-      <c r="K68" t="s">
-        <v>13</v>
-      </c>
-      <c r="L68" t="s">
-        <v>370</v>
-      </c>
       <c r="M68" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N68" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O68">
         <v>4.7</v>
@@ -6015,7 +6021,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C69" s="1">
         <v>95</v>
@@ -6024,34 +6030,34 @@
         <v>130</v>
       </c>
       <c r="E69" t="s">
+        <v>371</v>
+      </c>
+      <c r="F69" t="s">
         <v>372</v>
       </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>373</v>
       </c>
-      <c r="G69" t="s">
+      <c r="H69" t="s">
+        <v>338</v>
+      </c>
+      <c r="I69" t="s">
+        <v>624</v>
+      </c>
+      <c r="J69" t="s">
+        <v>626</v>
+      </c>
+      <c r="K69" t="s">
+        <v>90</v>
+      </c>
+      <c r="L69" t="s">
         <v>374</v>
       </c>
-      <c r="H69" t="s">
-        <v>339</v>
-      </c>
-      <c r="I69" t="s">
-        <v>625</v>
-      </c>
-      <c r="J69" t="s">
-        <v>627</v>
-      </c>
-      <c r="K69" t="s">
-        <v>91</v>
-      </c>
-      <c r="L69" t="s">
-        <v>375</v>
-      </c>
       <c r="M69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N69" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O69">
         <v>4.8</v>
@@ -6065,7 +6071,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C70" s="1">
         <v>1500</v>
@@ -6074,34 +6080,34 @@
         <v>1750</v>
       </c>
       <c r="E70" t="s">
+        <v>376</v>
+      </c>
+      <c r="F70" t="s">
         <v>377</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>378</v>
       </c>
-      <c r="G70" t="s">
+      <c r="H70" t="s">
+        <v>338</v>
+      </c>
+      <c r="I70" t="s">
+        <v>624</v>
+      </c>
+      <c r="J70" t="s">
+        <v>626</v>
+      </c>
+      <c r="K70" t="s">
+        <v>12</v>
+      </c>
+      <c r="L70" t="s">
         <v>379</v>
       </c>
-      <c r="H70" t="s">
-        <v>339</v>
-      </c>
-      <c r="I70" t="s">
-        <v>625</v>
-      </c>
-      <c r="J70" t="s">
-        <v>627</v>
-      </c>
-      <c r="K70" t="s">
-        <v>13</v>
-      </c>
-      <c r="L70" t="s">
-        <v>380</v>
-      </c>
       <c r="M70" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N70" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O70">
         <v>4.9000000000000004</v>
@@ -6115,7 +6121,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C71" s="1">
         <v>320</v>
@@ -6124,34 +6130,34 @@
         <v>390</v>
       </c>
       <c r="E71" t="s">
+        <v>381</v>
+      </c>
+      <c r="F71" t="s">
         <v>382</v>
       </c>
-      <c r="F71" t="s">
+      <c r="G71" t="s">
         <v>383</v>
       </c>
-      <c r="G71" t="s">
+      <c r="H71" t="s">
+        <v>338</v>
+      </c>
+      <c r="I71" t="s">
+        <v>624</v>
+      </c>
+      <c r="J71" t="s">
+        <v>626</v>
+      </c>
+      <c r="K71" t="s">
+        <v>90</v>
+      </c>
+      <c r="L71" t="s">
         <v>384</v>
       </c>
-      <c r="H71" t="s">
-        <v>339</v>
-      </c>
-      <c r="I71" t="s">
-        <v>625</v>
-      </c>
-      <c r="J71" t="s">
-        <v>627</v>
-      </c>
-      <c r="K71" t="s">
-        <v>91</v>
-      </c>
-      <c r="L71" t="s">
-        <v>385</v>
-      </c>
       <c r="M71" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O71">
         <v>4</v>
@@ -6165,7 +6171,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C72" s="1">
         <v>1800</v>
@@ -6174,34 +6180,34 @@
         <v>2100</v>
       </c>
       <c r="E72" t="s">
+        <v>386</v>
+      </c>
+      <c r="F72" t="s">
         <v>387</v>
       </c>
-      <c r="F72" t="s">
+      <c r="G72" t="s">
         <v>388</v>
       </c>
-      <c r="G72" t="s">
+      <c r="H72" t="s">
         <v>389</v>
       </c>
-      <c r="H72" t="s">
+      <c r="I72" t="s">
+        <v>624</v>
+      </c>
+      <c r="J72" t="s">
+        <v>626</v>
+      </c>
+      <c r="K72" t="s">
+        <v>12</v>
+      </c>
+      <c r="L72" t="s">
         <v>390</v>
       </c>
-      <c r="I72" t="s">
-        <v>625</v>
-      </c>
-      <c r="J72" t="s">
-        <v>627</v>
-      </c>
-      <c r="K72" t="s">
-        <v>13</v>
-      </c>
-      <c r="L72" t="s">
-        <v>391</v>
-      </c>
       <c r="M72" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N72" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O72">
         <v>4.0999999999999996</v>
@@ -6215,7 +6221,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C73" s="1">
         <v>450</v>
@@ -6224,34 +6230,34 @@
         <v>550</v>
       </c>
       <c r="E73" t="s">
+        <v>392</v>
+      </c>
+      <c r="F73" t="s">
         <v>393</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>394</v>
       </c>
-      <c r="G73" t="s">
+      <c r="H73" t="s">
+        <v>389</v>
+      </c>
+      <c r="I73" t="s">
+        <v>624</v>
+      </c>
+      <c r="J73" t="s">
+        <v>626</v>
+      </c>
+      <c r="K73" t="s">
+        <v>90</v>
+      </c>
+      <c r="L73" t="s">
         <v>395</v>
       </c>
-      <c r="H73" t="s">
-        <v>390</v>
-      </c>
-      <c r="I73" t="s">
-        <v>625</v>
-      </c>
-      <c r="J73" t="s">
-        <v>627</v>
-      </c>
-      <c r="K73" t="s">
-        <v>91</v>
-      </c>
-      <c r="L73" t="s">
-        <v>396</v>
-      </c>
       <c r="M73" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N73" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O73">
         <v>4.2</v>
@@ -6265,7 +6271,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C74" s="1">
         <v>310</v>
@@ -6274,34 +6280,34 @@
         <v>380</v>
       </c>
       <c r="E74" t="s">
+        <v>397</v>
+      </c>
+      <c r="F74" t="s">
         <v>398</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>399</v>
       </c>
-      <c r="G74" t="s">
+      <c r="H74" t="s">
+        <v>389</v>
+      </c>
+      <c r="I74" t="s">
+        <v>624</v>
+      </c>
+      <c r="J74" t="s">
+        <v>626</v>
+      </c>
+      <c r="K74" t="s">
+        <v>12</v>
+      </c>
+      <c r="L74" t="s">
         <v>400</v>
       </c>
-      <c r="H74" t="s">
-        <v>390</v>
-      </c>
-      <c r="I74" t="s">
-        <v>625</v>
-      </c>
-      <c r="J74" t="s">
-        <v>627</v>
-      </c>
-      <c r="K74" t="s">
-        <v>13</v>
-      </c>
-      <c r="L74" t="s">
-        <v>401</v>
-      </c>
       <c r="M74" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N74" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O74">
         <v>4.3</v>
@@ -6315,7 +6321,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C75" s="1">
         <v>1200</v>
@@ -6324,34 +6330,34 @@
         <v>1450</v>
       </c>
       <c r="E75" t="s">
+        <v>402</v>
+      </c>
+      <c r="F75" t="s">
         <v>403</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>404</v>
       </c>
-      <c r="G75" t="s">
+      <c r="H75" t="s">
+        <v>389</v>
+      </c>
+      <c r="I75" t="s">
+        <v>624</v>
+      </c>
+      <c r="J75" t="s">
+        <v>626</v>
+      </c>
+      <c r="K75" t="s">
+        <v>90</v>
+      </c>
+      <c r="L75" t="s">
         <v>405</v>
       </c>
-      <c r="H75" t="s">
-        <v>390</v>
-      </c>
-      <c r="I75" t="s">
-        <v>625</v>
-      </c>
-      <c r="J75" t="s">
-        <v>627</v>
-      </c>
-      <c r="K75" t="s">
-        <v>91</v>
-      </c>
-      <c r="L75" t="s">
-        <v>406</v>
-      </c>
       <c r="M75" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O75">
         <v>4.4000000000000004</v>
@@ -6365,7 +6371,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C76" s="1">
         <v>600</v>
@@ -6374,34 +6380,34 @@
         <v>700</v>
       </c>
       <c r="E76" t="s">
+        <v>407</v>
+      </c>
+      <c r="F76" t="s">
         <v>408</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>409</v>
       </c>
-      <c r="G76" t="s">
+      <c r="H76" t="s">
+        <v>389</v>
+      </c>
+      <c r="I76" t="s">
+        <v>624</v>
+      </c>
+      <c r="J76" t="s">
+        <v>626</v>
+      </c>
+      <c r="K76" t="s">
+        <v>12</v>
+      </c>
+      <c r="L76" t="s">
         <v>410</v>
       </c>
-      <c r="H76" t="s">
-        <v>390</v>
-      </c>
-      <c r="I76" t="s">
-        <v>625</v>
-      </c>
-      <c r="J76" t="s">
-        <v>627</v>
-      </c>
-      <c r="K76" t="s">
-        <v>13</v>
-      </c>
-      <c r="L76" t="s">
-        <v>411</v>
-      </c>
       <c r="M76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N76" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O76">
         <v>4.5</v>
@@ -6415,7 +6421,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C77" s="1">
         <v>180</v>
@@ -6424,34 +6430,34 @@
         <v>240</v>
       </c>
       <c r="E77" t="s">
+        <v>412</v>
+      </c>
+      <c r="F77" t="s">
         <v>413</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>414</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
+        <v>389</v>
+      </c>
+      <c r="I77" t="s">
+        <v>624</v>
+      </c>
+      <c r="J77" t="s">
+        <v>626</v>
+      </c>
+      <c r="K77" t="s">
+        <v>90</v>
+      </c>
+      <c r="L77" t="s">
         <v>415</v>
       </c>
-      <c r="H77" t="s">
-        <v>390</v>
-      </c>
-      <c r="I77" t="s">
-        <v>625</v>
-      </c>
-      <c r="J77" t="s">
-        <v>627</v>
-      </c>
-      <c r="K77" t="s">
-        <v>91</v>
-      </c>
-      <c r="L77" t="s">
-        <v>416</v>
-      </c>
       <c r="M77" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N77" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O77">
         <v>4.5999999999999996</v>
@@ -6465,7 +6471,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C78" s="1">
         <v>220</v>
@@ -6474,34 +6480,34 @@
         <v>280</v>
       </c>
       <c r="E78" t="s">
+        <v>417</v>
+      </c>
+      <c r="F78" t="s">
         <v>418</v>
       </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>419</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
+        <v>389</v>
+      </c>
+      <c r="I78" t="s">
+        <v>624</v>
+      </c>
+      <c r="J78" t="s">
+        <v>626</v>
+      </c>
+      <c r="K78" t="s">
+        <v>12</v>
+      </c>
+      <c r="L78" t="s">
         <v>420</v>
       </c>
-      <c r="H78" t="s">
-        <v>390</v>
-      </c>
-      <c r="I78" t="s">
-        <v>625</v>
-      </c>
-      <c r="J78" t="s">
-        <v>627</v>
-      </c>
-      <c r="K78" t="s">
-        <v>13</v>
-      </c>
-      <c r="L78" t="s">
-        <v>421</v>
-      </c>
       <c r="M78" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N78" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O78">
         <v>4.7</v>
@@ -6515,7 +6521,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C79" s="1">
         <v>80</v>
@@ -6524,34 +6530,34 @@
         <v>115</v>
       </c>
       <c r="E79" t="s">
+        <v>422</v>
+      </c>
+      <c r="F79" t="s">
         <v>423</v>
       </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>424</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
+        <v>389</v>
+      </c>
+      <c r="I79" t="s">
+        <v>624</v>
+      </c>
+      <c r="J79" t="s">
+        <v>626</v>
+      </c>
+      <c r="K79" t="s">
+        <v>90</v>
+      </c>
+      <c r="L79" t="s">
         <v>425</v>
       </c>
-      <c r="H79" t="s">
-        <v>390</v>
-      </c>
-      <c r="I79" t="s">
-        <v>625</v>
-      </c>
-      <c r="J79" t="s">
-        <v>627</v>
-      </c>
-      <c r="K79" t="s">
-        <v>91</v>
-      </c>
-      <c r="L79" t="s">
-        <v>426</v>
-      </c>
       <c r="M79" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N79" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O79">
         <v>4.8</v>
@@ -6565,7 +6571,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C80" s="1">
         <v>260</v>
@@ -6574,34 +6580,34 @@
         <v>310</v>
       </c>
       <c r="E80" t="s">
+        <v>427</v>
+      </c>
+      <c r="F80" t="s">
         <v>428</v>
       </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>429</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
+        <v>389</v>
+      </c>
+      <c r="I80" t="s">
+        <v>624</v>
+      </c>
+      <c r="J80" t="s">
+        <v>626</v>
+      </c>
+      <c r="K80" t="s">
+        <v>12</v>
+      </c>
+      <c r="L80" t="s">
         <v>430</v>
       </c>
-      <c r="H80" t="s">
-        <v>390</v>
-      </c>
-      <c r="I80" t="s">
-        <v>625</v>
-      </c>
-      <c r="J80" t="s">
-        <v>627</v>
-      </c>
-      <c r="K80" t="s">
-        <v>13</v>
-      </c>
-      <c r="L80" t="s">
-        <v>431</v>
-      </c>
       <c r="M80" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N80" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O80">
         <v>4.9000000000000004</v>
@@ -6615,7 +6621,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C81" s="1">
         <v>110</v>
@@ -6624,34 +6630,34 @@
         <v>145</v>
       </c>
       <c r="E81" t="s">
+        <v>432</v>
+      </c>
+      <c r="F81" t="s">
         <v>433</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>434</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
+        <v>389</v>
+      </c>
+      <c r="I81" t="s">
+        <v>624</v>
+      </c>
+      <c r="J81" t="s">
+        <v>626</v>
+      </c>
+      <c r="K81" t="s">
+        <v>90</v>
+      </c>
+      <c r="L81" t="s">
         <v>435</v>
       </c>
-      <c r="H81" t="s">
-        <v>390</v>
-      </c>
-      <c r="I81" t="s">
-        <v>625</v>
-      </c>
-      <c r="J81" t="s">
-        <v>627</v>
-      </c>
-      <c r="K81" t="s">
-        <v>91</v>
-      </c>
-      <c r="L81" t="s">
-        <v>436</v>
-      </c>
       <c r="M81" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N81" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O81">
         <v>4</v>
@@ -6665,7 +6671,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C82" s="1">
         <v>75</v>
@@ -6674,34 +6680,34 @@
         <v>110</v>
       </c>
       <c r="E82" t="s">
+        <v>437</v>
+      </c>
+      <c r="F82" t="s">
         <v>438</v>
       </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>439</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
+        <v>64</v>
+      </c>
+      <c r="I82" t="s">
+        <v>624</v>
+      </c>
+      <c r="J82" t="s">
+        <v>626</v>
+      </c>
+      <c r="K82" t="s">
+        <v>12</v>
+      </c>
+      <c r="L82" t="s">
         <v>440</v>
       </c>
-      <c r="H82" t="s">
-        <v>65</v>
-      </c>
-      <c r="I82" t="s">
-        <v>625</v>
-      </c>
-      <c r="J82" t="s">
-        <v>627</v>
-      </c>
-      <c r="K82" t="s">
-        <v>13</v>
-      </c>
-      <c r="L82" t="s">
-        <v>441</v>
-      </c>
       <c r="M82" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N82" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O82">
         <v>4.0999999999999996</v>
@@ -6715,7 +6721,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C83" s="1">
         <v>120</v>
@@ -6724,34 +6730,34 @@
         <v>160</v>
       </c>
       <c r="E83" t="s">
+        <v>442</v>
+      </c>
+      <c r="F83" t="s">
         <v>443</v>
       </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>444</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
+        <v>64</v>
+      </c>
+      <c r="I83" t="s">
+        <v>624</v>
+      </c>
+      <c r="J83" t="s">
+        <v>626</v>
+      </c>
+      <c r="K83" t="s">
+        <v>90</v>
+      </c>
+      <c r="L83" t="s">
         <v>445</v>
       </c>
-      <c r="H83" t="s">
-        <v>65</v>
-      </c>
-      <c r="I83" t="s">
-        <v>625</v>
-      </c>
-      <c r="J83" t="s">
-        <v>627</v>
-      </c>
-      <c r="K83" t="s">
-        <v>91</v>
-      </c>
-      <c r="L83" t="s">
-        <v>446</v>
-      </c>
       <c r="M83" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N83" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O83">
         <v>4.2</v>
@@ -6765,7 +6771,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C84" s="1">
         <v>140</v>
@@ -6774,34 +6780,34 @@
         <v>190</v>
       </c>
       <c r="E84" t="s">
+        <v>447</v>
+      </c>
+      <c r="F84" t="s">
         <v>448</v>
       </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>449</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
+        <v>64</v>
+      </c>
+      <c r="I84" t="s">
+        <v>624</v>
+      </c>
+      <c r="J84" t="s">
+        <v>626</v>
+      </c>
+      <c r="K84" t="s">
+        <v>12</v>
+      </c>
+      <c r="L84" t="s">
         <v>450</v>
       </c>
-      <c r="H84" t="s">
-        <v>65</v>
-      </c>
-      <c r="I84" t="s">
-        <v>625</v>
-      </c>
-      <c r="J84" t="s">
-        <v>627</v>
-      </c>
-      <c r="K84" t="s">
-        <v>13</v>
-      </c>
-      <c r="L84" t="s">
-        <v>451</v>
-      </c>
       <c r="M84" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N84" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O84">
         <v>4.3</v>
@@ -6815,7 +6821,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C85" s="1">
         <v>20</v>
@@ -6824,34 +6830,34 @@
         <v>30</v>
       </c>
       <c r="E85" t="s">
+        <v>452</v>
+      </c>
+      <c r="F85" t="s">
         <v>453</v>
       </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>454</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
+        <v>64</v>
+      </c>
+      <c r="I85" t="s">
+        <v>624</v>
+      </c>
+      <c r="J85" t="s">
+        <v>626</v>
+      </c>
+      <c r="K85" t="s">
+        <v>90</v>
+      </c>
+      <c r="L85" t="s">
         <v>455</v>
       </c>
-      <c r="H85" t="s">
-        <v>65</v>
-      </c>
-      <c r="I85" t="s">
-        <v>625</v>
-      </c>
-      <c r="J85" t="s">
-        <v>627</v>
-      </c>
-      <c r="K85" t="s">
-        <v>91</v>
-      </c>
-      <c r="L85" t="s">
-        <v>456</v>
-      </c>
       <c r="M85" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O85">
         <v>4.4000000000000004</v>
@@ -6865,7 +6871,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C86" s="1">
         <v>110</v>
@@ -6874,34 +6880,34 @@
         <v>145</v>
       </c>
       <c r="E86" t="s">
+        <v>457</v>
+      </c>
+      <c r="F86" t="s">
         <v>458</v>
       </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>459</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
+        <v>64</v>
+      </c>
+      <c r="I86" t="s">
+        <v>624</v>
+      </c>
+      <c r="J86" t="s">
+        <v>626</v>
+      </c>
+      <c r="K86" t="s">
+        <v>12</v>
+      </c>
+      <c r="L86" t="s">
         <v>460</v>
       </c>
-      <c r="H86" t="s">
-        <v>65</v>
-      </c>
-      <c r="I86" t="s">
-        <v>625</v>
-      </c>
-      <c r="J86" t="s">
-        <v>627</v>
-      </c>
-      <c r="K86" t="s">
-        <v>13</v>
-      </c>
-      <c r="L86" t="s">
-        <v>461</v>
-      </c>
       <c r="M86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N86" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O86">
         <v>4.5</v>
@@ -6915,7 +6921,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C87" s="1">
         <v>45</v>
@@ -6924,34 +6930,34 @@
         <v>60</v>
       </c>
       <c r="E87" t="s">
+        <v>462</v>
+      </c>
+      <c r="F87" t="s">
         <v>463</v>
       </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>464</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
+        <v>64</v>
+      </c>
+      <c r="I87" t="s">
+        <v>624</v>
+      </c>
+      <c r="J87" t="s">
+        <v>626</v>
+      </c>
+      <c r="K87" t="s">
+        <v>90</v>
+      </c>
+      <c r="L87" t="s">
         <v>465</v>
       </c>
-      <c r="H87" t="s">
-        <v>65</v>
-      </c>
-      <c r="I87" t="s">
-        <v>625</v>
-      </c>
-      <c r="J87" t="s">
-        <v>627</v>
-      </c>
-      <c r="K87" t="s">
-        <v>91</v>
-      </c>
-      <c r="L87" t="s">
-        <v>466</v>
-      </c>
       <c r="M87" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N87" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O87">
         <v>4.5999999999999996</v>
@@ -6965,7 +6971,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C88" s="1">
         <v>65</v>
@@ -6974,34 +6980,34 @@
         <v>85</v>
       </c>
       <c r="E88" t="s">
+        <v>467</v>
+      </c>
+      <c r="F88" t="s">
         <v>468</v>
       </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>469</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
+        <v>64</v>
+      </c>
+      <c r="I88" t="s">
+        <v>624</v>
+      </c>
+      <c r="J88" t="s">
+        <v>626</v>
+      </c>
+      <c r="K88" t="s">
+        <v>12</v>
+      </c>
+      <c r="L88" t="s">
         <v>470</v>
       </c>
-      <c r="H88" t="s">
-        <v>65</v>
-      </c>
-      <c r="I88" t="s">
-        <v>625</v>
-      </c>
-      <c r="J88" t="s">
-        <v>627</v>
-      </c>
-      <c r="K88" t="s">
-        <v>13</v>
-      </c>
-      <c r="L88" t="s">
-        <v>471</v>
-      </c>
       <c r="M88" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N88" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O88">
         <v>4.7</v>
@@ -7015,7 +7021,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C89" s="1">
         <v>15</v>
@@ -7024,34 +7030,34 @@
         <v>25</v>
       </c>
       <c r="E89" t="s">
+        <v>472</v>
+      </c>
+      <c r="F89" t="s">
         <v>473</v>
       </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>474</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
+        <v>64</v>
+      </c>
+      <c r="I89" t="s">
+        <v>624</v>
+      </c>
+      <c r="J89" t="s">
+        <v>626</v>
+      </c>
+      <c r="K89" t="s">
+        <v>90</v>
+      </c>
+      <c r="L89" t="s">
         <v>475</v>
       </c>
-      <c r="H89" t="s">
-        <v>65</v>
-      </c>
-      <c r="I89" t="s">
-        <v>625</v>
-      </c>
-      <c r="J89" t="s">
-        <v>627</v>
-      </c>
-      <c r="K89" t="s">
-        <v>91</v>
-      </c>
-      <c r="L89" t="s">
-        <v>476</v>
-      </c>
       <c r="M89" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N89" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O89">
         <v>4.8</v>
@@ -7065,7 +7071,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C90" s="1">
         <v>30</v>
@@ -7074,34 +7080,34 @@
         <v>45</v>
       </c>
       <c r="E90" t="s">
+        <v>477</v>
+      </c>
+      <c r="F90" t="s">
         <v>478</v>
       </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>479</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
+        <v>64</v>
+      </c>
+      <c r="I90" t="s">
+        <v>624</v>
+      </c>
+      <c r="J90" t="s">
+        <v>626</v>
+      </c>
+      <c r="K90" t="s">
+        <v>12</v>
+      </c>
+      <c r="L90" t="s">
         <v>480</v>
       </c>
-      <c r="H90" t="s">
-        <v>65</v>
-      </c>
-      <c r="I90" t="s">
-        <v>625</v>
-      </c>
-      <c r="J90" t="s">
-        <v>627</v>
-      </c>
-      <c r="K90" t="s">
-        <v>13</v>
-      </c>
-      <c r="L90" t="s">
-        <v>481</v>
-      </c>
       <c r="M90" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N90" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O90">
         <v>4.9000000000000004</v>
@@ -7115,7 +7121,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C91" s="1">
         <v>40</v>
@@ -7124,34 +7130,34 @@
         <v>55</v>
       </c>
       <c r="E91" t="s">
+        <v>482</v>
+      </c>
+      <c r="F91" t="s">
         <v>483</v>
       </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>484</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
+        <v>64</v>
+      </c>
+      <c r="I91" t="s">
+        <v>624</v>
+      </c>
+      <c r="J91" t="s">
+        <v>626</v>
+      </c>
+      <c r="K91" t="s">
+        <v>90</v>
+      </c>
+      <c r="L91" t="s">
         <v>485</v>
       </c>
-      <c r="H91" t="s">
-        <v>65</v>
-      </c>
-      <c r="I91" t="s">
-        <v>625</v>
-      </c>
-      <c r="J91" t="s">
-        <v>627</v>
-      </c>
-      <c r="K91" t="s">
-        <v>91</v>
-      </c>
-      <c r="L91" t="s">
-        <v>486</v>
-      </c>
       <c r="M91" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N91" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O91">
         <v>4</v>
@@ -7165,7 +7171,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C92" s="1">
         <v>600</v>
@@ -7174,34 +7180,34 @@
         <v>750</v>
       </c>
       <c r="E92" t="s">
+        <v>487</v>
+      </c>
+      <c r="F92" t="s">
         <v>488</v>
       </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>489</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>490</v>
       </c>
-      <c r="H92" t="s">
+      <c r="I92" t="s">
+        <v>624</v>
+      </c>
+      <c r="J92" t="s">
+        <v>626</v>
+      </c>
+      <c r="K92" t="s">
+        <v>12</v>
+      </c>
+      <c r="L92" t="s">
         <v>491</v>
       </c>
-      <c r="I92" t="s">
-        <v>625</v>
-      </c>
-      <c r="J92" t="s">
-        <v>627</v>
-      </c>
-      <c r="K92" t="s">
-        <v>13</v>
-      </c>
-      <c r="L92" t="s">
-        <v>492</v>
-      </c>
       <c r="M92" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N92" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O92">
         <v>4.0999999999999996</v>
@@ -7215,7 +7221,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C93" s="1">
         <v>25</v>
@@ -7224,34 +7230,34 @@
         <v>38</v>
       </c>
       <c r="E93" t="s">
+        <v>493</v>
+      </c>
+      <c r="F93" t="s">
         <v>494</v>
       </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>495</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
+        <v>490</v>
+      </c>
+      <c r="I93" t="s">
+        <v>624</v>
+      </c>
+      <c r="J93" t="s">
+        <v>626</v>
+      </c>
+      <c r="K93" t="s">
+        <v>90</v>
+      </c>
+      <c r="L93" t="s">
         <v>496</v>
       </c>
-      <c r="H93" t="s">
-        <v>491</v>
-      </c>
-      <c r="I93" t="s">
-        <v>625</v>
-      </c>
-      <c r="J93" t="s">
-        <v>627</v>
-      </c>
-      <c r="K93" t="s">
-        <v>91</v>
-      </c>
-      <c r="L93" t="s">
-        <v>497</v>
-      </c>
       <c r="M93" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N93" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O93">
         <v>4.2</v>
@@ -7265,7 +7271,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C94" s="1">
         <v>480</v>
@@ -7274,34 +7280,34 @@
         <v>580</v>
       </c>
       <c r="E94" t="s">
+        <v>498</v>
+      </c>
+      <c r="F94" t="s">
         <v>499</v>
       </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>500</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
+        <v>490</v>
+      </c>
+      <c r="I94" t="s">
+        <v>624</v>
+      </c>
+      <c r="J94" t="s">
+        <v>626</v>
+      </c>
+      <c r="K94" t="s">
+        <v>12</v>
+      </c>
+      <c r="L94" t="s">
         <v>501</v>
       </c>
-      <c r="H94" t="s">
-        <v>491</v>
-      </c>
-      <c r="I94" t="s">
-        <v>625</v>
-      </c>
-      <c r="J94" t="s">
-        <v>627</v>
-      </c>
-      <c r="K94" t="s">
-        <v>13</v>
-      </c>
-      <c r="L94" t="s">
-        <v>502</v>
-      </c>
       <c r="M94" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N94" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O94">
         <v>4.3</v>
@@ -7315,7 +7321,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C95" s="1">
         <v>290</v>
@@ -7324,34 +7330,34 @@
         <v>360</v>
       </c>
       <c r="E95" t="s">
+        <v>503</v>
+      </c>
+      <c r="F95" t="s">
         <v>504</v>
       </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>505</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
+        <v>490</v>
+      </c>
+      <c r="I95" t="s">
+        <v>624</v>
+      </c>
+      <c r="J95" t="s">
+        <v>626</v>
+      </c>
+      <c r="K95" t="s">
+        <v>90</v>
+      </c>
+      <c r="L95" t="s">
         <v>506</v>
       </c>
-      <c r="H95" t="s">
-        <v>491</v>
-      </c>
-      <c r="I95" t="s">
-        <v>625</v>
-      </c>
-      <c r="J95" t="s">
-        <v>627</v>
-      </c>
-      <c r="K95" t="s">
-        <v>91</v>
-      </c>
-      <c r="L95" t="s">
-        <v>507</v>
-      </c>
       <c r="M95" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O95">
         <v>4.4000000000000004</v>
@@ -7365,7 +7371,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C96" s="1">
         <v>90</v>
@@ -7374,34 +7380,34 @@
         <v>125</v>
       </c>
       <c r="E96" t="s">
+        <v>508</v>
+      </c>
+      <c r="F96" t="s">
         <v>509</v>
       </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>510</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
+        <v>490</v>
+      </c>
+      <c r="I96" t="s">
+        <v>624</v>
+      </c>
+      <c r="J96" t="s">
+        <v>626</v>
+      </c>
+      <c r="K96" t="s">
+        <v>12</v>
+      </c>
+      <c r="L96" t="s">
         <v>511</v>
       </c>
-      <c r="H96" t="s">
-        <v>491</v>
-      </c>
-      <c r="I96" t="s">
-        <v>625</v>
-      </c>
-      <c r="J96" t="s">
-        <v>627</v>
-      </c>
-      <c r="K96" t="s">
-        <v>13</v>
-      </c>
-      <c r="L96" t="s">
-        <v>512</v>
-      </c>
       <c r="M96" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N96" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O96">
         <v>4.5</v>
@@ -7415,7 +7421,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C97" s="1">
         <v>40</v>
@@ -7424,34 +7430,34 @@
         <v>55</v>
       </c>
       <c r="E97" t="s">
+        <v>513</v>
+      </c>
+      <c r="F97" t="s">
         <v>514</v>
       </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>515</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
+        <v>490</v>
+      </c>
+      <c r="I97" t="s">
+        <v>624</v>
+      </c>
+      <c r="J97" t="s">
+        <v>626</v>
+      </c>
+      <c r="K97" t="s">
+        <v>90</v>
+      </c>
+      <c r="L97" t="s">
         <v>516</v>
       </c>
-      <c r="H97" t="s">
-        <v>491</v>
-      </c>
-      <c r="I97" t="s">
-        <v>625</v>
-      </c>
-      <c r="J97" t="s">
-        <v>627</v>
-      </c>
-      <c r="K97" t="s">
-        <v>91</v>
-      </c>
-      <c r="L97" t="s">
-        <v>517</v>
-      </c>
       <c r="M97" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N97" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O97">
         <v>4.5999999999999996</v>
@@ -7465,7 +7471,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C98" s="1">
         <v>60</v>
@@ -7474,34 +7480,34 @@
         <v>80</v>
       </c>
       <c r="E98" t="s">
+        <v>518</v>
+      </c>
+      <c r="F98" t="s">
         <v>519</v>
       </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>520</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
+        <v>490</v>
+      </c>
+      <c r="I98" t="s">
+        <v>624</v>
+      </c>
+      <c r="J98" t="s">
+        <v>626</v>
+      </c>
+      <c r="K98" t="s">
+        <v>12</v>
+      </c>
+      <c r="L98" t="s">
         <v>521</v>
       </c>
-      <c r="H98" t="s">
-        <v>491</v>
-      </c>
-      <c r="I98" t="s">
-        <v>625</v>
-      </c>
-      <c r="J98" t="s">
-        <v>627</v>
-      </c>
-      <c r="K98" t="s">
-        <v>13</v>
-      </c>
-      <c r="L98" t="s">
-        <v>522</v>
-      </c>
       <c r="M98" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N98" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O98">
         <v>4.7</v>
@@ -7515,7 +7521,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C99" s="1">
         <v>75</v>
@@ -7524,34 +7530,34 @@
         <v>105</v>
       </c>
       <c r="E99" t="s">
+        <v>523</v>
+      </c>
+      <c r="F99" t="s">
         <v>524</v>
       </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>525</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
+        <v>490</v>
+      </c>
+      <c r="I99" t="s">
+        <v>624</v>
+      </c>
+      <c r="J99" t="s">
+        <v>626</v>
+      </c>
+      <c r="K99" t="s">
+        <v>90</v>
+      </c>
+      <c r="L99" t="s">
         <v>526</v>
       </c>
-      <c r="H99" t="s">
-        <v>491</v>
-      </c>
-      <c r="I99" t="s">
-        <v>625</v>
-      </c>
-      <c r="J99" t="s">
-        <v>627</v>
-      </c>
-      <c r="K99" t="s">
-        <v>91</v>
-      </c>
-      <c r="L99" t="s">
-        <v>527</v>
-      </c>
       <c r="M99" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N99" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O99">
         <v>4.8</v>
@@ -7565,7 +7571,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C100" s="1">
         <v>55</v>
@@ -7574,34 +7580,34 @@
         <v>75</v>
       </c>
       <c r="E100" t="s">
+        <v>528</v>
+      </c>
+      <c r="F100" t="s">
         <v>529</v>
       </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>530</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
+        <v>490</v>
+      </c>
+      <c r="I100" t="s">
+        <v>624</v>
+      </c>
+      <c r="J100" t="s">
+        <v>626</v>
+      </c>
+      <c r="K100" t="s">
+        <v>12</v>
+      </c>
+      <c r="L100" t="s">
         <v>531</v>
       </c>
-      <c r="H100" t="s">
-        <v>491</v>
-      </c>
-      <c r="I100" t="s">
-        <v>625</v>
-      </c>
-      <c r="J100" t="s">
-        <v>627</v>
-      </c>
-      <c r="K100" t="s">
-        <v>13</v>
-      </c>
-      <c r="L100" t="s">
-        <v>532</v>
-      </c>
       <c r="M100" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N100" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O100">
         <v>4.9000000000000004</v>
@@ -7615,7 +7621,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C101" s="1">
         <v>350</v>
@@ -7624,34 +7630,34 @@
         <v>420</v>
       </c>
       <c r="E101" t="s">
+        <v>533</v>
+      </c>
+      <c r="F101" t="s">
         <v>534</v>
       </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>535</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
+        <v>490</v>
+      </c>
+      <c r="I101" t="s">
+        <v>624</v>
+      </c>
+      <c r="J101" t="s">
+        <v>626</v>
+      </c>
+      <c r="K101" t="s">
+        <v>90</v>
+      </c>
+      <c r="L101" t="s">
         <v>536</v>
       </c>
-      <c r="H101" t="s">
-        <v>491</v>
-      </c>
-      <c r="I101" t="s">
-        <v>625</v>
-      </c>
-      <c r="J101" t="s">
-        <v>627</v>
-      </c>
-      <c r="K101" t="s">
-        <v>91</v>
-      </c>
-      <c r="L101" t="s">
-        <v>537</v>
-      </c>
       <c r="M101" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N101" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O101">
         <v>4</v>
@@ -7663,7 +7669,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A3:H101 K1 A2:H2 K2:L2 K3:L101 N1:P1 N2:P2 N3:P101" numberStoredAsText="1"/>
+    <ignoredError sqref="A3:H101 A2:H2 K2:L2 K3:L101 N1:O1 N2:P2 N3:P101" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
@@ -7672,94 +7678,94 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>538</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>238</v>
-      </c>
-      <c r="B7" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B8" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>339</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>389</v>
+      </c>
+      <c r="B10" t="s">
         <v>545</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>390</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>490</v>
+      </c>
+      <c r="B11" t="s">
         <v>546</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>491</v>
-      </c>
-      <c r="B11" t="s">
-        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -7773,121 +7779,121 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" t="s">
         <v>548</v>
-      </c>
-      <c r="C1" t="s">
-        <v>549</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>549</v>
+      </c>
+      <c r="F1" t="s">
         <v>550</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>551</v>
       </c>
-      <c r="G1" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1770051311268</v>
       </c>
       <c r="B2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C2" t="s">
         <v>553</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>554</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>555</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>556</v>
       </c>
-      <c r="F2" t="s">
-        <v>557</v>
-      </c>
       <c r="G2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1770051311269</v>
       </c>
       <c r="B3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C3" t="s">
         <v>558</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>559</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>555</v>
+      </c>
+      <c r="F3" t="s">
         <v>560</v>
       </c>
-      <c r="E3" t="s">
-        <v>556</v>
-      </c>
-      <c r="F3" t="s">
-        <v>561</v>
-      </c>
       <c r="G3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1770051311270</v>
       </c>
       <c r="B4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C4" t="s">
         <v>562</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>563</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>555</v>
+      </c>
+      <c r="F4" t="s">
         <v>564</v>
       </c>
-      <c r="E4" t="s">
-        <v>556</v>
-      </c>
-      <c r="F4" t="s">
-        <v>565</v>
-      </c>
       <c r="G4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1770051311271</v>
       </c>
       <c r="B5" t="s">
+        <v>565</v>
+      </c>
+      <c r="C5" t="s">
         <v>566</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>567</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>568</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>569</v>
       </c>
-      <c r="F5" t="s">
-        <v>570</v>
-      </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -7901,71 +7907,71 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B1" t="s">
         <v>571</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D1" t="s">
         <v>572</v>
       </c>
-      <c r="C1" t="s">
-        <v>550</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>573</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>574</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>575</v>
       </c>
       <c r="B2">
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B3">
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3">
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D4" t="s">
         <v>579</v>
-      </c>
-      <c r="D4" t="s">
-        <v>580</v>
       </c>
       <c r="E4">
         <v>2000</v>
@@ -7982,83 +7988,83 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" t="s">
         <v>582</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>583</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>584</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>585</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>586</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>587</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>588</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>589</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>591</v>
       </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>593</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>594</v>
       </c>
-      <c r="C6" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>596</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>597</v>
-      </c>
-      <c r="C7" t="s">
-        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -8072,21 +8078,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -8100,216 +8106,216 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1" t="s">
+        <v>549</v>
+      </c>
+      <c r="C1" t="s">
         <v>599</v>
       </c>
-      <c r="B1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>600</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>602</v>
-      </c>
       <c r="B2" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C2">
         <v>5</v>
       </c>
       <c r="D2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>603</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>604</v>
-      </c>
       <c r="B3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C4">
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C5">
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C6">
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B7" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C7">
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B8" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B10" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B11" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B12" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C12">
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B14" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C14">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C15">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6D613A7-B48B-4F92-B51A-C26B6A70A1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A26DDC-A383-4371-8935-7B798B6C07CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -306,7 +306,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="123">
   <si>
     <t>id</t>
   </si>
@@ -639,9 +639,6 @@
   </si>
   <si>
     <t>سماعة لاسلكية ام 10 تي دبليو اس جديدة مع علبة شحن لاسلكية بلوتوث 5.1 9D صوت ممتاز باس عميق مقاومة للماء بتصنيف IPX7 مع ميكروفون ووقت تشغيل 6 ساعات</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/41btGX2zKxS._AC_SX466_.jpg</t>
   </si>
   <si>
     <t>https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg
@@ -667,9 +664,6 @@
 </t>
   </si>
   <si>
-    <t>https://m.media-amazon.com/images/I/61UYwVC+4xL._AC_SX466_.jpg</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/61UYwVC+4xL._AC_SX466_.jpg
 https://m.media-amazon.com/images/I/61r2RtNCxWL._AC_SX466_.jpg
 https://m.media-amazon.com/images/I/71cO4JetbhL._AC_SX466_.jpg
@@ -686,9 +680,6 @@
   </si>
   <si>
     <t>كيبورد يقوم بالعمل المكثف للكتابة والبرمجة وتحرير الوسائط المتعددة</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/51aabhr5+YL._AC_SX466_.jpg</t>
   </si>
   <si>
     <t>https://m.media-amazon.com/images/I/51aabhr5+YL._AC_SX466_.jpg
@@ -763,11 +754,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1114,7 +1104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -1202,23 +1192,23 @@
       <c r="F2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>112</v>
+      <c r="G2" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="H2" t="s">
         <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J2" t="s">
         <v>93</v>
       </c>
       <c r="K2" t="s">
-        <v>115</v>
-      </c>
-      <c r="L2" s="5" t="s">
         <v>114</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>113</v>
       </c>
       <c r="N2" t="s">
         <v>9</v>
@@ -1235,7 +1225,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -1243,14 +1233,14 @@
       <c r="D3" s="1">
         <v>181</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>118</v>
+      <c r="G3" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="H3" t="s">
         <v>97</v>
@@ -1261,8 +1251,8 @@
       <c r="K3" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="5" t="s">
-        <v>119</v>
+      <c r="L3" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="N3" t="s">
         <v>9</v>
@@ -1279,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1288,13 +1278,13 @@
         <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>121</v>
       </c>
       <c r="H4" t="s">
         <v>97</v>
@@ -1306,7 +1296,7 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -1318,405 +1308,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-    </row>
-    <row r="20" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-    </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-    </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-    </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-    </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-    </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-    </row>
-    <row r="37" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-    </row>
-    <row r="38" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-    </row>
-    <row r="39" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-    </row>
-    <row r="40" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-    </row>
-    <row r="41" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-    </row>
-    <row r="44" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-    </row>
-    <row r="45" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-    </row>
-    <row r="46" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-    </row>
-    <row r="47" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-    </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-    </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-    </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-    </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-    </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-    </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-    </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-    </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-    </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-    </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-    </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-    </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-    </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-    </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-    </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-    </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-    </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-    </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-    </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-    </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-    </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-    </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-    </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-    </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-    </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-    </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-    </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-    </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-    </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-    </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-    </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-    </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-    </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-    </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-    </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-    </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-    </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-    </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-    </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-    </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-    </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-    </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-    </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-    </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-    </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-    </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-    </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{40D8E011-90E2-480D-A25E-B8BD71860524}"/>
-    <hyperlink ref="G2" r:id="rId2" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{59AA8C82-2EB5-49A3-B780-EF1BB44A6EC0}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{FA272AB0-1BD2-4B9B-838E-583684763F2C}"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{59AA8C82-2EB5-49A3-B780-EF1BB44A6EC0}"/>
+    <hyperlink ref="F2" r:id="rId2" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{38E3BF75-EF4F-40C4-A5AD-A77F06B07B76}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A4 A2 K4 N1:O1 N2:P2 N3:P4 A3 K3" numberStoredAsText="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -1,38 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mashily\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A26DDC-A383-4371-8935-7B798B6C07CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE0D83E1-AF1B-4CA5-8B8E-00CD2DA5D26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Products" sheetId="1" r:id="rId1"/>
-    <sheet name="Categories" sheetId="2" r:id="rId2"/>
-    <sheet name="Videos" sheetId="3" r:id="rId3"/>
-    <sheet name="Coupons" sheetId="4" r:id="rId4"/>
-    <sheet name="Settings" sheetId="5" r:id="rId5"/>
-    <sheet name="Statuses" sheetId="6" r:id="rId6"/>
-    <sheet name="Notifications" sheetId="7" r:id="rId7"/>
+    <sheet name="Ticker" sheetId="8" r:id="rId1"/>
+    <sheet name="Products" sheetId="1" r:id="rId2"/>
+    <sheet name="Categories" sheetId="2" r:id="rId3"/>
+    <sheet name="Videos" sheetId="3" r:id="rId4"/>
+    <sheet name="Coupons" sheetId="4" r:id="rId5"/>
+    <sheet name="Settings" sheetId="5" r:id="rId6"/>
+    <sheet name="Statuses" sheetId="6" r:id="rId7"/>
+    <sheet name="Notifications" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -306,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="126">
   <si>
     <t>id</t>
   </si>
@@ -507,9 +497,6 @@
   </si>
   <si>
     <t>الرسالة</t>
-  </si>
-  <si>
-    <t>المدة (ثانية)</t>
   </si>
   <si>
     <t>فعال</t>
@@ -688,6 +675,18 @@
   </si>
   <si>
     <t>لوحة مفاتيح بسلك ومنفذ USB مريحة للعين</t>
+  </si>
+  <si>
+    <t>مدة العرض (ثانية)</t>
+  </si>
+  <si>
+    <t>سرعة الحركة (ثانية)</t>
+  </si>
+  <si>
+    <t>مدة الظهور (ثانية)</t>
+  </si>
+  <si>
+    <t>الانتظار قبل التالي (ثانية)</t>
   </si>
 </sst>
 </file>
@@ -697,7 +696,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -732,6 +731,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -754,7 +761,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -764,6 +771,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1103,6 +1111,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD01485-0D00-419E-A382-2485D3722BA1}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="43.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1128,40 +1250,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" t="s">
         <v>84</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>85</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>86</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>87</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>88</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>89</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>90</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>91</v>
       </c>
-      <c r="J1" t="s">
-        <v>92</v>
-      </c>
       <c r="K1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M1" t="s">
         <v>95</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" t="s">
-        <v>96</v>
       </c>
       <c r="N1" t="s">
         <v>4</v>
@@ -1178,7 +1300,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="1">
         <v>110</v>
@@ -1187,28 +1309,28 @@
         <v>149</v>
       </c>
       <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I2" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" t="s">
+        <v>113</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>93</v>
-      </c>
-      <c r="K2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="N2" t="s">
         <v>9</v>
@@ -1225,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -1234,25 +1356,25 @@
         <v>181</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N3" t="s">
         <v>9</v>
@@ -1269,7 +1391,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1278,25 +1400,25 @@
         <v>125</v>
       </c>
       <c r="E4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -1321,7 +1443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1340,50 +1462,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1516,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1522,7 +1644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1603,7 +1725,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1693,7 +1815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -1721,225 +1843,144 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="D1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
+        <v>77</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>60</v>
+        <v>78</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" t="s">
-        <v>60</v>
+        <v>80</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
+        <v>81</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
+        <v>82</v>
+      </c>
+      <c r="B9">
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
-      </c>
-      <c r="D13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14">
-        <v>4</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15">
-        <v>4</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:D15" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mashily\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE0D83E1-AF1B-4CA5-8B8E-00CD2DA5D26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DABFBD-6912-44A0-A2FF-E3B9D5872F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -296,7 +296,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
   <si>
     <t>id</t>
   </si>
@@ -687,6 +687,81 @@
   </si>
   <si>
     <t>الانتظار قبل التالي (ثانية)</t>
+  </si>
+  <si>
+    <t>brand_name</t>
+  </si>
+  <si>
+    <t>مشالى</t>
+  </si>
+  <si>
+    <t>اسم العلامة التجارية الظاهر في رأس الموقع</t>
+  </si>
+  <si>
+    <t>site_name</t>
+  </si>
+  <si>
+    <t>متجر مشالى | الإلكترونيات</t>
+  </si>
+  <si>
+    <t>اسم وعنوان الموقع</t>
+  </si>
+  <si>
+    <t>app_name</t>
+  </si>
+  <si>
+    <t>الاسم الكامل لتطبيق الهاتف المثبت</t>
+  </si>
+  <si>
+    <t>short_name</t>
+  </si>
+  <si>
+    <t>الاسم المختصر لأيقونة التطبيق المثبت</t>
+  </si>
+  <si>
+    <t>site_tagline</t>
+  </si>
+  <si>
+    <t>للإلكترونيات والفيديوهات التعليمية</t>
+  </si>
+  <si>
+    <t>العبارة أسفل شعار المتجر</t>
+  </si>
+  <si>
+    <t>site_description</t>
+  </si>
+  <si>
+    <t>متجر مشالى للإلكترونيات والفيديوهات التعليمية</t>
+  </si>
+  <si>
+    <t>وصف الموقع للمتصفح والمشاركة</t>
+  </si>
+  <si>
+    <t>academy_name</t>
+  </si>
+  <si>
+    <t>أكاديمية مشالى التعليمية</t>
+  </si>
+  <si>
+    <t>اسم صفحة الأكاديمية</t>
+  </si>
+  <si>
+    <t>academy_description</t>
+  </si>
+  <si>
+    <t>منصتك الأولى لتعلم صيانة الإلكترونيات والبرمجة وأحدث التقنيات.</t>
+  </si>
+  <si>
+    <t>وصف صفحة الأكاديمية</t>
+  </si>
+  <si>
+    <t>theme_color</t>
+  </si>
+  <si>
+    <t>#2e8b57</t>
+  </si>
+  <si>
+    <t>لون شريط المتصفح والتطبيق بصيغة HEX</t>
   </si>
 </sst>
 </file>
@@ -1727,8 +1802,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="90.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.25" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1805,6 +1885,105 @@
       </c>
       <c r="C7" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B9" t="s">
+        <v>130</v>
+      </c>
+      <c r="C9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+      <c r="B10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>136</v>
+      </c>
+      <c r="B12" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>145</v>
+      </c>
+      <c r="B15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C16" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -1819,6 +1998,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1851,7 +2033,7 @@
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mashily\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47DABFBD-6912-44A0-A2FF-E3B9D5872F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65BB87B-3B76-4775-8374-7B3474B6AA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -22,7 +22,18 @@
     <sheet name="Statuses" sheetId="6" r:id="rId7"/>
     <sheet name="Notifications" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -296,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="160">
   <si>
     <t>id</t>
   </si>
@@ -433,9 +444,6 @@
     <t>SAVE10</t>
   </si>
   <si>
-    <t>WELCOME</t>
-  </si>
-  <si>
     <t>fixed</t>
   </si>
   <si>
@@ -502,49 +510,13 @@
     <t>فعال</t>
   </si>
   <si>
-    <t>عرض خاص هذا الأسبوع - خصم 20% على المعالجات!</t>
-  </si>
-  <si>
     <t>نعم</t>
   </si>
   <si>
     <t>🔥 أهلاً بكم في متجر مشالى للإلكترونيات - جودة نثق بها 🔥</t>
   </si>
   <si>
-    <t>🚚 شحن مجاني للطلبات فوق 500 ج.م هذا الأسبوع</t>
-  </si>
-  <si>
     <t>🎁 خصم 15% على الإكسسوارات حتى نهاية الشهر</t>
-  </si>
-  <si>
-    <t>⚡ وصل حديثاً: ساعة ذكية Ultra - اطلبها الآن</t>
-  </si>
-  <si>
-    <t>📦 توصيل سريع لجميع المحافظات خلال 48 ساعة</t>
-  </si>
-  <si>
-    <t>أحمد من القاهرة اشترى رسيفر سيناتور 🔥</t>
-  </si>
-  <si>
-    <t>محمد من المنصورة طلب قطعة واي فاي ⚡</t>
-  </si>
-  <si>
-    <t>خالد من طنطا انضم للأكاديمية الآن ✅</t>
-  </si>
-  <si>
-    <t>عميل جديد طلب وصلة HDMI أصلية 🔌</t>
-  </si>
-  <si>
-    <t>تم شحن طلب جديد إلى الإسكندرية بنجاح 🚚</t>
-  </si>
-  <si>
-    <t>سارة من الجيزة اشترت ساعة ذكية Ultra ⌚</t>
-  </si>
-  <si>
-    <t>مصطفى من أسيوط طلب باور بانك 🔋</t>
-  </si>
-  <si>
-    <t>تم توصيل طلب إلى المنصورة بنجاح ✅</t>
   </si>
   <si>
     <t>title</t>
@@ -692,18 +664,12 @@
     <t>brand_name</t>
   </si>
   <si>
-    <t>مشالى</t>
-  </si>
-  <si>
     <t>اسم العلامة التجارية الظاهر في رأس الموقع</t>
   </si>
   <si>
     <t>site_name</t>
   </si>
   <si>
-    <t>متجر مشالى | الإلكترونيات</t>
-  </si>
-  <si>
     <t>اسم وعنوان الموقع</t>
   </si>
   <si>
@@ -722,18 +688,12 @@
     <t>site_tagline</t>
   </si>
   <si>
-    <t>للإلكترونيات والفيديوهات التعليمية</t>
-  </si>
-  <si>
     <t>العبارة أسفل شعار المتجر</t>
   </si>
   <si>
     <t>site_description</t>
   </si>
   <si>
-    <t>متجر مشالى للإلكترونيات والفيديوهات التعليمية</t>
-  </si>
-  <si>
     <t>وصف الموقع للمتصفح والمشاركة</t>
   </si>
   <si>
@@ -762,6 +722,88 @@
   </si>
   <si>
     <t>لون شريط المتصفح والتطبيق بصيغة HEX</t>
+  </si>
+  <si>
+    <t>عرض خاص هذا الأسبوع - خصم 20% على جميع الالكترونيات !</t>
+  </si>
+  <si>
+    <t>🚚 شحن مجاني للطلبات فوق 5000 ج.م هذا الأسبوع</t>
+  </si>
+  <si>
+    <t>اللهم صل وسلم وبارك على سيدنا محمد عدد كمال الله وكما يليق بكماله</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قرآن </t>
+  </si>
+  <si>
+    <t xml:space="preserve">الشيخ محمد رفعت </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=vTXjOWqkk1o</t>
+  </si>
+  <si>
+    <t>M@shily</t>
+  </si>
+  <si>
+    <t>الإلكترونيات والفيديوهات التعليمية</t>
+  </si>
+  <si>
+    <t>متجر مشالى لبيع للإلكترونيات والفيديوهات التعليمية</t>
+  </si>
+  <si>
+    <t>مشالى لتجارة للالكترونيات</t>
+  </si>
+  <si>
+    <t>متجر مشالى | لتجارة الإلكترونيات</t>
+  </si>
+  <si>
+    <t>حصري</t>
+  </si>
+  <si>
+    <t>🔥محمد من المنصورة اشترى سماعه + بور 🔥</t>
+  </si>
+  <si>
+    <t>⚡محمد من المنصورة طلب قطعة واي فاي ⚡</t>
+  </si>
+  <si>
+    <t>✅خالد من طنطا انضم للأكاديمية الآن ✅</t>
+  </si>
+  <si>
+    <t>♥عميل جديد طلب وصلة HDMI أصلية 🔌</t>
+  </si>
+  <si>
+    <t>♥تم شحن طلب جديد إلى الإسكندرية بنجاح 🚚</t>
+  </si>
+  <si>
+    <t>⌚سارة من الجيزة اشترت ساعة ذكية Ultra ⌚</t>
+  </si>
+  <si>
+    <t>⌚مصطفى من المنصورة طلب باور بانك 🔋</t>
+  </si>
+  <si>
+    <t>✅تم توصيل طلب إلى المنصورة بنجاح ✅</t>
+  </si>
+  <si>
+    <t>✅✅✅✅✅✅✅✅✅✅</t>
+  </si>
+  <si>
+    <t>Power Bank 10000mAh</t>
+  </si>
+  <si>
+    <t>G-Power GP-PB016 Power Bank 10000mAh, 22.5W Quick Charging Portable Battery Pack, Built-in 4 Charging Cables, Type-C &amp; USB Input, Multi-Device Charging, Strong LED Flashlight – Black</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg
+https://m.media-amazon.com/images/I/41daSCnIgCL._AC_SR38,50_.jpg
+https://m.media-amazon.com/images/I/41xIe-0J9pL._AC_SX679_.jpg
+https://m.media-amazon.com/images/I/71YsLoo3QfL._AC_SX679_.jpg
+https://www.amazon.eg/vdp/167f68facc1147dabdfaf47ed8dc85b9?aci=amzn1.ive.vendor.video.167f68facc1147dabdfaf47ed8dc85b9&amp;ref=dp_vse_ibvc0</t>
+  </si>
+  <si>
+    <t>♥</t>
+  </si>
+  <si>
+    <t>جديد وحضري</t>
   </si>
 </sst>
 </file>
@@ -771,7 +813,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -814,6 +856,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color rgb="FF0F1111"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -836,7 +884,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -847,6 +895,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1187,32 +1240,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD01485-0D00-419E-A382-2485D3722BA1}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="115.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1221,77 +1274,63 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>20</v>
-      </c>
-      <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1301,15 +1340,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.25" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="10.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="46.375" customWidth="1"/>
-    <col min="6" max="6" width="37.875" customWidth="1"/>
-    <col min="7" max="7" width="38.75" customWidth="1"/>
+    <col min="6" max="6" width="56.25" customWidth="1"/>
+    <col min="7" max="7" width="47.875" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
@@ -1325,40 +1364,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="D1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E1" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="F1" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G1" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="H1" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="I1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="J1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K1" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="M1" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="N1" t="s">
         <v>4</v>
@@ -1370,12 +1409,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="236.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1">
         <v>110</v>
@@ -1384,28 +1423,28 @@
         <v>149</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="J2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="N2" t="s">
         <v>9</v>
@@ -1417,12 +1456,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="189" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -1431,25 +1470,25 @@
         <v>181</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J3" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="N3" t="s">
         <v>9</v>
@@ -1461,12 +1500,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="141.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1475,25 +1514,25 @@
         <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="H4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="J4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -1503,18 +1542,55 @@
       </c>
       <c r="P4">
         <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="173.25" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="H5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J5" t="s">
+        <v>158</v>
+      </c>
+      <c r="K5" t="s">
+        <v>159</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{59AA8C82-2EB5-49A3-B780-EF1BB44A6EC0}"/>
     <hyperlink ref="F2" r:id="rId2" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{38E3BF75-EF4F-40C4-A5AD-A77F06B07B76}"/>
+    <hyperlink ref="F5" r:id="rId3" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{88FCABF5-8E78-44D2-8CC9-22AFE69F3414}"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{26122205-7BEA-4E14-B486-C728327086D0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="A4 A2 K4 N1:O1 N2:P2 N3:P4 A3 K3" numberStoredAsText="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1537,50 +1613,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1593,8 +1669,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.25" customWidth="1"/>
+    <col min="2" max="2" width="23.875" customWidth="1"/>
+    <col min="3" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="6" max="6" width="11.375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1621,22 +1705,22 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1770051311268</v>
+        <v>1770051311267</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
+        <v>138</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>137</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" t="s">
-        <v>24</v>
+      <c r="F2" s="7">
+        <v>0.46505787037037039</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
@@ -1644,22 +1728,22 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1770051311269</v>
+        <v>1770051311268</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E3" t="s">
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s">
         <v>9</v>
@@ -1667,22 +1751,22 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1770051311270</v>
+        <v>1770051311269</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
         <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -1690,31 +1774,54 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1770051311271</v>
+        <v>1770051311270</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1770051311271</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{68493181-F98E-438B-88DD-7AEA2299D695}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G5" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 G3:G5 E2 G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1723,6 +1830,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1776,26 +1886,29 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>45</v>
+      <c r="A4" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" t="s">
         <v>46</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
       </c>
       <c r="E4">
         <v>2000</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{55418756-44A1-4CB8-B869-52774045291C}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E3 B4:E4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1812,7 +1925,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" t="s">
         <v>39</v>
@@ -1823,167 +1936,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
         <v>52</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>53</v>
-      </c>
-      <c r="C3" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
         <v>55</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
         <v>60</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="C10" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B12" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C12" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C13" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="C14" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -1996,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
@@ -2015,6 +2128,11 @@
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2145,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
@@ -2038,128 +2156,142 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="B2">
         <v>4</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>147</v>
       </c>
       <c r="B3">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="B4">
         <v>4</v>
       </c>
       <c r="C4">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="B5">
         <v>4</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="B7">
         <v>4</v>
       </c>
       <c r="C7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>152</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>82</v>
+        <v>153</v>
       </c>
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65BB87B-3B76-4775-8374-7B3474B6AA16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4073DD4F-D919-4140-B043-F8D27736FA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="161">
   <si>
     <t>id</t>
   </si>
@@ -800,10 +800,13 @@
 https://www.amazon.eg/vdp/167f68facc1147dabdfaf47ed8dc85b9?aci=amzn1.ive.vendor.video.167f68facc1147dabdfaf47ed8dc85b9&amp;ref=dp_vse_ibvc0</t>
   </si>
   <si>
-    <t>♥</t>
-  </si>
-  <si>
     <t>جديد وحضري</t>
+  </si>
+  <si>
+    <t>موجود</t>
+  </si>
+  <si>
+    <t>موجووود</t>
   </si>
 </sst>
 </file>
@@ -884,7 +887,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -900,6 +903,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1552,10 +1556,10 @@
         <v>155</v>
       </c>
       <c r="C5" s="1">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E5" t="s">
         <v>156</v>
@@ -1569,14 +1573,20 @@
       <c r="H5" t="s">
         <v>84</v>
       </c>
+      <c r="I5" t="s">
+        <v>160</v>
+      </c>
       <c r="J5" t="s">
+        <v>159</v>
+      </c>
+      <c r="K5" t="s">
         <v>158</v>
-      </c>
-      <c r="K5" t="s">
-        <v>159</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>156</v>
+      </c>
+      <c r="M5" s="9">
+        <v>46296</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4073DD4F-D919-4140-B043-F8D27736FA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630B418-5965-40E4-A3F8-5F29661819F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="172">
   <si>
     <t>id</t>
   </si>
@@ -445,9 +445,6 @@
   </si>
   <si>
     <t>fixed</t>
-  </si>
-  <si>
-    <t>2026-10-31</t>
   </si>
   <si>
     <t>المفتاح</t>
@@ -742,9 +739,6 @@
     <t>https://www.youtube.com/watch?v=vTXjOWqkk1o</t>
   </si>
   <si>
-    <t>M@shily</t>
-  </si>
-  <si>
     <t>الإلكترونيات والفيديوهات التعليمية</t>
   </si>
   <si>
@@ -791,22 +785,62 @@
   </si>
   <si>
     <t>G-Power GP-PB016 Power Bank 10000mAh, 22.5W Quick Charging Portable Battery Pack, Built-in 4 Charging Cables, Type-C &amp; USB Input, Multi-Device Charging, Strong LED Flashlight – Black</t>
+  </si>
+  <si>
+    <t>جديد وحضري</t>
+  </si>
+  <si>
+    <t>موجود</t>
+  </si>
+  <si>
+    <t>موجووود</t>
+  </si>
+  <si>
+    <t>mashily</t>
+  </si>
+  <si>
+    <t>mashilyy</t>
   </si>
   <si>
     <t>https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg
 https://m.media-amazon.com/images/I/41daSCnIgCL._AC_SR38,50_.jpg
 https://m.media-amazon.com/images/I/41xIe-0J9pL._AC_SX679_.jpg
-https://m.media-amazon.com/images/I/71YsLoo3QfL._AC_SX679_.jpg
-https://www.amazon.eg/vdp/167f68facc1147dabdfaf47ed8dc85b9?aci=amzn1.ive.vendor.video.167f68facc1147dabdfaf47ed8dc85b9&amp;ref=dp_vse_ibvc0</t>
-  </si>
-  <si>
-    <t>جديد وحضري</t>
-  </si>
-  <si>
-    <t>موجود</t>
-  </si>
-  <si>
-    <t>موجووود</t>
+https://m.media-amazon.com/images/I/71YsLoo3QfL._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كابل بور </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كابل بور  ثلاثي </t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71--+XWN5UL._AC_SX466_.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كابل معدات تبريد أنثى إلى ذكر بطول 1.8 م مع قابس 90 درجة لأجهزة الكمبيوتر والشاشات والطابعات وأجهزة الكهرباء </t>
+  </si>
+  <si>
+    <t xml:space="preserve">كابل بور ثلاثة لشواحن اللاب توب وغيرها من الاستخدامات </t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41Zm4dSYXML._AC_SX466_.jpg</t>
+  </si>
+  <si>
+    <t>ملصق لكيبورد الكمبيوتر باللغة العربية</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ملصق لكيبورد الكمبيوتر باللغة العربية </t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61a9otcqBYL._AC_SX679_.jpg
+https://m.media-amazon.com/images/I/51-MMDUaCSL._AC_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61r8fPKQSEL._AC_SX679_.jpg
+https://m.media-amazon.com/images/I/618afv2hU5L._AC_SX679_.jpg</t>
+  </si>
+  <si>
+    <t>جديد ملصقات كيبورد باللغة العربية بديلة مقاومة للغبار ومقاومة للماء للكمبيوتر واللاب توب وكيبورد سطح المكتب قطعة واحدة</t>
   </si>
 </sst>
 </file>
@@ -1255,21 +1289,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1278,12 +1312,12 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>30</v>
@@ -1292,12 +1326,12 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1306,12 +1340,12 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1320,12 +1354,12 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B6">
         <v>50</v>
@@ -1334,7 +1368,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1344,7 +1378,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -1368,40 +1402,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
         <v>70</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>71</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>72</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>73</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>74</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>75</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>76</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>77</v>
       </c>
-      <c r="J1" t="s">
-        <v>78</v>
-      </c>
       <c r="K1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M1" t="s">
         <v>81</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="M1" t="s">
-        <v>82</v>
       </c>
       <c r="N1" t="s">
         <v>4</v>
@@ -1418,7 +1452,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C2" s="1">
         <v>110</v>
@@ -1427,28 +1461,28 @@
         <v>149</v>
       </c>
       <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="H2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K2" t="s">
+        <v>99</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="J2" t="s">
-        <v>79</v>
-      </c>
-      <c r="K2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="N2" t="s">
         <v>9</v>
@@ -1465,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -1474,25 +1508,25 @@
         <v>181</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K3" t="s">
         <v>11</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N3" t="s">
         <v>9</v>
@@ -1509,7 +1543,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1518,25 +1552,25 @@
         <v>125</v>
       </c>
       <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K4" t="s">
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -1548,45 +1582,161 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="173.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="162.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="1">
+        <v>125</v>
+      </c>
+      <c r="D5" s="1">
+        <v>150</v>
+      </c>
+      <c r="E5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K5" t="s">
         <v>155</v>
       </c>
-      <c r="C5" s="1">
-        <v>150</v>
-      </c>
-      <c r="D5" s="1">
-        <v>120</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" t="s">
-        <v>160</v>
-      </c>
-      <c r="J5" t="s">
-        <v>159</v>
-      </c>
-      <c r="K5" t="s">
-        <v>158</v>
-      </c>
       <c r="L5" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="M5" s="9">
         <v>46296</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="1">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F6" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H6" t="s">
+        <v>82</v>
+      </c>
+      <c r="L6" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="1">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G7" t="s">
+        <v>163</v>
+      </c>
+      <c r="H7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>20</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="H8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L8" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C9" s="1">
+        <v>10</v>
+      </c>
+      <c r="D9" s="1">
+        <v>20</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="H9" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1594,7 +1744,7 @@
     <hyperlink ref="G2" r:id="rId1" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{59AA8C82-2EB5-49A3-B780-EF1BB44A6EC0}"/>
     <hyperlink ref="F2" r:id="rId2" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{38E3BF75-EF4F-40C4-A5AD-A77F06B07B76}"/>
     <hyperlink ref="F5" r:id="rId3" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{88FCABF5-8E78-44D2-8CC9-22AFE69F3414}"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{26122205-7BEA-4E14-B486-C728327086D0}"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{2094F7BE-8E2F-489F-80D9-3FCF9259626A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -1623,50 +1773,50 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1718,13 +1868,13 @@
         <v>1770051311267</v>
       </c>
       <c r="B2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>139</v>
-      </c>
       <c r="D2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -1838,7 +1988,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="19.25" customWidth="1"/>
@@ -1896,8 +2046,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>140</v>
+      <c r="A4" t="s">
+        <v>158</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -1906,19 +2056,33 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>2000</v>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{55418756-44A1-4CB8-B869-52774045291C}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E3 B4:E4" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E2 B4:C4 B3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1935,7 +2099,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B1" t="s">
         <v>39</v>
@@ -1946,167 +2110,167 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
         <v>48</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>52</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
         <v>54</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6" t="s">
         <v>59</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" t="s">
         <v>62</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>63</v>
-      </c>
-      <c r="C7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" t="s">
         <v>113</v>
-      </c>
-      <c r="B8" t="s">
-        <v>143</v>
-      </c>
-      <c r="C8" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C9" t="s">
         <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C10" t="s">
         <v>117</v>
-      </c>
-      <c r="B10" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" t="s">
         <v>119</v>
-      </c>
-      <c r="B11" t="s">
-        <v>143</v>
-      </c>
-      <c r="C11" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B12" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" t="s">
         <v>121</v>
-      </c>
-      <c r="B12" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B13" t="s">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s">
         <v>123</v>
-      </c>
-      <c r="B13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C13" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" t="s">
         <v>125</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>126</v>
-      </c>
-      <c r="C14" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>127</v>
+      </c>
+      <c r="B15" t="s">
         <v>128</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>129</v>
-      </c>
-      <c r="C15" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>130</v>
+      </c>
+      <c r="B16" t="s">
         <v>131</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>132</v>
-      </c>
-      <c r="C16" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2142,7 +2306,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2166,21 +2330,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2189,12 +2353,12 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -2203,12 +2367,12 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -2217,12 +2381,12 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2231,12 +2395,12 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -2245,12 +2409,12 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -2259,12 +2423,12 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -2273,12 +2437,12 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -2287,12 +2451,12 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -2301,7 +2465,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630B418-5965-40E4-A3F8-5F29661819F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B46E53-252F-40E2-9CF5-A09DA3A6666E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="180">
   <si>
     <t>id</t>
   </si>
@@ -841,6 +841,33 @@
   </si>
   <si>
     <t>جديد ملصقات كيبورد باللغة العربية بديلة مقاومة للغبار ومقاومة للماء للكمبيوتر واللاب توب وكيبورد سطح المكتب قطعة واحدة</t>
+  </si>
+  <si>
+    <t>كابل VGA</t>
+  </si>
+  <si>
+    <t>كابل شاشة VGA</t>
+  </si>
+  <si>
+    <t>كابل VGA اتصال شاشة موثوق للشاشات والكمبيوتر واللابتوب وأجهزة العرض بطول 1.5 متر، لون أسود</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41AOB-DrrbL._SX466_.jpg</t>
+  </si>
+  <si>
+    <t>كابل HDMI 4K</t>
+  </si>
+  <si>
+    <t>كابل HDMI 4K </t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61mDpMvA2AL._AC_SX466_.jpg
+https://m.media-amazon.com/images/I/514-7QHBeVL._AC_SX466_.jpg
+https://m.media-amazon.com/images/I/41Mt6JLcn9L._AC_SX466_.jpg
+https://m.media-amazon.com/images/I/51se5XhiDVL._AC_SX466_.jpg</t>
+  </si>
+  <si>
+    <t>♥جديد</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -1737,6 +1764,67 @@
       </c>
       <c r="L9" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C10" s="1">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" t="s">
+        <v>175</v>
+      </c>
+      <c r="H10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L10" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="126" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="1">
+        <v>50</v>
+      </c>
+      <c r="D11" s="1">
+        <v>60</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H11" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B46E53-252F-40E2-9CF5-A09DA3A6666E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838DDC00-9204-47B5-BC38-626BE138824B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -307,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="179">
   <si>
     <t>id</t>
   </si>
@@ -796,12 +796,6 @@
     <t>موجووود</t>
   </si>
   <si>
-    <t>mashily</t>
-  </si>
-  <si>
-    <t>mashilyy</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg
 https://m.media-amazon.com/images/I/41daSCnIgCL._AC_SR38,50_.jpg
 https://m.media-amazon.com/images/I/41xIe-0J9pL._AC_SX679_.jpg
@@ -868,6 +862,9 @@
   </si>
   <si>
     <t>♥جديد</t>
+  </si>
+  <si>
+    <t>لا</t>
   </si>
 </sst>
 </file>
@@ -948,7 +945,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -965,6 +962,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1339,7 +1339,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1367,7 +1367,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1381,7 +1381,7 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1626,10 +1626,10 @@
         <v>154</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H5" t="s">
         <v>83</v>
@@ -1655,7 +1655,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
@@ -1664,19 +1664,19 @@
         <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H6" t="s">
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1684,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1">
         <v>25</v>
@@ -1693,19 +1693,19 @@
         <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H7" t="s">
         <v>82</v>
       </c>
       <c r="L7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="63" x14ac:dyDescent="0.25">
@@ -1713,7 +1713,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1722,19 +1722,19 @@
         <v>20</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H8" t="s">
         <v>82</v>
       </c>
       <c r="L8" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="63" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -1751,19 +1751,19 @@
         <v>20</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H9" t="s">
         <v>82</v>
       </c>
       <c r="L9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
@@ -1771,7 +1771,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C10" s="1">
         <v>35</v>
@@ -1780,19 +1780,19 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
+        <v>171</v>
+      </c>
+      <c r="F10" t="s">
         <v>173</v>
       </c>
-      <c r="F10" t="s">
-        <v>175</v>
-      </c>
       <c r="G10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H10" t="s">
         <v>82</v>
       </c>
       <c r="L10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="126" x14ac:dyDescent="0.25">
@@ -1800,7 +1800,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1809,22 +1809,22 @@
         <v>60</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
         <v>82</v>
       </c>
       <c r="K11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2124,7 +2124,7 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -2134,8 +2134,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>158</v>
+      <c r="A4" s="10">
+        <v>12345</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -2151,8 +2151,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>159</v>
+      <c r="A5" s="10">
+        <v>14521</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -2170,7 +2170,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E2 B4:C4 B3:E3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E2 B4:C4 B3 D3:E3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2364,7 +2364,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C7" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C6 A7 C7" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\28-9-2026\30-9-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838DDC00-9204-47B5-BC38-626BE138824B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C541B2A-D7C4-4544-B1DD-2B124C789155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -22,18 +22,7 @@
     <sheet name="Statuses" sheetId="6" r:id="rId7"/>
     <sheet name="Notifications" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -41,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>pc</author>
+    <author>mashily</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{1C26C0FE-B19C-4F7F-AAB3-194C51C740E6}">
@@ -302,12 +292,45 @@
         </r>
       </text>
     </comment>
+    <comment ref="Q1" authorId="1" shapeId="0" xr:uid="{1E55362A-0B3A-4B1B-869A-A4456968BC71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>mashily:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="48"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>بداية العرض لو ترك فارغ يبدا من تاريخ الي نهاية العرض end بنفس الصيغة</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="184">
   <si>
     <t>id</t>
   </si>
@@ -865,6 +888,21 @@
   </si>
   <si>
     <t>لا</t>
+  </si>
+  <si>
+    <t>offer_start</t>
+  </si>
+  <si>
+    <t>الصاروح ( لاصق )</t>
+  </si>
+  <si>
+    <t>مادة لاصقة مصنوعة من سيانوأكريلات بشكل عصا، مواد لاصقة قوية، شفاف،</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61FStXQ+rbL._SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NjtJUqu-dX4&amp;pp=ygUX2YTYp9i12YIg2KfZhNi12KfYsdmI2K4%3D</t>
   </si>
 </sst>
 </file>
@@ -874,7 +912,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -923,6 +961,29 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="48"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF0F1111"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -945,7 +1006,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -964,6 +1025,18 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1405,7 +1478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -1419,12 +1492,14 @@
     <col min="10" max="10" width="8.625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="49.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="32.375" customWidth="1"/>
+    <col min="14" max="14" width="10.375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="5.625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1473,8 +1548,11 @@
       <c r="P1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q1" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1521,7 +1599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1565,7 +1643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1609,7 +1687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="162.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="162.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1650,7 +1728,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1679,7 +1757,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1708,7 +1786,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="63" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1737,7 +1815,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="63" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1766,7 +1844,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1795,7 +1873,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="126" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="126" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1825,6 +1903,53 @@
       </c>
       <c r="L11" s="8" t="s">
         <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="12">
+        <v>15</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="H12" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="11"/>
+      <c r="L12" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="M12" s="14">
+        <v>46300.999305555553</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="O12" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="P12" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q12" s="14">
+        <v>46270.999305555553</v>
       </c>
     </row>
   </sheetData>
@@ -1835,10 +1960,11 @@
     <hyperlink ref="G5" r:id="rId4" display="https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg" xr:uid="{2094F7BE-8E2F-489F-80D9-3FCF9259626A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
   <ignoredErrors>
     <ignoredError sqref="A4 A2 K4 N1:O1 N2:P2 N3:P4 A3 K3" numberStoredAsText="1"/>
   </ignoredErrors>
-  <legacyDrawing r:id="rId5"/>
+  <legacyDrawing r:id="rId6"/>
 </worksheet>
 </file>
 
@@ -1861,26 +1987,26 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1893,10 +2019,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C541B2A-D7C4-4544-B1DD-2B124C789155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417D209-675A-49A9-91D2-7271A7C864B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,7 +330,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="185">
   <si>
     <t>id</t>
   </si>
@@ -623,9 +623,6 @@
     <t>https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg
 https://m.media-amazon.com/images/I/51D21amEkzS._AC_SX466_.jpg
 https://m.media-amazon.com/images/I/51ubafjFQ4S._AC_SX466_.jpg</t>
-  </si>
-  <si>
-    <t>stock</t>
   </si>
   <si>
     <t>التحكم باللمس] ما عليك سوى النقر مرة واحدة لتشغيل/الإيقاف المؤقت أو الرد على المكالمات. نقرة مزدوجة للتخطي للأمام/الخلف. اضغط لضبط مستوى الصوت
@@ -816,9 +813,6 @@
     <t>موجود</t>
   </si>
   <si>
-    <t>موجووود</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/6191-uciSZL._AC_SX679_.jpg
 https://m.media-amazon.com/images/I/41daSCnIgCL._AC_SR38,50_.jpg
 https://m.media-amazon.com/images/I/41xIe-0J9pL._AC_SX679_.jpg
@@ -903,6 +897,15 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=NjtJUqu-dX4&amp;pp=ygUX2YTYp9i12YIg2KfZhNi12KfYsdmI2K4%3D</t>
+  </si>
+  <si>
+    <t>متوفر</t>
+  </si>
+  <si>
+    <t>غير متوفر</t>
+  </si>
+  <si>
+    <t>الصاروح المستورد ( لاصق )</t>
   </si>
 </sst>
 </file>
@@ -912,7 +915,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -984,6 +987,12 @@
       <family val="2"/>
       <charset val="178"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1006,7 +1015,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1037,6 +1046,9 @@
     </xf>
     <xf numFmtId="22" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1392,10 +1404,10 @@
         <v>64</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>65</v>
@@ -1403,7 +1415,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1412,7 +1424,7 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1426,12 +1438,12 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1440,7 +1452,7 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1454,12 +1466,12 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6">
         <v>50</v>
@@ -1478,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -1549,7 +1561,7 @@
         <v>6</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1578,16 +1590,16 @@
         <v>83</v>
       </c>
       <c r="I2" t="s">
-        <v>97</v>
+        <v>182</v>
       </c>
       <c r="J2" t="s">
         <v>78</v>
       </c>
       <c r="K2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N2" t="s">
         <v>9</v>
@@ -1604,7 +1616,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C3" s="1">
         <v>125</v>
@@ -1613,17 +1625,20 @@
         <v>181</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="G3" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H3" t="s">
         <v>82</v>
       </c>
+      <c r="I3" t="s">
+        <v>182</v>
+      </c>
       <c r="J3" t="s">
         <v>78</v>
       </c>
@@ -1631,7 +1646,7 @@
         <v>11</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3" t="s">
         <v>9</v>
@@ -1648,7 +1663,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C4" s="1">
         <v>100</v>
@@ -1657,17 +1672,20 @@
         <v>125</v>
       </c>
       <c r="E4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
         <v>82</v>
       </c>
+      <c r="I4" t="s">
+        <v>182</v>
+      </c>
       <c r="J4" t="s">
         <v>78</v>
       </c>
@@ -1675,7 +1693,7 @@
         <v>12</v>
       </c>
       <c r="L4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N4" t="s">
         <v>9</v>
@@ -1692,7 +1710,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1">
         <v>125</v>
@@ -1701,28 +1719,28 @@
         <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H5" t="s">
         <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="J5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M5" s="9">
         <v>46296</v>
@@ -1733,7 +1751,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1">
         <v>25</v>
@@ -1742,19 +1760,22 @@
         <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H6" t="s">
         <v>82</v>
       </c>
+      <c r="I6" t="s">
+        <v>182</v>
+      </c>
       <c r="L6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1762,7 +1783,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1">
         <v>25</v>
@@ -1771,19 +1792,22 @@
         <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H7" t="s">
         <v>82</v>
       </c>
+      <c r="I7" t="s">
+        <v>182</v>
+      </c>
       <c r="L7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="63" x14ac:dyDescent="0.25">
@@ -1791,7 +1815,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1800,19 +1824,22 @@
         <v>20</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H8" t="s">
         <v>82</v>
       </c>
+      <c r="I8" t="s">
+        <v>182</v>
+      </c>
       <c r="L8" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="63" x14ac:dyDescent="0.25">
@@ -1820,7 +1847,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C9" s="1">
         <v>10</v>
@@ -1829,19 +1856,22 @@
         <v>20</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H9" t="s">
         <v>82</v>
       </c>
+      <c r="I9" t="s">
+        <v>182</v>
+      </c>
       <c r="L9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
@@ -1849,7 +1879,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C10" s="1">
         <v>35</v>
@@ -1858,19 +1888,22 @@
         <v>50</v>
       </c>
       <c r="E10" t="s">
+        <v>169</v>
+      </c>
+      <c r="F10" t="s">
         <v>171</v>
       </c>
-      <c r="F10" t="s">
-        <v>173</v>
-      </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
         <v>82</v>
       </c>
+      <c r="I10" t="s">
+        <v>182</v>
+      </c>
       <c r="L10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="126" x14ac:dyDescent="0.25">
@@ -1878,7 +1911,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C11" s="1">
         <v>50</v>
@@ -1887,22 +1920,25 @@
         <v>60</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
         <v>82</v>
       </c>
+      <c r="I11" t="s">
+        <v>182</v>
+      </c>
       <c r="K11" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="46.5" x14ac:dyDescent="0.25">
@@ -1910,7 +1946,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C12" s="12">
         <v>10</v>
@@ -1919,28 +1955,30 @@
         <v>15</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="11"/>
+      <c r="I12" s="11" t="s">
+        <v>182</v>
+      </c>
       <c r="J12" s="11"/>
       <c r="K12" s="11"/>
       <c r="L12" s="13" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M12" s="14">
         <v>46300.999305555553</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O12" s="11">
         <v>4.5</v>
@@ -1952,7 +1990,67 @@
         <v>46270.999305555553</v>
       </c>
     </row>
+    <row r="13" spans="1:17" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="C13" s="12">
+        <v>100</v>
+      </c>
+      <c r="D13" s="12">
+        <v>150</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="M13" s="14">
+        <v>46300.999305555553</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="O13" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="P13" s="11">
+        <v>12</v>
+      </c>
+      <c r="Q13" s="14">
+        <v>46270.999305555553</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I12 I14:I1000" xr:uid="{4ED6D524-EEDC-44F1-9C02-CEF2B0AB3571}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"متوفر,غير متوفر"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"متوفر,غير متوفر"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{59AA8C82-2EB5-49A3-B780-EF1BB44A6EC0}"/>
     <hyperlink ref="F2" r:id="rId2" display="https://m.media-amazon.com/images/I/51hz8pROUWS._AC_.jpg" xr:uid="{38E3BF75-EF4F-40C4-A5AD-A77F06B07B76}"/>
@@ -2082,13 +2180,13 @@
         <v>1770051311267</v>
       </c>
       <c r="B2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
         <v>23</v>
@@ -2390,101 +2488,101 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" t="s">
         <v>112</v>
-      </c>
-      <c r="B8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
         <v>114</v>
-      </c>
-      <c r="B9" t="s">
-        <v>142</v>
-      </c>
-      <c r="C9" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" t="s">
         <v>116</v>
-      </c>
-      <c r="B10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C10" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" t="s">
         <v>118</v>
-      </c>
-      <c r="B11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
         <v>120</v>
-      </c>
-      <c r="B12" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" t="s">
         <v>122</v>
-      </c>
-      <c r="B13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C13" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" t="s">
         <v>124</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>125</v>
-      </c>
-      <c r="C14" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B15" t="s">
         <v>127</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>128</v>
-      </c>
-      <c r="C15" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
         <v>130</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>131</v>
-      </c>
-      <c r="C16" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2520,7 +2618,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2547,10 +2645,10 @@
         <v>64</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>65</v>
@@ -2558,7 +2656,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -2572,7 +2670,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -2586,7 +2684,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -2600,7 +2698,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -2614,7 +2712,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -2628,7 +2726,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -2642,7 +2740,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -2656,7 +2754,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -2670,7 +2768,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B10">
         <v>10</v>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417D209-675A-49A9-91D2-7271A7C864B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C04388D-136E-47CF-94BE-194ED811EF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -19,9 +19,13 @@
     <sheet name="Videos" sheetId="3" r:id="rId4"/>
     <sheet name="Coupons" sheetId="4" r:id="rId5"/>
     <sheet name="Settings" sheetId="5" r:id="rId6"/>
-    <sheet name="Statuses" sheetId="6" r:id="rId7"/>
-    <sheet name="Notifications" sheetId="7" r:id="rId8"/>
+    <sheet name="Popups" sheetId="9" r:id="rId7"/>
+    <sheet name="Statuses" sheetId="6" r:id="rId8"/>
+    <sheet name="Notifications" sheetId="7" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Popups!$A$1:$M$1</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
@@ -330,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="202">
   <si>
     <t>id</t>
   </si>
@@ -906,6 +910,57 @@
   </si>
   <si>
     <t>الصاروح المستورد ( لاصق )</t>
+  </si>
+  <si>
+    <t>المكان</t>
+  </si>
+  <si>
+    <t>رابط الصورة</t>
+  </si>
+  <si>
+    <t>نص الزر</t>
+  </si>
+  <si>
+    <t>رابط الزر</t>
+  </si>
+  <si>
+    <t>يبدأ في</t>
+  </si>
+  <si>
+    <t>ينتهي في</t>
+  </si>
+  <si>
+    <t>تأثير احتفالي</t>
+  </si>
+  <si>
+    <t>مدة التأثير (ثانية)</t>
+  </si>
+  <si>
+    <t>الكل</t>
+  </si>
+  <si>
+    <t>رموز التأثير (|)</t>
+  </si>
+  <si>
+    <t>ترحيب مؤقت</t>
+  </si>
+  <si>
+    <t>أهلاً بك في متجر مشالي</t>
+  </si>
+  <si>
+    <t>تصفح أحدث المنتجات وتابع العروض المؤقتة قبل انتهائها.</t>
+  </si>
+  <si>
+    <t>تصفح المتجر</t>
+  </si>
+  <si>
+    <t>index.html</t>
+  </si>
+  <si>
+    <t>2026-10-07 23:59</t>
+  </si>
+  <si>
+    <t>🎈|❤️|🎉|✨|💛</t>
   </si>
 </sst>
 </file>
@@ -994,12 +1049,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1015,7 +1076,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1050,6 +1111,11 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2594,6 +2660,4142 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{724E297C-E4EA-4AA3-B0EF-D35314885408}">
+  <dimension ref="A1:N1000"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.625" customWidth="1"/>
+    <col min="5" max="5" width="54.625" customWidth="1"/>
+    <col min="6" max="6" width="42.625" customWidth="1"/>
+    <col min="7" max="7" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.625" customWidth="1"/>
+    <col min="9" max="9" width="5.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.625" customWidth="1"/>
+    <col min="14" max="14" width="34.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="K2" s="4">
+        <v>12</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="M2" s="4">
+        <v>3</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+    </row>
+    <row r="17" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+    </row>
+    <row r="19" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+    </row>
+    <row r="21" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+    </row>
+    <row r="22" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+    </row>
+    <row r="23" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="18"/>
+      <c r="J23" s="18"/>
+    </row>
+    <row r="24" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I24" s="18"/>
+      <c r="J24" s="18"/>
+    </row>
+    <row r="25" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I25" s="18"/>
+      <c r="J25" s="18"/>
+    </row>
+    <row r="26" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I26" s="18"/>
+      <c r="J26" s="18"/>
+    </row>
+    <row r="27" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+    </row>
+    <row r="28" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+    </row>
+    <row r="29" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+    </row>
+    <row r="30" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+    </row>
+    <row r="31" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I31" s="18"/>
+      <c r="J31" s="18"/>
+    </row>
+    <row r="32" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I32" s="18"/>
+      <c r="J32" s="18"/>
+    </row>
+    <row r="33" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+    </row>
+    <row r="35" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+    </row>
+    <row r="36" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I36" s="18"/>
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+    </row>
+    <row r="38" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I38" s="18"/>
+      <c r="J38" s="18"/>
+    </row>
+    <row r="39" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+    </row>
+    <row r="40" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+    </row>
+    <row r="41" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+    </row>
+    <row r="42" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+    </row>
+    <row r="43" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+    </row>
+    <row r="44" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+    </row>
+    <row r="46" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+    </row>
+    <row r="48" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+    </row>
+    <row r="49" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+    </row>
+    <row r="50" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+    </row>
+    <row r="51" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I51" s="18"/>
+      <c r="J51" s="18"/>
+    </row>
+    <row r="52" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I52" s="18"/>
+      <c r="J52" s="18"/>
+    </row>
+    <row r="53" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I53" s="18"/>
+      <c r="J53" s="18"/>
+    </row>
+    <row r="54" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+    </row>
+    <row r="55" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+    </row>
+    <row r="56" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I56" s="18"/>
+      <c r="J56" s="18"/>
+    </row>
+    <row r="57" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I57" s="18"/>
+      <c r="J57" s="18"/>
+    </row>
+    <row r="58" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I58" s="18"/>
+      <c r="J58" s="18"/>
+    </row>
+    <row r="59" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I59" s="18"/>
+      <c r="J59" s="18"/>
+    </row>
+    <row r="60" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I60" s="18"/>
+      <c r="J60" s="18"/>
+    </row>
+    <row r="61" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+    </row>
+    <row r="62" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+    </row>
+    <row r="63" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+    </row>
+    <row r="64" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+    </row>
+    <row r="65" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+    </row>
+    <row r="66" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+    </row>
+    <row r="67" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+    </row>
+    <row r="68" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I68" s="18"/>
+      <c r="J68" s="18"/>
+    </row>
+    <row r="69" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+    </row>
+    <row r="70" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+    </row>
+    <row r="71" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+    </row>
+    <row r="72" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+    </row>
+    <row r="73" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+    </row>
+    <row r="74" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+    </row>
+    <row r="75" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+    </row>
+    <row r="76" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+    </row>
+    <row r="77" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+    </row>
+    <row r="78" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+    </row>
+    <row r="79" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I79" s="18"/>
+      <c r="J79" s="18"/>
+    </row>
+    <row r="80" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I80" s="18"/>
+      <c r="J80" s="18"/>
+    </row>
+    <row r="81" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I81" s="18"/>
+      <c r="J81" s="18"/>
+    </row>
+    <row r="82" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I82" s="18"/>
+      <c r="J82" s="18"/>
+    </row>
+    <row r="83" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I83" s="18"/>
+      <c r="J83" s="18"/>
+    </row>
+    <row r="84" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I84" s="18"/>
+      <c r="J84" s="18"/>
+    </row>
+    <row r="85" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I85" s="18"/>
+      <c r="J85" s="18"/>
+    </row>
+    <row r="86" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I86" s="18"/>
+      <c r="J86" s="18"/>
+    </row>
+    <row r="87" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I87" s="18"/>
+      <c r="J87" s="18"/>
+    </row>
+    <row r="88" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I88" s="18"/>
+      <c r="J88" s="18"/>
+    </row>
+    <row r="89" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I89" s="18"/>
+      <c r="J89" s="18"/>
+    </row>
+    <row r="90" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I90" s="18"/>
+      <c r="J90" s="18"/>
+    </row>
+    <row r="91" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+    </row>
+    <row r="92" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I92" s="18"/>
+      <c r="J92" s="18"/>
+    </row>
+    <row r="93" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I93" s="18"/>
+      <c r="J93" s="18"/>
+    </row>
+    <row r="94" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I94" s="18"/>
+      <c r="J94" s="18"/>
+    </row>
+    <row r="95" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I95" s="18"/>
+      <c r="J95" s="18"/>
+    </row>
+    <row r="96" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I96" s="18"/>
+      <c r="J96" s="18"/>
+    </row>
+    <row r="97" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I97" s="18"/>
+      <c r="J97" s="18"/>
+    </row>
+    <row r="98" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I98" s="18"/>
+      <c r="J98" s="18"/>
+    </row>
+    <row r="99" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I99" s="18"/>
+      <c r="J99" s="18"/>
+    </row>
+    <row r="100" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I100" s="18"/>
+      <c r="J100" s="18"/>
+    </row>
+    <row r="101" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I101" s="18"/>
+      <c r="J101" s="18"/>
+    </row>
+    <row r="102" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I102" s="18"/>
+      <c r="J102" s="18"/>
+    </row>
+    <row r="103" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I103" s="18"/>
+      <c r="J103" s="18"/>
+    </row>
+    <row r="104" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I104" s="18"/>
+      <c r="J104" s="18"/>
+    </row>
+    <row r="105" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I105" s="18"/>
+      <c r="J105" s="18"/>
+    </row>
+    <row r="106" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I106" s="18"/>
+      <c r="J106" s="18"/>
+    </row>
+    <row r="107" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I107" s="18"/>
+      <c r="J107" s="18"/>
+    </row>
+    <row r="108" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I108" s="18"/>
+      <c r="J108" s="18"/>
+    </row>
+    <row r="109" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I109" s="18"/>
+      <c r="J109" s="18"/>
+    </row>
+    <row r="110" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I110" s="18"/>
+      <c r="J110" s="18"/>
+    </row>
+    <row r="111" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I111" s="18"/>
+      <c r="J111" s="18"/>
+    </row>
+    <row r="112" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I112" s="18"/>
+      <c r="J112" s="18"/>
+    </row>
+    <row r="113" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I113" s="18"/>
+      <c r="J113" s="18"/>
+    </row>
+    <row r="114" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I114" s="18"/>
+      <c r="J114" s="18"/>
+    </row>
+    <row r="115" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I115" s="18"/>
+      <c r="J115" s="18"/>
+    </row>
+    <row r="116" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I116" s="18"/>
+      <c r="J116" s="18"/>
+    </row>
+    <row r="117" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I117" s="18"/>
+      <c r="J117" s="18"/>
+    </row>
+    <row r="118" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I118" s="18"/>
+      <c r="J118" s="18"/>
+    </row>
+    <row r="119" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I119" s="18"/>
+      <c r="J119" s="18"/>
+    </row>
+    <row r="120" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I120" s="18"/>
+      <c r="J120" s="18"/>
+    </row>
+    <row r="121" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I121" s="18"/>
+      <c r="J121" s="18"/>
+    </row>
+    <row r="122" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I122" s="18"/>
+      <c r="J122" s="18"/>
+    </row>
+    <row r="123" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I123" s="18"/>
+      <c r="J123" s="18"/>
+    </row>
+    <row r="124" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I124" s="18"/>
+      <c r="J124" s="18"/>
+    </row>
+    <row r="125" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I125" s="18"/>
+      <c r="J125" s="18"/>
+    </row>
+    <row r="126" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I126" s="18"/>
+      <c r="J126" s="18"/>
+    </row>
+    <row r="127" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I127" s="18"/>
+      <c r="J127" s="18"/>
+    </row>
+    <row r="128" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I128" s="18"/>
+      <c r="J128" s="18"/>
+    </row>
+    <row r="129" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I129" s="18"/>
+      <c r="J129" s="18"/>
+    </row>
+    <row r="130" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I130" s="18"/>
+      <c r="J130" s="18"/>
+    </row>
+    <row r="131" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I131" s="18"/>
+      <c r="J131" s="18"/>
+    </row>
+    <row r="132" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I132" s="18"/>
+      <c r="J132" s="18"/>
+    </row>
+    <row r="133" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I133" s="18"/>
+      <c r="J133" s="18"/>
+    </row>
+    <row r="134" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I134" s="18"/>
+      <c r="J134" s="18"/>
+    </row>
+    <row r="135" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I135" s="18"/>
+      <c r="J135" s="18"/>
+    </row>
+    <row r="136" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I136" s="18"/>
+      <c r="J136" s="18"/>
+    </row>
+    <row r="137" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I137" s="18"/>
+      <c r="J137" s="18"/>
+    </row>
+    <row r="138" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I138" s="18"/>
+      <c r="J138" s="18"/>
+    </row>
+    <row r="139" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I139" s="18"/>
+      <c r="J139" s="18"/>
+    </row>
+    <row r="140" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I140" s="18"/>
+      <c r="J140" s="18"/>
+    </row>
+    <row r="141" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I141" s="18"/>
+      <c r="J141" s="18"/>
+    </row>
+    <row r="142" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I142" s="18"/>
+      <c r="J142" s="18"/>
+    </row>
+    <row r="143" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I143" s="18"/>
+      <c r="J143" s="18"/>
+    </row>
+    <row r="144" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I144" s="18"/>
+      <c r="J144" s="18"/>
+    </row>
+    <row r="145" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I145" s="18"/>
+      <c r="J145" s="18"/>
+    </row>
+    <row r="146" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I146" s="18"/>
+      <c r="J146" s="18"/>
+    </row>
+    <row r="147" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I147" s="18"/>
+      <c r="J147" s="18"/>
+    </row>
+    <row r="148" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I148" s="18"/>
+      <c r="J148" s="18"/>
+    </row>
+    <row r="149" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I149" s="18"/>
+      <c r="J149" s="18"/>
+    </row>
+    <row r="150" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I150" s="18"/>
+      <c r="J150" s="18"/>
+    </row>
+    <row r="151" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I151" s="18"/>
+      <c r="J151" s="18"/>
+    </row>
+    <row r="152" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I152" s="18"/>
+      <c r="J152" s="18"/>
+    </row>
+    <row r="153" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I153" s="18"/>
+      <c r="J153" s="18"/>
+    </row>
+    <row r="154" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I154" s="18"/>
+      <c r="J154" s="18"/>
+    </row>
+    <row r="155" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I155" s="18"/>
+      <c r="J155" s="18"/>
+    </row>
+    <row r="156" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I156" s="18"/>
+      <c r="J156" s="18"/>
+    </row>
+    <row r="157" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I157" s="18"/>
+      <c r="J157" s="18"/>
+    </row>
+    <row r="158" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I158" s="18"/>
+      <c r="J158" s="18"/>
+    </row>
+    <row r="159" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I159" s="18"/>
+      <c r="J159" s="18"/>
+    </row>
+    <row r="160" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I160" s="18"/>
+      <c r="J160" s="18"/>
+    </row>
+    <row r="161" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I161" s="18"/>
+      <c r="J161" s="18"/>
+    </row>
+    <row r="162" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I162" s="18"/>
+      <c r="J162" s="18"/>
+    </row>
+    <row r="163" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I163" s="18"/>
+      <c r="J163" s="18"/>
+    </row>
+    <row r="164" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I164" s="18"/>
+      <c r="J164" s="18"/>
+    </row>
+    <row r="165" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I165" s="18"/>
+      <c r="J165" s="18"/>
+    </row>
+    <row r="166" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I166" s="18"/>
+      <c r="J166" s="18"/>
+    </row>
+    <row r="167" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I167" s="18"/>
+      <c r="J167" s="18"/>
+    </row>
+    <row r="168" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I168" s="18"/>
+      <c r="J168" s="18"/>
+    </row>
+    <row r="169" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I169" s="18"/>
+      <c r="J169" s="18"/>
+    </row>
+    <row r="170" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I170" s="18"/>
+      <c r="J170" s="18"/>
+    </row>
+    <row r="171" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I171" s="18"/>
+      <c r="J171" s="18"/>
+    </row>
+    <row r="172" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I172" s="18"/>
+      <c r="J172" s="18"/>
+    </row>
+    <row r="173" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I173" s="18"/>
+      <c r="J173" s="18"/>
+    </row>
+    <row r="174" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I174" s="18"/>
+      <c r="J174" s="18"/>
+    </row>
+    <row r="175" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I175" s="18"/>
+      <c r="J175" s="18"/>
+    </row>
+    <row r="176" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I176" s="18"/>
+      <c r="J176" s="18"/>
+    </row>
+    <row r="177" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I177" s="18"/>
+      <c r="J177" s="18"/>
+    </row>
+    <row r="178" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I178" s="18"/>
+      <c r="J178" s="18"/>
+    </row>
+    <row r="179" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I179" s="18"/>
+      <c r="J179" s="18"/>
+    </row>
+    <row r="180" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I180" s="18"/>
+      <c r="J180" s="18"/>
+    </row>
+    <row r="181" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I181" s="18"/>
+      <c r="J181" s="18"/>
+    </row>
+    <row r="182" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I182" s="18"/>
+      <c r="J182" s="18"/>
+    </row>
+    <row r="183" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I183" s="18"/>
+      <c r="J183" s="18"/>
+    </row>
+    <row r="184" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I184" s="18"/>
+      <c r="J184" s="18"/>
+    </row>
+    <row r="185" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I185" s="18"/>
+      <c r="J185" s="18"/>
+    </row>
+    <row r="186" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I186" s="18"/>
+      <c r="J186" s="18"/>
+    </row>
+    <row r="187" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I187" s="18"/>
+      <c r="J187" s="18"/>
+    </row>
+    <row r="188" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I188" s="18"/>
+      <c r="J188" s="18"/>
+    </row>
+    <row r="189" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I189" s="18"/>
+      <c r="J189" s="18"/>
+    </row>
+    <row r="190" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I190" s="18"/>
+      <c r="J190" s="18"/>
+    </row>
+    <row r="191" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I191" s="18"/>
+      <c r="J191" s="18"/>
+    </row>
+    <row r="192" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I192" s="18"/>
+      <c r="J192" s="18"/>
+    </row>
+    <row r="193" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I193" s="18"/>
+      <c r="J193" s="18"/>
+    </row>
+    <row r="194" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I194" s="18"/>
+      <c r="J194" s="18"/>
+    </row>
+    <row r="195" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I195" s="18"/>
+      <c r="J195" s="18"/>
+    </row>
+    <row r="196" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I196" s="18"/>
+      <c r="J196" s="18"/>
+    </row>
+    <row r="197" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I197" s="18"/>
+      <c r="J197" s="18"/>
+    </row>
+    <row r="198" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I198" s="18"/>
+      <c r="J198" s="18"/>
+    </row>
+    <row r="199" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I199" s="18"/>
+      <c r="J199" s="18"/>
+    </row>
+    <row r="200" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I200" s="18"/>
+      <c r="J200" s="18"/>
+    </row>
+    <row r="201" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I201" s="18"/>
+      <c r="J201" s="18"/>
+    </row>
+    <row r="202" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I202" s="18"/>
+      <c r="J202" s="18"/>
+    </row>
+    <row r="203" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I203" s="18"/>
+      <c r="J203" s="18"/>
+    </row>
+    <row r="204" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I204" s="18"/>
+      <c r="J204" s="18"/>
+    </row>
+    <row r="205" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I205" s="18"/>
+      <c r="J205" s="18"/>
+    </row>
+    <row r="206" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I206" s="18"/>
+      <c r="J206" s="18"/>
+    </row>
+    <row r="207" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I207" s="18"/>
+      <c r="J207" s="18"/>
+    </row>
+    <row r="208" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I208" s="18"/>
+      <c r="J208" s="18"/>
+    </row>
+    <row r="209" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I209" s="18"/>
+      <c r="J209" s="18"/>
+    </row>
+    <row r="210" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I210" s="18"/>
+      <c r="J210" s="18"/>
+    </row>
+    <row r="211" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I211" s="18"/>
+      <c r="J211" s="18"/>
+    </row>
+    <row r="212" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I212" s="18"/>
+      <c r="J212" s="18"/>
+    </row>
+    <row r="213" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I213" s="18"/>
+      <c r="J213" s="18"/>
+    </row>
+    <row r="214" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I214" s="18"/>
+      <c r="J214" s="18"/>
+    </row>
+    <row r="215" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I215" s="18"/>
+      <c r="J215" s="18"/>
+    </row>
+    <row r="216" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I216" s="18"/>
+      <c r="J216" s="18"/>
+    </row>
+    <row r="217" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I217" s="18"/>
+      <c r="J217" s="18"/>
+    </row>
+    <row r="218" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I218" s="18"/>
+      <c r="J218" s="18"/>
+    </row>
+    <row r="219" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I219" s="18"/>
+      <c r="J219" s="18"/>
+    </row>
+    <row r="220" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I220" s="18"/>
+      <c r="J220" s="18"/>
+    </row>
+    <row r="221" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I221" s="18"/>
+      <c r="J221" s="18"/>
+    </row>
+    <row r="222" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I222" s="18"/>
+      <c r="J222" s="18"/>
+    </row>
+    <row r="223" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I223" s="18"/>
+      <c r="J223" s="18"/>
+    </row>
+    <row r="224" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I224" s="18"/>
+      <c r="J224" s="18"/>
+    </row>
+    <row r="225" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I225" s="18"/>
+      <c r="J225" s="18"/>
+    </row>
+    <row r="226" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I226" s="18"/>
+      <c r="J226" s="18"/>
+    </row>
+    <row r="227" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I227" s="18"/>
+      <c r="J227" s="18"/>
+    </row>
+    <row r="228" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I228" s="18"/>
+      <c r="J228" s="18"/>
+    </row>
+    <row r="229" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I229" s="18"/>
+      <c r="J229" s="18"/>
+    </row>
+    <row r="230" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I230" s="18"/>
+      <c r="J230" s="18"/>
+    </row>
+    <row r="231" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I231" s="18"/>
+      <c r="J231" s="18"/>
+    </row>
+    <row r="232" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I232" s="18"/>
+      <c r="J232" s="18"/>
+    </row>
+    <row r="233" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I233" s="18"/>
+      <c r="J233" s="18"/>
+    </row>
+    <row r="234" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I234" s="18"/>
+      <c r="J234" s="18"/>
+    </row>
+    <row r="235" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I235" s="18"/>
+      <c r="J235" s="18"/>
+    </row>
+    <row r="236" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I236" s="18"/>
+      <c r="J236" s="18"/>
+    </row>
+    <row r="237" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I237" s="18"/>
+      <c r="J237" s="18"/>
+    </row>
+    <row r="238" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I238" s="18"/>
+      <c r="J238" s="18"/>
+    </row>
+    <row r="239" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I239" s="18"/>
+      <c r="J239" s="18"/>
+    </row>
+    <row r="240" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I240" s="18"/>
+      <c r="J240" s="18"/>
+    </row>
+    <row r="241" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I241" s="18"/>
+      <c r="J241" s="18"/>
+    </row>
+    <row r="242" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I242" s="18"/>
+      <c r="J242" s="18"/>
+    </row>
+    <row r="243" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I243" s="18"/>
+      <c r="J243" s="18"/>
+    </row>
+    <row r="244" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I244" s="18"/>
+      <c r="J244" s="18"/>
+    </row>
+    <row r="245" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I245" s="18"/>
+      <c r="J245" s="18"/>
+    </row>
+    <row r="246" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I246" s="18"/>
+      <c r="J246" s="18"/>
+    </row>
+    <row r="247" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I247" s="18"/>
+      <c r="J247" s="18"/>
+    </row>
+    <row r="248" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I248" s="18"/>
+      <c r="J248" s="18"/>
+    </row>
+    <row r="249" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I249" s="18"/>
+      <c r="J249" s="18"/>
+    </row>
+    <row r="250" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I250" s="18"/>
+      <c r="J250" s="18"/>
+    </row>
+    <row r="251" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I251" s="18"/>
+      <c r="J251" s="18"/>
+    </row>
+    <row r="252" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I252" s="18"/>
+      <c r="J252" s="18"/>
+    </row>
+    <row r="253" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I253" s="18"/>
+      <c r="J253" s="18"/>
+    </row>
+    <row r="254" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I254" s="18"/>
+      <c r="J254" s="18"/>
+    </row>
+    <row r="255" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I255" s="18"/>
+      <c r="J255" s="18"/>
+    </row>
+    <row r="256" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I256" s="18"/>
+      <c r="J256" s="18"/>
+    </row>
+    <row r="257" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I257" s="18"/>
+      <c r="J257" s="18"/>
+    </row>
+    <row r="258" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I258" s="18"/>
+      <c r="J258" s="18"/>
+    </row>
+    <row r="259" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I259" s="18"/>
+      <c r="J259" s="18"/>
+    </row>
+    <row r="260" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I260" s="18"/>
+      <c r="J260" s="18"/>
+    </row>
+    <row r="261" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I261" s="18"/>
+      <c r="J261" s="18"/>
+    </row>
+    <row r="262" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I262" s="18"/>
+      <c r="J262" s="18"/>
+    </row>
+    <row r="263" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I263" s="18"/>
+      <c r="J263" s="18"/>
+    </row>
+    <row r="264" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I264" s="18"/>
+      <c r="J264" s="18"/>
+    </row>
+    <row r="265" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I265" s="18"/>
+      <c r="J265" s="18"/>
+    </row>
+    <row r="266" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I266" s="18"/>
+      <c r="J266" s="18"/>
+    </row>
+    <row r="267" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I267" s="18"/>
+      <c r="J267" s="18"/>
+    </row>
+    <row r="268" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I268" s="18"/>
+      <c r="J268" s="18"/>
+    </row>
+    <row r="269" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I269" s="18"/>
+      <c r="J269" s="18"/>
+    </row>
+    <row r="270" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I270" s="18"/>
+      <c r="J270" s="18"/>
+    </row>
+    <row r="271" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I271" s="18"/>
+      <c r="J271" s="18"/>
+    </row>
+    <row r="272" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I272" s="18"/>
+      <c r="J272" s="18"/>
+    </row>
+    <row r="273" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I273" s="18"/>
+      <c r="J273" s="18"/>
+    </row>
+    <row r="274" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I274" s="18"/>
+      <c r="J274" s="18"/>
+    </row>
+    <row r="275" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I275" s="18"/>
+      <c r="J275" s="18"/>
+    </row>
+    <row r="276" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I276" s="18"/>
+      <c r="J276" s="18"/>
+    </row>
+    <row r="277" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I277" s="18"/>
+      <c r="J277" s="18"/>
+    </row>
+    <row r="278" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I278" s="18"/>
+      <c r="J278" s="18"/>
+    </row>
+    <row r="279" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I279" s="18"/>
+      <c r="J279" s="18"/>
+    </row>
+    <row r="280" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I280" s="18"/>
+      <c r="J280" s="18"/>
+    </row>
+    <row r="281" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I281" s="18"/>
+      <c r="J281" s="18"/>
+    </row>
+    <row r="282" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I282" s="18"/>
+      <c r="J282" s="18"/>
+    </row>
+    <row r="283" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I283" s="18"/>
+      <c r="J283" s="18"/>
+    </row>
+    <row r="284" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I284" s="18"/>
+      <c r="J284" s="18"/>
+    </row>
+    <row r="285" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I285" s="18"/>
+      <c r="J285" s="18"/>
+    </row>
+    <row r="286" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I286" s="18"/>
+      <c r="J286" s="18"/>
+    </row>
+    <row r="287" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I287" s="18"/>
+      <c r="J287" s="18"/>
+    </row>
+    <row r="288" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I288" s="18"/>
+      <c r="J288" s="18"/>
+    </row>
+    <row r="289" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I289" s="18"/>
+      <c r="J289" s="18"/>
+    </row>
+    <row r="290" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I290" s="18"/>
+      <c r="J290" s="18"/>
+    </row>
+    <row r="291" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I291" s="18"/>
+      <c r="J291" s="18"/>
+    </row>
+    <row r="292" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I292" s="18"/>
+      <c r="J292" s="18"/>
+    </row>
+    <row r="293" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I293" s="18"/>
+      <c r="J293" s="18"/>
+    </row>
+    <row r="294" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I294" s="18"/>
+      <c r="J294" s="18"/>
+    </row>
+    <row r="295" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I295" s="18"/>
+      <c r="J295" s="18"/>
+    </row>
+    <row r="296" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I296" s="18"/>
+      <c r="J296" s="18"/>
+    </row>
+    <row r="297" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I297" s="18"/>
+      <c r="J297" s="18"/>
+    </row>
+    <row r="298" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I298" s="18"/>
+      <c r="J298" s="18"/>
+    </row>
+    <row r="299" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I299" s="18"/>
+      <c r="J299" s="18"/>
+    </row>
+    <row r="300" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I300" s="18"/>
+      <c r="J300" s="18"/>
+    </row>
+    <row r="301" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I301" s="18"/>
+      <c r="J301" s="18"/>
+    </row>
+    <row r="302" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I302" s="18"/>
+      <c r="J302" s="18"/>
+    </row>
+    <row r="303" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I303" s="18"/>
+      <c r="J303" s="18"/>
+    </row>
+    <row r="304" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I304" s="18"/>
+      <c r="J304" s="18"/>
+    </row>
+    <row r="305" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I305" s="18"/>
+      <c r="J305" s="18"/>
+    </row>
+    <row r="306" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I306" s="18"/>
+      <c r="J306" s="18"/>
+    </row>
+    <row r="307" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I307" s="18"/>
+      <c r="J307" s="18"/>
+    </row>
+    <row r="308" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I308" s="18"/>
+      <c r="J308" s="18"/>
+    </row>
+    <row r="309" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I309" s="18"/>
+      <c r="J309" s="18"/>
+    </row>
+    <row r="310" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I310" s="18"/>
+      <c r="J310" s="18"/>
+    </row>
+    <row r="311" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I311" s="18"/>
+      <c r="J311" s="18"/>
+    </row>
+    <row r="312" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I312" s="18"/>
+      <c r="J312" s="18"/>
+    </row>
+    <row r="313" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I313" s="18"/>
+      <c r="J313" s="18"/>
+    </row>
+    <row r="314" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I314" s="18"/>
+      <c r="J314" s="18"/>
+    </row>
+    <row r="315" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I315" s="18"/>
+      <c r="J315" s="18"/>
+    </row>
+    <row r="316" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I316" s="18"/>
+      <c r="J316" s="18"/>
+    </row>
+    <row r="317" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I317" s="18"/>
+      <c r="J317" s="18"/>
+    </row>
+    <row r="318" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I318" s="18"/>
+      <c r="J318" s="18"/>
+    </row>
+    <row r="319" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I319" s="18"/>
+      <c r="J319" s="18"/>
+    </row>
+    <row r="320" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I320" s="18"/>
+      <c r="J320" s="18"/>
+    </row>
+    <row r="321" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I321" s="18"/>
+      <c r="J321" s="18"/>
+    </row>
+    <row r="322" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I322" s="18"/>
+      <c r="J322" s="18"/>
+    </row>
+    <row r="323" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I323" s="18"/>
+      <c r="J323" s="18"/>
+    </row>
+    <row r="324" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I324" s="18"/>
+      <c r="J324" s="18"/>
+    </row>
+    <row r="325" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I325" s="18"/>
+      <c r="J325" s="18"/>
+    </row>
+    <row r="326" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I326" s="18"/>
+      <c r="J326" s="18"/>
+    </row>
+    <row r="327" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I327" s="18"/>
+      <c r="J327" s="18"/>
+    </row>
+    <row r="328" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I328" s="18"/>
+      <c r="J328" s="18"/>
+    </row>
+    <row r="329" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I329" s="18"/>
+      <c r="J329" s="18"/>
+    </row>
+    <row r="330" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I330" s="18"/>
+      <c r="J330" s="18"/>
+    </row>
+    <row r="331" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I331" s="18"/>
+      <c r="J331" s="18"/>
+    </row>
+    <row r="332" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I332" s="18"/>
+      <c r="J332" s="18"/>
+    </row>
+    <row r="333" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I333" s="18"/>
+      <c r="J333" s="18"/>
+    </row>
+    <row r="334" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I334" s="18"/>
+      <c r="J334" s="18"/>
+    </row>
+    <row r="335" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I335" s="18"/>
+      <c r="J335" s="18"/>
+    </row>
+    <row r="336" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I336" s="18"/>
+      <c r="J336" s="18"/>
+    </row>
+    <row r="337" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I337" s="18"/>
+      <c r="J337" s="18"/>
+    </row>
+    <row r="338" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I338" s="18"/>
+      <c r="J338" s="18"/>
+    </row>
+    <row r="339" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I339" s="18"/>
+      <c r="J339" s="18"/>
+    </row>
+    <row r="340" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I340" s="18"/>
+      <c r="J340" s="18"/>
+    </row>
+    <row r="341" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I341" s="18"/>
+      <c r="J341" s="18"/>
+    </row>
+    <row r="342" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I342" s="18"/>
+      <c r="J342" s="18"/>
+    </row>
+    <row r="343" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I343" s="18"/>
+      <c r="J343" s="18"/>
+    </row>
+    <row r="344" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I344" s="18"/>
+      <c r="J344" s="18"/>
+    </row>
+    <row r="345" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I345" s="18"/>
+      <c r="J345" s="18"/>
+    </row>
+    <row r="346" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I346" s="18"/>
+      <c r="J346" s="18"/>
+    </row>
+    <row r="347" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I347" s="18"/>
+      <c r="J347" s="18"/>
+    </row>
+    <row r="348" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I348" s="18"/>
+      <c r="J348" s="18"/>
+    </row>
+    <row r="349" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I349" s="18"/>
+      <c r="J349" s="18"/>
+    </row>
+    <row r="350" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I350" s="18"/>
+      <c r="J350" s="18"/>
+    </row>
+    <row r="351" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I351" s="18"/>
+      <c r="J351" s="18"/>
+    </row>
+    <row r="352" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I352" s="18"/>
+      <c r="J352" s="18"/>
+    </row>
+    <row r="353" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I353" s="18"/>
+      <c r="J353" s="18"/>
+    </row>
+    <row r="354" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I354" s="18"/>
+      <c r="J354" s="18"/>
+    </row>
+    <row r="355" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I355" s="18"/>
+      <c r="J355" s="18"/>
+    </row>
+    <row r="356" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I356" s="18"/>
+      <c r="J356" s="18"/>
+    </row>
+    <row r="357" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I357" s="18"/>
+      <c r="J357" s="18"/>
+    </row>
+    <row r="358" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I358" s="18"/>
+      <c r="J358" s="18"/>
+    </row>
+    <row r="359" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I359" s="18"/>
+      <c r="J359" s="18"/>
+    </row>
+    <row r="360" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I360" s="18"/>
+      <c r="J360" s="18"/>
+    </row>
+    <row r="361" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I361" s="18"/>
+      <c r="J361" s="18"/>
+    </row>
+    <row r="362" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I362" s="18"/>
+      <c r="J362" s="18"/>
+    </row>
+    <row r="363" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I363" s="18"/>
+      <c r="J363" s="18"/>
+    </row>
+    <row r="364" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I364" s="18"/>
+      <c r="J364" s="18"/>
+    </row>
+    <row r="365" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I365" s="18"/>
+      <c r="J365" s="18"/>
+    </row>
+    <row r="366" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I366" s="18"/>
+      <c r="J366" s="18"/>
+    </row>
+    <row r="367" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I367" s="18"/>
+      <c r="J367" s="18"/>
+    </row>
+    <row r="368" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I368" s="18"/>
+      <c r="J368" s="18"/>
+    </row>
+    <row r="369" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I369" s="18"/>
+      <c r="J369" s="18"/>
+    </row>
+    <row r="370" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I370" s="18"/>
+      <c r="J370" s="18"/>
+    </row>
+    <row r="371" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I371" s="18"/>
+      <c r="J371" s="18"/>
+    </row>
+    <row r="372" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I372" s="18"/>
+      <c r="J372" s="18"/>
+    </row>
+    <row r="373" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I373" s="18"/>
+      <c r="J373" s="18"/>
+    </row>
+    <row r="374" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I374" s="18"/>
+      <c r="J374" s="18"/>
+    </row>
+    <row r="375" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I375" s="18"/>
+      <c r="J375" s="18"/>
+    </row>
+    <row r="376" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I376" s="18"/>
+      <c r="J376" s="18"/>
+    </row>
+    <row r="377" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I377" s="18"/>
+      <c r="J377" s="18"/>
+    </row>
+    <row r="378" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I378" s="18"/>
+      <c r="J378" s="18"/>
+    </row>
+    <row r="379" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I379" s="18"/>
+      <c r="J379" s="18"/>
+    </row>
+    <row r="380" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I380" s="18"/>
+      <c r="J380" s="18"/>
+    </row>
+    <row r="381" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I381" s="18"/>
+      <c r="J381" s="18"/>
+    </row>
+    <row r="382" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I382" s="18"/>
+      <c r="J382" s="18"/>
+    </row>
+    <row r="383" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I383" s="18"/>
+      <c r="J383" s="18"/>
+    </row>
+    <row r="384" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I384" s="18"/>
+      <c r="J384" s="18"/>
+    </row>
+    <row r="385" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I385" s="18"/>
+      <c r="J385" s="18"/>
+    </row>
+    <row r="386" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I386" s="18"/>
+      <c r="J386" s="18"/>
+    </row>
+    <row r="387" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I387" s="18"/>
+      <c r="J387" s="18"/>
+    </row>
+    <row r="388" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I388" s="18"/>
+      <c r="J388" s="18"/>
+    </row>
+    <row r="389" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I389" s="18"/>
+      <c r="J389" s="18"/>
+    </row>
+    <row r="390" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I390" s="18"/>
+      <c r="J390" s="18"/>
+    </row>
+    <row r="391" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I391" s="18"/>
+      <c r="J391" s="18"/>
+    </row>
+    <row r="392" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I392" s="18"/>
+      <c r="J392" s="18"/>
+    </row>
+    <row r="393" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I393" s="18"/>
+      <c r="J393" s="18"/>
+    </row>
+    <row r="394" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I394" s="18"/>
+      <c r="J394" s="18"/>
+    </row>
+    <row r="395" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I395" s="18"/>
+      <c r="J395" s="18"/>
+    </row>
+    <row r="396" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I396" s="18"/>
+      <c r="J396" s="18"/>
+    </row>
+    <row r="397" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I397" s="18"/>
+      <c r="J397" s="18"/>
+    </row>
+    <row r="398" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I398" s="18"/>
+      <c r="J398" s="18"/>
+    </row>
+    <row r="399" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I399" s="18"/>
+      <c r="J399" s="18"/>
+    </row>
+    <row r="400" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I400" s="18"/>
+      <c r="J400" s="18"/>
+    </row>
+    <row r="401" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I401" s="18"/>
+      <c r="J401" s="18"/>
+    </row>
+    <row r="402" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I402" s="18"/>
+      <c r="J402" s="18"/>
+    </row>
+    <row r="403" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I403" s="18"/>
+      <c r="J403" s="18"/>
+    </row>
+    <row r="404" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I404" s="18"/>
+      <c r="J404" s="18"/>
+    </row>
+    <row r="405" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I405" s="18"/>
+      <c r="J405" s="18"/>
+    </row>
+    <row r="406" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I406" s="18"/>
+      <c r="J406" s="18"/>
+    </row>
+    <row r="407" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I407" s="18"/>
+      <c r="J407" s="18"/>
+    </row>
+    <row r="408" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I408" s="18"/>
+      <c r="J408" s="18"/>
+    </row>
+    <row r="409" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I409" s="18"/>
+      <c r="J409" s="18"/>
+    </row>
+    <row r="410" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I410" s="18"/>
+      <c r="J410" s="18"/>
+    </row>
+    <row r="411" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I411" s="18"/>
+      <c r="J411" s="18"/>
+    </row>
+    <row r="412" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I412" s="18"/>
+      <c r="J412" s="18"/>
+    </row>
+    <row r="413" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I413" s="18"/>
+      <c r="J413" s="18"/>
+    </row>
+    <row r="414" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I414" s="18"/>
+      <c r="J414" s="18"/>
+    </row>
+    <row r="415" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I415" s="18"/>
+      <c r="J415" s="18"/>
+    </row>
+    <row r="416" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I416" s="18"/>
+      <c r="J416" s="18"/>
+    </row>
+    <row r="417" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I417" s="18"/>
+      <c r="J417" s="18"/>
+    </row>
+    <row r="418" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I418" s="18"/>
+      <c r="J418" s="18"/>
+    </row>
+    <row r="419" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I419" s="18"/>
+      <c r="J419" s="18"/>
+    </row>
+    <row r="420" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I420" s="18"/>
+      <c r="J420" s="18"/>
+    </row>
+    <row r="421" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I421" s="18"/>
+      <c r="J421" s="18"/>
+    </row>
+    <row r="422" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I422" s="18"/>
+      <c r="J422" s="18"/>
+    </row>
+    <row r="423" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I423" s="18"/>
+      <c r="J423" s="18"/>
+    </row>
+    <row r="424" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I424" s="18"/>
+      <c r="J424" s="18"/>
+    </row>
+    <row r="425" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I425" s="18"/>
+      <c r="J425" s="18"/>
+    </row>
+    <row r="426" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I426" s="18"/>
+      <c r="J426" s="18"/>
+    </row>
+    <row r="427" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I427" s="18"/>
+      <c r="J427" s="18"/>
+    </row>
+    <row r="428" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I428" s="18"/>
+      <c r="J428" s="18"/>
+    </row>
+    <row r="429" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I429" s="18"/>
+      <c r="J429" s="18"/>
+    </row>
+    <row r="430" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I430" s="18"/>
+      <c r="J430" s="18"/>
+    </row>
+    <row r="431" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I431" s="18"/>
+      <c r="J431" s="18"/>
+    </row>
+    <row r="432" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I432" s="18"/>
+      <c r="J432" s="18"/>
+    </row>
+    <row r="433" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I433" s="18"/>
+      <c r="J433" s="18"/>
+    </row>
+    <row r="434" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I434" s="18"/>
+      <c r="J434" s="18"/>
+    </row>
+    <row r="435" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I435" s="18"/>
+      <c r="J435" s="18"/>
+    </row>
+    <row r="436" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I436" s="18"/>
+      <c r="J436" s="18"/>
+    </row>
+    <row r="437" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I437" s="18"/>
+      <c r="J437" s="18"/>
+    </row>
+    <row r="438" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I438" s="18"/>
+      <c r="J438" s="18"/>
+    </row>
+    <row r="439" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I439" s="18"/>
+      <c r="J439" s="18"/>
+    </row>
+    <row r="440" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I440" s="18"/>
+      <c r="J440" s="18"/>
+    </row>
+    <row r="441" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I441" s="18"/>
+      <c r="J441" s="18"/>
+    </row>
+    <row r="442" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I442" s="18"/>
+      <c r="J442" s="18"/>
+    </row>
+    <row r="443" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I443" s="18"/>
+      <c r="J443" s="18"/>
+    </row>
+    <row r="444" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I444" s="18"/>
+      <c r="J444" s="18"/>
+    </row>
+    <row r="445" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I445" s="18"/>
+      <c r="J445" s="18"/>
+    </row>
+    <row r="446" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I446" s="18"/>
+      <c r="J446" s="18"/>
+    </row>
+    <row r="447" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I447" s="18"/>
+      <c r="J447" s="18"/>
+    </row>
+    <row r="448" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I448" s="18"/>
+      <c r="J448" s="18"/>
+    </row>
+    <row r="449" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I449" s="18"/>
+      <c r="J449" s="18"/>
+    </row>
+    <row r="450" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I450" s="18"/>
+      <c r="J450" s="18"/>
+    </row>
+    <row r="451" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I451" s="18"/>
+      <c r="J451" s="18"/>
+    </row>
+    <row r="452" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I452" s="18"/>
+      <c r="J452" s="18"/>
+    </row>
+    <row r="453" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I453" s="18"/>
+      <c r="J453" s="18"/>
+    </row>
+    <row r="454" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I454" s="18"/>
+      <c r="J454" s="18"/>
+    </row>
+    <row r="455" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I455" s="18"/>
+      <c r="J455" s="18"/>
+    </row>
+    <row r="456" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I456" s="18"/>
+      <c r="J456" s="18"/>
+    </row>
+    <row r="457" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I457" s="18"/>
+      <c r="J457" s="18"/>
+    </row>
+    <row r="458" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I458" s="18"/>
+      <c r="J458" s="18"/>
+    </row>
+    <row r="459" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I459" s="18"/>
+      <c r="J459" s="18"/>
+    </row>
+    <row r="460" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I460" s="18"/>
+      <c r="J460" s="18"/>
+    </row>
+    <row r="461" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I461" s="18"/>
+      <c r="J461" s="18"/>
+    </row>
+    <row r="462" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I462" s="18"/>
+      <c r="J462" s="18"/>
+    </row>
+    <row r="463" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I463" s="18"/>
+      <c r="J463" s="18"/>
+    </row>
+    <row r="464" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I464" s="18"/>
+      <c r="J464" s="18"/>
+    </row>
+    <row r="465" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I465" s="18"/>
+      <c r="J465" s="18"/>
+    </row>
+    <row r="466" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I466" s="18"/>
+      <c r="J466" s="18"/>
+    </row>
+    <row r="467" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I467" s="18"/>
+      <c r="J467" s="18"/>
+    </row>
+    <row r="468" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I468" s="18"/>
+      <c r="J468" s="18"/>
+    </row>
+    <row r="469" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I469" s="18"/>
+      <c r="J469" s="18"/>
+    </row>
+    <row r="470" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I470" s="18"/>
+      <c r="J470" s="18"/>
+    </row>
+    <row r="471" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I471" s="18"/>
+      <c r="J471" s="18"/>
+    </row>
+    <row r="472" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I472" s="18"/>
+      <c r="J472" s="18"/>
+    </row>
+    <row r="473" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I473" s="18"/>
+      <c r="J473" s="18"/>
+    </row>
+    <row r="474" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I474" s="18"/>
+      <c r="J474" s="18"/>
+    </row>
+    <row r="475" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I475" s="18"/>
+      <c r="J475" s="18"/>
+    </row>
+    <row r="476" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I476" s="18"/>
+      <c r="J476" s="18"/>
+    </row>
+    <row r="477" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I477" s="18"/>
+      <c r="J477" s="18"/>
+    </row>
+    <row r="478" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I478" s="18"/>
+      <c r="J478" s="18"/>
+    </row>
+    <row r="479" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I479" s="18"/>
+      <c r="J479" s="18"/>
+    </row>
+    <row r="480" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I480" s="18"/>
+      <c r="J480" s="18"/>
+    </row>
+    <row r="481" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I481" s="18"/>
+      <c r="J481" s="18"/>
+    </row>
+    <row r="482" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I482" s="18"/>
+      <c r="J482" s="18"/>
+    </row>
+    <row r="483" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I483" s="18"/>
+      <c r="J483" s="18"/>
+    </row>
+    <row r="484" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I484" s="18"/>
+      <c r="J484" s="18"/>
+    </row>
+    <row r="485" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I485" s="18"/>
+      <c r="J485" s="18"/>
+    </row>
+    <row r="486" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I486" s="18"/>
+      <c r="J486" s="18"/>
+    </row>
+    <row r="487" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I487" s="18"/>
+      <c r="J487" s="18"/>
+    </row>
+    <row r="488" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I488" s="18"/>
+      <c r="J488" s="18"/>
+    </row>
+    <row r="489" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I489" s="18"/>
+      <c r="J489" s="18"/>
+    </row>
+    <row r="490" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I490" s="18"/>
+      <c r="J490" s="18"/>
+    </row>
+    <row r="491" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I491" s="18"/>
+      <c r="J491" s="18"/>
+    </row>
+    <row r="492" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I492" s="18"/>
+      <c r="J492" s="18"/>
+    </row>
+    <row r="493" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I493" s="18"/>
+      <c r="J493" s="18"/>
+    </row>
+    <row r="494" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I494" s="18"/>
+      <c r="J494" s="18"/>
+    </row>
+    <row r="495" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I495" s="18"/>
+      <c r="J495" s="18"/>
+    </row>
+    <row r="496" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I496" s="18"/>
+      <c r="J496" s="18"/>
+    </row>
+    <row r="497" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I497" s="18"/>
+      <c r="J497" s="18"/>
+    </row>
+    <row r="498" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I498" s="18"/>
+      <c r="J498" s="18"/>
+    </row>
+    <row r="499" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I499" s="18"/>
+      <c r="J499" s="18"/>
+    </row>
+    <row r="500" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I500" s="18"/>
+      <c r="J500" s="18"/>
+    </row>
+    <row r="501" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I501" s="18"/>
+      <c r="J501" s="18"/>
+    </row>
+    <row r="502" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I502" s="18"/>
+      <c r="J502" s="18"/>
+    </row>
+    <row r="503" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I503" s="18"/>
+      <c r="J503" s="18"/>
+    </row>
+    <row r="504" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I504" s="18"/>
+      <c r="J504" s="18"/>
+    </row>
+    <row r="505" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I505" s="18"/>
+      <c r="J505" s="18"/>
+    </row>
+    <row r="506" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I506" s="18"/>
+      <c r="J506" s="18"/>
+    </row>
+    <row r="507" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I507" s="18"/>
+      <c r="J507" s="18"/>
+    </row>
+    <row r="508" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I508" s="18"/>
+      <c r="J508" s="18"/>
+    </row>
+    <row r="509" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I509" s="18"/>
+      <c r="J509" s="18"/>
+    </row>
+    <row r="510" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I510" s="18"/>
+      <c r="J510" s="18"/>
+    </row>
+    <row r="511" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I511" s="18"/>
+      <c r="J511" s="18"/>
+    </row>
+    <row r="512" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I512" s="18"/>
+      <c r="J512" s="18"/>
+    </row>
+    <row r="513" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I513" s="18"/>
+      <c r="J513" s="18"/>
+    </row>
+    <row r="514" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I514" s="18"/>
+      <c r="J514" s="18"/>
+    </row>
+    <row r="515" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I515" s="18"/>
+      <c r="J515" s="18"/>
+    </row>
+    <row r="516" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I516" s="18"/>
+      <c r="J516" s="18"/>
+    </row>
+    <row r="517" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I517" s="18"/>
+      <c r="J517" s="18"/>
+    </row>
+    <row r="518" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I518" s="18"/>
+      <c r="J518" s="18"/>
+    </row>
+    <row r="519" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I519" s="18"/>
+      <c r="J519" s="18"/>
+    </row>
+    <row r="520" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I520" s="18"/>
+      <c r="J520" s="18"/>
+    </row>
+    <row r="521" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I521" s="18"/>
+      <c r="J521" s="18"/>
+    </row>
+    <row r="522" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I522" s="18"/>
+      <c r="J522" s="18"/>
+    </row>
+    <row r="523" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I523" s="18"/>
+      <c r="J523" s="18"/>
+    </row>
+    <row r="524" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I524" s="18"/>
+      <c r="J524" s="18"/>
+    </row>
+    <row r="525" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I525" s="18"/>
+      <c r="J525" s="18"/>
+    </row>
+    <row r="526" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I526" s="18"/>
+      <c r="J526" s="18"/>
+    </row>
+    <row r="527" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I527" s="18"/>
+      <c r="J527" s="18"/>
+    </row>
+    <row r="528" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I528" s="18"/>
+      <c r="J528" s="18"/>
+    </row>
+    <row r="529" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I529" s="18"/>
+      <c r="J529" s="18"/>
+    </row>
+    <row r="530" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I530" s="18"/>
+      <c r="J530" s="18"/>
+    </row>
+    <row r="531" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I531" s="18"/>
+      <c r="J531" s="18"/>
+    </row>
+    <row r="532" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I532" s="18"/>
+      <c r="J532" s="18"/>
+    </row>
+    <row r="533" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I533" s="18"/>
+      <c r="J533" s="18"/>
+    </row>
+    <row r="534" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I534" s="18"/>
+      <c r="J534" s="18"/>
+    </row>
+    <row r="535" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I535" s="18"/>
+      <c r="J535" s="18"/>
+    </row>
+    <row r="536" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I536" s="18"/>
+      <c r="J536" s="18"/>
+    </row>
+    <row r="537" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I537" s="18"/>
+      <c r="J537" s="18"/>
+    </row>
+    <row r="538" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I538" s="18"/>
+      <c r="J538" s="18"/>
+    </row>
+    <row r="539" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I539" s="18"/>
+      <c r="J539" s="18"/>
+    </row>
+    <row r="540" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I540" s="18"/>
+      <c r="J540" s="18"/>
+    </row>
+    <row r="541" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I541" s="18"/>
+      <c r="J541" s="18"/>
+    </row>
+    <row r="542" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I542" s="18"/>
+      <c r="J542" s="18"/>
+    </row>
+    <row r="543" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I543" s="18"/>
+      <c r="J543" s="18"/>
+    </row>
+    <row r="544" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I544" s="18"/>
+      <c r="J544" s="18"/>
+    </row>
+    <row r="545" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I545" s="18"/>
+      <c r="J545" s="18"/>
+    </row>
+    <row r="546" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I546" s="18"/>
+      <c r="J546" s="18"/>
+    </row>
+    <row r="547" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I547" s="18"/>
+      <c r="J547" s="18"/>
+    </row>
+    <row r="548" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I548" s="18"/>
+      <c r="J548" s="18"/>
+    </row>
+    <row r="549" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I549" s="18"/>
+      <c r="J549" s="18"/>
+    </row>
+    <row r="550" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I550" s="18"/>
+      <c r="J550" s="18"/>
+    </row>
+    <row r="551" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I551" s="18"/>
+      <c r="J551" s="18"/>
+    </row>
+    <row r="552" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I552" s="18"/>
+      <c r="J552" s="18"/>
+    </row>
+    <row r="553" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I553" s="18"/>
+      <c r="J553" s="18"/>
+    </row>
+    <row r="554" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I554" s="18"/>
+      <c r="J554" s="18"/>
+    </row>
+    <row r="555" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I555" s="18"/>
+      <c r="J555" s="18"/>
+    </row>
+    <row r="556" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I556" s="18"/>
+      <c r="J556" s="18"/>
+    </row>
+    <row r="557" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I557" s="18"/>
+      <c r="J557" s="18"/>
+    </row>
+    <row r="558" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I558" s="18"/>
+      <c r="J558" s="18"/>
+    </row>
+    <row r="559" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I559" s="18"/>
+      <c r="J559" s="18"/>
+    </row>
+    <row r="560" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I560" s="18"/>
+      <c r="J560" s="18"/>
+    </row>
+    <row r="561" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I561" s="18"/>
+      <c r="J561" s="18"/>
+    </row>
+    <row r="562" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I562" s="18"/>
+      <c r="J562" s="18"/>
+    </row>
+    <row r="563" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I563" s="18"/>
+      <c r="J563" s="18"/>
+    </row>
+    <row r="564" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I564" s="18"/>
+      <c r="J564" s="18"/>
+    </row>
+    <row r="565" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I565" s="18"/>
+      <c r="J565" s="18"/>
+    </row>
+    <row r="566" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I566" s="18"/>
+      <c r="J566" s="18"/>
+    </row>
+    <row r="567" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I567" s="18"/>
+      <c r="J567" s="18"/>
+    </row>
+    <row r="568" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I568" s="18"/>
+      <c r="J568" s="18"/>
+    </row>
+    <row r="569" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I569" s="18"/>
+      <c r="J569" s="18"/>
+    </row>
+    <row r="570" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I570" s="18"/>
+      <c r="J570" s="18"/>
+    </row>
+    <row r="571" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I571" s="18"/>
+      <c r="J571" s="18"/>
+    </row>
+    <row r="572" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I572" s="18"/>
+      <c r="J572" s="18"/>
+    </row>
+    <row r="573" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I573" s="18"/>
+      <c r="J573" s="18"/>
+    </row>
+    <row r="574" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I574" s="18"/>
+      <c r="J574" s="18"/>
+    </row>
+    <row r="575" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I575" s="18"/>
+      <c r="J575" s="18"/>
+    </row>
+    <row r="576" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I576" s="18"/>
+      <c r="J576" s="18"/>
+    </row>
+    <row r="577" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I577" s="18"/>
+      <c r="J577" s="18"/>
+    </row>
+    <row r="578" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I578" s="18"/>
+      <c r="J578" s="18"/>
+    </row>
+    <row r="579" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I579" s="18"/>
+      <c r="J579" s="18"/>
+    </row>
+    <row r="580" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I580" s="18"/>
+      <c r="J580" s="18"/>
+    </row>
+    <row r="581" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I581" s="18"/>
+      <c r="J581" s="18"/>
+    </row>
+    <row r="582" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I582" s="18"/>
+      <c r="J582" s="18"/>
+    </row>
+    <row r="583" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I583" s="18"/>
+      <c r="J583" s="18"/>
+    </row>
+    <row r="584" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I584" s="18"/>
+      <c r="J584" s="18"/>
+    </row>
+    <row r="585" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I585" s="18"/>
+      <c r="J585" s="18"/>
+    </row>
+    <row r="586" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I586" s="18"/>
+      <c r="J586" s="18"/>
+    </row>
+    <row r="587" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I587" s="18"/>
+      <c r="J587" s="18"/>
+    </row>
+    <row r="588" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I588" s="18"/>
+      <c r="J588" s="18"/>
+    </row>
+    <row r="589" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I589" s="18"/>
+      <c r="J589" s="18"/>
+    </row>
+    <row r="590" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I590" s="18"/>
+      <c r="J590" s="18"/>
+    </row>
+    <row r="591" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I591" s="18"/>
+      <c r="J591" s="18"/>
+    </row>
+    <row r="592" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I592" s="18"/>
+      <c r="J592" s="18"/>
+    </row>
+    <row r="593" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I593" s="18"/>
+      <c r="J593" s="18"/>
+    </row>
+    <row r="594" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I594" s="18"/>
+      <c r="J594" s="18"/>
+    </row>
+    <row r="595" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I595" s="18"/>
+      <c r="J595" s="18"/>
+    </row>
+    <row r="596" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I596" s="18"/>
+      <c r="J596" s="18"/>
+    </row>
+    <row r="597" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I597" s="18"/>
+      <c r="J597" s="18"/>
+    </row>
+    <row r="598" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I598" s="18"/>
+      <c r="J598" s="18"/>
+    </row>
+    <row r="599" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I599" s="18"/>
+      <c r="J599" s="18"/>
+    </row>
+    <row r="600" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I600" s="18"/>
+      <c r="J600" s="18"/>
+    </row>
+    <row r="601" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I601" s="18"/>
+      <c r="J601" s="18"/>
+    </row>
+    <row r="602" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I602" s="18"/>
+      <c r="J602" s="18"/>
+    </row>
+    <row r="603" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I603" s="18"/>
+      <c r="J603" s="18"/>
+    </row>
+    <row r="604" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I604" s="18"/>
+      <c r="J604" s="18"/>
+    </row>
+    <row r="605" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I605" s="18"/>
+      <c r="J605" s="18"/>
+    </row>
+    <row r="606" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I606" s="18"/>
+      <c r="J606" s="18"/>
+    </row>
+    <row r="607" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I607" s="18"/>
+      <c r="J607" s="18"/>
+    </row>
+    <row r="608" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I608" s="18"/>
+      <c r="J608" s="18"/>
+    </row>
+    <row r="609" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I609" s="18"/>
+      <c r="J609" s="18"/>
+    </row>
+    <row r="610" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I610" s="18"/>
+      <c r="J610" s="18"/>
+    </row>
+    <row r="611" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I611" s="18"/>
+      <c r="J611" s="18"/>
+    </row>
+    <row r="612" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I612" s="18"/>
+      <c r="J612" s="18"/>
+    </row>
+    <row r="613" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I613" s="18"/>
+      <c r="J613" s="18"/>
+    </row>
+    <row r="614" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I614" s="18"/>
+      <c r="J614" s="18"/>
+    </row>
+    <row r="615" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I615" s="18"/>
+      <c r="J615" s="18"/>
+    </row>
+    <row r="616" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I616" s="18"/>
+      <c r="J616" s="18"/>
+    </row>
+    <row r="617" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I617" s="18"/>
+      <c r="J617" s="18"/>
+    </row>
+    <row r="618" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I618" s="18"/>
+      <c r="J618" s="18"/>
+    </row>
+    <row r="619" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I619" s="18"/>
+      <c r="J619" s="18"/>
+    </row>
+    <row r="620" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I620" s="18"/>
+      <c r="J620" s="18"/>
+    </row>
+    <row r="621" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I621" s="18"/>
+      <c r="J621" s="18"/>
+    </row>
+    <row r="622" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I622" s="18"/>
+      <c r="J622" s="18"/>
+    </row>
+    <row r="623" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I623" s="18"/>
+      <c r="J623" s="18"/>
+    </row>
+    <row r="624" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I624" s="18"/>
+      <c r="J624" s="18"/>
+    </row>
+    <row r="625" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I625" s="18"/>
+      <c r="J625" s="18"/>
+    </row>
+    <row r="626" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I626" s="18"/>
+      <c r="J626" s="18"/>
+    </row>
+    <row r="627" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I627" s="18"/>
+      <c r="J627" s="18"/>
+    </row>
+    <row r="628" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I628" s="18"/>
+      <c r="J628" s="18"/>
+    </row>
+    <row r="629" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I629" s="18"/>
+      <c r="J629" s="18"/>
+    </row>
+    <row r="630" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I630" s="18"/>
+      <c r="J630" s="18"/>
+    </row>
+    <row r="631" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I631" s="18"/>
+      <c r="J631" s="18"/>
+    </row>
+    <row r="632" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I632" s="18"/>
+      <c r="J632" s="18"/>
+    </row>
+    <row r="633" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I633" s="18"/>
+      <c r="J633" s="18"/>
+    </row>
+    <row r="634" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I634" s="18"/>
+      <c r="J634" s="18"/>
+    </row>
+    <row r="635" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I635" s="18"/>
+      <c r="J635" s="18"/>
+    </row>
+    <row r="636" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I636" s="18"/>
+      <c r="J636" s="18"/>
+    </row>
+    <row r="637" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I637" s="18"/>
+      <c r="J637" s="18"/>
+    </row>
+    <row r="638" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I638" s="18"/>
+      <c r="J638" s="18"/>
+    </row>
+    <row r="639" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I639" s="18"/>
+      <c r="J639" s="18"/>
+    </row>
+    <row r="640" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I640" s="18"/>
+      <c r="J640" s="18"/>
+    </row>
+    <row r="641" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I641" s="18"/>
+      <c r="J641" s="18"/>
+    </row>
+    <row r="642" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I642" s="18"/>
+      <c r="J642" s="18"/>
+    </row>
+    <row r="643" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I643" s="18"/>
+      <c r="J643" s="18"/>
+    </row>
+    <row r="644" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I644" s="18"/>
+      <c r="J644" s="18"/>
+    </row>
+    <row r="645" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I645" s="18"/>
+      <c r="J645" s="18"/>
+    </row>
+    <row r="646" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I646" s="18"/>
+      <c r="J646" s="18"/>
+    </row>
+    <row r="647" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I647" s="18"/>
+      <c r="J647" s="18"/>
+    </row>
+    <row r="648" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I648" s="18"/>
+      <c r="J648" s="18"/>
+    </row>
+    <row r="649" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I649" s="18"/>
+      <c r="J649" s="18"/>
+    </row>
+    <row r="650" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I650" s="18"/>
+      <c r="J650" s="18"/>
+    </row>
+    <row r="651" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I651" s="18"/>
+      <c r="J651" s="18"/>
+    </row>
+    <row r="652" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I652" s="18"/>
+      <c r="J652" s="18"/>
+    </row>
+    <row r="653" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I653" s="18"/>
+      <c r="J653" s="18"/>
+    </row>
+    <row r="654" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I654" s="18"/>
+      <c r="J654" s="18"/>
+    </row>
+    <row r="655" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I655" s="18"/>
+      <c r="J655" s="18"/>
+    </row>
+    <row r="656" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I656" s="18"/>
+      <c r="J656" s="18"/>
+    </row>
+    <row r="657" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I657" s="18"/>
+      <c r="J657" s="18"/>
+    </row>
+    <row r="658" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I658" s="18"/>
+      <c r="J658" s="18"/>
+    </row>
+    <row r="659" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I659" s="18"/>
+      <c r="J659" s="18"/>
+    </row>
+    <row r="660" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I660" s="18"/>
+      <c r="J660" s="18"/>
+    </row>
+    <row r="661" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I661" s="18"/>
+      <c r="J661" s="18"/>
+    </row>
+    <row r="662" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I662" s="18"/>
+      <c r="J662" s="18"/>
+    </row>
+    <row r="663" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I663" s="18"/>
+      <c r="J663" s="18"/>
+    </row>
+    <row r="664" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I664" s="18"/>
+      <c r="J664" s="18"/>
+    </row>
+    <row r="665" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I665" s="18"/>
+      <c r="J665" s="18"/>
+    </row>
+    <row r="666" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I666" s="18"/>
+      <c r="J666" s="18"/>
+    </row>
+    <row r="667" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I667" s="18"/>
+      <c r="J667" s="18"/>
+    </row>
+    <row r="668" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I668" s="18"/>
+      <c r="J668" s="18"/>
+    </row>
+    <row r="669" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I669" s="18"/>
+      <c r="J669" s="18"/>
+    </row>
+    <row r="670" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I670" s="18"/>
+      <c r="J670" s="18"/>
+    </row>
+    <row r="671" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I671" s="18"/>
+      <c r="J671" s="18"/>
+    </row>
+    <row r="672" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I672" s="18"/>
+      <c r="J672" s="18"/>
+    </row>
+    <row r="673" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I673" s="18"/>
+      <c r="J673" s="18"/>
+    </row>
+    <row r="674" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I674" s="18"/>
+      <c r="J674" s="18"/>
+    </row>
+    <row r="675" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I675" s="18"/>
+      <c r="J675" s="18"/>
+    </row>
+    <row r="676" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I676" s="18"/>
+      <c r="J676" s="18"/>
+    </row>
+    <row r="677" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I677" s="18"/>
+      <c r="J677" s="18"/>
+    </row>
+    <row r="678" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I678" s="18"/>
+      <c r="J678" s="18"/>
+    </row>
+    <row r="679" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I679" s="18"/>
+      <c r="J679" s="18"/>
+    </row>
+    <row r="680" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I680" s="18"/>
+      <c r="J680" s="18"/>
+    </row>
+    <row r="681" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I681" s="18"/>
+      <c r="J681" s="18"/>
+    </row>
+    <row r="682" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I682" s="18"/>
+      <c r="J682" s="18"/>
+    </row>
+    <row r="683" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I683" s="18"/>
+      <c r="J683" s="18"/>
+    </row>
+    <row r="684" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I684" s="18"/>
+      <c r="J684" s="18"/>
+    </row>
+    <row r="685" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I685" s="18"/>
+      <c r="J685" s="18"/>
+    </row>
+    <row r="686" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I686" s="18"/>
+      <c r="J686" s="18"/>
+    </row>
+    <row r="687" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I687" s="18"/>
+      <c r="J687" s="18"/>
+    </row>
+    <row r="688" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I688" s="18"/>
+      <c r="J688" s="18"/>
+    </row>
+    <row r="689" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I689" s="18"/>
+      <c r="J689" s="18"/>
+    </row>
+    <row r="690" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I690" s="18"/>
+      <c r="J690" s="18"/>
+    </row>
+    <row r="691" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I691" s="18"/>
+      <c r="J691" s="18"/>
+    </row>
+    <row r="692" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I692" s="18"/>
+      <c r="J692" s="18"/>
+    </row>
+    <row r="693" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I693" s="18"/>
+      <c r="J693" s="18"/>
+    </row>
+    <row r="694" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I694" s="18"/>
+      <c r="J694" s="18"/>
+    </row>
+    <row r="695" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I695" s="18"/>
+      <c r="J695" s="18"/>
+    </row>
+    <row r="696" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I696" s="18"/>
+      <c r="J696" s="18"/>
+    </row>
+    <row r="697" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I697" s="18"/>
+      <c r="J697" s="18"/>
+    </row>
+    <row r="698" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I698" s="18"/>
+      <c r="J698" s="18"/>
+    </row>
+    <row r="699" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I699" s="18"/>
+      <c r="J699" s="18"/>
+    </row>
+    <row r="700" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I700" s="18"/>
+      <c r="J700" s="18"/>
+    </row>
+    <row r="701" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I701" s="18"/>
+      <c r="J701" s="18"/>
+    </row>
+    <row r="702" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I702" s="18"/>
+      <c r="J702" s="18"/>
+    </row>
+    <row r="703" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I703" s="18"/>
+      <c r="J703" s="18"/>
+    </row>
+    <row r="704" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I704" s="18"/>
+      <c r="J704" s="18"/>
+    </row>
+    <row r="705" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I705" s="18"/>
+      <c r="J705" s="18"/>
+    </row>
+    <row r="706" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I706" s="18"/>
+      <c r="J706" s="18"/>
+    </row>
+    <row r="707" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I707" s="18"/>
+      <c r="J707" s="18"/>
+    </row>
+    <row r="708" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I708" s="18"/>
+      <c r="J708" s="18"/>
+    </row>
+    <row r="709" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I709" s="18"/>
+      <c r="J709" s="18"/>
+    </row>
+    <row r="710" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I710" s="18"/>
+      <c r="J710" s="18"/>
+    </row>
+    <row r="711" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I711" s="18"/>
+      <c r="J711" s="18"/>
+    </row>
+    <row r="712" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I712" s="18"/>
+      <c r="J712" s="18"/>
+    </row>
+    <row r="713" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I713" s="18"/>
+      <c r="J713" s="18"/>
+    </row>
+    <row r="714" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I714" s="18"/>
+      <c r="J714" s="18"/>
+    </row>
+    <row r="715" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I715" s="18"/>
+      <c r="J715" s="18"/>
+    </row>
+    <row r="716" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I716" s="18"/>
+      <c r="J716" s="18"/>
+    </row>
+    <row r="717" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I717" s="18"/>
+      <c r="J717" s="18"/>
+    </row>
+    <row r="718" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I718" s="18"/>
+      <c r="J718" s="18"/>
+    </row>
+    <row r="719" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I719" s="18"/>
+      <c r="J719" s="18"/>
+    </row>
+    <row r="720" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I720" s="18"/>
+      <c r="J720" s="18"/>
+    </row>
+    <row r="721" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I721" s="18"/>
+      <c r="J721" s="18"/>
+    </row>
+    <row r="722" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I722" s="18"/>
+      <c r="J722" s="18"/>
+    </row>
+    <row r="723" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I723" s="18"/>
+      <c r="J723" s="18"/>
+    </row>
+    <row r="724" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I724" s="18"/>
+      <c r="J724" s="18"/>
+    </row>
+    <row r="725" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I725" s="18"/>
+      <c r="J725" s="18"/>
+    </row>
+    <row r="726" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I726" s="18"/>
+      <c r="J726" s="18"/>
+    </row>
+    <row r="727" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I727" s="18"/>
+      <c r="J727" s="18"/>
+    </row>
+    <row r="728" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I728" s="18"/>
+      <c r="J728" s="18"/>
+    </row>
+    <row r="729" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I729" s="18"/>
+      <c r="J729" s="18"/>
+    </row>
+    <row r="730" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I730" s="18"/>
+      <c r="J730" s="18"/>
+    </row>
+    <row r="731" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I731" s="18"/>
+      <c r="J731" s="18"/>
+    </row>
+    <row r="732" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I732" s="18"/>
+      <c r="J732" s="18"/>
+    </row>
+    <row r="733" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I733" s="18"/>
+      <c r="J733" s="18"/>
+    </row>
+    <row r="734" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I734" s="18"/>
+      <c r="J734" s="18"/>
+    </row>
+    <row r="735" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I735" s="18"/>
+      <c r="J735" s="18"/>
+    </row>
+    <row r="736" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I736" s="18"/>
+      <c r="J736" s="18"/>
+    </row>
+    <row r="737" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I737" s="18"/>
+      <c r="J737" s="18"/>
+    </row>
+    <row r="738" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I738" s="18"/>
+      <c r="J738" s="18"/>
+    </row>
+    <row r="739" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I739" s="18"/>
+      <c r="J739" s="18"/>
+    </row>
+    <row r="740" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I740" s="18"/>
+      <c r="J740" s="18"/>
+    </row>
+    <row r="741" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I741" s="18"/>
+      <c r="J741" s="18"/>
+    </row>
+    <row r="742" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I742" s="18"/>
+      <c r="J742" s="18"/>
+    </row>
+    <row r="743" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I743" s="18"/>
+      <c r="J743" s="18"/>
+    </row>
+    <row r="744" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I744" s="18"/>
+      <c r="J744" s="18"/>
+    </row>
+    <row r="745" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I745" s="18"/>
+      <c r="J745" s="18"/>
+    </row>
+    <row r="746" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I746" s="18"/>
+      <c r="J746" s="18"/>
+    </row>
+    <row r="747" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I747" s="18"/>
+      <c r="J747" s="18"/>
+    </row>
+    <row r="748" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I748" s="18"/>
+      <c r="J748" s="18"/>
+    </row>
+    <row r="749" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I749" s="18"/>
+      <c r="J749" s="18"/>
+    </row>
+    <row r="750" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I750" s="18"/>
+      <c r="J750" s="18"/>
+    </row>
+    <row r="751" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I751" s="18"/>
+      <c r="J751" s="18"/>
+    </row>
+    <row r="752" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I752" s="18"/>
+      <c r="J752" s="18"/>
+    </row>
+    <row r="753" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I753" s="18"/>
+      <c r="J753" s="18"/>
+    </row>
+    <row r="754" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I754" s="18"/>
+      <c r="J754" s="18"/>
+    </row>
+    <row r="755" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I755" s="18"/>
+      <c r="J755" s="18"/>
+    </row>
+    <row r="756" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I756" s="18"/>
+      <c r="J756" s="18"/>
+    </row>
+    <row r="757" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I757" s="18"/>
+      <c r="J757" s="18"/>
+    </row>
+    <row r="758" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I758" s="18"/>
+      <c r="J758" s="18"/>
+    </row>
+    <row r="759" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I759" s="18"/>
+      <c r="J759" s="18"/>
+    </row>
+    <row r="760" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I760" s="18"/>
+      <c r="J760" s="18"/>
+    </row>
+    <row r="761" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I761" s="18"/>
+      <c r="J761" s="18"/>
+    </row>
+    <row r="762" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I762" s="18"/>
+      <c r="J762" s="18"/>
+    </row>
+    <row r="763" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I763" s="18"/>
+      <c r="J763" s="18"/>
+    </row>
+    <row r="764" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I764" s="18"/>
+      <c r="J764" s="18"/>
+    </row>
+    <row r="765" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I765" s="18"/>
+      <c r="J765" s="18"/>
+    </row>
+    <row r="766" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I766" s="18"/>
+      <c r="J766" s="18"/>
+    </row>
+    <row r="767" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I767" s="18"/>
+      <c r="J767" s="18"/>
+    </row>
+    <row r="768" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I768" s="18"/>
+      <c r="J768" s="18"/>
+    </row>
+    <row r="769" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I769" s="18"/>
+      <c r="J769" s="18"/>
+    </row>
+    <row r="770" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I770" s="18"/>
+      <c r="J770" s="18"/>
+    </row>
+    <row r="771" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I771" s="18"/>
+      <c r="J771" s="18"/>
+    </row>
+    <row r="772" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I772" s="18"/>
+      <c r="J772" s="18"/>
+    </row>
+    <row r="773" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I773" s="18"/>
+      <c r="J773" s="18"/>
+    </row>
+    <row r="774" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I774" s="18"/>
+      <c r="J774" s="18"/>
+    </row>
+    <row r="775" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I775" s="18"/>
+      <c r="J775" s="18"/>
+    </row>
+    <row r="776" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I776" s="18"/>
+      <c r="J776" s="18"/>
+    </row>
+    <row r="777" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I777" s="18"/>
+      <c r="J777" s="18"/>
+    </row>
+    <row r="778" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I778" s="18"/>
+      <c r="J778" s="18"/>
+    </row>
+    <row r="779" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I779" s="18"/>
+      <c r="J779" s="18"/>
+    </row>
+    <row r="780" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I780" s="18"/>
+      <c r="J780" s="18"/>
+    </row>
+    <row r="781" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I781" s="18"/>
+      <c r="J781" s="18"/>
+    </row>
+    <row r="782" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I782" s="18"/>
+      <c r="J782" s="18"/>
+    </row>
+    <row r="783" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I783" s="18"/>
+      <c r="J783" s="18"/>
+    </row>
+    <row r="784" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I784" s="18"/>
+      <c r="J784" s="18"/>
+    </row>
+    <row r="785" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I785" s="18"/>
+      <c r="J785" s="18"/>
+    </row>
+    <row r="786" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I786" s="18"/>
+      <c r="J786" s="18"/>
+    </row>
+    <row r="787" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I787" s="18"/>
+      <c r="J787" s="18"/>
+    </row>
+    <row r="788" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I788" s="18"/>
+      <c r="J788" s="18"/>
+    </row>
+    <row r="789" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I789" s="18"/>
+      <c r="J789" s="18"/>
+    </row>
+    <row r="790" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I790" s="18"/>
+      <c r="J790" s="18"/>
+    </row>
+    <row r="791" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I791" s="18"/>
+      <c r="J791" s="18"/>
+    </row>
+    <row r="792" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I792" s="18"/>
+      <c r="J792" s="18"/>
+    </row>
+    <row r="793" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I793" s="18"/>
+      <c r="J793" s="18"/>
+    </row>
+    <row r="794" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I794" s="18"/>
+      <c r="J794" s="18"/>
+    </row>
+    <row r="795" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I795" s="18"/>
+      <c r="J795" s="18"/>
+    </row>
+    <row r="796" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I796" s="18"/>
+      <c r="J796" s="18"/>
+    </row>
+    <row r="797" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I797" s="18"/>
+      <c r="J797" s="18"/>
+    </row>
+    <row r="798" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I798" s="18"/>
+      <c r="J798" s="18"/>
+    </row>
+    <row r="799" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I799" s="18"/>
+      <c r="J799" s="18"/>
+    </row>
+    <row r="800" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I800" s="18"/>
+      <c r="J800" s="18"/>
+    </row>
+    <row r="801" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I801" s="18"/>
+      <c r="J801" s="18"/>
+    </row>
+    <row r="802" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I802" s="18"/>
+      <c r="J802" s="18"/>
+    </row>
+    <row r="803" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I803" s="18"/>
+      <c r="J803" s="18"/>
+    </row>
+    <row r="804" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I804" s="18"/>
+      <c r="J804" s="18"/>
+    </row>
+    <row r="805" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I805" s="18"/>
+      <c r="J805" s="18"/>
+    </row>
+    <row r="806" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I806" s="18"/>
+      <c r="J806" s="18"/>
+    </row>
+    <row r="807" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I807" s="18"/>
+      <c r="J807" s="18"/>
+    </row>
+    <row r="808" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I808" s="18"/>
+      <c r="J808" s="18"/>
+    </row>
+    <row r="809" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I809" s="18"/>
+      <c r="J809" s="18"/>
+    </row>
+    <row r="810" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I810" s="18"/>
+      <c r="J810" s="18"/>
+    </row>
+    <row r="811" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I811" s="18"/>
+      <c r="J811" s="18"/>
+    </row>
+    <row r="812" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I812" s="18"/>
+      <c r="J812" s="18"/>
+    </row>
+    <row r="813" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I813" s="18"/>
+      <c r="J813" s="18"/>
+    </row>
+    <row r="814" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I814" s="18"/>
+      <c r="J814" s="18"/>
+    </row>
+    <row r="815" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I815" s="18"/>
+      <c r="J815" s="18"/>
+    </row>
+    <row r="816" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I816" s="18"/>
+      <c r="J816" s="18"/>
+    </row>
+    <row r="817" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I817" s="18"/>
+      <c r="J817" s="18"/>
+    </row>
+    <row r="818" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I818" s="18"/>
+      <c r="J818" s="18"/>
+    </row>
+    <row r="819" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I819" s="18"/>
+      <c r="J819" s="18"/>
+    </row>
+    <row r="820" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I820" s="18"/>
+      <c r="J820" s="18"/>
+    </row>
+    <row r="821" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I821" s="18"/>
+      <c r="J821" s="18"/>
+    </row>
+    <row r="822" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I822" s="18"/>
+      <c r="J822" s="18"/>
+    </row>
+    <row r="823" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I823" s="18"/>
+      <c r="J823" s="18"/>
+    </row>
+    <row r="824" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I824" s="18"/>
+      <c r="J824" s="18"/>
+    </row>
+    <row r="825" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I825" s="18"/>
+      <c r="J825" s="18"/>
+    </row>
+    <row r="826" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I826" s="18"/>
+      <c r="J826" s="18"/>
+    </row>
+    <row r="827" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I827" s="18"/>
+      <c r="J827" s="18"/>
+    </row>
+    <row r="828" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I828" s="18"/>
+      <c r="J828" s="18"/>
+    </row>
+    <row r="829" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I829" s="18"/>
+      <c r="J829" s="18"/>
+    </row>
+    <row r="830" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I830" s="18"/>
+      <c r="J830" s="18"/>
+    </row>
+    <row r="831" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I831" s="18"/>
+      <c r="J831" s="18"/>
+    </row>
+    <row r="832" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I832" s="18"/>
+      <c r="J832" s="18"/>
+    </row>
+    <row r="833" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I833" s="18"/>
+      <c r="J833" s="18"/>
+    </row>
+    <row r="834" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I834" s="18"/>
+      <c r="J834" s="18"/>
+    </row>
+    <row r="835" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I835" s="18"/>
+      <c r="J835" s="18"/>
+    </row>
+    <row r="836" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I836" s="18"/>
+      <c r="J836" s="18"/>
+    </row>
+    <row r="837" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I837" s="18"/>
+      <c r="J837" s="18"/>
+    </row>
+    <row r="838" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I838" s="18"/>
+      <c r="J838" s="18"/>
+    </row>
+    <row r="839" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I839" s="18"/>
+      <c r="J839" s="18"/>
+    </row>
+    <row r="840" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I840" s="18"/>
+      <c r="J840" s="18"/>
+    </row>
+    <row r="841" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I841" s="18"/>
+      <c r="J841" s="18"/>
+    </row>
+    <row r="842" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I842" s="18"/>
+      <c r="J842" s="18"/>
+    </row>
+    <row r="843" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I843" s="18"/>
+      <c r="J843" s="18"/>
+    </row>
+    <row r="844" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I844" s="18"/>
+      <c r="J844" s="18"/>
+    </row>
+    <row r="845" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I845" s="18"/>
+      <c r="J845" s="18"/>
+    </row>
+    <row r="846" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I846" s="18"/>
+      <c r="J846" s="18"/>
+    </row>
+    <row r="847" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I847" s="18"/>
+      <c r="J847" s="18"/>
+    </row>
+    <row r="848" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I848" s="18"/>
+      <c r="J848" s="18"/>
+    </row>
+    <row r="849" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I849" s="18"/>
+      <c r="J849" s="18"/>
+    </row>
+    <row r="850" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I850" s="18"/>
+      <c r="J850" s="18"/>
+    </row>
+    <row r="851" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I851" s="18"/>
+      <c r="J851" s="18"/>
+    </row>
+    <row r="852" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I852" s="18"/>
+      <c r="J852" s="18"/>
+    </row>
+    <row r="853" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I853" s="18"/>
+      <c r="J853" s="18"/>
+    </row>
+    <row r="854" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I854" s="18"/>
+      <c r="J854" s="18"/>
+    </row>
+    <row r="855" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I855" s="18"/>
+      <c r="J855" s="18"/>
+    </row>
+    <row r="856" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I856" s="18"/>
+      <c r="J856" s="18"/>
+    </row>
+    <row r="857" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I857" s="18"/>
+      <c r="J857" s="18"/>
+    </row>
+    <row r="858" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I858" s="18"/>
+      <c r="J858" s="18"/>
+    </row>
+    <row r="859" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I859" s="18"/>
+      <c r="J859" s="18"/>
+    </row>
+    <row r="860" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I860" s="18"/>
+      <c r="J860" s="18"/>
+    </row>
+    <row r="861" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I861" s="18"/>
+      <c r="J861" s="18"/>
+    </row>
+    <row r="862" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I862" s="18"/>
+      <c r="J862" s="18"/>
+    </row>
+    <row r="863" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I863" s="18"/>
+      <c r="J863" s="18"/>
+    </row>
+    <row r="864" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I864" s="18"/>
+      <c r="J864" s="18"/>
+    </row>
+    <row r="865" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I865" s="18"/>
+      <c r="J865" s="18"/>
+    </row>
+    <row r="866" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I866" s="18"/>
+      <c r="J866" s="18"/>
+    </row>
+    <row r="867" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I867" s="18"/>
+      <c r="J867" s="18"/>
+    </row>
+    <row r="868" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I868" s="18"/>
+      <c r="J868" s="18"/>
+    </row>
+    <row r="869" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I869" s="18"/>
+      <c r="J869" s="18"/>
+    </row>
+    <row r="870" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I870" s="18"/>
+      <c r="J870" s="18"/>
+    </row>
+    <row r="871" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I871" s="18"/>
+      <c r="J871" s="18"/>
+    </row>
+    <row r="872" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I872" s="18"/>
+      <c r="J872" s="18"/>
+    </row>
+    <row r="873" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I873" s="18"/>
+      <c r="J873" s="18"/>
+    </row>
+    <row r="874" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I874" s="18"/>
+      <c r="J874" s="18"/>
+    </row>
+    <row r="875" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I875" s="18"/>
+      <c r="J875" s="18"/>
+    </row>
+    <row r="876" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I876" s="18"/>
+      <c r="J876" s="18"/>
+    </row>
+    <row r="877" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I877" s="18"/>
+      <c r="J877" s="18"/>
+    </row>
+    <row r="878" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I878" s="18"/>
+      <c r="J878" s="18"/>
+    </row>
+    <row r="879" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I879" s="18"/>
+      <c r="J879" s="18"/>
+    </row>
+    <row r="880" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I880" s="18"/>
+      <c r="J880" s="18"/>
+    </row>
+    <row r="881" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I881" s="18"/>
+      <c r="J881" s="18"/>
+    </row>
+    <row r="882" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I882" s="18"/>
+      <c r="J882" s="18"/>
+    </row>
+    <row r="883" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I883" s="18"/>
+      <c r="J883" s="18"/>
+    </row>
+    <row r="884" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I884" s="18"/>
+      <c r="J884" s="18"/>
+    </row>
+    <row r="885" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I885" s="18"/>
+      <c r="J885" s="18"/>
+    </row>
+    <row r="886" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I886" s="18"/>
+      <c r="J886" s="18"/>
+    </row>
+    <row r="887" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I887" s="18"/>
+      <c r="J887" s="18"/>
+    </row>
+    <row r="888" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I888" s="18"/>
+      <c r="J888" s="18"/>
+    </row>
+    <row r="889" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I889" s="18"/>
+      <c r="J889" s="18"/>
+    </row>
+    <row r="890" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I890" s="18"/>
+      <c r="J890" s="18"/>
+    </row>
+    <row r="891" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I891" s="18"/>
+      <c r="J891" s="18"/>
+    </row>
+    <row r="892" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I892" s="18"/>
+      <c r="J892" s="18"/>
+    </row>
+    <row r="893" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I893" s="18"/>
+      <c r="J893" s="18"/>
+    </row>
+    <row r="894" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I894" s="18"/>
+      <c r="J894" s="18"/>
+    </row>
+    <row r="895" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I895" s="18"/>
+      <c r="J895" s="18"/>
+    </row>
+    <row r="896" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I896" s="18"/>
+      <c r="J896" s="18"/>
+    </row>
+    <row r="897" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I897" s="18"/>
+      <c r="J897" s="18"/>
+    </row>
+    <row r="898" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I898" s="18"/>
+      <c r="J898" s="18"/>
+    </row>
+    <row r="899" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I899" s="18"/>
+      <c r="J899" s="18"/>
+    </row>
+    <row r="900" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I900" s="18"/>
+      <c r="J900" s="18"/>
+    </row>
+    <row r="901" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I901" s="18"/>
+      <c r="J901" s="18"/>
+    </row>
+    <row r="902" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I902" s="18"/>
+      <c r="J902" s="18"/>
+    </row>
+    <row r="903" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I903" s="18"/>
+      <c r="J903" s="18"/>
+    </row>
+    <row r="904" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I904" s="18"/>
+      <c r="J904" s="18"/>
+    </row>
+    <row r="905" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I905" s="18"/>
+      <c r="J905" s="18"/>
+    </row>
+    <row r="906" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I906" s="18"/>
+      <c r="J906" s="18"/>
+    </row>
+    <row r="907" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I907" s="18"/>
+      <c r="J907" s="18"/>
+    </row>
+    <row r="908" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I908" s="18"/>
+      <c r="J908" s="18"/>
+    </row>
+    <row r="909" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I909" s="18"/>
+      <c r="J909" s="18"/>
+    </row>
+    <row r="910" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I910" s="18"/>
+      <c r="J910" s="18"/>
+    </row>
+    <row r="911" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I911" s="18"/>
+      <c r="J911" s="18"/>
+    </row>
+    <row r="912" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I912" s="18"/>
+      <c r="J912" s="18"/>
+    </row>
+    <row r="913" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I913" s="18"/>
+      <c r="J913" s="18"/>
+    </row>
+    <row r="914" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I914" s="18"/>
+      <c r="J914" s="18"/>
+    </row>
+    <row r="915" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I915" s="18"/>
+      <c r="J915" s="18"/>
+    </row>
+    <row r="916" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I916" s="18"/>
+      <c r="J916" s="18"/>
+    </row>
+    <row r="917" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I917" s="18"/>
+      <c r="J917" s="18"/>
+    </row>
+    <row r="918" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I918" s="18"/>
+      <c r="J918" s="18"/>
+    </row>
+    <row r="919" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I919" s="18"/>
+      <c r="J919" s="18"/>
+    </row>
+    <row r="920" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I920" s="18"/>
+      <c r="J920" s="18"/>
+    </row>
+    <row r="921" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I921" s="18"/>
+      <c r="J921" s="18"/>
+    </row>
+    <row r="922" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I922" s="18"/>
+      <c r="J922" s="18"/>
+    </row>
+    <row r="923" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I923" s="18"/>
+      <c r="J923" s="18"/>
+    </row>
+    <row r="924" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I924" s="18"/>
+      <c r="J924" s="18"/>
+    </row>
+    <row r="925" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I925" s="18"/>
+      <c r="J925" s="18"/>
+    </row>
+    <row r="926" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I926" s="18"/>
+      <c r="J926" s="18"/>
+    </row>
+    <row r="927" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I927" s="18"/>
+      <c r="J927" s="18"/>
+    </row>
+    <row r="928" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I928" s="18"/>
+      <c r="J928" s="18"/>
+    </row>
+    <row r="929" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I929" s="18"/>
+      <c r="J929" s="18"/>
+    </row>
+    <row r="930" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I930" s="18"/>
+      <c r="J930" s="18"/>
+    </row>
+    <row r="931" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I931" s="18"/>
+      <c r="J931" s="18"/>
+    </row>
+    <row r="932" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I932" s="18"/>
+      <c r="J932" s="18"/>
+    </row>
+    <row r="933" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I933" s="18"/>
+      <c r="J933" s="18"/>
+    </row>
+    <row r="934" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I934" s="18"/>
+      <c r="J934" s="18"/>
+    </row>
+    <row r="935" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I935" s="18"/>
+      <c r="J935" s="18"/>
+    </row>
+    <row r="936" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I936" s="18"/>
+      <c r="J936" s="18"/>
+    </row>
+    <row r="937" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I937" s="18"/>
+      <c r="J937" s="18"/>
+    </row>
+    <row r="938" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I938" s="18"/>
+      <c r="J938" s="18"/>
+    </row>
+    <row r="939" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I939" s="18"/>
+      <c r="J939" s="18"/>
+    </row>
+    <row r="940" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I940" s="18"/>
+      <c r="J940" s="18"/>
+    </row>
+    <row r="941" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I941" s="18"/>
+      <c r="J941" s="18"/>
+    </row>
+    <row r="942" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I942" s="18"/>
+      <c r="J942" s="18"/>
+    </row>
+    <row r="943" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I943" s="18"/>
+      <c r="J943" s="18"/>
+    </row>
+    <row r="944" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I944" s="18"/>
+      <c r="J944" s="18"/>
+    </row>
+    <row r="945" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I945" s="18"/>
+      <c r="J945" s="18"/>
+    </row>
+    <row r="946" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I946" s="18"/>
+      <c r="J946" s="18"/>
+    </row>
+    <row r="947" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I947" s="18"/>
+      <c r="J947" s="18"/>
+    </row>
+    <row r="948" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I948" s="18"/>
+      <c r="J948" s="18"/>
+    </row>
+    <row r="949" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I949" s="18"/>
+      <c r="J949" s="18"/>
+    </row>
+    <row r="950" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I950" s="18"/>
+      <c r="J950" s="18"/>
+    </row>
+    <row r="951" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I951" s="18"/>
+      <c r="J951" s="18"/>
+    </row>
+    <row r="952" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I952" s="18"/>
+      <c r="J952" s="18"/>
+    </row>
+    <row r="953" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I953" s="18"/>
+      <c r="J953" s="18"/>
+    </row>
+    <row r="954" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I954" s="18"/>
+      <c r="J954" s="18"/>
+    </row>
+    <row r="955" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I955" s="18"/>
+      <c r="J955" s="18"/>
+    </row>
+    <row r="956" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I956" s="18"/>
+      <c r="J956" s="18"/>
+    </row>
+    <row r="957" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I957" s="18"/>
+      <c r="J957" s="18"/>
+    </row>
+    <row r="958" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I958" s="18"/>
+      <c r="J958" s="18"/>
+    </row>
+    <row r="959" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I959" s="18"/>
+      <c r="J959" s="18"/>
+    </row>
+    <row r="960" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I960" s="18"/>
+      <c r="J960" s="18"/>
+    </row>
+    <row r="961" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I961" s="18"/>
+      <c r="J961" s="18"/>
+    </row>
+    <row r="962" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I962" s="18"/>
+      <c r="J962" s="18"/>
+    </row>
+    <row r="963" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I963" s="18"/>
+      <c r="J963" s="18"/>
+    </row>
+    <row r="964" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I964" s="18"/>
+      <c r="J964" s="18"/>
+    </row>
+    <row r="965" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I965" s="18"/>
+      <c r="J965" s="18"/>
+    </row>
+    <row r="966" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I966" s="18"/>
+      <c r="J966" s="18"/>
+    </row>
+    <row r="967" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I967" s="18"/>
+      <c r="J967" s="18"/>
+    </row>
+    <row r="968" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I968" s="18"/>
+      <c r="J968" s="18"/>
+    </row>
+    <row r="969" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I969" s="18"/>
+      <c r="J969" s="18"/>
+    </row>
+    <row r="970" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I970" s="18"/>
+      <c r="J970" s="18"/>
+    </row>
+    <row r="971" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I971" s="18"/>
+      <c r="J971" s="18"/>
+    </row>
+    <row r="972" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I972" s="18"/>
+      <c r="J972" s="18"/>
+    </row>
+    <row r="973" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I973" s="18"/>
+      <c r="J973" s="18"/>
+    </row>
+    <row r="974" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I974" s="18"/>
+      <c r="J974" s="18"/>
+    </row>
+    <row r="975" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I975" s="18"/>
+      <c r="J975" s="18"/>
+    </row>
+    <row r="976" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I976" s="18"/>
+      <c r="J976" s="18"/>
+    </row>
+    <row r="977" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I977" s="18"/>
+      <c r="J977" s="18"/>
+    </row>
+    <row r="978" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I978" s="18"/>
+      <c r="J978" s="18"/>
+    </row>
+    <row r="979" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I979" s="18"/>
+      <c r="J979" s="18"/>
+    </row>
+    <row r="980" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I980" s="18"/>
+      <c r="J980" s="18"/>
+    </row>
+    <row r="981" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I981" s="18"/>
+      <c r="J981" s="18"/>
+    </row>
+    <row r="982" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I982" s="18"/>
+      <c r="J982" s="18"/>
+    </row>
+    <row r="983" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I983" s="18"/>
+      <c r="J983" s="18"/>
+    </row>
+    <row r="984" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I984" s="18"/>
+      <c r="J984" s="18"/>
+    </row>
+    <row r="985" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I985" s="18"/>
+      <c r="J985" s="18"/>
+    </row>
+    <row r="986" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I986" s="18"/>
+      <c r="J986" s="18"/>
+    </row>
+    <row r="987" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I987" s="18"/>
+      <c r="J987" s="18"/>
+    </row>
+    <row r="988" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I988" s="18"/>
+      <c r="J988" s="18"/>
+    </row>
+    <row r="989" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I989" s="18"/>
+      <c r="J989" s="18"/>
+    </row>
+    <row r="990" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I990" s="18"/>
+      <c r="J990" s="18"/>
+    </row>
+    <row r="991" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I991" s="18"/>
+      <c r="J991" s="18"/>
+    </row>
+    <row r="992" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I992" s="18"/>
+      <c r="J992" s="18"/>
+    </row>
+    <row r="993" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I993" s="18"/>
+      <c r="J993" s="18"/>
+    </row>
+    <row r="994" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I994" s="18"/>
+      <c r="J994" s="18"/>
+    </row>
+    <row r="995" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I995" s="18"/>
+      <c r="J995" s="18"/>
+    </row>
+    <row r="996" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I996" s="18"/>
+      <c r="J996" s="18"/>
+    </row>
+    <row r="997" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I997" s="18"/>
+      <c r="J997" s="18"/>
+    </row>
+    <row r="998" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I998" s="18"/>
+      <c r="J998" s="18"/>
+    </row>
+    <row r="999" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I999" s="18"/>
+      <c r="J999" s="18"/>
+    </row>
+    <row r="1000" spans="9:10" x14ac:dyDescent="0.25">
+      <c r="I1000" s="18"/>
+      <c r="J1000" s="18"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M1" xr:uid="{724E297C-E4EA-4AA3-B0EF-D35314885408}"/>
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A1000 L2:L1000" xr:uid="{4F15A065-C3F1-44CE-8504-8F1F48403056}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"نعم,لا"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"نعم,لا"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B1000" xr:uid="{633026AA-4F70-499A-A21B-3878BDE73479}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"الكل,المتجر,الأكاديمية"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"الكل,المتجر,الأكاديمية"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" sqref="N2:N1000" xr:uid="{5A6E1D0A-EEF1-4E59-8745-DFDECF383DAE}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"❤️,🎈,🎉,✨,💛,🌟,🎊"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"❤️,🎈,🎉,✨,💛,🌟,🎊"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -2629,7 +6831,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C04388D-136E-47CF-94BE-194ED811EF9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64BD605-CD4F-4974-A046-2F58EF992B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2664,9 +2664,7 @@
   <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="8.75" customWidth="1"/>
     <col min="4" max="4" width="32.625" customWidth="1"/>
     <col min="5" max="5" width="54.625" customWidth="1"/>
     <col min="6" max="6" width="42.625" customWidth="1"/>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64BD605-CD4F-4974-A046-2F58EF992B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B048-8402-4C59-9F5D-F3FC7B95A975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="236">
   <si>
     <t>id</t>
   </si>
@@ -961,6 +961,117 @@
   </si>
   <si>
     <t>🎈|❤️|🎉|✨|💛</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كاميرات </t>
+  </si>
+  <si>
+    <t xml:space="preserve">اكسسوارات </t>
+  </si>
+  <si>
+    <t>fa fa-camera</t>
+  </si>
+  <si>
+    <t>fa fa-battery-full</t>
+  </si>
+  <si>
+    <t>رأس شاحن</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> رأس شاحن من Twins </t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41yM6XDBtdL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61RWhmJBicL._AC_UF350,350_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>شاحن سامسونج ALK-178  مزود بفتحة شحن تايب سي وusb</t>
+  </si>
+  <si>
+    <t>شاحن سامسونج + منفذ tybe C</t>
+  </si>
+  <si>
+    <t>https://hrmaka.com/public/uploads/all/l5DFgt7e5M5BbINebdSSNNg7iEEGOASLwE0cCjCy.jpg</t>
+  </si>
+  <si>
+    <t>شاحن سامسونج + وصلة الشاحن سامسونج</t>
+  </si>
+  <si>
+    <t>شاحن سامسونج sc07v</t>
+  </si>
+  <si>
+    <t>شاحن سامسونج + 2 usb وصلة سامسونج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شاحن سامسونج + 2 usb وصلة سامسونج شاحن سريع 4.8 أمبير </t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTdfnt9jjqvtDBkNStaiZHPYW27_TIVL6FPj6G3BzsgPvIaNS2UiR-MqWsN&amp;s=10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شاحن ديجيتال للبطاريات </t>
+  </si>
+  <si>
+    <t>شاحن بطارية شامل للمكتب</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/61FI1pfCX-L._AC_SL1500_.jpg
+https://m.media-amazon.com/images/I/61nzAxf4fUL._AC_SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>https://makerselectronics.com/wp-content/uploads/2023/10/1600-2-1600x1600.jpg
+https://makerselectronics.com/wp-content/uploads/2023/10/1600-1-1600x1600.jpg
+https://makerselectronics.com/wp-content/uploads/2023/10/1600-1600x1600.jpg</t>
+  </si>
+  <si>
+    <t>وصلة شاحن One DEPOT Type-C USB TO USB Data Cable 1M S01T 2.4A</t>
+  </si>
+  <si>
+    <t>كابل شحن تايب سي (نوع C) D161 لنقل بيانات فائق السرعة بقدرة 12 وات- 2.4 امبير بطول 1 متر من سكاي دولفين، لمحول الشحن</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/614tfWd9kLL._SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>https://makerselectronics.com/wp-content/uploads/2023/10/700-3.jpg
+https://makerselectronics.com/wp-content/uploads/2023/10/700-4.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وصلة شاحن One DEPOT Micro USB TO USB Data Cable 1M S01V 2.4A
+</t>
+  </si>
+  <si>
+    <t>https://images-bucket.bonanzastatic.com/afu/images/e982/b9e1/881c_10342555972/whats-app-image-2021-03-27-at-6-00-52-pm.jpg</t>
+  </si>
+  <si>
+    <t>وصلة شاحن سامسونجFast Charging 2.4A BATTERY T01</t>
+  </si>
+  <si>
+    <t>كابل شحن وبيانات 6 امبير من (يو اس بى) الى (تايب سى) يدعم اعلى سرعة للشحن - لجميع الهواتف الذكية</t>
+  </si>
+  <si>
+    <t>كابل شحن وبيانات 6 امبير من (يو اس بى) الى (مايكرو) يدعم اعلى سرعة للشحن - لجميع الهواتف الذكية</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/iconixdistributions/?locale=fr_FR</t>
+  </si>
+  <si>
+    <t>https://btech.com/en/p/83d97840-5850-4f66-896e-49eadc9660eb</t>
+  </si>
+  <si>
+    <t>https://i.ebayimg.com/images/g/d7kAAOSwsjZoQga-/s-l1600.webp
+https://i.ebayimg.com/images/g/e2kAAOSwU8FoQga-/s-l1600.webp
+https://i.ebayimg.com/images/g/EwEAAOSwPQloQga9/s-l1600.webp
+https://i.ebayimg.com/images/g/lmMAAOSw69RoQga-/s-l1600.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">كابل 120 وات 6 امبير سوبر فاست كابل متعدد 3 في 1  لكل الهواتف والايفون </t>
+  </si>
+  <si>
+    <t>كابل 120 وات 6 امبير سوبر فاست كابل متعدد 3 في 1  لكل الهواتف والايفون  
+3-in-1 Multi Charging Cable – USB to iPhone/ Micro USB / Type-C 1.2M 120 w super fast charge 6 a</t>
   </si>
 </sst>
 </file>
@@ -970,7 +1081,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1048,6 +1159,31 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="17"/>
+      <color rgb="FF333333"/>
+      <name val="R-font"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF313133"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="17"/>
+      <color rgb="FF191919"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1076,7 +1212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1116,6 +1252,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1457,7 +1608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDD01485-0D00-419E-A382-2485D3722BA1}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="115.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
@@ -1465,7 +1616,7 @@
     <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="5" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>64</v>
       </c>
@@ -1479,7 +1630,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>132</v>
       </c>
@@ -1493,7 +1644,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -1507,7 +1658,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>133</v>
       </c>
@@ -1521,7 +1672,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1535,7 +1686,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>134</v>
       </c>
@@ -1556,8 +1707,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.25" bestFit="1" customWidth="1"/>
@@ -1577,7 +1728,7 @@
     <col min="17" max="17" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1630,7 +1781,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="50.25" customHeight="1">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1677,7 +1828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="50.25" customHeight="1">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1724,7 +1875,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="50.25" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1771,7 +1922,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="162.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="162.75">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1812,7 +1963,7 @@
         <v>46296</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1844,7 +1995,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1876,7 +2027,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="63" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="63">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1908,7 +2059,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="63" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="63">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1940,7 +2091,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="23.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1972,7 +2123,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="126" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="126">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2007,7 +2158,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="46.5">
       <c r="A12" s="11">
         <v>11</v>
       </c>
@@ -2056,7 +2207,7 @@
         <v>46270.999305555553</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="46.5">
       <c r="A13" s="11">
         <v>12</v>
       </c>
@@ -2102,6 +2253,471 @@
       </c>
       <c r="Q13" s="14">
         <v>46270.999305555553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="21.75">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14" s="1">
+        <v>40</v>
+      </c>
+      <c r="D14" s="1">
+        <v>55</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14" t="s">
+        <v>208</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="O14">
+        <v>3</v>
+      </c>
+      <c r="P14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C15" s="1">
+        <v>80</v>
+      </c>
+      <c r="D15" s="1">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F15" t="s">
+        <v>209</v>
+      </c>
+      <c r="G15" t="s">
+        <v>209</v>
+      </c>
+      <c r="H15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" t="s">
+        <v>182</v>
+      </c>
+      <c r="L15" t="s">
+        <v>210</v>
+      </c>
+      <c r="O15">
+        <v>5</v>
+      </c>
+      <c r="P15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" s="1">
+        <v>35</v>
+      </c>
+      <c r="D16" s="1">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" t="s">
+        <v>212</v>
+      </c>
+      <c r="G16" t="s">
+        <v>212</v>
+      </c>
+      <c r="H16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" t="s">
+        <v>182</v>
+      </c>
+      <c r="L16" t="s">
+        <v>213</v>
+      </c>
+      <c r="O16">
+        <v>4</v>
+      </c>
+      <c r="P16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>215</v>
+      </c>
+      <c r="C17" s="1">
+        <v>50</v>
+      </c>
+      <c r="D17" s="1">
+        <v>65</v>
+      </c>
+      <c r="E17" t="s">
+        <v>216</v>
+      </c>
+      <c r="F17" t="s">
+        <v>217</v>
+      </c>
+      <c r="G17" t="s">
+        <v>217</v>
+      </c>
+      <c r="H17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" t="s">
+        <v>182</v>
+      </c>
+      <c r="L17" t="s">
+        <v>216</v>
+      </c>
+      <c r="M17" s="14">
+        <v>46305.999305555553</v>
+      </c>
+      <c r="O17">
+        <v>5</v>
+      </c>
+      <c r="P17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="63">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>218</v>
+      </c>
+      <c r="C18" s="1">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1">
+        <v>75</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H18" t="s">
+        <v>83</v>
+      </c>
+      <c r="I18" t="s">
+        <v>182</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="M18" s="14">
+        <v>46305.999305555553</v>
+      </c>
+      <c r="O18">
+        <v>3</v>
+      </c>
+      <c r="P18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="94.5">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>222</v>
+      </c>
+      <c r="C19" s="1">
+        <v>35</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" t="s">
+        <v>182</v>
+      </c>
+      <c r="L19" t="s">
+        <v>222</v>
+      </c>
+      <c r="O19">
+        <v>5</v>
+      </c>
+      <c r="P19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="139.5">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="1">
+        <v>35</v>
+      </c>
+      <c r="D20" s="1">
+        <v>20</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" t="s">
+        <v>224</v>
+      </c>
+      <c r="G20" t="s">
+        <v>224</v>
+      </c>
+      <c r="H20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I20" t="s">
+        <v>182</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="O20">
+        <v>5</v>
+      </c>
+      <c r="P20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="63">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="1">
+        <v>35</v>
+      </c>
+      <c r="D21" s="1">
+        <v>20</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H21" t="s">
+        <v>83</v>
+      </c>
+      <c r="I21" t="s">
+        <v>182</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="O21">
+        <v>5</v>
+      </c>
+      <c r="P21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="93">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="1">
+        <v>45</v>
+      </c>
+      <c r="D22" s="1">
+        <v>30</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="F22" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" t="s">
+        <v>182</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="O22">
+        <v>5</v>
+      </c>
+      <c r="P22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="337.5">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="C23" s="1">
+        <v>50</v>
+      </c>
+      <c r="D23" s="1">
+        <v>35</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="F23" t="s">
+        <v>232</v>
+      </c>
+      <c r="G23" t="s">
+        <v>232</v>
+      </c>
+      <c r="H23" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" t="s">
+        <v>182</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="O23">
+        <v>5</v>
+      </c>
+      <c r="P23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" ht="337.5">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="1">
+        <v>45</v>
+      </c>
+      <c r="D24" s="1">
+        <v>30</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="F24" t="s">
+        <v>231</v>
+      </c>
+      <c r="G24" t="s">
+        <v>231</v>
+      </c>
+      <c r="H24" t="s">
+        <v>83</v>
+      </c>
+      <c r="I24" t="s">
+        <v>182</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="O24">
+        <v>5</v>
+      </c>
+      <c r="P24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="130.5">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="1">
+        <v>90</v>
+      </c>
+      <c r="D25" s="1">
+        <v>50</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="H25" t="s">
+        <v>83</v>
+      </c>
+      <c r="I25" t="s">
+        <v>182</v>
+      </c>
+      <c r="L25" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="M25" s="14">
+        <v>46305.999305555553</v>
+      </c>
+      <c r="O25">
+        <v>5</v>
+      </c>
+      <c r="P25">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2134,14 +2750,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="28.625" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -2149,7 +2765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>86</v>
       </c>
@@ -2157,7 +2773,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -2165,7 +2781,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>83</v>
       </c>
@@ -2173,7 +2789,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>85</v>
       </c>
@@ -2181,7 +2797,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>84</v>
       </c>
@@ -2189,11 +2805,27 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>87</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
         <v>92</v>
       </c>
     </row>
@@ -2208,7 +2840,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="2" max="2" width="23.875" customWidth="1"/>
@@ -2218,7 +2850,7 @@
     <col min="6" max="6" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2241,7 +2873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1770051311267</v>
       </c>
@@ -2264,7 +2896,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>1770051311268</v>
       </c>
@@ -2287,7 +2919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>1770051311269</v>
       </c>
@@ -2310,7 +2942,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>1770051311270</v>
       </c>
@@ -2333,7 +2965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>1770051311271</v>
       </c>
@@ -2367,12 +2999,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="4" max="4" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>38</v>
       </c>
@@ -2389,7 +3021,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -2406,7 +3038,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>44</v>
       </c>
@@ -2423,7 +3055,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="10">
         <v>12345</v>
       </c>
@@ -2440,7 +3072,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="10">
         <v>14521</v>
       </c>
@@ -2468,14 +3100,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="90.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>46</v>
       </c>
@@ -2486,7 +3118,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2497,7 +3129,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -2508,7 +3140,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -2519,7 +3151,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>56</v>
       </c>
@@ -2530,7 +3162,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -2541,7 +3173,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2552,7 +3184,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>111</v>
       </c>
@@ -2563,7 +3195,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>113</v>
       </c>
@@ -2574,7 +3206,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>115</v>
       </c>
@@ -2585,7 +3217,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>117</v>
       </c>
@@ -2596,7 +3228,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>119</v>
       </c>
@@ -2607,7 +3239,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>121</v>
       </c>
@@ -2618,7 +3250,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>123</v>
       </c>
@@ -2629,7 +3261,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>126</v>
       </c>
@@ -2640,7 +3272,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -2662,7 +3294,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{724E297C-E4EA-4AA3-B0EF-D35314885408}">
   <dimension ref="A1:N1000"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="3" width="8.75" customWidth="1"/>
     <col min="4" max="4" width="32.625" customWidth="1"/>
@@ -2678,7 +3310,7 @@
     <col min="14" max="14" width="34.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14">
       <c r="A1" s="16" t="s">
         <v>65</v>
       </c>
@@ -2722,7 +3354,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>66</v>
       </c>
@@ -2763,3995 +3395,3995 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14">
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14">
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14">
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14">
       <c r="I6" s="18"/>
       <c r="J6" s="18"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14">
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14">
       <c r="I8" s="18"/>
       <c r="J8" s="18"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14">
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14">
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14">
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14">
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14">
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14">
       <c r="I14" s="18"/>
       <c r="J14" s="18"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14">
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14">
       <c r="I16" s="18"/>
       <c r="J16" s="18"/>
     </row>
-    <row r="17" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:10">
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:10">
       <c r="I18" s="18"/>
       <c r="J18" s="18"/>
     </row>
-    <row r="19" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:10">
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:10">
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
     </row>
-    <row r="21" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:10">
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:10">
       <c r="I22" s="18"/>
       <c r="J22" s="18"/>
     </row>
-    <row r="23" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="9:10">
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="9:10">
       <c r="I24" s="18"/>
       <c r="J24" s="18"/>
     </row>
-    <row r="25" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="9:10">
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="9:10">
       <c r="I26" s="18"/>
       <c r="J26" s="18"/>
     </row>
-    <row r="27" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="9:10">
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="9:10">
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
     </row>
-    <row r="29" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="9:10">
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="9:10">
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
     </row>
-    <row r="31" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="9:10">
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="9:10">
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
     </row>
-    <row r="33" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="9:10">
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
     </row>
-    <row r="34" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="9:10">
       <c r="I34" s="18"/>
       <c r="J34" s="18"/>
     </row>
-    <row r="35" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="9:10">
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="9:10">
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
     </row>
-    <row r="37" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="9:10">
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
     </row>
-    <row r="38" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="9:10">
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
     </row>
-    <row r="39" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="9:10">
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
     </row>
-    <row r="40" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="9:10">
       <c r="I40" s="18"/>
       <c r="J40" s="18"/>
     </row>
-    <row r="41" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="9:10">
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
     </row>
-    <row r="42" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="9:10">
       <c r="I42" s="18"/>
       <c r="J42" s="18"/>
     </row>
-    <row r="43" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="9:10">
       <c r="I43" s="18"/>
       <c r="J43" s="18"/>
     </row>
-    <row r="44" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="9:10">
       <c r="I44" s="18"/>
       <c r="J44" s="18"/>
     </row>
-    <row r="45" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="9:10">
       <c r="I45" s="18"/>
       <c r="J45" s="18"/>
     </row>
-    <row r="46" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="9:10">
       <c r="I46" s="18"/>
       <c r="J46" s="18"/>
     </row>
-    <row r="47" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="9:10">
       <c r="I47" s="18"/>
       <c r="J47" s="18"/>
     </row>
-    <row r="48" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="9:10">
       <c r="I48" s="18"/>
       <c r="J48" s="18"/>
     </row>
-    <row r="49" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="9:10">
       <c r="I49" s="18"/>
       <c r="J49" s="18"/>
     </row>
-    <row r="50" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="9:10">
       <c r="I50" s="18"/>
       <c r="J50" s="18"/>
     </row>
-    <row r="51" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="9:10">
       <c r="I51" s="18"/>
       <c r="J51" s="18"/>
     </row>
-    <row r="52" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="9:10">
       <c r="I52" s="18"/>
       <c r="J52" s="18"/>
     </row>
-    <row r="53" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="9:10">
       <c r="I53" s="18"/>
       <c r="J53" s="18"/>
     </row>
-    <row r="54" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="9:10">
       <c r="I54" s="18"/>
       <c r="J54" s="18"/>
     </row>
-    <row r="55" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="9:10">
       <c r="I55" s="18"/>
       <c r="J55" s="18"/>
     </row>
-    <row r="56" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="9:10">
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
     </row>
-    <row r="57" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="9:10">
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
     </row>
-    <row r="58" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="9:10">
       <c r="I58" s="18"/>
       <c r="J58" s="18"/>
     </row>
-    <row r="59" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="9:10">
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
     </row>
-    <row r="60" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="9:10">
       <c r="I60" s="18"/>
       <c r="J60" s="18"/>
     </row>
-    <row r="61" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="9:10">
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
     </row>
-    <row r="62" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="9:10">
       <c r="I62" s="18"/>
       <c r="J62" s="18"/>
     </row>
-    <row r="63" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="9:10">
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
     </row>
-    <row r="64" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="9:10">
       <c r="I64" s="18"/>
       <c r="J64" s="18"/>
     </row>
-    <row r="65" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="9:10">
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
     </row>
-    <row r="66" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="9:10">
       <c r="I66" s="18"/>
       <c r="J66" s="18"/>
     </row>
-    <row r="67" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="9:10">
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
     </row>
-    <row r="68" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="9:10">
       <c r="I68" s="18"/>
       <c r="J68" s="18"/>
     </row>
-    <row r="69" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="9:10">
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
     </row>
-    <row r="70" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="9:10">
       <c r="I70" s="18"/>
       <c r="J70" s="18"/>
     </row>
-    <row r="71" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="9:10">
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
     </row>
-    <row r="72" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="9:10">
       <c r="I72" s="18"/>
       <c r="J72" s="18"/>
     </row>
-    <row r="73" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="9:10">
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
     </row>
-    <row r="74" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="9:10">
       <c r="I74" s="18"/>
       <c r="J74" s="18"/>
     </row>
-    <row r="75" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="9:10">
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
     </row>
-    <row r="76" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="9:10">
       <c r="I76" s="18"/>
       <c r="J76" s="18"/>
     </row>
-    <row r="77" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="9:10">
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
     </row>
-    <row r="78" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="9:10">
       <c r="I78" s="18"/>
       <c r="J78" s="18"/>
     </row>
-    <row r="79" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="9:10">
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
     </row>
-    <row r="80" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="9:10">
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
     </row>
-    <row r="81" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="9:10">
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
     </row>
-    <row r="82" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="9:10">
       <c r="I82" s="18"/>
       <c r="J82" s="18"/>
     </row>
-    <row r="83" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="9:10">
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
     </row>
-    <row r="84" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="9:10">
       <c r="I84" s="18"/>
       <c r="J84" s="18"/>
     </row>
-    <row r="85" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="9:10">
       <c r="I85" s="18"/>
       <c r="J85" s="18"/>
     </row>
-    <row r="86" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="9:10">
       <c r="I86" s="18"/>
       <c r="J86" s="18"/>
     </row>
-    <row r="87" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="9:10">
       <c r="I87" s="18"/>
       <c r="J87" s="18"/>
     </row>
-    <row r="88" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="9:10">
       <c r="I88" s="18"/>
       <c r="J88" s="18"/>
     </row>
-    <row r="89" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="9:10">
       <c r="I89" s="18"/>
       <c r="J89" s="18"/>
     </row>
-    <row r="90" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="9:10">
       <c r="I90" s="18"/>
       <c r="J90" s="18"/>
     </row>
-    <row r="91" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="9:10">
       <c r="I91" s="18"/>
       <c r="J91" s="18"/>
     </row>
-    <row r="92" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="9:10">
       <c r="I92" s="18"/>
       <c r="J92" s="18"/>
     </row>
-    <row r="93" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="9:10">
       <c r="I93" s="18"/>
       <c r="J93" s="18"/>
     </row>
-    <row r="94" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="9:10">
       <c r="I94" s="18"/>
       <c r="J94" s="18"/>
     </row>
-    <row r="95" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="9:10">
       <c r="I95" s="18"/>
       <c r="J95" s="18"/>
     </row>
-    <row r="96" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="9:10">
       <c r="I96" s="18"/>
       <c r="J96" s="18"/>
     </row>
-    <row r="97" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="9:10">
       <c r="I97" s="18"/>
       <c r="J97" s="18"/>
     </row>
-    <row r="98" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="9:10">
       <c r="I98" s="18"/>
       <c r="J98" s="18"/>
     </row>
-    <row r="99" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="9:10">
       <c r="I99" s="18"/>
       <c r="J99" s="18"/>
     </row>
-    <row r="100" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="9:10">
       <c r="I100" s="18"/>
       <c r="J100" s="18"/>
     </row>
-    <row r="101" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="9:10">
       <c r="I101" s="18"/>
       <c r="J101" s="18"/>
     </row>
-    <row r="102" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="9:10">
       <c r="I102" s="18"/>
       <c r="J102" s="18"/>
     </row>
-    <row r="103" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="9:10">
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
     </row>
-    <row r="104" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="9:10">
       <c r="I104" s="18"/>
       <c r="J104" s="18"/>
     </row>
-    <row r="105" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="9:10">
       <c r="I105" s="18"/>
       <c r="J105" s="18"/>
     </row>
-    <row r="106" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="9:10">
       <c r="I106" s="18"/>
       <c r="J106" s="18"/>
     </row>
-    <row r="107" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="9:10">
       <c r="I107" s="18"/>
       <c r="J107" s="18"/>
     </row>
-    <row r="108" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="9:10">
       <c r="I108" s="18"/>
       <c r="J108" s="18"/>
     </row>
-    <row r="109" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="9:10">
       <c r="I109" s="18"/>
       <c r="J109" s="18"/>
     </row>
-    <row r="110" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="9:10">
       <c r="I110" s="18"/>
       <c r="J110" s="18"/>
     </row>
-    <row r="111" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="9:10">
       <c r="I111" s="18"/>
       <c r="J111" s="18"/>
     </row>
-    <row r="112" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="9:10">
       <c r="I112" s="18"/>
       <c r="J112" s="18"/>
     </row>
-    <row r="113" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="9:10">
       <c r="I113" s="18"/>
       <c r="J113" s="18"/>
     </row>
-    <row r="114" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="9:10">
       <c r="I114" s="18"/>
       <c r="J114" s="18"/>
     </row>
-    <row r="115" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="9:10">
       <c r="I115" s="18"/>
       <c r="J115" s="18"/>
     </row>
-    <row r="116" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="9:10">
       <c r="I116" s="18"/>
       <c r="J116" s="18"/>
     </row>
-    <row r="117" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="9:10">
       <c r="I117" s="18"/>
       <c r="J117" s="18"/>
     </row>
-    <row r="118" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="9:10">
       <c r="I118" s="18"/>
       <c r="J118" s="18"/>
     </row>
-    <row r="119" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="9:10">
       <c r="I119" s="18"/>
       <c r="J119" s="18"/>
     </row>
-    <row r="120" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="9:10">
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
     </row>
-    <row r="121" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="9:10">
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
     </row>
-    <row r="122" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="9:10">
       <c r="I122" s="18"/>
       <c r="J122" s="18"/>
     </row>
-    <row r="123" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="9:10">
       <c r="I123" s="18"/>
       <c r="J123" s="18"/>
     </row>
-    <row r="124" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="9:10">
       <c r="I124" s="18"/>
       <c r="J124" s="18"/>
     </row>
-    <row r="125" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="9:10">
       <c r="I125" s="18"/>
       <c r="J125" s="18"/>
     </row>
-    <row r="126" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="9:10">
       <c r="I126" s="18"/>
       <c r="J126" s="18"/>
     </row>
-    <row r="127" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="9:10">
       <c r="I127" s="18"/>
       <c r="J127" s="18"/>
     </row>
-    <row r="128" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="9:10">
       <c r="I128" s="18"/>
       <c r="J128" s="18"/>
     </row>
-    <row r="129" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="9:10">
       <c r="I129" s="18"/>
       <c r="J129" s="18"/>
     </row>
-    <row r="130" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="9:10">
       <c r="I130" s="18"/>
       <c r="J130" s="18"/>
     </row>
-    <row r="131" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="9:10">
       <c r="I131" s="18"/>
       <c r="J131" s="18"/>
     </row>
-    <row r="132" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="9:10">
       <c r="I132" s="18"/>
       <c r="J132" s="18"/>
     </row>
-    <row r="133" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="9:10">
       <c r="I133" s="18"/>
       <c r="J133" s="18"/>
     </row>
-    <row r="134" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="9:10">
       <c r="I134" s="18"/>
       <c r="J134" s="18"/>
     </row>
-    <row r="135" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="9:10">
       <c r="I135" s="18"/>
       <c r="J135" s="18"/>
     </row>
-    <row r="136" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="9:10">
       <c r="I136" s="18"/>
       <c r="J136" s="18"/>
     </row>
-    <row r="137" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="9:10">
       <c r="I137" s="18"/>
       <c r="J137" s="18"/>
     </row>
-    <row r="138" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="9:10">
       <c r="I138" s="18"/>
       <c r="J138" s="18"/>
     </row>
-    <row r="139" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="9:10">
       <c r="I139" s="18"/>
       <c r="J139" s="18"/>
     </row>
-    <row r="140" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="9:10">
       <c r="I140" s="18"/>
       <c r="J140" s="18"/>
     </row>
-    <row r="141" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="9:10">
       <c r="I141" s="18"/>
       <c r="J141" s="18"/>
     </row>
-    <row r="142" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="9:10">
       <c r="I142" s="18"/>
       <c r="J142" s="18"/>
     </row>
-    <row r="143" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="9:10">
       <c r="I143" s="18"/>
       <c r="J143" s="18"/>
     </row>
-    <row r="144" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="9:10">
       <c r="I144" s="18"/>
       <c r="J144" s="18"/>
     </row>
-    <row r="145" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="9:10">
       <c r="I145" s="18"/>
       <c r="J145" s="18"/>
     </row>
-    <row r="146" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="9:10">
       <c r="I146" s="18"/>
       <c r="J146" s="18"/>
     </row>
-    <row r="147" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="9:10">
       <c r="I147" s="18"/>
       <c r="J147" s="18"/>
     </row>
-    <row r="148" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="9:10">
       <c r="I148" s="18"/>
       <c r="J148" s="18"/>
     </row>
-    <row r="149" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="9:10">
       <c r="I149" s="18"/>
       <c r="J149" s="18"/>
     </row>
-    <row r="150" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="9:10">
       <c r="I150" s="18"/>
       <c r="J150" s="18"/>
     </row>
-    <row r="151" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="9:10">
       <c r="I151" s="18"/>
       <c r="J151" s="18"/>
     </row>
-    <row r="152" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="9:10">
       <c r="I152" s="18"/>
       <c r="J152" s="18"/>
     </row>
-    <row r="153" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="9:10">
       <c r="I153" s="18"/>
       <c r="J153" s="18"/>
     </row>
-    <row r="154" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="9:10">
       <c r="I154" s="18"/>
       <c r="J154" s="18"/>
     </row>
-    <row r="155" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="9:10">
       <c r="I155" s="18"/>
       <c r="J155" s="18"/>
     </row>
-    <row r="156" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="9:10">
       <c r="I156" s="18"/>
       <c r="J156" s="18"/>
     </row>
-    <row r="157" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="9:10">
       <c r="I157" s="18"/>
       <c r="J157" s="18"/>
     </row>
-    <row r="158" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="9:10">
       <c r="I158" s="18"/>
       <c r="J158" s="18"/>
     </row>
-    <row r="159" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="9:10">
       <c r="I159" s="18"/>
       <c r="J159" s="18"/>
     </row>
-    <row r="160" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="9:10">
       <c r="I160" s="18"/>
       <c r="J160" s="18"/>
     </row>
-    <row r="161" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="9:10">
       <c r="I161" s="18"/>
       <c r="J161" s="18"/>
     </row>
-    <row r="162" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="9:10">
       <c r="I162" s="18"/>
       <c r="J162" s="18"/>
     </row>
-    <row r="163" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="9:10">
       <c r="I163" s="18"/>
       <c r="J163" s="18"/>
     </row>
-    <row r="164" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="9:10">
       <c r="I164" s="18"/>
       <c r="J164" s="18"/>
     </row>
-    <row r="165" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="9:10">
       <c r="I165" s="18"/>
       <c r="J165" s="18"/>
     </row>
-    <row r="166" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="9:10">
       <c r="I166" s="18"/>
       <c r="J166" s="18"/>
     </row>
-    <row r="167" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="9:10">
       <c r="I167" s="18"/>
       <c r="J167" s="18"/>
     </row>
-    <row r="168" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="9:10">
       <c r="I168" s="18"/>
       <c r="J168" s="18"/>
     </row>
-    <row r="169" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="9:10">
       <c r="I169" s="18"/>
       <c r="J169" s="18"/>
     </row>
-    <row r="170" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="9:10">
       <c r="I170" s="18"/>
       <c r="J170" s="18"/>
     </row>
-    <row r="171" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="9:10">
       <c r="I171" s="18"/>
       <c r="J171" s="18"/>
     </row>
-    <row r="172" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="9:10">
       <c r="I172" s="18"/>
       <c r="J172" s="18"/>
     </row>
-    <row r="173" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="9:10">
       <c r="I173" s="18"/>
       <c r="J173" s="18"/>
     </row>
-    <row r="174" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="9:10">
       <c r="I174" s="18"/>
       <c r="J174" s="18"/>
     </row>
-    <row r="175" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="9:10">
       <c r="I175" s="18"/>
       <c r="J175" s="18"/>
     </row>
-    <row r="176" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="9:10">
       <c r="I176" s="18"/>
       <c r="J176" s="18"/>
     </row>
-    <row r="177" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="9:10">
       <c r="I177" s="18"/>
       <c r="J177" s="18"/>
     </row>
-    <row r="178" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="9:10">
       <c r="I178" s="18"/>
       <c r="J178" s="18"/>
     </row>
-    <row r="179" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="9:10">
       <c r="I179" s="18"/>
       <c r="J179" s="18"/>
     </row>
-    <row r="180" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="9:10">
       <c r="I180" s="18"/>
       <c r="J180" s="18"/>
     </row>
-    <row r="181" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="9:10">
       <c r="I181" s="18"/>
       <c r="J181" s="18"/>
     </row>
-    <row r="182" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="9:10">
       <c r="I182" s="18"/>
       <c r="J182" s="18"/>
     </row>
-    <row r="183" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="9:10">
       <c r="I183" s="18"/>
       <c r="J183" s="18"/>
     </row>
-    <row r="184" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="9:10">
       <c r="I184" s="18"/>
       <c r="J184" s="18"/>
     </row>
-    <row r="185" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="9:10">
       <c r="I185" s="18"/>
       <c r="J185" s="18"/>
     </row>
-    <row r="186" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="9:10">
       <c r="I186" s="18"/>
       <c r="J186" s="18"/>
     </row>
-    <row r="187" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="9:10">
       <c r="I187" s="18"/>
       <c r="J187" s="18"/>
     </row>
-    <row r="188" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="9:10">
       <c r="I188" s="18"/>
       <c r="J188" s="18"/>
     </row>
-    <row r="189" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="9:10">
       <c r="I189" s="18"/>
       <c r="J189" s="18"/>
     </row>
-    <row r="190" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="9:10">
       <c r="I190" s="18"/>
       <c r="J190" s="18"/>
     </row>
-    <row r="191" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="9:10">
       <c r="I191" s="18"/>
       <c r="J191" s="18"/>
     </row>
-    <row r="192" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="9:10">
       <c r="I192" s="18"/>
       <c r="J192" s="18"/>
     </row>
-    <row r="193" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="9:10">
       <c r="I193" s="18"/>
       <c r="J193" s="18"/>
     </row>
-    <row r="194" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="9:10">
       <c r="I194" s="18"/>
       <c r="J194" s="18"/>
     </row>
-    <row r="195" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="9:10">
       <c r="I195" s="18"/>
       <c r="J195" s="18"/>
     </row>
-    <row r="196" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="9:10">
       <c r="I196" s="18"/>
       <c r="J196" s="18"/>
     </row>
-    <row r="197" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="9:10">
       <c r="I197" s="18"/>
       <c r="J197" s="18"/>
     </row>
-    <row r="198" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="9:10">
       <c r="I198" s="18"/>
       <c r="J198" s="18"/>
     </row>
-    <row r="199" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="9:10">
       <c r="I199" s="18"/>
       <c r="J199" s="18"/>
     </row>
-    <row r="200" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="9:10">
       <c r="I200" s="18"/>
       <c r="J200" s="18"/>
     </row>
-    <row r="201" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="9:10">
       <c r="I201" s="18"/>
       <c r="J201" s="18"/>
     </row>
-    <row r="202" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="9:10">
       <c r="I202" s="18"/>
       <c r="J202" s="18"/>
     </row>
-    <row r="203" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="9:10">
       <c r="I203" s="18"/>
       <c r="J203" s="18"/>
     </row>
-    <row r="204" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="9:10">
       <c r="I204" s="18"/>
       <c r="J204" s="18"/>
     </row>
-    <row r="205" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="9:10">
       <c r="I205" s="18"/>
       <c r="J205" s="18"/>
     </row>
-    <row r="206" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="9:10">
       <c r="I206" s="18"/>
       <c r="J206" s="18"/>
     </row>
-    <row r="207" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="9:10">
       <c r="I207" s="18"/>
       <c r="J207" s="18"/>
     </row>
-    <row r="208" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="9:10">
       <c r="I208" s="18"/>
       <c r="J208" s="18"/>
     </row>
-    <row r="209" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="9:10">
       <c r="I209" s="18"/>
       <c r="J209" s="18"/>
     </row>
-    <row r="210" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="9:10">
       <c r="I210" s="18"/>
       <c r="J210" s="18"/>
     </row>
-    <row r="211" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="9:10">
       <c r="I211" s="18"/>
       <c r="J211" s="18"/>
     </row>
-    <row r="212" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="9:10">
       <c r="I212" s="18"/>
       <c r="J212" s="18"/>
     </row>
-    <row r="213" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="9:10">
       <c r="I213" s="18"/>
       <c r="J213" s="18"/>
     </row>
-    <row r="214" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="9:10">
       <c r="I214" s="18"/>
       <c r="J214" s="18"/>
     </row>
-    <row r="215" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="9:10">
       <c r="I215" s="18"/>
       <c r="J215" s="18"/>
     </row>
-    <row r="216" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="9:10">
       <c r="I216" s="18"/>
       <c r="J216" s="18"/>
     </row>
-    <row r="217" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="9:10">
       <c r="I217" s="18"/>
       <c r="J217" s="18"/>
     </row>
-    <row r="218" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="9:10">
       <c r="I218" s="18"/>
       <c r="J218" s="18"/>
     </row>
-    <row r="219" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="9:10">
       <c r="I219" s="18"/>
       <c r="J219" s="18"/>
     </row>
-    <row r="220" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="9:10">
       <c r="I220" s="18"/>
       <c r="J220" s="18"/>
     </row>
-    <row r="221" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="9:10">
       <c r="I221" s="18"/>
       <c r="J221" s="18"/>
     </row>
-    <row r="222" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="9:10">
       <c r="I222" s="18"/>
       <c r="J222" s="18"/>
     </row>
-    <row r="223" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="9:10">
       <c r="I223" s="18"/>
       <c r="J223" s="18"/>
     </row>
-    <row r="224" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="9:10">
       <c r="I224" s="18"/>
       <c r="J224" s="18"/>
     </row>
-    <row r="225" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="9:10">
       <c r="I225" s="18"/>
       <c r="J225" s="18"/>
     </row>
-    <row r="226" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="9:10">
       <c r="I226" s="18"/>
       <c r="J226" s="18"/>
     </row>
-    <row r="227" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="9:10">
       <c r="I227" s="18"/>
       <c r="J227" s="18"/>
     </row>
-    <row r="228" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="9:10">
       <c r="I228" s="18"/>
       <c r="J228" s="18"/>
     </row>
-    <row r="229" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="9:10">
       <c r="I229" s="18"/>
       <c r="J229" s="18"/>
     </row>
-    <row r="230" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="9:10">
       <c r="I230" s="18"/>
       <c r="J230" s="18"/>
     </row>
-    <row r="231" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="9:10">
       <c r="I231" s="18"/>
       <c r="J231" s="18"/>
     </row>
-    <row r="232" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="9:10">
       <c r="I232" s="18"/>
       <c r="J232" s="18"/>
     </row>
-    <row r="233" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="9:10">
       <c r="I233" s="18"/>
       <c r="J233" s="18"/>
     </row>
-    <row r="234" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="9:10">
       <c r="I234" s="18"/>
       <c r="J234" s="18"/>
     </row>
-    <row r="235" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="9:10">
       <c r="I235" s="18"/>
       <c r="J235" s="18"/>
     </row>
-    <row r="236" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="9:10">
       <c r="I236" s="18"/>
       <c r="J236" s="18"/>
     </row>
-    <row r="237" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="9:10">
       <c r="I237" s="18"/>
       <c r="J237" s="18"/>
     </row>
-    <row r="238" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="9:10">
       <c r="I238" s="18"/>
       <c r="J238" s="18"/>
     </row>
-    <row r="239" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="9:10">
       <c r="I239" s="18"/>
       <c r="J239" s="18"/>
     </row>
-    <row r="240" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="9:10">
       <c r="I240" s="18"/>
       <c r="J240" s="18"/>
     </row>
-    <row r="241" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="9:10">
       <c r="I241" s="18"/>
       <c r="J241" s="18"/>
     </row>
-    <row r="242" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="9:10">
       <c r="I242" s="18"/>
       <c r="J242" s="18"/>
     </row>
-    <row r="243" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="9:10">
       <c r="I243" s="18"/>
       <c r="J243" s="18"/>
     </row>
-    <row r="244" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="9:10">
       <c r="I244" s="18"/>
       <c r="J244" s="18"/>
     </row>
-    <row r="245" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="9:10">
       <c r="I245" s="18"/>
       <c r="J245" s="18"/>
     </row>
-    <row r="246" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="9:10">
       <c r="I246" s="18"/>
       <c r="J246" s="18"/>
     </row>
-    <row r="247" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="9:10">
       <c r="I247" s="18"/>
       <c r="J247" s="18"/>
     </row>
-    <row r="248" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="9:10">
       <c r="I248" s="18"/>
       <c r="J248" s="18"/>
     </row>
-    <row r="249" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="9:10">
       <c r="I249" s="18"/>
       <c r="J249" s="18"/>
     </row>
-    <row r="250" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="9:10">
       <c r="I250" s="18"/>
       <c r="J250" s="18"/>
     </row>
-    <row r="251" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="9:10">
       <c r="I251" s="18"/>
       <c r="J251" s="18"/>
     </row>
-    <row r="252" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="9:10">
       <c r="I252" s="18"/>
       <c r="J252" s="18"/>
     </row>
-    <row r="253" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="9:10">
       <c r="I253" s="18"/>
       <c r="J253" s="18"/>
     </row>
-    <row r="254" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="9:10">
       <c r="I254" s="18"/>
       <c r="J254" s="18"/>
     </row>
-    <row r="255" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="9:10">
       <c r="I255" s="18"/>
       <c r="J255" s="18"/>
     </row>
-    <row r="256" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="9:10">
       <c r="I256" s="18"/>
       <c r="J256" s="18"/>
     </row>
-    <row r="257" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="257" spans="9:10">
       <c r="I257" s="18"/>
       <c r="J257" s="18"/>
     </row>
-    <row r="258" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="258" spans="9:10">
       <c r="I258" s="18"/>
       <c r="J258" s="18"/>
     </row>
-    <row r="259" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="259" spans="9:10">
       <c r="I259" s="18"/>
       <c r="J259" s="18"/>
     </row>
-    <row r="260" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="260" spans="9:10">
       <c r="I260" s="18"/>
       <c r="J260" s="18"/>
     </row>
-    <row r="261" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="261" spans="9:10">
       <c r="I261" s="18"/>
       <c r="J261" s="18"/>
     </row>
-    <row r="262" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="262" spans="9:10">
       <c r="I262" s="18"/>
       <c r="J262" s="18"/>
     </row>
-    <row r="263" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="263" spans="9:10">
       <c r="I263" s="18"/>
       <c r="J263" s="18"/>
     </row>
-    <row r="264" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="264" spans="9:10">
       <c r="I264" s="18"/>
       <c r="J264" s="18"/>
     </row>
-    <row r="265" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="265" spans="9:10">
       <c r="I265" s="18"/>
       <c r="J265" s="18"/>
     </row>
-    <row r="266" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="266" spans="9:10">
       <c r="I266" s="18"/>
       <c r="J266" s="18"/>
     </row>
-    <row r="267" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="267" spans="9:10">
       <c r="I267" s="18"/>
       <c r="J267" s="18"/>
     </row>
-    <row r="268" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="268" spans="9:10">
       <c r="I268" s="18"/>
       <c r="J268" s="18"/>
     </row>
-    <row r="269" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="269" spans="9:10">
       <c r="I269" s="18"/>
       <c r="J269" s="18"/>
     </row>
-    <row r="270" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="270" spans="9:10">
       <c r="I270" s="18"/>
       <c r="J270" s="18"/>
     </row>
-    <row r="271" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="271" spans="9:10">
       <c r="I271" s="18"/>
       <c r="J271" s="18"/>
     </row>
-    <row r="272" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="272" spans="9:10">
       <c r="I272" s="18"/>
       <c r="J272" s="18"/>
     </row>
-    <row r="273" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="273" spans="9:10">
       <c r="I273" s="18"/>
       <c r="J273" s="18"/>
     </row>
-    <row r="274" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="274" spans="9:10">
       <c r="I274" s="18"/>
       <c r="J274" s="18"/>
     </row>
-    <row r="275" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="275" spans="9:10">
       <c r="I275" s="18"/>
       <c r="J275" s="18"/>
     </row>
-    <row r="276" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="276" spans="9:10">
       <c r="I276" s="18"/>
       <c r="J276" s="18"/>
     </row>
-    <row r="277" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="277" spans="9:10">
       <c r="I277" s="18"/>
       <c r="J277" s="18"/>
     </row>
-    <row r="278" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="278" spans="9:10">
       <c r="I278" s="18"/>
       <c r="J278" s="18"/>
     </row>
-    <row r="279" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="279" spans="9:10">
       <c r="I279" s="18"/>
       <c r="J279" s="18"/>
     </row>
-    <row r="280" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="280" spans="9:10">
       <c r="I280" s="18"/>
       <c r="J280" s="18"/>
     </row>
-    <row r="281" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="281" spans="9:10">
       <c r="I281" s="18"/>
       <c r="J281" s="18"/>
     </row>
-    <row r="282" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="282" spans="9:10">
       <c r="I282" s="18"/>
       <c r="J282" s="18"/>
     </row>
-    <row r="283" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="283" spans="9:10">
       <c r="I283" s="18"/>
       <c r="J283" s="18"/>
     </row>
-    <row r="284" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="284" spans="9:10">
       <c r="I284" s="18"/>
       <c r="J284" s="18"/>
     </row>
-    <row r="285" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="285" spans="9:10">
       <c r="I285" s="18"/>
       <c r="J285" s="18"/>
     </row>
-    <row r="286" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="286" spans="9:10">
       <c r="I286" s="18"/>
       <c r="J286" s="18"/>
     </row>
-    <row r="287" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="287" spans="9:10">
       <c r="I287" s="18"/>
       <c r="J287" s="18"/>
     </row>
-    <row r="288" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="288" spans="9:10">
       <c r="I288" s="18"/>
       <c r="J288" s="18"/>
     </row>
-    <row r="289" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="289" spans="9:10">
       <c r="I289" s="18"/>
       <c r="J289" s="18"/>
     </row>
-    <row r="290" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="290" spans="9:10">
       <c r="I290" s="18"/>
       <c r="J290" s="18"/>
     </row>
-    <row r="291" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="291" spans="9:10">
       <c r="I291" s="18"/>
       <c r="J291" s="18"/>
     </row>
-    <row r="292" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="292" spans="9:10">
       <c r="I292" s="18"/>
       <c r="J292" s="18"/>
     </row>
-    <row r="293" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="293" spans="9:10">
       <c r="I293" s="18"/>
       <c r="J293" s="18"/>
     </row>
-    <row r="294" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="294" spans="9:10">
       <c r="I294" s="18"/>
       <c r="J294" s="18"/>
     </row>
-    <row r="295" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="295" spans="9:10">
       <c r="I295" s="18"/>
       <c r="J295" s="18"/>
     </row>
-    <row r="296" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="296" spans="9:10">
       <c r="I296" s="18"/>
       <c r="J296" s="18"/>
     </row>
-    <row r="297" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="297" spans="9:10">
       <c r="I297" s="18"/>
       <c r="J297" s="18"/>
     </row>
-    <row r="298" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="298" spans="9:10">
       <c r="I298" s="18"/>
       <c r="J298" s="18"/>
     </row>
-    <row r="299" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="299" spans="9:10">
       <c r="I299" s="18"/>
       <c r="J299" s="18"/>
     </row>
-    <row r="300" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="300" spans="9:10">
       <c r="I300" s="18"/>
       <c r="J300" s="18"/>
     </row>
-    <row r="301" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="301" spans="9:10">
       <c r="I301" s="18"/>
       <c r="J301" s="18"/>
     </row>
-    <row r="302" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="302" spans="9:10">
       <c r="I302" s="18"/>
       <c r="J302" s="18"/>
     </row>
-    <row r="303" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="303" spans="9:10">
       <c r="I303" s="18"/>
       <c r="J303" s="18"/>
     </row>
-    <row r="304" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="304" spans="9:10">
       <c r="I304" s="18"/>
       <c r="J304" s="18"/>
     </row>
-    <row r="305" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="305" spans="9:10">
       <c r="I305" s="18"/>
       <c r="J305" s="18"/>
     </row>
-    <row r="306" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="306" spans="9:10">
       <c r="I306" s="18"/>
       <c r="J306" s="18"/>
     </row>
-    <row r="307" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="307" spans="9:10">
       <c r="I307" s="18"/>
       <c r="J307" s="18"/>
     </row>
-    <row r="308" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="308" spans="9:10">
       <c r="I308" s="18"/>
       <c r="J308" s="18"/>
     </row>
-    <row r="309" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="309" spans="9:10">
       <c r="I309" s="18"/>
       <c r="J309" s="18"/>
     </row>
-    <row r="310" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="310" spans="9:10">
       <c r="I310" s="18"/>
       <c r="J310" s="18"/>
     </row>
-    <row r="311" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="311" spans="9:10">
       <c r="I311" s="18"/>
       <c r="J311" s="18"/>
     </row>
-    <row r="312" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="312" spans="9:10">
       <c r="I312" s="18"/>
       <c r="J312" s="18"/>
     </row>
-    <row r="313" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="313" spans="9:10">
       <c r="I313" s="18"/>
       <c r="J313" s="18"/>
     </row>
-    <row r="314" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="314" spans="9:10">
       <c r="I314" s="18"/>
       <c r="J314" s="18"/>
     </row>
-    <row r="315" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="315" spans="9:10">
       <c r="I315" s="18"/>
       <c r="J315" s="18"/>
     </row>
-    <row r="316" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="316" spans="9:10">
       <c r="I316" s="18"/>
       <c r="J316" s="18"/>
     </row>
-    <row r="317" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="317" spans="9:10">
       <c r="I317" s="18"/>
       <c r="J317" s="18"/>
     </row>
-    <row r="318" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="318" spans="9:10">
       <c r="I318" s="18"/>
       <c r="J318" s="18"/>
     </row>
-    <row r="319" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="319" spans="9:10">
       <c r="I319" s="18"/>
       <c r="J319" s="18"/>
     </row>
-    <row r="320" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="320" spans="9:10">
       <c r="I320" s="18"/>
       <c r="J320" s="18"/>
     </row>
-    <row r="321" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="321" spans="9:10">
       <c r="I321" s="18"/>
       <c r="J321" s="18"/>
     </row>
-    <row r="322" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="322" spans="9:10">
       <c r="I322" s="18"/>
       <c r="J322" s="18"/>
     </row>
-    <row r="323" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="323" spans="9:10">
       <c r="I323" s="18"/>
       <c r="J323" s="18"/>
     </row>
-    <row r="324" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="324" spans="9:10">
       <c r="I324" s="18"/>
       <c r="J324" s="18"/>
     </row>
-    <row r="325" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="325" spans="9:10">
       <c r="I325" s="18"/>
       <c r="J325" s="18"/>
     </row>
-    <row r="326" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="326" spans="9:10">
       <c r="I326" s="18"/>
       <c r="J326" s="18"/>
     </row>
-    <row r="327" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="327" spans="9:10">
       <c r="I327" s="18"/>
       <c r="J327" s="18"/>
     </row>
-    <row r="328" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="328" spans="9:10">
       <c r="I328" s="18"/>
       <c r="J328" s="18"/>
     </row>
-    <row r="329" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="329" spans="9:10">
       <c r="I329" s="18"/>
       <c r="J329" s="18"/>
     </row>
-    <row r="330" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="330" spans="9:10">
       <c r="I330" s="18"/>
       <c r="J330" s="18"/>
     </row>
-    <row r="331" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="331" spans="9:10">
       <c r="I331" s="18"/>
       <c r="J331" s="18"/>
     </row>
-    <row r="332" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="332" spans="9:10">
       <c r="I332" s="18"/>
       <c r="J332" s="18"/>
     </row>
-    <row r="333" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="333" spans="9:10">
       <c r="I333" s="18"/>
       <c r="J333" s="18"/>
     </row>
-    <row r="334" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="334" spans="9:10">
       <c r="I334" s="18"/>
       <c r="J334" s="18"/>
     </row>
-    <row r="335" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="335" spans="9:10">
       <c r="I335" s="18"/>
       <c r="J335" s="18"/>
     </row>
-    <row r="336" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="336" spans="9:10">
       <c r="I336" s="18"/>
       <c r="J336" s="18"/>
     </row>
-    <row r="337" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="337" spans="9:10">
       <c r="I337" s="18"/>
       <c r="J337" s="18"/>
     </row>
-    <row r="338" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="338" spans="9:10">
       <c r="I338" s="18"/>
       <c r="J338" s="18"/>
     </row>
-    <row r="339" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="339" spans="9:10">
       <c r="I339" s="18"/>
       <c r="J339" s="18"/>
     </row>
-    <row r="340" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="340" spans="9:10">
       <c r="I340" s="18"/>
       <c r="J340" s="18"/>
     </row>
-    <row r="341" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="341" spans="9:10">
       <c r="I341" s="18"/>
       <c r="J341" s="18"/>
     </row>
-    <row r="342" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="342" spans="9:10">
       <c r="I342" s="18"/>
       <c r="J342" s="18"/>
     </row>
-    <row r="343" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="343" spans="9:10">
       <c r="I343" s="18"/>
       <c r="J343" s="18"/>
     </row>
-    <row r="344" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="344" spans="9:10">
       <c r="I344" s="18"/>
       <c r="J344" s="18"/>
     </row>
-    <row r="345" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="345" spans="9:10">
       <c r="I345" s="18"/>
       <c r="J345" s="18"/>
     </row>
-    <row r="346" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="346" spans="9:10">
       <c r="I346" s="18"/>
       <c r="J346" s="18"/>
     </row>
-    <row r="347" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="347" spans="9:10">
       <c r="I347" s="18"/>
       <c r="J347" s="18"/>
     </row>
-    <row r="348" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="348" spans="9:10">
       <c r="I348" s="18"/>
       <c r="J348" s="18"/>
     </row>
-    <row r="349" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="349" spans="9:10">
       <c r="I349" s="18"/>
       <c r="J349" s="18"/>
     </row>
-    <row r="350" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="350" spans="9:10">
       <c r="I350" s="18"/>
       <c r="J350" s="18"/>
     </row>
-    <row r="351" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="351" spans="9:10">
       <c r="I351" s="18"/>
       <c r="J351" s="18"/>
     </row>
-    <row r="352" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="352" spans="9:10">
       <c r="I352" s="18"/>
       <c r="J352" s="18"/>
     </row>
-    <row r="353" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="353" spans="9:10">
       <c r="I353" s="18"/>
       <c r="J353" s="18"/>
     </row>
-    <row r="354" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="354" spans="9:10">
       <c r="I354" s="18"/>
       <c r="J354" s="18"/>
     </row>
-    <row r="355" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="355" spans="9:10">
       <c r="I355" s="18"/>
       <c r="J355" s="18"/>
     </row>
-    <row r="356" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="356" spans="9:10">
       <c r="I356" s="18"/>
       <c r="J356" s="18"/>
     </row>
-    <row r="357" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="357" spans="9:10">
       <c r="I357" s="18"/>
       <c r="J357" s="18"/>
     </row>
-    <row r="358" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="358" spans="9:10">
       <c r="I358" s="18"/>
       <c r="J358" s="18"/>
     </row>
-    <row r="359" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="359" spans="9:10">
       <c r="I359" s="18"/>
       <c r="J359" s="18"/>
     </row>
-    <row r="360" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="360" spans="9:10">
       <c r="I360" s="18"/>
       <c r="J360" s="18"/>
     </row>
-    <row r="361" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="361" spans="9:10">
       <c r="I361" s="18"/>
       <c r="J361" s="18"/>
     </row>
-    <row r="362" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="362" spans="9:10">
       <c r="I362" s="18"/>
       <c r="J362" s="18"/>
     </row>
-    <row r="363" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="363" spans="9:10">
       <c r="I363" s="18"/>
       <c r="J363" s="18"/>
     </row>
-    <row r="364" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="364" spans="9:10">
       <c r="I364" s="18"/>
       <c r="J364" s="18"/>
     </row>
-    <row r="365" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="365" spans="9:10">
       <c r="I365" s="18"/>
       <c r="J365" s="18"/>
     </row>
-    <row r="366" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="366" spans="9:10">
       <c r="I366" s="18"/>
       <c r="J366" s="18"/>
     </row>
-    <row r="367" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="367" spans="9:10">
       <c r="I367" s="18"/>
       <c r="J367" s="18"/>
     </row>
-    <row r="368" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="368" spans="9:10">
       <c r="I368" s="18"/>
       <c r="J368" s="18"/>
     </row>
-    <row r="369" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="369" spans="9:10">
       <c r="I369" s="18"/>
       <c r="J369" s="18"/>
     </row>
-    <row r="370" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="370" spans="9:10">
       <c r="I370" s="18"/>
       <c r="J370" s="18"/>
     </row>
-    <row r="371" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="371" spans="9:10">
       <c r="I371" s="18"/>
       <c r="J371" s="18"/>
     </row>
-    <row r="372" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="372" spans="9:10">
       <c r="I372" s="18"/>
       <c r="J372" s="18"/>
     </row>
-    <row r="373" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="373" spans="9:10">
       <c r="I373" s="18"/>
       <c r="J373" s="18"/>
     </row>
-    <row r="374" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="374" spans="9:10">
       <c r="I374" s="18"/>
       <c r="J374" s="18"/>
     </row>
-    <row r="375" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="375" spans="9:10">
       <c r="I375" s="18"/>
       <c r="J375" s="18"/>
     </row>
-    <row r="376" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="376" spans="9:10">
       <c r="I376" s="18"/>
       <c r="J376" s="18"/>
     </row>
-    <row r="377" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="377" spans="9:10">
       <c r="I377" s="18"/>
       <c r="J377" s="18"/>
     </row>
-    <row r="378" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="378" spans="9:10">
       <c r="I378" s="18"/>
       <c r="J378" s="18"/>
     </row>
-    <row r="379" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="379" spans="9:10">
       <c r="I379" s="18"/>
       <c r="J379" s="18"/>
     </row>
-    <row r="380" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="380" spans="9:10">
       <c r="I380" s="18"/>
       <c r="J380" s="18"/>
     </row>
-    <row r="381" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="381" spans="9:10">
       <c r="I381" s="18"/>
       <c r="J381" s="18"/>
     </row>
-    <row r="382" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="382" spans="9:10">
       <c r="I382" s="18"/>
       <c r="J382" s="18"/>
     </row>
-    <row r="383" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="383" spans="9:10">
       <c r="I383" s="18"/>
       <c r="J383" s="18"/>
     </row>
-    <row r="384" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="384" spans="9:10">
       <c r="I384" s="18"/>
       <c r="J384" s="18"/>
     </row>
-    <row r="385" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="385" spans="9:10">
       <c r="I385" s="18"/>
       <c r="J385" s="18"/>
     </row>
-    <row r="386" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="386" spans="9:10">
       <c r="I386" s="18"/>
       <c r="J386" s="18"/>
     </row>
-    <row r="387" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="387" spans="9:10">
       <c r="I387" s="18"/>
       <c r="J387" s="18"/>
     </row>
-    <row r="388" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="388" spans="9:10">
       <c r="I388" s="18"/>
       <c r="J388" s="18"/>
     </row>
-    <row r="389" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="389" spans="9:10">
       <c r="I389" s="18"/>
       <c r="J389" s="18"/>
     </row>
-    <row r="390" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="390" spans="9:10">
       <c r="I390" s="18"/>
       <c r="J390" s="18"/>
     </row>
-    <row r="391" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="391" spans="9:10">
       <c r="I391" s="18"/>
       <c r="J391" s="18"/>
     </row>
-    <row r="392" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="392" spans="9:10">
       <c r="I392" s="18"/>
       <c r="J392" s="18"/>
     </row>
-    <row r="393" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="393" spans="9:10">
       <c r="I393" s="18"/>
       <c r="J393" s="18"/>
     </row>
-    <row r="394" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="394" spans="9:10">
       <c r="I394" s="18"/>
       <c r="J394" s="18"/>
     </row>
-    <row r="395" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="395" spans="9:10">
       <c r="I395" s="18"/>
       <c r="J395" s="18"/>
     </row>
-    <row r="396" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="396" spans="9:10">
       <c r="I396" s="18"/>
       <c r="J396" s="18"/>
     </row>
-    <row r="397" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="397" spans="9:10">
       <c r="I397" s="18"/>
       <c r="J397" s="18"/>
     </row>
-    <row r="398" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="398" spans="9:10">
       <c r="I398" s="18"/>
       <c r="J398" s="18"/>
     </row>
-    <row r="399" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="399" spans="9:10">
       <c r="I399" s="18"/>
       <c r="J399" s="18"/>
     </row>
-    <row r="400" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="400" spans="9:10">
       <c r="I400" s="18"/>
       <c r="J400" s="18"/>
     </row>
-    <row r="401" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="401" spans="9:10">
       <c r="I401" s="18"/>
       <c r="J401" s="18"/>
     </row>
-    <row r="402" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="402" spans="9:10">
       <c r="I402" s="18"/>
       <c r="J402" s="18"/>
     </row>
-    <row r="403" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="403" spans="9:10">
       <c r="I403" s="18"/>
       <c r="J403" s="18"/>
     </row>
-    <row r="404" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="404" spans="9:10">
       <c r="I404" s="18"/>
       <c r="J404" s="18"/>
     </row>
-    <row r="405" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="405" spans="9:10">
       <c r="I405" s="18"/>
       <c r="J405" s="18"/>
     </row>
-    <row r="406" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="406" spans="9:10">
       <c r="I406" s="18"/>
       <c r="J406" s="18"/>
     </row>
-    <row r="407" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="407" spans="9:10">
       <c r="I407" s="18"/>
       <c r="J407" s="18"/>
     </row>
-    <row r="408" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="408" spans="9:10">
       <c r="I408" s="18"/>
       <c r="J408" s="18"/>
     </row>
-    <row r="409" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="409" spans="9:10">
       <c r="I409" s="18"/>
       <c r="J409" s="18"/>
     </row>
-    <row r="410" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="410" spans="9:10">
       <c r="I410" s="18"/>
       <c r="J410" s="18"/>
     </row>
-    <row r="411" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="411" spans="9:10">
       <c r="I411" s="18"/>
       <c r="J411" s="18"/>
     </row>
-    <row r="412" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="412" spans="9:10">
       <c r="I412" s="18"/>
       <c r="J412" s="18"/>
     </row>
-    <row r="413" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="413" spans="9:10">
       <c r="I413" s="18"/>
       <c r="J413" s="18"/>
     </row>
-    <row r="414" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="414" spans="9:10">
       <c r="I414" s="18"/>
       <c r="J414" s="18"/>
     </row>
-    <row r="415" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="415" spans="9:10">
       <c r="I415" s="18"/>
       <c r="J415" s="18"/>
     </row>
-    <row r="416" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="416" spans="9:10">
       <c r="I416" s="18"/>
       <c r="J416" s="18"/>
     </row>
-    <row r="417" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="417" spans="9:10">
       <c r="I417" s="18"/>
       <c r="J417" s="18"/>
     </row>
-    <row r="418" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="418" spans="9:10">
       <c r="I418" s="18"/>
       <c r="J418" s="18"/>
     </row>
-    <row r="419" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="419" spans="9:10">
       <c r="I419" s="18"/>
       <c r="J419" s="18"/>
     </row>
-    <row r="420" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="420" spans="9:10">
       <c r="I420" s="18"/>
       <c r="J420" s="18"/>
     </row>
-    <row r="421" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="421" spans="9:10">
       <c r="I421" s="18"/>
       <c r="J421" s="18"/>
     </row>
-    <row r="422" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="422" spans="9:10">
       <c r="I422" s="18"/>
       <c r="J422" s="18"/>
     </row>
-    <row r="423" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="423" spans="9:10">
       <c r="I423" s="18"/>
       <c r="J423" s="18"/>
     </row>
-    <row r="424" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="424" spans="9:10">
       <c r="I424" s="18"/>
       <c r="J424" s="18"/>
     </row>
-    <row r="425" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="425" spans="9:10">
       <c r="I425" s="18"/>
       <c r="J425" s="18"/>
     </row>
-    <row r="426" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="426" spans="9:10">
       <c r="I426" s="18"/>
       <c r="J426" s="18"/>
     </row>
-    <row r="427" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="427" spans="9:10">
       <c r="I427" s="18"/>
       <c r="J427" s="18"/>
     </row>
-    <row r="428" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="428" spans="9:10">
       <c r="I428" s="18"/>
       <c r="J428" s="18"/>
     </row>
-    <row r="429" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="429" spans="9:10">
       <c r="I429" s="18"/>
       <c r="J429" s="18"/>
     </row>
-    <row r="430" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="430" spans="9:10">
       <c r="I430" s="18"/>
       <c r="J430" s="18"/>
     </row>
-    <row r="431" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="431" spans="9:10">
       <c r="I431" s="18"/>
       <c r="J431" s="18"/>
     </row>
-    <row r="432" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="432" spans="9:10">
       <c r="I432" s="18"/>
       <c r="J432" s="18"/>
     </row>
-    <row r="433" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="433" spans="9:10">
       <c r="I433" s="18"/>
       <c r="J433" s="18"/>
     </row>
-    <row r="434" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="434" spans="9:10">
       <c r="I434" s="18"/>
       <c r="J434" s="18"/>
     </row>
-    <row r="435" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="435" spans="9:10">
       <c r="I435" s="18"/>
       <c r="J435" s="18"/>
     </row>
-    <row r="436" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="436" spans="9:10">
       <c r="I436" s="18"/>
       <c r="J436" s="18"/>
     </row>
-    <row r="437" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="437" spans="9:10">
       <c r="I437" s="18"/>
       <c r="J437" s="18"/>
     </row>
-    <row r="438" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="438" spans="9:10">
       <c r="I438" s="18"/>
       <c r="J438" s="18"/>
     </row>
-    <row r="439" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="439" spans="9:10">
       <c r="I439" s="18"/>
       <c r="J439" s="18"/>
     </row>
-    <row r="440" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="440" spans="9:10">
       <c r="I440" s="18"/>
       <c r="J440" s="18"/>
     </row>
-    <row r="441" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="441" spans="9:10">
       <c r="I441" s="18"/>
       <c r="J441" s="18"/>
     </row>
-    <row r="442" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="442" spans="9:10">
       <c r="I442" s="18"/>
       <c r="J442" s="18"/>
     </row>
-    <row r="443" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="443" spans="9:10">
       <c r="I443" s="18"/>
       <c r="J443" s="18"/>
     </row>
-    <row r="444" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="444" spans="9:10">
       <c r="I444" s="18"/>
       <c r="J444" s="18"/>
     </row>
-    <row r="445" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="445" spans="9:10">
       <c r="I445" s="18"/>
       <c r="J445" s="18"/>
     </row>
-    <row r="446" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="446" spans="9:10">
       <c r="I446" s="18"/>
       <c r="J446" s="18"/>
     </row>
-    <row r="447" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="447" spans="9:10">
       <c r="I447" s="18"/>
       <c r="J447" s="18"/>
     </row>
-    <row r="448" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="448" spans="9:10">
       <c r="I448" s="18"/>
       <c r="J448" s="18"/>
     </row>
-    <row r="449" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="449" spans="9:10">
       <c r="I449" s="18"/>
       <c r="J449" s="18"/>
     </row>
-    <row r="450" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="450" spans="9:10">
       <c r="I450" s="18"/>
       <c r="J450" s="18"/>
     </row>
-    <row r="451" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="451" spans="9:10">
       <c r="I451" s="18"/>
       <c r="J451" s="18"/>
     </row>
-    <row r="452" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="452" spans="9:10">
       <c r="I452" s="18"/>
       <c r="J452" s="18"/>
     </row>
-    <row r="453" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="453" spans="9:10">
       <c r="I453" s="18"/>
       <c r="J453" s="18"/>
     </row>
-    <row r="454" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="454" spans="9:10">
       <c r="I454" s="18"/>
       <c r="J454" s="18"/>
     </row>
-    <row r="455" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="455" spans="9:10">
       <c r="I455" s="18"/>
       <c r="J455" s="18"/>
     </row>
-    <row r="456" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="456" spans="9:10">
       <c r="I456" s="18"/>
       <c r="J456" s="18"/>
     </row>
-    <row r="457" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="457" spans="9:10">
       <c r="I457" s="18"/>
       <c r="J457" s="18"/>
     </row>
-    <row r="458" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="458" spans="9:10">
       <c r="I458" s="18"/>
       <c r="J458" s="18"/>
     </row>
-    <row r="459" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="459" spans="9:10">
       <c r="I459" s="18"/>
       <c r="J459" s="18"/>
     </row>
-    <row r="460" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="460" spans="9:10">
       <c r="I460" s="18"/>
       <c r="J460" s="18"/>
     </row>
-    <row r="461" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="461" spans="9:10">
       <c r="I461" s="18"/>
       <c r="J461" s="18"/>
     </row>
-    <row r="462" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="462" spans="9:10">
       <c r="I462" s="18"/>
       <c r="J462" s="18"/>
     </row>
-    <row r="463" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="463" spans="9:10">
       <c r="I463" s="18"/>
       <c r="J463" s="18"/>
     </row>
-    <row r="464" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="464" spans="9:10">
       <c r="I464" s="18"/>
       <c r="J464" s="18"/>
     </row>
-    <row r="465" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="465" spans="9:10">
       <c r="I465" s="18"/>
       <c r="J465" s="18"/>
     </row>
-    <row r="466" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="466" spans="9:10">
       <c r="I466" s="18"/>
       <c r="J466" s="18"/>
     </row>
-    <row r="467" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="467" spans="9:10">
       <c r="I467" s="18"/>
       <c r="J467" s="18"/>
     </row>
-    <row r="468" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="468" spans="9:10">
       <c r="I468" s="18"/>
       <c r="J468" s="18"/>
     </row>
-    <row r="469" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="469" spans="9:10">
       <c r="I469" s="18"/>
       <c r="J469" s="18"/>
     </row>
-    <row r="470" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="470" spans="9:10">
       <c r="I470" s="18"/>
       <c r="J470" s="18"/>
     </row>
-    <row r="471" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="471" spans="9:10">
       <c r="I471" s="18"/>
       <c r="J471" s="18"/>
     </row>
-    <row r="472" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="472" spans="9:10">
       <c r="I472" s="18"/>
       <c r="J472" s="18"/>
     </row>
-    <row r="473" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="473" spans="9:10">
       <c r="I473" s="18"/>
       <c r="J473" s="18"/>
     </row>
-    <row r="474" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="474" spans="9:10">
       <c r="I474" s="18"/>
       <c r="J474" s="18"/>
     </row>
-    <row r="475" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="475" spans="9:10">
       <c r="I475" s="18"/>
       <c r="J475" s="18"/>
     </row>
-    <row r="476" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="476" spans="9:10">
       <c r="I476" s="18"/>
       <c r="J476" s="18"/>
     </row>
-    <row r="477" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="477" spans="9:10">
       <c r="I477" s="18"/>
       <c r="J477" s="18"/>
     </row>
-    <row r="478" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="478" spans="9:10">
       <c r="I478" s="18"/>
       <c r="J478" s="18"/>
     </row>
-    <row r="479" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="479" spans="9:10">
       <c r="I479" s="18"/>
       <c r="J479" s="18"/>
     </row>
-    <row r="480" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="480" spans="9:10">
       <c r="I480" s="18"/>
       <c r="J480" s="18"/>
     </row>
-    <row r="481" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="481" spans="9:10">
       <c r="I481" s="18"/>
       <c r="J481" s="18"/>
     </row>
-    <row r="482" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="482" spans="9:10">
       <c r="I482" s="18"/>
       <c r="J482" s="18"/>
     </row>
-    <row r="483" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="483" spans="9:10">
       <c r="I483" s="18"/>
       <c r="J483" s="18"/>
     </row>
-    <row r="484" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="484" spans="9:10">
       <c r="I484" s="18"/>
       <c r="J484" s="18"/>
     </row>
-    <row r="485" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="485" spans="9:10">
       <c r="I485" s="18"/>
       <c r="J485" s="18"/>
     </row>
-    <row r="486" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="486" spans="9:10">
       <c r="I486" s="18"/>
       <c r="J486" s="18"/>
     </row>
-    <row r="487" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="487" spans="9:10">
       <c r="I487" s="18"/>
       <c r="J487" s="18"/>
     </row>
-    <row r="488" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="488" spans="9:10">
       <c r="I488" s="18"/>
       <c r="J488" s="18"/>
     </row>
-    <row r="489" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="489" spans="9:10">
       <c r="I489" s="18"/>
       <c r="J489" s="18"/>
     </row>
-    <row r="490" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="490" spans="9:10">
       <c r="I490" s="18"/>
       <c r="J490" s="18"/>
     </row>
-    <row r="491" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="491" spans="9:10">
       <c r="I491" s="18"/>
       <c r="J491" s="18"/>
     </row>
-    <row r="492" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="492" spans="9:10">
       <c r="I492" s="18"/>
       <c r="J492" s="18"/>
     </row>
-    <row r="493" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="493" spans="9:10">
       <c r="I493" s="18"/>
       <c r="J493" s="18"/>
     </row>
-    <row r="494" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="494" spans="9:10">
       <c r="I494" s="18"/>
       <c r="J494" s="18"/>
     </row>
-    <row r="495" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="495" spans="9:10">
       <c r="I495" s="18"/>
       <c r="J495" s="18"/>
     </row>
-    <row r="496" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="496" spans="9:10">
       <c r="I496" s="18"/>
       <c r="J496" s="18"/>
     </row>
-    <row r="497" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="497" spans="9:10">
       <c r="I497" s="18"/>
       <c r="J497" s="18"/>
     </row>
-    <row r="498" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="498" spans="9:10">
       <c r="I498" s="18"/>
       <c r="J498" s="18"/>
     </row>
-    <row r="499" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="499" spans="9:10">
       <c r="I499" s="18"/>
       <c r="J499" s="18"/>
     </row>
-    <row r="500" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="500" spans="9:10">
       <c r="I500" s="18"/>
       <c r="J500" s="18"/>
     </row>
-    <row r="501" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="501" spans="9:10">
       <c r="I501" s="18"/>
       <c r="J501" s="18"/>
     </row>
-    <row r="502" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="502" spans="9:10">
       <c r="I502" s="18"/>
       <c r="J502" s="18"/>
     </row>
-    <row r="503" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="503" spans="9:10">
       <c r="I503" s="18"/>
       <c r="J503" s="18"/>
     </row>
-    <row r="504" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="504" spans="9:10">
       <c r="I504" s="18"/>
       <c r="J504" s="18"/>
     </row>
-    <row r="505" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="505" spans="9:10">
       <c r="I505" s="18"/>
       <c r="J505" s="18"/>
     </row>
-    <row r="506" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="506" spans="9:10">
       <c r="I506" s="18"/>
       <c r="J506" s="18"/>
     </row>
-    <row r="507" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="507" spans="9:10">
       <c r="I507" s="18"/>
       <c r="J507" s="18"/>
     </row>
-    <row r="508" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="508" spans="9:10">
       <c r="I508" s="18"/>
       <c r="J508" s="18"/>
     </row>
-    <row r="509" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="509" spans="9:10">
       <c r="I509" s="18"/>
       <c r="J509" s="18"/>
     </row>
-    <row r="510" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="510" spans="9:10">
       <c r="I510" s="18"/>
       <c r="J510" s="18"/>
     </row>
-    <row r="511" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="511" spans="9:10">
       <c r="I511" s="18"/>
       <c r="J511" s="18"/>
     </row>
-    <row r="512" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="512" spans="9:10">
       <c r="I512" s="18"/>
       <c r="J512" s="18"/>
     </row>
-    <row r="513" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="513" spans="9:10">
       <c r="I513" s="18"/>
       <c r="J513" s="18"/>
     </row>
-    <row r="514" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="514" spans="9:10">
       <c r="I514" s="18"/>
       <c r="J514" s="18"/>
     </row>
-    <row r="515" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="515" spans="9:10">
       <c r="I515" s="18"/>
       <c r="J515" s="18"/>
     </row>
-    <row r="516" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="516" spans="9:10">
       <c r="I516" s="18"/>
       <c r="J516" s="18"/>
     </row>
-    <row r="517" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="517" spans="9:10">
       <c r="I517" s="18"/>
       <c r="J517" s="18"/>
     </row>
-    <row r="518" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="518" spans="9:10">
       <c r="I518" s="18"/>
       <c r="J518" s="18"/>
     </row>
-    <row r="519" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="519" spans="9:10">
       <c r="I519" s="18"/>
       <c r="J519" s="18"/>
     </row>
-    <row r="520" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="520" spans="9:10">
       <c r="I520" s="18"/>
       <c r="J520" s="18"/>
     </row>
-    <row r="521" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="521" spans="9:10">
       <c r="I521" s="18"/>
       <c r="J521" s="18"/>
     </row>
-    <row r="522" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="522" spans="9:10">
       <c r="I522" s="18"/>
       <c r="J522" s="18"/>
     </row>
-    <row r="523" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="523" spans="9:10">
       <c r="I523" s="18"/>
       <c r="J523" s="18"/>
     </row>
-    <row r="524" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="524" spans="9:10">
       <c r="I524" s="18"/>
       <c r="J524" s="18"/>
     </row>
-    <row r="525" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="525" spans="9:10">
       <c r="I525" s="18"/>
       <c r="J525" s="18"/>
     </row>
-    <row r="526" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="526" spans="9:10">
       <c r="I526" s="18"/>
       <c r="J526" s="18"/>
     </row>
-    <row r="527" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="527" spans="9:10">
       <c r="I527" s="18"/>
       <c r="J527" s="18"/>
     </row>
-    <row r="528" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="528" spans="9:10">
       <c r="I528" s="18"/>
       <c r="J528" s="18"/>
     </row>
-    <row r="529" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="529" spans="9:10">
       <c r="I529" s="18"/>
       <c r="J529" s="18"/>
     </row>
-    <row r="530" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="530" spans="9:10">
       <c r="I530" s="18"/>
       <c r="J530" s="18"/>
     </row>
-    <row r="531" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="531" spans="9:10">
       <c r="I531" s="18"/>
       <c r="J531" s="18"/>
     </row>
-    <row r="532" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="532" spans="9:10">
       <c r="I532" s="18"/>
       <c r="J532" s="18"/>
     </row>
-    <row r="533" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="533" spans="9:10">
       <c r="I533" s="18"/>
       <c r="J533" s="18"/>
     </row>
-    <row r="534" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="534" spans="9:10">
       <c r="I534" s="18"/>
       <c r="J534" s="18"/>
     </row>
-    <row r="535" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="535" spans="9:10">
       <c r="I535" s="18"/>
       <c r="J535" s="18"/>
     </row>
-    <row r="536" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="536" spans="9:10">
       <c r="I536" s="18"/>
       <c r="J536" s="18"/>
     </row>
-    <row r="537" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="537" spans="9:10">
       <c r="I537" s="18"/>
       <c r="J537" s="18"/>
     </row>
-    <row r="538" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="538" spans="9:10">
       <c r="I538" s="18"/>
       <c r="J538" s="18"/>
     </row>
-    <row r="539" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="539" spans="9:10">
       <c r="I539" s="18"/>
       <c r="J539" s="18"/>
     </row>
-    <row r="540" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="540" spans="9:10">
       <c r="I540" s="18"/>
       <c r="J540" s="18"/>
     </row>
-    <row r="541" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="541" spans="9:10">
       <c r="I541" s="18"/>
       <c r="J541" s="18"/>
     </row>
-    <row r="542" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="542" spans="9:10">
       <c r="I542" s="18"/>
       <c r="J542" s="18"/>
     </row>
-    <row r="543" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="543" spans="9:10">
       <c r="I543" s="18"/>
       <c r="J543" s="18"/>
     </row>
-    <row r="544" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="544" spans="9:10">
       <c r="I544" s="18"/>
       <c r="J544" s="18"/>
     </row>
-    <row r="545" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="545" spans="9:10">
       <c r="I545" s="18"/>
       <c r="J545" s="18"/>
     </row>
-    <row r="546" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="546" spans="9:10">
       <c r="I546" s="18"/>
       <c r="J546" s="18"/>
     </row>
-    <row r="547" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="547" spans="9:10">
       <c r="I547" s="18"/>
       <c r="J547" s="18"/>
     </row>
-    <row r="548" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="548" spans="9:10">
       <c r="I548" s="18"/>
       <c r="J548" s="18"/>
     </row>
-    <row r="549" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="549" spans="9:10">
       <c r="I549" s="18"/>
       <c r="J549" s="18"/>
     </row>
-    <row r="550" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="550" spans="9:10">
       <c r="I550" s="18"/>
       <c r="J550" s="18"/>
     </row>
-    <row r="551" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="551" spans="9:10">
       <c r="I551" s="18"/>
       <c r="J551" s="18"/>
     </row>
-    <row r="552" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="552" spans="9:10">
       <c r="I552" s="18"/>
       <c r="J552" s="18"/>
     </row>
-    <row r="553" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="553" spans="9:10">
       <c r="I553" s="18"/>
       <c r="J553" s="18"/>
     </row>
-    <row r="554" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="554" spans="9:10">
       <c r="I554" s="18"/>
       <c r="J554" s="18"/>
     </row>
-    <row r="555" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="555" spans="9:10">
       <c r="I555" s="18"/>
       <c r="J555" s="18"/>
     </row>
-    <row r="556" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="556" spans="9:10">
       <c r="I556" s="18"/>
       <c r="J556" s="18"/>
     </row>
-    <row r="557" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="557" spans="9:10">
       <c r="I557" s="18"/>
       <c r="J557" s="18"/>
     </row>
-    <row r="558" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="558" spans="9:10">
       <c r="I558" s="18"/>
       <c r="J558" s="18"/>
     </row>
-    <row r="559" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="559" spans="9:10">
       <c r="I559" s="18"/>
       <c r="J559" s="18"/>
     </row>
-    <row r="560" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="560" spans="9:10">
       <c r="I560" s="18"/>
       <c r="J560" s="18"/>
     </row>
-    <row r="561" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="561" spans="9:10">
       <c r="I561" s="18"/>
       <c r="J561" s="18"/>
     </row>
-    <row r="562" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="562" spans="9:10">
       <c r="I562" s="18"/>
       <c r="J562" s="18"/>
     </row>
-    <row r="563" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="563" spans="9:10">
       <c r="I563" s="18"/>
       <c r="J563" s="18"/>
     </row>
-    <row r="564" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="564" spans="9:10">
       <c r="I564" s="18"/>
       <c r="J564" s="18"/>
     </row>
-    <row r="565" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="565" spans="9:10">
       <c r="I565" s="18"/>
       <c r="J565" s="18"/>
     </row>
-    <row r="566" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="566" spans="9:10">
       <c r="I566" s="18"/>
       <c r="J566" s="18"/>
     </row>
-    <row r="567" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="567" spans="9:10">
       <c r="I567" s="18"/>
       <c r="J567" s="18"/>
     </row>
-    <row r="568" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="568" spans="9:10">
       <c r="I568" s="18"/>
       <c r="J568" s="18"/>
     </row>
-    <row r="569" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="569" spans="9:10">
       <c r="I569" s="18"/>
       <c r="J569" s="18"/>
     </row>
-    <row r="570" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="570" spans="9:10">
       <c r="I570" s="18"/>
       <c r="J570" s="18"/>
     </row>
-    <row r="571" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="571" spans="9:10">
       <c r="I571" s="18"/>
       <c r="J571" s="18"/>
     </row>
-    <row r="572" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="572" spans="9:10">
       <c r="I572" s="18"/>
       <c r="J572" s="18"/>
     </row>
-    <row r="573" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="573" spans="9:10">
       <c r="I573" s="18"/>
       <c r="J573" s="18"/>
     </row>
-    <row r="574" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="574" spans="9:10">
       <c r="I574" s="18"/>
       <c r="J574" s="18"/>
     </row>
-    <row r="575" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="575" spans="9:10">
       <c r="I575" s="18"/>
       <c r="J575" s="18"/>
     </row>
-    <row r="576" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="576" spans="9:10">
       <c r="I576" s="18"/>
       <c r="J576" s="18"/>
     </row>
-    <row r="577" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="577" spans="9:10">
       <c r="I577" s="18"/>
       <c r="J577" s="18"/>
     </row>
-    <row r="578" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="578" spans="9:10">
       <c r="I578" s="18"/>
       <c r="J578" s="18"/>
     </row>
-    <row r="579" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="579" spans="9:10">
       <c r="I579" s="18"/>
       <c r="J579" s="18"/>
     </row>
-    <row r="580" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="580" spans="9:10">
       <c r="I580" s="18"/>
       <c r="J580" s="18"/>
     </row>
-    <row r="581" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="581" spans="9:10">
       <c r="I581" s="18"/>
       <c r="J581" s="18"/>
     </row>
-    <row r="582" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="582" spans="9:10">
       <c r="I582" s="18"/>
       <c r="J582" s="18"/>
     </row>
-    <row r="583" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="583" spans="9:10">
       <c r="I583" s="18"/>
       <c r="J583" s="18"/>
     </row>
-    <row r="584" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="584" spans="9:10">
       <c r="I584" s="18"/>
       <c r="J584" s="18"/>
     </row>
-    <row r="585" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="585" spans="9:10">
       <c r="I585" s="18"/>
       <c r="J585" s="18"/>
     </row>
-    <row r="586" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="586" spans="9:10">
       <c r="I586" s="18"/>
       <c r="J586" s="18"/>
     </row>
-    <row r="587" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="587" spans="9:10">
       <c r="I587" s="18"/>
       <c r="J587" s="18"/>
     </row>
-    <row r="588" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="588" spans="9:10">
       <c r="I588" s="18"/>
       <c r="J588" s="18"/>
     </row>
-    <row r="589" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="589" spans="9:10">
       <c r="I589" s="18"/>
       <c r="J589" s="18"/>
     </row>
-    <row r="590" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="590" spans="9:10">
       <c r="I590" s="18"/>
       <c r="J590" s="18"/>
     </row>
-    <row r="591" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="591" spans="9:10">
       <c r="I591" s="18"/>
       <c r="J591" s="18"/>
     </row>
-    <row r="592" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="592" spans="9:10">
       <c r="I592" s="18"/>
       <c r="J592" s="18"/>
     </row>
-    <row r="593" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="593" spans="9:10">
       <c r="I593" s="18"/>
       <c r="J593" s="18"/>
     </row>
-    <row r="594" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="594" spans="9:10">
       <c r="I594" s="18"/>
       <c r="J594" s="18"/>
     </row>
-    <row r="595" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="595" spans="9:10">
       <c r="I595" s="18"/>
       <c r="J595" s="18"/>
     </row>
-    <row r="596" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="596" spans="9:10">
       <c r="I596" s="18"/>
       <c r="J596" s="18"/>
     </row>
-    <row r="597" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="597" spans="9:10">
       <c r="I597" s="18"/>
       <c r="J597" s="18"/>
     </row>
-    <row r="598" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="598" spans="9:10">
       <c r="I598" s="18"/>
       <c r="J598" s="18"/>
     </row>
-    <row r="599" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="599" spans="9:10">
       <c r="I599" s="18"/>
       <c r="J599" s="18"/>
     </row>
-    <row r="600" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="600" spans="9:10">
       <c r="I600" s="18"/>
       <c r="J600" s="18"/>
     </row>
-    <row r="601" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="601" spans="9:10">
       <c r="I601" s="18"/>
       <c r="J601" s="18"/>
     </row>
-    <row r="602" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="602" spans="9:10">
       <c r="I602" s="18"/>
       <c r="J602" s="18"/>
     </row>
-    <row r="603" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="603" spans="9:10">
       <c r="I603" s="18"/>
       <c r="J603" s="18"/>
     </row>
-    <row r="604" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="604" spans="9:10">
       <c r="I604" s="18"/>
       <c r="J604" s="18"/>
     </row>
-    <row r="605" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="605" spans="9:10">
       <c r="I605" s="18"/>
       <c r="J605" s="18"/>
     </row>
-    <row r="606" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="606" spans="9:10">
       <c r="I606" s="18"/>
       <c r="J606" s="18"/>
     </row>
-    <row r="607" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="607" spans="9:10">
       <c r="I607" s="18"/>
       <c r="J607" s="18"/>
     </row>
-    <row r="608" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="608" spans="9:10">
       <c r="I608" s="18"/>
       <c r="J608" s="18"/>
     </row>
-    <row r="609" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="609" spans="9:10">
       <c r="I609" s="18"/>
       <c r="J609" s="18"/>
     </row>
-    <row r="610" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="610" spans="9:10">
       <c r="I610" s="18"/>
       <c r="J610" s="18"/>
     </row>
-    <row r="611" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="611" spans="9:10">
       <c r="I611" s="18"/>
       <c r="J611" s="18"/>
     </row>
-    <row r="612" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="612" spans="9:10">
       <c r="I612" s="18"/>
       <c r="J612" s="18"/>
     </row>
-    <row r="613" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="613" spans="9:10">
       <c r="I613" s="18"/>
       <c r="J613" s="18"/>
     </row>
-    <row r="614" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="614" spans="9:10">
       <c r="I614" s="18"/>
       <c r="J614" s="18"/>
     </row>
-    <row r="615" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="615" spans="9:10">
       <c r="I615" s="18"/>
       <c r="J615" s="18"/>
     </row>
-    <row r="616" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="616" spans="9:10">
       <c r="I616" s="18"/>
       <c r="J616" s="18"/>
     </row>
-    <row r="617" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="617" spans="9:10">
       <c r="I617" s="18"/>
       <c r="J617" s="18"/>
     </row>
-    <row r="618" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="618" spans="9:10">
       <c r="I618" s="18"/>
       <c r="J618" s="18"/>
     </row>
-    <row r="619" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="619" spans="9:10">
       <c r="I619" s="18"/>
       <c r="J619" s="18"/>
     </row>
-    <row r="620" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="620" spans="9:10">
       <c r="I620" s="18"/>
       <c r="J620" s="18"/>
     </row>
-    <row r="621" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="621" spans="9:10">
       <c r="I621" s="18"/>
       <c r="J621" s="18"/>
     </row>
-    <row r="622" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="622" spans="9:10">
       <c r="I622" s="18"/>
       <c r="J622" s="18"/>
     </row>
-    <row r="623" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="623" spans="9:10">
       <c r="I623" s="18"/>
       <c r="J623" s="18"/>
     </row>
-    <row r="624" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="624" spans="9:10">
       <c r="I624" s="18"/>
       <c r="J624" s="18"/>
     </row>
-    <row r="625" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="625" spans="9:10">
       <c r="I625" s="18"/>
       <c r="J625" s="18"/>
     </row>
-    <row r="626" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="626" spans="9:10">
       <c r="I626" s="18"/>
       <c r="J626" s="18"/>
     </row>
-    <row r="627" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="627" spans="9:10">
       <c r="I627" s="18"/>
       <c r="J627" s="18"/>
     </row>
-    <row r="628" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="628" spans="9:10">
       <c r="I628" s="18"/>
       <c r="J628" s="18"/>
     </row>
-    <row r="629" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="629" spans="9:10">
       <c r="I629" s="18"/>
       <c r="J629" s="18"/>
     </row>
-    <row r="630" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="630" spans="9:10">
       <c r="I630" s="18"/>
       <c r="J630" s="18"/>
     </row>
-    <row r="631" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="631" spans="9:10">
       <c r="I631" s="18"/>
       <c r="J631" s="18"/>
     </row>
-    <row r="632" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="632" spans="9:10">
       <c r="I632" s="18"/>
       <c r="J632" s="18"/>
     </row>
-    <row r="633" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="633" spans="9:10">
       <c r="I633" s="18"/>
       <c r="J633" s="18"/>
     </row>
-    <row r="634" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="634" spans="9:10">
       <c r="I634" s="18"/>
       <c r="J634" s="18"/>
     </row>
-    <row r="635" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="635" spans="9:10">
       <c r="I635" s="18"/>
       <c r="J635" s="18"/>
     </row>
-    <row r="636" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="636" spans="9:10">
       <c r="I636" s="18"/>
       <c r="J636" s="18"/>
     </row>
-    <row r="637" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="637" spans="9:10">
       <c r="I637" s="18"/>
       <c r="J637" s="18"/>
     </row>
-    <row r="638" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="638" spans="9:10">
       <c r="I638" s="18"/>
       <c r="J638" s="18"/>
     </row>
-    <row r="639" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="639" spans="9:10">
       <c r="I639" s="18"/>
       <c r="J639" s="18"/>
     </row>
-    <row r="640" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="640" spans="9:10">
       <c r="I640" s="18"/>
       <c r="J640" s="18"/>
     </row>
-    <row r="641" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="641" spans="9:10">
       <c r="I641" s="18"/>
       <c r="J641" s="18"/>
     </row>
-    <row r="642" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="642" spans="9:10">
       <c r="I642" s="18"/>
       <c r="J642" s="18"/>
     </row>
-    <row r="643" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="643" spans="9:10">
       <c r="I643" s="18"/>
       <c r="J643" s="18"/>
     </row>
-    <row r="644" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="644" spans="9:10">
       <c r="I644" s="18"/>
       <c r="J644" s="18"/>
     </row>
-    <row r="645" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="645" spans="9:10">
       <c r="I645" s="18"/>
       <c r="J645" s="18"/>
     </row>
-    <row r="646" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="646" spans="9:10">
       <c r="I646" s="18"/>
       <c r="J646" s="18"/>
     </row>
-    <row r="647" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="647" spans="9:10">
       <c r="I647" s="18"/>
       <c r="J647" s="18"/>
     </row>
-    <row r="648" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="648" spans="9:10">
       <c r="I648" s="18"/>
       <c r="J648" s="18"/>
     </row>
-    <row r="649" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="649" spans="9:10">
       <c r="I649" s="18"/>
       <c r="J649" s="18"/>
     </row>
-    <row r="650" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="650" spans="9:10">
       <c r="I650" s="18"/>
       <c r="J650" s="18"/>
     </row>
-    <row r="651" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="651" spans="9:10">
       <c r="I651" s="18"/>
       <c r="J651" s="18"/>
     </row>
-    <row r="652" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="652" spans="9:10">
       <c r="I652" s="18"/>
       <c r="J652" s="18"/>
     </row>
-    <row r="653" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="653" spans="9:10">
       <c r="I653" s="18"/>
       <c r="J653" s="18"/>
     </row>
-    <row r="654" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="654" spans="9:10">
       <c r="I654" s="18"/>
       <c r="J654" s="18"/>
     </row>
-    <row r="655" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="655" spans="9:10">
       <c r="I655" s="18"/>
       <c r="J655" s="18"/>
     </row>
-    <row r="656" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="656" spans="9:10">
       <c r="I656" s="18"/>
       <c r="J656" s="18"/>
     </row>
-    <row r="657" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="657" spans="9:10">
       <c r="I657" s="18"/>
       <c r="J657" s="18"/>
     </row>
-    <row r="658" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="658" spans="9:10">
       <c r="I658" s="18"/>
       <c r="J658" s="18"/>
     </row>
-    <row r="659" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="659" spans="9:10">
       <c r="I659" s="18"/>
       <c r="J659" s="18"/>
     </row>
-    <row r="660" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="660" spans="9:10">
       <c r="I660" s="18"/>
       <c r="J660" s="18"/>
     </row>
-    <row r="661" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="661" spans="9:10">
       <c r="I661" s="18"/>
       <c r="J661" s="18"/>
     </row>
-    <row r="662" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="662" spans="9:10">
       <c r="I662" s="18"/>
       <c r="J662" s="18"/>
     </row>
-    <row r="663" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="663" spans="9:10">
       <c r="I663" s="18"/>
       <c r="J663" s="18"/>
     </row>
-    <row r="664" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="664" spans="9:10">
       <c r="I664" s="18"/>
       <c r="J664" s="18"/>
     </row>
-    <row r="665" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="665" spans="9:10">
       <c r="I665" s="18"/>
       <c r="J665" s="18"/>
     </row>
-    <row r="666" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="666" spans="9:10">
       <c r="I666" s="18"/>
       <c r="J666" s="18"/>
     </row>
-    <row r="667" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="667" spans="9:10">
       <c r="I667" s="18"/>
       <c r="J667" s="18"/>
     </row>
-    <row r="668" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="668" spans="9:10">
       <c r="I668" s="18"/>
       <c r="J668" s="18"/>
     </row>
-    <row r="669" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="669" spans="9:10">
       <c r="I669" s="18"/>
       <c r="J669" s="18"/>
     </row>
-    <row r="670" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="670" spans="9:10">
       <c r="I670" s="18"/>
       <c r="J670" s="18"/>
     </row>
-    <row r="671" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="671" spans="9:10">
       <c r="I671" s="18"/>
       <c r="J671" s="18"/>
     </row>
-    <row r="672" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="672" spans="9:10">
       <c r="I672" s="18"/>
       <c r="J672" s="18"/>
     </row>
-    <row r="673" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="673" spans="9:10">
       <c r="I673" s="18"/>
       <c r="J673" s="18"/>
     </row>
-    <row r="674" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="674" spans="9:10">
       <c r="I674" s="18"/>
       <c r="J674" s="18"/>
     </row>
-    <row r="675" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="675" spans="9:10">
       <c r="I675" s="18"/>
       <c r="J675" s="18"/>
     </row>
-    <row r="676" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="676" spans="9:10">
       <c r="I676" s="18"/>
       <c r="J676" s="18"/>
     </row>
-    <row r="677" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="677" spans="9:10">
       <c r="I677" s="18"/>
       <c r="J677" s="18"/>
     </row>
-    <row r="678" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="678" spans="9:10">
       <c r="I678" s="18"/>
       <c r="J678" s="18"/>
     </row>
-    <row r="679" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="679" spans="9:10">
       <c r="I679" s="18"/>
       <c r="J679" s="18"/>
     </row>
-    <row r="680" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="680" spans="9:10">
       <c r="I680" s="18"/>
       <c r="J680" s="18"/>
     </row>
-    <row r="681" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="681" spans="9:10">
       <c r="I681" s="18"/>
       <c r="J681" s="18"/>
     </row>
-    <row r="682" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="682" spans="9:10">
       <c r="I682" s="18"/>
       <c r="J682" s="18"/>
     </row>
-    <row r="683" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="683" spans="9:10">
       <c r="I683" s="18"/>
       <c r="J683" s="18"/>
     </row>
-    <row r="684" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="684" spans="9:10">
       <c r="I684" s="18"/>
       <c r="J684" s="18"/>
     </row>
-    <row r="685" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="685" spans="9:10">
       <c r="I685" s="18"/>
       <c r="J685" s="18"/>
     </row>
-    <row r="686" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="686" spans="9:10">
       <c r="I686" s="18"/>
       <c r="J686" s="18"/>
     </row>
-    <row r="687" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="687" spans="9:10">
       <c r="I687" s="18"/>
       <c r="J687" s="18"/>
     </row>
-    <row r="688" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="688" spans="9:10">
       <c r="I688" s="18"/>
       <c r="J688" s="18"/>
     </row>
-    <row r="689" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="689" spans="9:10">
       <c r="I689" s="18"/>
       <c r="J689" s="18"/>
     </row>
-    <row r="690" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="690" spans="9:10">
       <c r="I690" s="18"/>
       <c r="J690" s="18"/>
     </row>
-    <row r="691" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="691" spans="9:10">
       <c r="I691" s="18"/>
       <c r="J691" s="18"/>
     </row>
-    <row r="692" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="692" spans="9:10">
       <c r="I692" s="18"/>
       <c r="J692" s="18"/>
     </row>
-    <row r="693" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="693" spans="9:10">
       <c r="I693" s="18"/>
       <c r="J693" s="18"/>
     </row>
-    <row r="694" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="694" spans="9:10">
       <c r="I694" s="18"/>
       <c r="J694" s="18"/>
     </row>
-    <row r="695" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="695" spans="9:10">
       <c r="I695" s="18"/>
       <c r="J695" s="18"/>
     </row>
-    <row r="696" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="696" spans="9:10">
       <c r="I696" s="18"/>
       <c r="J696" s="18"/>
     </row>
-    <row r="697" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="697" spans="9:10">
       <c r="I697" s="18"/>
       <c r="J697" s="18"/>
     </row>
-    <row r="698" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="698" spans="9:10">
       <c r="I698" s="18"/>
       <c r="J698" s="18"/>
     </row>
-    <row r="699" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="699" spans="9:10">
       <c r="I699" s="18"/>
       <c r="J699" s="18"/>
     </row>
-    <row r="700" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="700" spans="9:10">
       <c r="I700" s="18"/>
       <c r="J700" s="18"/>
     </row>
-    <row r="701" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="701" spans="9:10">
       <c r="I701" s="18"/>
       <c r="J701" s="18"/>
     </row>
-    <row r="702" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="702" spans="9:10">
       <c r="I702" s="18"/>
       <c r="J702" s="18"/>
     </row>
-    <row r="703" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="703" spans="9:10">
       <c r="I703" s="18"/>
       <c r="J703" s="18"/>
     </row>
-    <row r="704" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="704" spans="9:10">
       <c r="I704" s="18"/>
       <c r="J704" s="18"/>
     </row>
-    <row r="705" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="705" spans="9:10">
       <c r="I705" s="18"/>
       <c r="J705" s="18"/>
     </row>
-    <row r="706" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="706" spans="9:10">
       <c r="I706" s="18"/>
       <c r="J706" s="18"/>
     </row>
-    <row r="707" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="707" spans="9:10">
       <c r="I707" s="18"/>
       <c r="J707" s="18"/>
     </row>
-    <row r="708" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="708" spans="9:10">
       <c r="I708" s="18"/>
       <c r="J708" s="18"/>
     </row>
-    <row r="709" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="709" spans="9:10">
       <c r="I709" s="18"/>
       <c r="J709" s="18"/>
     </row>
-    <row r="710" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="710" spans="9:10">
       <c r="I710" s="18"/>
       <c r="J710" s="18"/>
     </row>
-    <row r="711" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="711" spans="9:10">
       <c r="I711" s="18"/>
       <c r="J711" s="18"/>
     </row>
-    <row r="712" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="712" spans="9:10">
       <c r="I712" s="18"/>
       <c r="J712" s="18"/>
     </row>
-    <row r="713" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="713" spans="9:10">
       <c r="I713" s="18"/>
       <c r="J713" s="18"/>
     </row>
-    <row r="714" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="714" spans="9:10">
       <c r="I714" s="18"/>
       <c r="J714" s="18"/>
     </row>
-    <row r="715" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="715" spans="9:10">
       <c r="I715" s="18"/>
       <c r="J715" s="18"/>
     </row>
-    <row r="716" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="716" spans="9:10">
       <c r="I716" s="18"/>
       <c r="J716" s="18"/>
     </row>
-    <row r="717" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="717" spans="9:10">
       <c r="I717" s="18"/>
       <c r="J717" s="18"/>
     </row>
-    <row r="718" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="718" spans="9:10">
       <c r="I718" s="18"/>
       <c r="J718" s="18"/>
     </row>
-    <row r="719" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="719" spans="9:10">
       <c r="I719" s="18"/>
       <c r="J719" s="18"/>
     </row>
-    <row r="720" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="720" spans="9:10">
       <c r="I720" s="18"/>
       <c r="J720" s="18"/>
     </row>
-    <row r="721" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="721" spans="9:10">
       <c r="I721" s="18"/>
       <c r="J721" s="18"/>
     </row>
-    <row r="722" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="722" spans="9:10">
       <c r="I722" s="18"/>
       <c r="J722" s="18"/>
     </row>
-    <row r="723" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="723" spans="9:10">
       <c r="I723" s="18"/>
       <c r="J723" s="18"/>
     </row>
-    <row r="724" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="724" spans="9:10">
       <c r="I724" s="18"/>
       <c r="J724" s="18"/>
     </row>
-    <row r="725" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="725" spans="9:10">
       <c r="I725" s="18"/>
       <c r="J725" s="18"/>
     </row>
-    <row r="726" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="726" spans="9:10">
       <c r="I726" s="18"/>
       <c r="J726" s="18"/>
     </row>
-    <row r="727" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="727" spans="9:10">
       <c r="I727" s="18"/>
       <c r="J727" s="18"/>
     </row>
-    <row r="728" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="728" spans="9:10">
       <c r="I728" s="18"/>
       <c r="J728" s="18"/>
     </row>
-    <row r="729" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="729" spans="9:10">
       <c r="I729" s="18"/>
       <c r="J729" s="18"/>
     </row>
-    <row r="730" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="730" spans="9:10">
       <c r="I730" s="18"/>
       <c r="J730" s="18"/>
     </row>
-    <row r="731" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="731" spans="9:10">
       <c r="I731" s="18"/>
       <c r="J731" s="18"/>
     </row>
-    <row r="732" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="732" spans="9:10">
       <c r="I732" s="18"/>
       <c r="J732" s="18"/>
     </row>
-    <row r="733" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="733" spans="9:10">
       <c r="I733" s="18"/>
       <c r="J733" s="18"/>
     </row>
-    <row r="734" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="734" spans="9:10">
       <c r="I734" s="18"/>
       <c r="J734" s="18"/>
     </row>
-    <row r="735" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="735" spans="9:10">
       <c r="I735" s="18"/>
       <c r="J735" s="18"/>
     </row>
-    <row r="736" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="736" spans="9:10">
       <c r="I736" s="18"/>
       <c r="J736" s="18"/>
     </row>
-    <row r="737" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="737" spans="9:10">
       <c r="I737" s="18"/>
       <c r="J737" s="18"/>
     </row>
-    <row r="738" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="738" spans="9:10">
       <c r="I738" s="18"/>
       <c r="J738" s="18"/>
     </row>
-    <row r="739" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="739" spans="9:10">
       <c r="I739" s="18"/>
       <c r="J739" s="18"/>
     </row>
-    <row r="740" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="740" spans="9:10">
       <c r="I740" s="18"/>
       <c r="J740" s="18"/>
     </row>
-    <row r="741" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="741" spans="9:10">
       <c r="I741" s="18"/>
       <c r="J741" s="18"/>
     </row>
-    <row r="742" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="742" spans="9:10">
       <c r="I742" s="18"/>
       <c r="J742" s="18"/>
     </row>
-    <row r="743" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="743" spans="9:10">
       <c r="I743" s="18"/>
       <c r="J743" s="18"/>
     </row>
-    <row r="744" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="744" spans="9:10">
       <c r="I744" s="18"/>
       <c r="J744" s="18"/>
     </row>
-    <row r="745" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="745" spans="9:10">
       <c r="I745" s="18"/>
       <c r="J745" s="18"/>
     </row>
-    <row r="746" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="746" spans="9:10">
       <c r="I746" s="18"/>
       <c r="J746" s="18"/>
     </row>
-    <row r="747" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="747" spans="9:10">
       <c r="I747" s="18"/>
       <c r="J747" s="18"/>
     </row>
-    <row r="748" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="748" spans="9:10">
       <c r="I748" s="18"/>
       <c r="J748" s="18"/>
     </row>
-    <row r="749" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="749" spans="9:10">
       <c r="I749" s="18"/>
       <c r="J749" s="18"/>
     </row>
-    <row r="750" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="750" spans="9:10">
       <c r="I750" s="18"/>
       <c r="J750" s="18"/>
     </row>
-    <row r="751" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="751" spans="9:10">
       <c r="I751" s="18"/>
       <c r="J751" s="18"/>
     </row>
-    <row r="752" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="752" spans="9:10">
       <c r="I752" s="18"/>
       <c r="J752" s="18"/>
     </row>
-    <row r="753" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="753" spans="9:10">
       <c r="I753" s="18"/>
       <c r="J753" s="18"/>
     </row>
-    <row r="754" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="754" spans="9:10">
       <c r="I754" s="18"/>
       <c r="J754" s="18"/>
     </row>
-    <row r="755" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="755" spans="9:10">
       <c r="I755" s="18"/>
       <c r="J755" s="18"/>
     </row>
-    <row r="756" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="756" spans="9:10">
       <c r="I756" s="18"/>
       <c r="J756" s="18"/>
     </row>
-    <row r="757" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="757" spans="9:10">
       <c r="I757" s="18"/>
       <c r="J757" s="18"/>
     </row>
-    <row r="758" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="758" spans="9:10">
       <c r="I758" s="18"/>
       <c r="J758" s="18"/>
     </row>
-    <row r="759" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="759" spans="9:10">
       <c r="I759" s="18"/>
       <c r="J759" s="18"/>
     </row>
-    <row r="760" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="760" spans="9:10">
       <c r="I760" s="18"/>
       <c r="J760" s="18"/>
     </row>
-    <row r="761" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="761" spans="9:10">
       <c r="I761" s="18"/>
       <c r="J761" s="18"/>
     </row>
-    <row r="762" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="762" spans="9:10">
       <c r="I762" s="18"/>
       <c r="J762" s="18"/>
     </row>
-    <row r="763" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="763" spans="9:10">
       <c r="I763" s="18"/>
       <c r="J763" s="18"/>
     </row>
-    <row r="764" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="764" spans="9:10">
       <c r="I764" s="18"/>
       <c r="J764" s="18"/>
     </row>
-    <row r="765" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="765" spans="9:10">
       <c r="I765" s="18"/>
       <c r="J765" s="18"/>
     </row>
-    <row r="766" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="766" spans="9:10">
       <c r="I766" s="18"/>
       <c r="J766" s="18"/>
     </row>
-    <row r="767" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="767" spans="9:10">
       <c r="I767" s="18"/>
       <c r="J767" s="18"/>
     </row>
-    <row r="768" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="768" spans="9:10">
       <c r="I768" s="18"/>
       <c r="J768" s="18"/>
     </row>
-    <row r="769" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="769" spans="9:10">
       <c r="I769" s="18"/>
       <c r="J769" s="18"/>
     </row>
-    <row r="770" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="770" spans="9:10">
       <c r="I770" s="18"/>
       <c r="J770" s="18"/>
     </row>
-    <row r="771" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="771" spans="9:10">
       <c r="I771" s="18"/>
       <c r="J771" s="18"/>
     </row>
-    <row r="772" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="772" spans="9:10">
       <c r="I772" s="18"/>
       <c r="J772" s="18"/>
     </row>
-    <row r="773" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="773" spans="9:10">
       <c r="I773" s="18"/>
       <c r="J773" s="18"/>
     </row>
-    <row r="774" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="774" spans="9:10">
       <c r="I774" s="18"/>
       <c r="J774" s="18"/>
     </row>
-    <row r="775" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="775" spans="9:10">
       <c r="I775" s="18"/>
       <c r="J775" s="18"/>
     </row>
-    <row r="776" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="776" spans="9:10">
       <c r="I776" s="18"/>
       <c r="J776" s="18"/>
     </row>
-    <row r="777" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="777" spans="9:10">
       <c r="I777" s="18"/>
       <c r="J777" s="18"/>
     </row>
-    <row r="778" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="778" spans="9:10">
       <c r="I778" s="18"/>
       <c r="J778" s="18"/>
     </row>
-    <row r="779" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="779" spans="9:10">
       <c r="I779" s="18"/>
       <c r="J779" s="18"/>
     </row>
-    <row r="780" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="780" spans="9:10">
       <c r="I780" s="18"/>
       <c r="J780" s="18"/>
     </row>
-    <row r="781" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="781" spans="9:10">
       <c r="I781" s="18"/>
       <c r="J781" s="18"/>
     </row>
-    <row r="782" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="782" spans="9:10">
       <c r="I782" s="18"/>
       <c r="J782" s="18"/>
     </row>
-    <row r="783" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="783" spans="9:10">
       <c r="I783" s="18"/>
       <c r="J783" s="18"/>
     </row>
-    <row r="784" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="784" spans="9:10">
       <c r="I784" s="18"/>
       <c r="J784" s="18"/>
     </row>
-    <row r="785" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="785" spans="9:10">
       <c r="I785" s="18"/>
       <c r="J785" s="18"/>
     </row>
-    <row r="786" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="786" spans="9:10">
       <c r="I786" s="18"/>
       <c r="J786" s="18"/>
     </row>
-    <row r="787" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="787" spans="9:10">
       <c r="I787" s="18"/>
       <c r="J787" s="18"/>
     </row>
-    <row r="788" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="788" spans="9:10">
       <c r="I788" s="18"/>
       <c r="J788" s="18"/>
     </row>
-    <row r="789" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="789" spans="9:10">
       <c r="I789" s="18"/>
       <c r="J789" s="18"/>
     </row>
-    <row r="790" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="790" spans="9:10">
       <c r="I790" s="18"/>
       <c r="J790" s="18"/>
     </row>
-    <row r="791" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="791" spans="9:10">
       <c r="I791" s="18"/>
       <c r="J791" s="18"/>
     </row>
-    <row r="792" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="792" spans="9:10">
       <c r="I792" s="18"/>
       <c r="J792" s="18"/>
     </row>
-    <row r="793" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="793" spans="9:10">
       <c r="I793" s="18"/>
       <c r="J793" s="18"/>
     </row>
-    <row r="794" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="794" spans="9:10">
       <c r="I794" s="18"/>
       <c r="J794" s="18"/>
     </row>
-    <row r="795" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="795" spans="9:10">
       <c r="I795" s="18"/>
       <c r="J795" s="18"/>
     </row>
-    <row r="796" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="796" spans="9:10">
       <c r="I796" s="18"/>
       <c r="J796" s="18"/>
     </row>
-    <row r="797" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="797" spans="9:10">
       <c r="I797" s="18"/>
       <c r="J797" s="18"/>
     </row>
-    <row r="798" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="798" spans="9:10">
       <c r="I798" s="18"/>
       <c r="J798" s="18"/>
     </row>
-    <row r="799" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="799" spans="9:10">
       <c r="I799" s="18"/>
       <c r="J799" s="18"/>
     </row>
-    <row r="800" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="800" spans="9:10">
       <c r="I800" s="18"/>
       <c r="J800" s="18"/>
     </row>
-    <row r="801" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="801" spans="9:10">
       <c r="I801" s="18"/>
       <c r="J801" s="18"/>
     </row>
-    <row r="802" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="802" spans="9:10">
       <c r="I802" s="18"/>
       <c r="J802" s="18"/>
     </row>
-    <row r="803" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="803" spans="9:10">
       <c r="I803" s="18"/>
       <c r="J803" s="18"/>
     </row>
-    <row r="804" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="804" spans="9:10">
       <c r="I804" s="18"/>
       <c r="J804" s="18"/>
     </row>
-    <row r="805" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="805" spans="9:10">
       <c r="I805" s="18"/>
       <c r="J805" s="18"/>
     </row>
-    <row r="806" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="806" spans="9:10">
       <c r="I806" s="18"/>
       <c r="J806" s="18"/>
     </row>
-    <row r="807" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="807" spans="9:10">
       <c r="I807" s="18"/>
       <c r="J807" s="18"/>
     </row>
-    <row r="808" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="808" spans="9:10">
       <c r="I808" s="18"/>
       <c r="J808" s="18"/>
     </row>
-    <row r="809" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="809" spans="9:10">
       <c r="I809" s="18"/>
       <c r="J809" s="18"/>
     </row>
-    <row r="810" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="810" spans="9:10">
       <c r="I810" s="18"/>
       <c r="J810" s="18"/>
     </row>
-    <row r="811" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="811" spans="9:10">
       <c r="I811" s="18"/>
       <c r="J811" s="18"/>
     </row>
-    <row r="812" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="812" spans="9:10">
       <c r="I812" s="18"/>
       <c r="J812" s="18"/>
     </row>
-    <row r="813" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="813" spans="9:10">
       <c r="I813" s="18"/>
       <c r="J813" s="18"/>
     </row>
-    <row r="814" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="814" spans="9:10">
       <c r="I814" s="18"/>
       <c r="J814" s="18"/>
     </row>
-    <row r="815" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="815" spans="9:10">
       <c r="I815" s="18"/>
       <c r="J815" s="18"/>
     </row>
-    <row r="816" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="816" spans="9:10">
       <c r="I816" s="18"/>
       <c r="J816" s="18"/>
     </row>
-    <row r="817" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="817" spans="9:10">
       <c r="I817" s="18"/>
       <c r="J817" s="18"/>
     </row>
-    <row r="818" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="818" spans="9:10">
       <c r="I818" s="18"/>
       <c r="J818" s="18"/>
     </row>
-    <row r="819" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="819" spans="9:10">
       <c r="I819" s="18"/>
       <c r="J819" s="18"/>
     </row>
-    <row r="820" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="820" spans="9:10">
       <c r="I820" s="18"/>
       <c r="J820" s="18"/>
     </row>
-    <row r="821" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="821" spans="9:10">
       <c r="I821" s="18"/>
       <c r="J821" s="18"/>
     </row>
-    <row r="822" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="822" spans="9:10">
       <c r="I822" s="18"/>
       <c r="J822" s="18"/>
     </row>
-    <row r="823" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="823" spans="9:10">
       <c r="I823" s="18"/>
       <c r="J823" s="18"/>
     </row>
-    <row r="824" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="824" spans="9:10">
       <c r="I824" s="18"/>
       <c r="J824" s="18"/>
     </row>
-    <row r="825" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="825" spans="9:10">
       <c r="I825" s="18"/>
       <c r="J825" s="18"/>
     </row>
-    <row r="826" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="826" spans="9:10">
       <c r="I826" s="18"/>
       <c r="J826" s="18"/>
     </row>
-    <row r="827" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="827" spans="9:10">
       <c r="I827" s="18"/>
       <c r="J827" s="18"/>
     </row>
-    <row r="828" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="828" spans="9:10">
       <c r="I828" s="18"/>
       <c r="J828" s="18"/>
     </row>
-    <row r="829" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="829" spans="9:10">
       <c r="I829" s="18"/>
       <c r="J829" s="18"/>
     </row>
-    <row r="830" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="830" spans="9:10">
       <c r="I830" s="18"/>
       <c r="J830" s="18"/>
     </row>
-    <row r="831" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="831" spans="9:10">
       <c r="I831" s="18"/>
       <c r="J831" s="18"/>
     </row>
-    <row r="832" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="832" spans="9:10">
       <c r="I832" s="18"/>
       <c r="J832" s="18"/>
     </row>
-    <row r="833" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="833" spans="9:10">
       <c r="I833" s="18"/>
       <c r="J833" s="18"/>
     </row>
-    <row r="834" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="834" spans="9:10">
       <c r="I834" s="18"/>
       <c r="J834" s="18"/>
     </row>
-    <row r="835" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="835" spans="9:10">
       <c r="I835" s="18"/>
       <c r="J835" s="18"/>
     </row>
-    <row r="836" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="836" spans="9:10">
       <c r="I836" s="18"/>
       <c r="J836" s="18"/>
     </row>
-    <row r="837" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="837" spans="9:10">
       <c r="I837" s="18"/>
       <c r="J837" s="18"/>
     </row>
-    <row r="838" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="838" spans="9:10">
       <c r="I838" s="18"/>
       <c r="J838" s="18"/>
     </row>
-    <row r="839" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="839" spans="9:10">
       <c r="I839" s="18"/>
       <c r="J839" s="18"/>
     </row>
-    <row r="840" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="840" spans="9:10">
       <c r="I840" s="18"/>
       <c r="J840" s="18"/>
     </row>
-    <row r="841" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="841" spans="9:10">
       <c r="I841" s="18"/>
       <c r="J841" s="18"/>
     </row>
-    <row r="842" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="842" spans="9:10">
       <c r="I842" s="18"/>
       <c r="J842" s="18"/>
     </row>
-    <row r="843" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="843" spans="9:10">
       <c r="I843" s="18"/>
       <c r="J843" s="18"/>
     </row>
-    <row r="844" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="844" spans="9:10">
       <c r="I844" s="18"/>
       <c r="J844" s="18"/>
     </row>
-    <row r="845" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="845" spans="9:10">
       <c r="I845" s="18"/>
       <c r="J845" s="18"/>
     </row>
-    <row r="846" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="846" spans="9:10">
       <c r="I846" s="18"/>
       <c r="J846" s="18"/>
     </row>
-    <row r="847" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="847" spans="9:10">
       <c r="I847" s="18"/>
       <c r="J847" s="18"/>
     </row>
-    <row r="848" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="848" spans="9:10">
       <c r="I848" s="18"/>
       <c r="J848" s="18"/>
     </row>
-    <row r="849" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="849" spans="9:10">
       <c r="I849" s="18"/>
       <c r="J849" s="18"/>
     </row>
-    <row r="850" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="850" spans="9:10">
       <c r="I850" s="18"/>
       <c r="J850" s="18"/>
     </row>
-    <row r="851" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="851" spans="9:10">
       <c r="I851" s="18"/>
       <c r="J851" s="18"/>
     </row>
-    <row r="852" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="852" spans="9:10">
       <c r="I852" s="18"/>
       <c r="J852" s="18"/>
     </row>
-    <row r="853" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="853" spans="9:10">
       <c r="I853" s="18"/>
       <c r="J853" s="18"/>
     </row>
-    <row r="854" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="854" spans="9:10">
       <c r="I854" s="18"/>
       <c r="J854" s="18"/>
     </row>
-    <row r="855" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="855" spans="9:10">
       <c r="I855" s="18"/>
       <c r="J855" s="18"/>
     </row>
-    <row r="856" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="856" spans="9:10">
       <c r="I856" s="18"/>
       <c r="J856" s="18"/>
     </row>
-    <row r="857" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="857" spans="9:10">
       <c r="I857" s="18"/>
       <c r="J857" s="18"/>
     </row>
-    <row r="858" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="858" spans="9:10">
       <c r="I858" s="18"/>
       <c r="J858" s="18"/>
     </row>
-    <row r="859" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="859" spans="9:10">
       <c r="I859" s="18"/>
       <c r="J859" s="18"/>
     </row>
-    <row r="860" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="860" spans="9:10">
       <c r="I860" s="18"/>
       <c r="J860" s="18"/>
     </row>
-    <row r="861" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="861" spans="9:10">
       <c r="I861" s="18"/>
       <c r="J861" s="18"/>
     </row>
-    <row r="862" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="862" spans="9:10">
       <c r="I862" s="18"/>
       <c r="J862" s="18"/>
     </row>
-    <row r="863" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="863" spans="9:10">
       <c r="I863" s="18"/>
       <c r="J863" s="18"/>
     </row>
-    <row r="864" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="864" spans="9:10">
       <c r="I864" s="18"/>
       <c r="J864" s="18"/>
     </row>
-    <row r="865" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="865" spans="9:10">
       <c r="I865" s="18"/>
       <c r="J865" s="18"/>
     </row>
-    <row r="866" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="866" spans="9:10">
       <c r="I866" s="18"/>
       <c r="J866" s="18"/>
     </row>
-    <row r="867" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="867" spans="9:10">
       <c r="I867" s="18"/>
       <c r="J867" s="18"/>
     </row>
-    <row r="868" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="868" spans="9:10">
       <c r="I868" s="18"/>
       <c r="J868" s="18"/>
     </row>
-    <row r="869" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="869" spans="9:10">
       <c r="I869" s="18"/>
       <c r="J869" s="18"/>
     </row>
-    <row r="870" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="870" spans="9:10">
       <c r="I870" s="18"/>
       <c r="J870" s="18"/>
     </row>
-    <row r="871" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="871" spans="9:10">
       <c r="I871" s="18"/>
       <c r="J871" s="18"/>
     </row>
-    <row r="872" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="872" spans="9:10">
       <c r="I872" s="18"/>
       <c r="J872" s="18"/>
     </row>
-    <row r="873" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="873" spans="9:10">
       <c r="I873" s="18"/>
       <c r="J873" s="18"/>
     </row>
-    <row r="874" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="874" spans="9:10">
       <c r="I874" s="18"/>
       <c r="J874" s="18"/>
     </row>
-    <row r="875" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="875" spans="9:10">
       <c r="I875" s="18"/>
       <c r="J875" s="18"/>
     </row>
-    <row r="876" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="876" spans="9:10">
       <c r="I876" s="18"/>
       <c r="J876" s="18"/>
     </row>
-    <row r="877" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="877" spans="9:10">
       <c r="I877" s="18"/>
       <c r="J877" s="18"/>
     </row>
-    <row r="878" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="878" spans="9:10">
       <c r="I878" s="18"/>
       <c r="J878" s="18"/>
     </row>
-    <row r="879" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="879" spans="9:10">
       <c r="I879" s="18"/>
       <c r="J879" s="18"/>
     </row>
-    <row r="880" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="880" spans="9:10">
       <c r="I880" s="18"/>
       <c r="J880" s="18"/>
     </row>
-    <row r="881" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="881" spans="9:10">
       <c r="I881" s="18"/>
       <c r="J881" s="18"/>
     </row>
-    <row r="882" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="882" spans="9:10">
       <c r="I882" s="18"/>
       <c r="J882" s="18"/>
     </row>
-    <row r="883" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="883" spans="9:10">
       <c r="I883" s="18"/>
       <c r="J883" s="18"/>
     </row>
-    <row r="884" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="884" spans="9:10">
       <c r="I884" s="18"/>
       <c r="J884" s="18"/>
     </row>
-    <row r="885" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="885" spans="9:10">
       <c r="I885" s="18"/>
       <c r="J885" s="18"/>
     </row>
-    <row r="886" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="886" spans="9:10">
       <c r="I886" s="18"/>
       <c r="J886" s="18"/>
     </row>
-    <row r="887" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="887" spans="9:10">
       <c r="I887" s="18"/>
       <c r="J887" s="18"/>
     </row>
-    <row r="888" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="888" spans="9:10">
       <c r="I888" s="18"/>
       <c r="J888" s="18"/>
     </row>
-    <row r="889" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="889" spans="9:10">
       <c r="I889" s="18"/>
       <c r="J889" s="18"/>
     </row>
-    <row r="890" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="890" spans="9:10">
       <c r="I890" s="18"/>
       <c r="J890" s="18"/>
     </row>
-    <row r="891" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="891" spans="9:10">
       <c r="I891" s="18"/>
       <c r="J891" s="18"/>
     </row>
-    <row r="892" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="892" spans="9:10">
       <c r="I892" s="18"/>
       <c r="J892" s="18"/>
     </row>
-    <row r="893" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="893" spans="9:10">
       <c r="I893" s="18"/>
       <c r="J893" s="18"/>
     </row>
-    <row r="894" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="894" spans="9:10">
       <c r="I894" s="18"/>
       <c r="J894" s="18"/>
     </row>
-    <row r="895" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="895" spans="9:10">
       <c r="I895" s="18"/>
       <c r="J895" s="18"/>
     </row>
-    <row r="896" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="896" spans="9:10">
       <c r="I896" s="18"/>
       <c r="J896" s="18"/>
     </row>
-    <row r="897" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="897" spans="9:10">
       <c r="I897" s="18"/>
       <c r="J897" s="18"/>
     </row>
-    <row r="898" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="898" spans="9:10">
       <c r="I898" s="18"/>
       <c r="J898" s="18"/>
     </row>
-    <row r="899" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="899" spans="9:10">
       <c r="I899" s="18"/>
       <c r="J899" s="18"/>
     </row>
-    <row r="900" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="900" spans="9:10">
       <c r="I900" s="18"/>
       <c r="J900" s="18"/>
     </row>
-    <row r="901" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="901" spans="9:10">
       <c r="I901" s="18"/>
       <c r="J901" s="18"/>
     </row>
-    <row r="902" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="902" spans="9:10">
       <c r="I902" s="18"/>
       <c r="J902" s="18"/>
     </row>
-    <row r="903" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="903" spans="9:10">
       <c r="I903" s="18"/>
       <c r="J903" s="18"/>
     </row>
-    <row r="904" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="904" spans="9:10">
       <c r="I904" s="18"/>
       <c r="J904" s="18"/>
     </row>
-    <row r="905" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="905" spans="9:10">
       <c r="I905" s="18"/>
       <c r="J905" s="18"/>
     </row>
-    <row r="906" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="906" spans="9:10">
       <c r="I906" s="18"/>
       <c r="J906" s="18"/>
     </row>
-    <row r="907" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="907" spans="9:10">
       <c r="I907" s="18"/>
       <c r="J907" s="18"/>
     </row>
-    <row r="908" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="908" spans="9:10">
       <c r="I908" s="18"/>
       <c r="J908" s="18"/>
     </row>
-    <row r="909" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="909" spans="9:10">
       <c r="I909" s="18"/>
       <c r="J909" s="18"/>
     </row>
-    <row r="910" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="910" spans="9:10">
       <c r="I910" s="18"/>
       <c r="J910" s="18"/>
     </row>
-    <row r="911" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="911" spans="9:10">
       <c r="I911" s="18"/>
       <c r="J911" s="18"/>
     </row>
-    <row r="912" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="912" spans="9:10">
       <c r="I912" s="18"/>
       <c r="J912" s="18"/>
     </row>
-    <row r="913" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="913" spans="9:10">
       <c r="I913" s="18"/>
       <c r="J913" s="18"/>
     </row>
-    <row r="914" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="914" spans="9:10">
       <c r="I914" s="18"/>
       <c r="J914" s="18"/>
     </row>
-    <row r="915" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="915" spans="9:10">
       <c r="I915" s="18"/>
       <c r="J915" s="18"/>
     </row>
-    <row r="916" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="916" spans="9:10">
       <c r="I916" s="18"/>
       <c r="J916" s="18"/>
     </row>
-    <row r="917" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="917" spans="9:10">
       <c r="I917" s="18"/>
       <c r="J917" s="18"/>
     </row>
-    <row r="918" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="918" spans="9:10">
       <c r="I918" s="18"/>
       <c r="J918" s="18"/>
     </row>
-    <row r="919" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="919" spans="9:10">
       <c r="I919" s="18"/>
       <c r="J919" s="18"/>
     </row>
-    <row r="920" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="920" spans="9:10">
       <c r="I920" s="18"/>
       <c r="J920" s="18"/>
     </row>
-    <row r="921" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="921" spans="9:10">
       <c r="I921" s="18"/>
       <c r="J921" s="18"/>
     </row>
-    <row r="922" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="922" spans="9:10">
       <c r="I922" s="18"/>
       <c r="J922" s="18"/>
     </row>
-    <row r="923" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="923" spans="9:10">
       <c r="I923" s="18"/>
       <c r="J923" s="18"/>
     </row>
-    <row r="924" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="924" spans="9:10">
       <c r="I924" s="18"/>
       <c r="J924" s="18"/>
     </row>
-    <row r="925" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="925" spans="9:10">
       <c r="I925" s="18"/>
       <c r="J925" s="18"/>
     </row>
-    <row r="926" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="926" spans="9:10">
       <c r="I926" s="18"/>
       <c r="J926" s="18"/>
     </row>
-    <row r="927" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="927" spans="9:10">
       <c r="I927" s="18"/>
       <c r="J927" s="18"/>
     </row>
-    <row r="928" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="928" spans="9:10">
       <c r="I928" s="18"/>
       <c r="J928" s="18"/>
     </row>
-    <row r="929" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="929" spans="9:10">
       <c r="I929" s="18"/>
       <c r="J929" s="18"/>
     </row>
-    <row r="930" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="930" spans="9:10">
       <c r="I930" s="18"/>
       <c r="J930" s="18"/>
     </row>
-    <row r="931" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="931" spans="9:10">
       <c r="I931" s="18"/>
       <c r="J931" s="18"/>
     </row>
-    <row r="932" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="932" spans="9:10">
       <c r="I932" s="18"/>
       <c r="J932" s="18"/>
     </row>
-    <row r="933" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="933" spans="9:10">
       <c r="I933" s="18"/>
       <c r="J933" s="18"/>
     </row>
-    <row r="934" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="934" spans="9:10">
       <c r="I934" s="18"/>
       <c r="J934" s="18"/>
     </row>
-    <row r="935" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="935" spans="9:10">
       <c r="I935" s="18"/>
       <c r="J935" s="18"/>
     </row>
-    <row r="936" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="936" spans="9:10">
       <c r="I936" s="18"/>
       <c r="J936" s="18"/>
     </row>
-    <row r="937" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="937" spans="9:10">
       <c r="I937" s="18"/>
       <c r="J937" s="18"/>
     </row>
-    <row r="938" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="938" spans="9:10">
       <c r="I938" s="18"/>
       <c r="J938" s="18"/>
     </row>
-    <row r="939" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="939" spans="9:10">
       <c r="I939" s="18"/>
       <c r="J939" s="18"/>
     </row>
-    <row r="940" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="940" spans="9:10">
       <c r="I940" s="18"/>
       <c r="J940" s="18"/>
     </row>
-    <row r="941" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="941" spans="9:10">
       <c r="I941" s="18"/>
       <c r="J941" s="18"/>
     </row>
-    <row r="942" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="942" spans="9:10">
       <c r="I942" s="18"/>
       <c r="J942" s="18"/>
     </row>
-    <row r="943" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="943" spans="9:10">
       <c r="I943" s="18"/>
       <c r="J943" s="18"/>
     </row>
-    <row r="944" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="944" spans="9:10">
       <c r="I944" s="18"/>
       <c r="J944" s="18"/>
     </row>
-    <row r="945" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="945" spans="9:10">
       <c r="I945" s="18"/>
       <c r="J945" s="18"/>
     </row>
-    <row r="946" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="946" spans="9:10">
       <c r="I946" s="18"/>
       <c r="J946" s="18"/>
     </row>
-    <row r="947" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="947" spans="9:10">
       <c r="I947" s="18"/>
       <c r="J947" s="18"/>
     </row>
-    <row r="948" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="948" spans="9:10">
       <c r="I948" s="18"/>
       <c r="J948" s="18"/>
     </row>
-    <row r="949" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="949" spans="9:10">
       <c r="I949" s="18"/>
       <c r="J949" s="18"/>
     </row>
-    <row r="950" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="950" spans="9:10">
       <c r="I950" s="18"/>
       <c r="J950" s="18"/>
     </row>
-    <row r="951" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="951" spans="9:10">
       <c r="I951" s="18"/>
       <c r="J951" s="18"/>
     </row>
-    <row r="952" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="952" spans="9:10">
       <c r="I952" s="18"/>
       <c r="J952" s="18"/>
     </row>
-    <row r="953" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="953" spans="9:10">
       <c r="I953" s="18"/>
       <c r="J953" s="18"/>
     </row>
-    <row r="954" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="954" spans="9:10">
       <c r="I954" s="18"/>
       <c r="J954" s="18"/>
     </row>
-    <row r="955" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="955" spans="9:10">
       <c r="I955" s="18"/>
       <c r="J955" s="18"/>
     </row>
-    <row r="956" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="956" spans="9:10">
       <c r="I956" s="18"/>
       <c r="J956" s="18"/>
     </row>
-    <row r="957" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="957" spans="9:10">
       <c r="I957" s="18"/>
       <c r="J957" s="18"/>
     </row>
-    <row r="958" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="958" spans="9:10">
       <c r="I958" s="18"/>
       <c r="J958" s="18"/>
     </row>
-    <row r="959" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="959" spans="9:10">
       <c r="I959" s="18"/>
       <c r="J959" s="18"/>
     </row>
-    <row r="960" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="960" spans="9:10">
       <c r="I960" s="18"/>
       <c r="J960" s="18"/>
     </row>
-    <row r="961" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="961" spans="9:10">
       <c r="I961" s="18"/>
       <c r="J961" s="18"/>
     </row>
-    <row r="962" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="962" spans="9:10">
       <c r="I962" s="18"/>
       <c r="J962" s="18"/>
     </row>
-    <row r="963" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="963" spans="9:10">
       <c r="I963" s="18"/>
       <c r="J963" s="18"/>
     </row>
-    <row r="964" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="964" spans="9:10">
       <c r="I964" s="18"/>
       <c r="J964" s="18"/>
     </row>
-    <row r="965" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="965" spans="9:10">
       <c r="I965" s="18"/>
       <c r="J965" s="18"/>
     </row>
-    <row r="966" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="966" spans="9:10">
       <c r="I966" s="18"/>
       <c r="J966" s="18"/>
     </row>
-    <row r="967" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="967" spans="9:10">
       <c r="I967" s="18"/>
       <c r="J967" s="18"/>
     </row>
-    <row r="968" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="968" spans="9:10">
       <c r="I968" s="18"/>
       <c r="J968" s="18"/>
     </row>
-    <row r="969" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="969" spans="9:10">
       <c r="I969" s="18"/>
       <c r="J969" s="18"/>
     </row>
-    <row r="970" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="970" spans="9:10">
       <c r="I970" s="18"/>
       <c r="J970" s="18"/>
     </row>
-    <row r="971" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="971" spans="9:10">
       <c r="I971" s="18"/>
       <c r="J971" s="18"/>
     </row>
-    <row r="972" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="972" spans="9:10">
       <c r="I972" s="18"/>
       <c r="J972" s="18"/>
     </row>
-    <row r="973" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="973" spans="9:10">
       <c r="I973" s="18"/>
       <c r="J973" s="18"/>
     </row>
-    <row r="974" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="974" spans="9:10">
       <c r="I974" s="18"/>
       <c r="J974" s="18"/>
     </row>
-    <row r="975" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="975" spans="9:10">
       <c r="I975" s="18"/>
       <c r="J975" s="18"/>
     </row>
-    <row r="976" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="976" spans="9:10">
       <c r="I976" s="18"/>
       <c r="J976" s="18"/>
     </row>
-    <row r="977" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="977" spans="9:10">
       <c r="I977" s="18"/>
       <c r="J977" s="18"/>
     </row>
-    <row r="978" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="978" spans="9:10">
       <c r="I978" s="18"/>
       <c r="J978" s="18"/>
     </row>
-    <row r="979" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="979" spans="9:10">
       <c r="I979" s="18"/>
       <c r="J979" s="18"/>
     </row>
-    <row r="980" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="980" spans="9:10">
       <c r="I980" s="18"/>
       <c r="J980" s="18"/>
     </row>
-    <row r="981" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="981" spans="9:10">
       <c r="I981" s="18"/>
       <c r="J981" s="18"/>
     </row>
-    <row r="982" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="982" spans="9:10">
       <c r="I982" s="18"/>
       <c r="J982" s="18"/>
     </row>
-    <row r="983" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="983" spans="9:10">
       <c r="I983" s="18"/>
       <c r="J983" s="18"/>
     </row>
-    <row r="984" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="984" spans="9:10">
       <c r="I984" s="18"/>
       <c r="J984" s="18"/>
     </row>
-    <row r="985" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="985" spans="9:10">
       <c r="I985" s="18"/>
       <c r="J985" s="18"/>
     </row>
-    <row r="986" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="986" spans="9:10">
       <c r="I986" s="18"/>
       <c r="J986" s="18"/>
     </row>
-    <row r="987" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="987" spans="9:10">
       <c r="I987" s="18"/>
       <c r="J987" s="18"/>
     </row>
-    <row r="988" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="988" spans="9:10">
       <c r="I988" s="18"/>
       <c r="J988" s="18"/>
     </row>
-    <row r="989" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="989" spans="9:10">
       <c r="I989" s="18"/>
       <c r="J989" s="18"/>
     </row>
-    <row r="990" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="990" spans="9:10">
       <c r="I990" s="18"/>
       <c r="J990" s="18"/>
     </row>
-    <row r="991" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="991" spans="9:10">
       <c r="I991" s="18"/>
       <c r="J991" s="18"/>
     </row>
-    <row r="992" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="992" spans="9:10">
       <c r="I992" s="18"/>
       <c r="J992" s="18"/>
     </row>
-    <row r="993" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="993" spans="9:10">
       <c r="I993" s="18"/>
       <c r="J993" s="18"/>
     </row>
-    <row r="994" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="994" spans="9:10">
       <c r="I994" s="18"/>
       <c r="J994" s="18"/>
     </row>
-    <row r="995" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="995" spans="9:10">
       <c r="I995" s="18"/>
       <c r="J995" s="18"/>
     </row>
-    <row r="996" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="996" spans="9:10">
       <c r="I996" s="18"/>
       <c r="J996" s="18"/>
     </row>
-    <row r="997" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="997" spans="9:10">
       <c r="I997" s="18"/>
       <c r="J997" s="18"/>
     </row>
-    <row r="998" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="998" spans="9:10">
       <c r="I998" s="18"/>
       <c r="J998" s="18"/>
     </row>
-    <row r="999" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="999" spans="9:10">
       <c r="I999" s="18"/>
       <c r="J999" s="18"/>
     </row>
-    <row r="1000" spans="9:10" x14ac:dyDescent="0.25">
+    <row r="1000" spans="9:10">
       <c r="I1000" s="18"/>
       <c r="J1000" s="18"/>
     </row>
@@ -6796,27 +7428,27 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="24.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
         <v>142</v>
       </c>
@@ -6832,7 +7464,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="33.125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.625" bestFit="1" customWidth="1"/>
@@ -6840,7 +7472,7 @@
     <col min="4" max="4" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="5" customFormat="1">
       <c r="A1" s="5" t="s">
         <v>64</v>
       </c>
@@ -6854,7 +7486,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>143</v>
       </c>
@@ -6868,7 +7500,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>144</v>
       </c>
@@ -6882,7 +7514,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>145</v>
       </c>
@@ -6896,7 +7528,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>146</v>
       </c>
@@ -6910,7 +7542,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>147</v>
       </c>
@@ -6924,7 +7556,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>148</v>
       </c>
@@ -6938,7 +7570,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>149</v>
       </c>
@@ -6952,7 +7584,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>150</v>
       </c>
@@ -6966,7 +7598,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>151</v>
       </c>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2700B048-8402-4C59-9F5D-F3FC7B95A975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEB13C5-6C27-4EAE-BF18-4AE00ED47291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="235">
   <si>
     <t>id</t>
   </si>
@@ -1055,12 +1055,6 @@
     <t>كابل شحن وبيانات 6 امبير من (يو اس بى) الى (مايكرو) يدعم اعلى سرعة للشحن - لجميع الهواتف الذكية</t>
   </si>
   <si>
-    <t>https://www.facebook.com/iconixdistributions/?locale=fr_FR</t>
-  </si>
-  <si>
-    <t>https://btech.com/en/p/83d97840-5850-4f66-896e-49eadc9660eb</t>
-  </si>
-  <si>
     <t>https://i.ebayimg.com/images/g/d7kAAOSwsjZoQga-/s-l1600.webp
 https://i.ebayimg.com/images/g/e2kAAOSwU8FoQga-/s-l1600.webp
 https://i.ebayimg.com/images/g/EwEAAOSwPQloQga9/s-l1600.webp
@@ -1072,6 +1066,9 @@
   <si>
     <t>كابل 120 وات 6 امبير سوبر فاست كابل متعدد 3 في 1  لكل الهواتف والايفون  
 3-in-1 Multi Charging Cable – USB to iPhone/ Micro USB / Type-C 1.2M 120 w super fast charge 6 a</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/51h95iRUqrL._SL1080_.jpg</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1078,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1103,12 +1100,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
@@ -1125,20 +1116,49 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FF0F1111"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="48"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1111"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1147,39 +1167,39 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="10"/>
       <color rgb="FF0F1111"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF1F2328"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="17"/>
+      <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="R-font"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="10"/>
       <color rgb="FF404040"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="24"/>
+      <sz val="10"/>
       <color rgb="FF313133"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="17"/>
+      <sz val="10"/>
       <color rgb="FF191919"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1210,61 +1230,66 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1616,17 +1641,17 @@
     <col min="4" max="4" width="4.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1728,997 +1753,1106 @@
     <col min="17" max="17" width="17.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" t="s">
+    <row r="1" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="11" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="50.25" customHeight="1">
-      <c r="A2">
+    <row r="2" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="12">
         <v>110</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="12">
         <v>149</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="N2" t="s">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="9">
         <v>4</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="9">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="50.25" customHeight="1">
-      <c r="A3">
+      <c r="Q2" s="9"/>
+    </row>
+    <row r="3" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="12">
         <v>125</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="12">
         <v>181</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="N3" t="s">
+      <c r="M3" s="9"/>
+      <c r="N3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="9">
         <v>4</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="9">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="50.25" customHeight="1">
-      <c r="A4">
+      <c r="Q3" s="9"/>
+    </row>
+    <row r="4" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="12">
         <v>100</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="12">
         <v>125</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="N4" t="s">
+      <c r="M4" s="9"/>
+      <c r="N4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="9">
         <v>5</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="9">
         <v>20</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="162.75">
-      <c r="A5">
+      <c r="Q4" s="9"/>
+    </row>
+    <row r="5" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="12">
         <v>125</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="12">
         <v>150</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="L5" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="16">
         <v>46296</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
-      <c r="A6">
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+    </row>
+    <row r="6" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="12">
         <v>25</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="12">
         <v>50</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L6" t="s">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7">
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+    </row>
+    <row r="7" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="12">
         <v>25</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="12">
         <v>50</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L7" t="s">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="63">
-      <c r="A8">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+    </row>
+    <row r="8" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="12">
         <v>5</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="12">
         <v>20</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L8" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="63">
-      <c r="A9">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+    </row>
+    <row r="9" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="12">
         <v>10</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="12">
         <v>20</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L9" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="23.25">
-      <c r="A10">
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+    </row>
+    <row r="10" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="12">
         <v>35</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="12">
         <v>50</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L10" t="s">
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="126">
-      <c r="A11">
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+    </row>
+    <row r="11" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="12">
         <v>50</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="12">
         <v>60</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="K11" t="s">
+      <c r="J11" s="9"/>
+      <c r="K11" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="L11" s="8" t="s">
+      <c r="L11" s="15" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="46.5">
-      <c r="A12" s="11">
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+    </row>
+    <row r="12" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="18">
         <v>10</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="18">
         <v>15</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="13" t="s">
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="20">
         <v>46300.999305555553</v>
       </c>
-      <c r="N12" s="11" t="s">
+      <c r="N12" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="17">
         <v>4.5</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="17">
         <v>12</v>
       </c>
-      <c r="Q12" s="14">
+      <c r="Q12" s="20">
         <v>46270.999305555553</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="46.5">
-      <c r="A13" s="11">
+    <row r="13" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="18">
         <v>100</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="18">
         <v>150</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="H13" s="11" t="s">
+      <c r="H13" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="13" t="s">
+      <c r="J13" s="9"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="20">
         <v>46300.999305555553</v>
       </c>
-      <c r="N13" s="11" t="s">
+      <c r="N13" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="17">
         <v>4.5</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="17">
         <v>12</v>
       </c>
-      <c r="Q13" s="14">
+      <c r="Q13" s="20">
         <v>46270.999305555553</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="21.75">
-      <c r="A14">
+    <row r="14" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A14" s="9">
         <v>13</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="12">
         <v>40</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="12">
         <v>55</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="9" t="s">
         <v>208</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L14" s="19" t="s">
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="O14">
+      <c r="M14" s="9"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9">
         <v>3</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="9">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15">
+      <c r="Q14" s="9"/>
+    </row>
+    <row r="15" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A15" s="9">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="12">
         <v>80</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="12">
         <v>105</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L15" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="O15">
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9">
         <v>5</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="9">
         <v>20</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16">
+      <c r="Q15" s="9"/>
+    </row>
+    <row r="16" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A16" s="9">
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="12">
         <v>35</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="12">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L16" t="s">
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="O16">
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9">
         <v>4</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17">
+      <c r="Q16" s="9"/>
+    </row>
+    <row r="17" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A17" s="9">
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="12">
         <v>50</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="12">
         <v>65</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L17" t="s">
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="20">
         <v>46305.999305555553</v>
       </c>
-      <c r="O17">
+      <c r="N17" s="9"/>
+      <c r="O17" s="9">
         <v>5</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="63">
-      <c r="A18">
+      <c r="Q17" s="9"/>
+    </row>
+    <row r="18" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A18" s="9">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="12">
         <v>50</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="12">
         <v>75</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L18" s="8" t="s">
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="20">
         <v>46305.999305555553</v>
       </c>
-      <c r="O18">
+      <c r="N18" s="9"/>
+      <c r="O18" s="9">
         <v>3</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="9">
         <v>15</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="94.5">
-      <c r="A19">
+      <c r="Q18" s="9"/>
+    </row>
+    <row r="19" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A19" s="9">
         <v>18</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="12">
+        <v>20</v>
+      </c>
+      <c r="D19" s="12">
         <v>35</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9">
+        <v>5</v>
+      </c>
+      <c r="P19" s="9">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="9"/>
+    </row>
+    <row r="20" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A20" s="9">
+        <v>19</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="12">
         <v>20</v>
       </c>
-      <c r="E19" t="s">
-        <v>222</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="H19" t="s">
+      <c r="D20" s="12">
+        <v>35</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I20" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L19" t="s">
-        <v>222</v>
-      </c>
-      <c r="O19">
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9">
         <v>5</v>
       </c>
-      <c r="P19">
+      <c r="P20" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="139.5">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="Q20" s="9"/>
+    </row>
+    <row r="21" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A21" s="9">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="12">
+        <v>20</v>
+      </c>
+      <c r="D21" s="12">
         <v>35</v>
       </c>
-      <c r="D20" s="1">
-        <v>20</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="F20" t="s">
-        <v>224</v>
-      </c>
-      <c r="G20" t="s">
-        <v>224</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="E21" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I21" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L20" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="O20">
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9">
         <v>5</v>
       </c>
-      <c r="P20">
+      <c r="P21" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="63">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="Q21" s="9"/>
+    </row>
+    <row r="22" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A22" s="9">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="C22" s="12">
+        <v>30</v>
+      </c>
+      <c r="D22" s="12">
+        <v>45</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="M22" s="9"/>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9">
+        <v>5</v>
+      </c>
+      <c r="P22" s="9">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="9"/>
+    </row>
+    <row r="23" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A23" s="9">
+        <v>22</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="C23" s="12">
         <v>35</v>
       </c>
-      <c r="D21" s="1">
-        <v>20</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="D23" s="12">
+        <v>50</v>
+      </c>
+      <c r="E23" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I23" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O21">
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9">
         <v>5</v>
       </c>
-      <c r="P21">
+      <c r="P23" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="93">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="Q23" s="9"/>
+    </row>
+    <row r="24" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A24" s="9">
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="C24" s="12">
+        <v>30</v>
+      </c>
+      <c r="D24" s="12">
         <v>45</v>
       </c>
-      <c r="D22" s="1">
-        <v>30</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="F22" t="s">
-        <v>227</v>
-      </c>
-      <c r="G22" t="s">
-        <v>227</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="E24" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H24" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I24" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L22" s="20" t="s">
-        <v>228</v>
-      </c>
-      <c r="O22">
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="M24" s="9"/>
+      <c r="N24" s="9"/>
+      <c r="O24" s="9">
         <v>5</v>
       </c>
-      <c r="P22">
+      <c r="P24" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="337.5">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="Q24" s="9"/>
+    </row>
+    <row r="25" spans="1:17" ht="48.75" customHeight="1">
+      <c r="A25" s="9">
+        <v>24</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="12">
         <v>50</v>
       </c>
-      <c r="D23" s="1">
-        <v>35</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="F23" t="s">
-        <v>232</v>
-      </c>
-      <c r="G23" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="D25" s="12">
+        <v>90</v>
+      </c>
+      <c r="E25" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I25" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="L23" s="21" t="s">
-        <v>229</v>
-      </c>
-      <c r="O23">
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="M25" s="20">
+        <v>46305.999305555553</v>
+      </c>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9">
         <v>5</v>
       </c>
-      <c r="P23">
+      <c r="P25" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="337.5">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="C24" s="1">
-        <v>45</v>
-      </c>
-      <c r="D24" s="1">
-        <v>30</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="F24" t="s">
-        <v>231</v>
-      </c>
-      <c r="G24" t="s">
-        <v>231</v>
-      </c>
-      <c r="H24" t="s">
-        <v>83</v>
-      </c>
-      <c r="I24" t="s">
-        <v>182</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="O24">
-        <v>5</v>
-      </c>
-      <c r="P24">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="130.5">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="C25" s="1">
-        <v>90</v>
-      </c>
-      <c r="D25" s="1">
-        <v>50</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="H25" t="s">
-        <v>83</v>
-      </c>
-      <c r="I25" t="s">
-        <v>182</v>
-      </c>
-      <c r="L25" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="M25" s="14">
-        <v>46305.999305555553</v>
-      </c>
-      <c r="O25">
-        <v>5</v>
-      </c>
-      <c r="P25">
-        <v>25</v>
-      </c>
+      <c r="Q25" s="9"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2880,7 +3014,7 @@
       <c r="B2" t="s">
         <v>136</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>137</v>
       </c>
       <c r="D2" t="s">
@@ -2889,7 +3023,7 @@
       <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>0.46505787037037039</v>
       </c>
       <c r="G2" t="s">
@@ -3056,7 +3190,7 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="10">
+      <c r="A4" s="5">
         <v>12345</v>
       </c>
       <c r="B4">
@@ -3073,7 +3207,7 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="10">
+      <c r="A5" s="5">
         <v>14521</v>
       </c>
       <c r="B5">
@@ -3311,4081 +3445,4081 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="H1" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="16" t="s">
+      <c r="I1" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J1" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="K1" s="16" t="s">
+      <c r="K1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="16" t="s">
+      <c r="L1" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="6" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="4" customFormat="1" ht="48" customHeight="1">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="48" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="1">
         <v>12</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="1">
         <v>3</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
     </row>
     <row r="17" spans="9:10">
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
     </row>
     <row r="18" spans="9:10">
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
     </row>
     <row r="19" spans="9:10">
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
     </row>
     <row r="20" spans="9:10">
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
     </row>
     <row r="21" spans="9:10">
-      <c r="I21" s="18"/>
-      <c r="J21" s="18"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
     </row>
     <row r="22" spans="9:10">
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
     </row>
     <row r="23" spans="9:10">
-      <c r="I23" s="18"/>
-      <c r="J23" s="18"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
     </row>
     <row r="24" spans="9:10">
-      <c r="I24" s="18"/>
-      <c r="J24" s="18"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
     </row>
     <row r="25" spans="9:10">
-      <c r="I25" s="18"/>
-      <c r="J25" s="18"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
     </row>
     <row r="26" spans="9:10">
-      <c r="I26" s="18"/>
-      <c r="J26" s="18"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
     </row>
     <row r="27" spans="9:10">
-      <c r="I27" s="18"/>
-      <c r="J27" s="18"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
     </row>
     <row r="28" spans="9:10">
-      <c r="I28" s="18"/>
-      <c r="J28" s="18"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
     </row>
     <row r="29" spans="9:10">
-      <c r="I29" s="18"/>
-      <c r="J29" s="18"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
     </row>
     <row r="30" spans="9:10">
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
     </row>
     <row r="31" spans="9:10">
-      <c r="I31" s="18"/>
-      <c r="J31" s="18"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
     </row>
     <row r="32" spans="9:10">
-      <c r="I32" s="18"/>
-      <c r="J32" s="18"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
     </row>
     <row r="33" spans="9:10">
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
     </row>
     <row r="34" spans="9:10">
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
     </row>
     <row r="35" spans="9:10">
-      <c r="I35" s="18"/>
-      <c r="J35" s="18"/>
+      <c r="I35" s="8"/>
+      <c r="J35" s="8"/>
     </row>
     <row r="36" spans="9:10">
-      <c r="I36" s="18"/>
-      <c r="J36" s="18"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
     </row>
     <row r="37" spans="9:10">
-      <c r="I37" s="18"/>
-      <c r="J37" s="18"/>
+      <c r="I37" s="8"/>
+      <c r="J37" s="8"/>
     </row>
     <row r="38" spans="9:10">
-      <c r="I38" s="18"/>
-      <c r="J38" s="18"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
     </row>
     <row r="39" spans="9:10">
-      <c r="I39" s="18"/>
-      <c r="J39" s="18"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
     </row>
     <row r="40" spans="9:10">
-      <c r="I40" s="18"/>
-      <c r="J40" s="18"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
     </row>
     <row r="41" spans="9:10">
-      <c r="I41" s="18"/>
-      <c r="J41" s="18"/>
+      <c r="I41" s="8"/>
+      <c r="J41" s="8"/>
     </row>
     <row r="42" spans="9:10">
-      <c r="I42" s="18"/>
-      <c r="J42" s="18"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
     </row>
     <row r="43" spans="9:10">
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
     </row>
     <row r="44" spans="9:10">
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
     </row>
     <row r="45" spans="9:10">
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
     </row>
     <row r="46" spans="9:10">
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
     </row>
     <row r="47" spans="9:10">
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
+      <c r="I47" s="8"/>
+      <c r="J47" s="8"/>
     </row>
     <row r="48" spans="9:10">
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
     </row>
     <row r="49" spans="9:10">
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
+      <c r="I49" s="8"/>
+      <c r="J49" s="8"/>
     </row>
     <row r="50" spans="9:10">
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
     </row>
     <row r="51" spans="9:10">
-      <c r="I51" s="18"/>
-      <c r="J51" s="18"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
     </row>
     <row r="52" spans="9:10">
-      <c r="I52" s="18"/>
-      <c r="J52" s="18"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
     </row>
     <row r="53" spans="9:10">
-      <c r="I53" s="18"/>
-      <c r="J53" s="18"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
     </row>
     <row r="54" spans="9:10">
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
     </row>
     <row r="55" spans="9:10">
-      <c r="I55" s="18"/>
-      <c r="J55" s="18"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
     </row>
     <row r="56" spans="9:10">
-      <c r="I56" s="18"/>
-      <c r="J56" s="18"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
     </row>
     <row r="57" spans="9:10">
-      <c r="I57" s="18"/>
-      <c r="J57" s="18"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
     </row>
     <row r="58" spans="9:10">
-      <c r="I58" s="18"/>
-      <c r="J58" s="18"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
     </row>
     <row r="59" spans="9:10">
-      <c r="I59" s="18"/>
-      <c r="J59" s="18"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
     </row>
     <row r="60" spans="9:10">
-      <c r="I60" s="18"/>
-      <c r="J60" s="18"/>
+      <c r="I60" s="8"/>
+      <c r="J60" s="8"/>
     </row>
     <row r="61" spans="9:10">
-      <c r="I61" s="18"/>
-      <c r="J61" s="18"/>
+      <c r="I61" s="8"/>
+      <c r="J61" s="8"/>
     </row>
     <row r="62" spans="9:10">
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
+      <c r="I62" s="8"/>
+      <c r="J62" s="8"/>
     </row>
     <row r="63" spans="9:10">
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
+      <c r="I63" s="8"/>
+      <c r="J63" s="8"/>
     </row>
     <row r="64" spans="9:10">
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
+      <c r="I64" s="8"/>
+      <c r="J64" s="8"/>
     </row>
     <row r="65" spans="9:10">
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
     </row>
     <row r="66" spans="9:10">
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
+      <c r="I66" s="8"/>
+      <c r="J66" s="8"/>
     </row>
     <row r="67" spans="9:10">
-      <c r="I67" s="18"/>
-      <c r="J67" s="18"/>
+      <c r="I67" s="8"/>
+      <c r="J67" s="8"/>
     </row>
     <row r="68" spans="9:10">
-      <c r="I68" s="18"/>
-      <c r="J68" s="18"/>
+      <c r="I68" s="8"/>
+      <c r="J68" s="8"/>
     </row>
     <row r="69" spans="9:10">
-      <c r="I69" s="18"/>
-      <c r="J69" s="18"/>
+      <c r="I69" s="8"/>
+      <c r="J69" s="8"/>
     </row>
     <row r="70" spans="9:10">
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
     </row>
     <row r="71" spans="9:10">
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
+      <c r="I71" s="8"/>
+      <c r="J71" s="8"/>
     </row>
     <row r="72" spans="9:10">
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
     </row>
     <row r="73" spans="9:10">
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
+      <c r="I73" s="8"/>
+      <c r="J73" s="8"/>
     </row>
     <row r="74" spans="9:10">
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
     </row>
     <row r="75" spans="9:10">
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
     </row>
     <row r="76" spans="9:10">
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
+      <c r="I76" s="8"/>
+      <c r="J76" s="8"/>
     </row>
     <row r="77" spans="9:10">
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
+      <c r="I77" s="8"/>
+      <c r="J77" s="8"/>
     </row>
     <row r="78" spans="9:10">
-      <c r="I78" s="18"/>
-      <c r="J78" s="18"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
     </row>
     <row r="79" spans="9:10">
-      <c r="I79" s="18"/>
-      <c r="J79" s="18"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
     </row>
     <row r="80" spans="9:10">
-      <c r="I80" s="18"/>
-      <c r="J80" s="18"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
     </row>
     <row r="81" spans="9:10">
-      <c r="I81" s="18"/>
-      <c r="J81" s="18"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
     </row>
     <row r="82" spans="9:10">
-      <c r="I82" s="18"/>
-      <c r="J82" s="18"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
     </row>
     <row r="83" spans="9:10">
-      <c r="I83" s="18"/>
-      <c r="J83" s="18"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
     </row>
     <row r="84" spans="9:10">
-      <c r="I84" s="18"/>
-      <c r="J84" s="18"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
     </row>
     <row r="85" spans="9:10">
-      <c r="I85" s="18"/>
-      <c r="J85" s="18"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
     </row>
     <row r="86" spans="9:10">
-      <c r="I86" s="18"/>
-      <c r="J86" s="18"/>
+      <c r="I86" s="8"/>
+      <c r="J86" s="8"/>
     </row>
     <row r="87" spans="9:10">
-      <c r="I87" s="18"/>
-      <c r="J87" s="18"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="8"/>
     </row>
     <row r="88" spans="9:10">
-      <c r="I88" s="18"/>
-      <c r="J88" s="18"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="8"/>
     </row>
     <row r="89" spans="9:10">
-      <c r="I89" s="18"/>
-      <c r="J89" s="18"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="8"/>
     </row>
     <row r="90" spans="9:10">
-      <c r="I90" s="18"/>
-      <c r="J90" s="18"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="8"/>
     </row>
     <row r="91" spans="9:10">
-      <c r="I91" s="18"/>
-      <c r="J91" s="18"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="8"/>
     </row>
     <row r="92" spans="9:10">
-      <c r="I92" s="18"/>
-      <c r="J92" s="18"/>
+      <c r="I92" s="8"/>
+      <c r="J92" s="8"/>
     </row>
     <row r="93" spans="9:10">
-      <c r="I93" s="18"/>
-      <c r="J93" s="18"/>
+      <c r="I93" s="8"/>
+      <c r="J93" s="8"/>
     </row>
     <row r="94" spans="9:10">
-      <c r="I94" s="18"/>
-      <c r="J94" s="18"/>
+      <c r="I94" s="8"/>
+      <c r="J94" s="8"/>
     </row>
     <row r="95" spans="9:10">
-      <c r="I95" s="18"/>
-      <c r="J95" s="18"/>
+      <c r="I95" s="8"/>
+      <c r="J95" s="8"/>
     </row>
     <row r="96" spans="9:10">
-      <c r="I96" s="18"/>
-      <c r="J96" s="18"/>
+      <c r="I96" s="8"/>
+      <c r="J96" s="8"/>
     </row>
     <row r="97" spans="9:10">
-      <c r="I97" s="18"/>
-      <c r="J97" s="18"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
     </row>
     <row r="98" spans="9:10">
-      <c r="I98" s="18"/>
-      <c r="J98" s="18"/>
+      <c r="I98" s="8"/>
+      <c r="J98" s="8"/>
     </row>
     <row r="99" spans="9:10">
-      <c r="I99" s="18"/>
-      <c r="J99" s="18"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
     </row>
     <row r="100" spans="9:10">
-      <c r="I100" s="18"/>
-      <c r="J100" s="18"/>
+      <c r="I100" s="8"/>
+      <c r="J100" s="8"/>
     </row>
     <row r="101" spans="9:10">
-      <c r="I101" s="18"/>
-      <c r="J101" s="18"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
     </row>
     <row r="102" spans="9:10">
-      <c r="I102" s="18"/>
-      <c r="J102" s="18"/>
+      <c r="I102" s="8"/>
+      <c r="J102" s="8"/>
     </row>
     <row r="103" spans="9:10">
-      <c r="I103" s="18"/>
-      <c r="J103" s="18"/>
+      <c r="I103" s="8"/>
+      <c r="J103" s="8"/>
     </row>
     <row r="104" spans="9:10">
-      <c r="I104" s="18"/>
-      <c r="J104" s="18"/>
+      <c r="I104" s="8"/>
+      <c r="J104" s="8"/>
     </row>
     <row r="105" spans="9:10">
-      <c r="I105" s="18"/>
-      <c r="J105" s="18"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
     </row>
     <row r="106" spans="9:10">
-      <c r="I106" s="18"/>
-      <c r="J106" s="18"/>
+      <c r="I106" s="8"/>
+      <c r="J106" s="8"/>
     </row>
     <row r="107" spans="9:10">
-      <c r="I107" s="18"/>
-      <c r="J107" s="18"/>
+      <c r="I107" s="8"/>
+      <c r="J107" s="8"/>
     </row>
     <row r="108" spans="9:10">
-      <c r="I108" s="18"/>
-      <c r="J108" s="18"/>
+      <c r="I108" s="8"/>
+      <c r="J108" s="8"/>
     </row>
     <row r="109" spans="9:10">
-      <c r="I109" s="18"/>
-      <c r="J109" s="18"/>
+      <c r="I109" s="8"/>
+      <c r="J109" s="8"/>
     </row>
     <row r="110" spans="9:10">
-      <c r="I110" s="18"/>
-      <c r="J110" s="18"/>
+      <c r="I110" s="8"/>
+      <c r="J110" s="8"/>
     </row>
     <row r="111" spans="9:10">
-      <c r="I111" s="18"/>
-      <c r="J111" s="18"/>
+      <c r="I111" s="8"/>
+      <c r="J111" s="8"/>
     </row>
     <row r="112" spans="9:10">
-      <c r="I112" s="18"/>
-      <c r="J112" s="18"/>
+      <c r="I112" s="8"/>
+      <c r="J112" s="8"/>
     </row>
     <row r="113" spans="9:10">
-      <c r="I113" s="18"/>
-      <c r="J113" s="18"/>
+      <c r="I113" s="8"/>
+      <c r="J113" s="8"/>
     </row>
     <row r="114" spans="9:10">
-      <c r="I114" s="18"/>
-      <c r="J114" s="18"/>
+      <c r="I114" s="8"/>
+      <c r="J114" s="8"/>
     </row>
     <row r="115" spans="9:10">
-      <c r="I115" s="18"/>
-      <c r="J115" s="18"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
     </row>
     <row r="116" spans="9:10">
-      <c r="I116" s="18"/>
-      <c r="J116" s="18"/>
+      <c r="I116" s="8"/>
+      <c r="J116" s="8"/>
     </row>
     <row r="117" spans="9:10">
-      <c r="I117" s="18"/>
-      <c r="J117" s="18"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
     </row>
     <row r="118" spans="9:10">
-      <c r="I118" s="18"/>
-      <c r="J118" s="18"/>
+      <c r="I118" s="8"/>
+      <c r="J118" s="8"/>
     </row>
     <row r="119" spans="9:10">
-      <c r="I119" s="18"/>
-      <c r="J119" s="18"/>
+      <c r="I119" s="8"/>
+      <c r="J119" s="8"/>
     </row>
     <row r="120" spans="9:10">
-      <c r="I120" s="18"/>
-      <c r="J120" s="18"/>
+      <c r="I120" s="8"/>
+      <c r="J120" s="8"/>
     </row>
     <row r="121" spans="9:10">
-      <c r="I121" s="18"/>
-      <c r="J121" s="18"/>
+      <c r="I121" s="8"/>
+      <c r="J121" s="8"/>
     </row>
     <row r="122" spans="9:10">
-      <c r="I122" s="18"/>
-      <c r="J122" s="18"/>
+      <c r="I122" s="8"/>
+      <c r="J122" s="8"/>
     </row>
     <row r="123" spans="9:10">
-      <c r="I123" s="18"/>
-      <c r="J123" s="18"/>
+      <c r="I123" s="8"/>
+      <c r="J123" s="8"/>
     </row>
     <row r="124" spans="9:10">
-      <c r="I124" s="18"/>
-      <c r="J124" s="18"/>
+      <c r="I124" s="8"/>
+      <c r="J124" s="8"/>
     </row>
     <row r="125" spans="9:10">
-      <c r="I125" s="18"/>
-      <c r="J125" s="18"/>
+      <c r="I125" s="8"/>
+      <c r="J125" s="8"/>
     </row>
     <row r="126" spans="9:10">
-      <c r="I126" s="18"/>
-      <c r="J126" s="18"/>
+      <c r="I126" s="8"/>
+      <c r="J126" s="8"/>
     </row>
     <row r="127" spans="9:10">
-      <c r="I127" s="18"/>
-      <c r="J127" s="18"/>
+      <c r="I127" s="8"/>
+      <c r="J127" s="8"/>
     </row>
     <row r="128" spans="9:10">
-      <c r="I128" s="18"/>
-      <c r="J128" s="18"/>
+      <c r="I128" s="8"/>
+      <c r="J128" s="8"/>
     </row>
     <row r="129" spans="9:10">
-      <c r="I129" s="18"/>
-      <c r="J129" s="18"/>
+      <c r="I129" s="8"/>
+      <c r="J129" s="8"/>
     </row>
     <row r="130" spans="9:10">
-      <c r="I130" s="18"/>
-      <c r="J130" s="18"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
     </row>
     <row r="131" spans="9:10">
-      <c r="I131" s="18"/>
-      <c r="J131" s="18"/>
+      <c r="I131" s="8"/>
+      <c r="J131" s="8"/>
     </row>
     <row r="132" spans="9:10">
-      <c r="I132" s="18"/>
-      <c r="J132" s="18"/>
+      <c r="I132" s="8"/>
+      <c r="J132" s="8"/>
     </row>
     <row r="133" spans="9:10">
-      <c r="I133" s="18"/>
-      <c r="J133" s="18"/>
+      <c r="I133" s="8"/>
+      <c r="J133" s="8"/>
     </row>
     <row r="134" spans="9:10">
-      <c r="I134" s="18"/>
-      <c r="J134" s="18"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8"/>
     </row>
     <row r="135" spans="9:10">
-      <c r="I135" s="18"/>
-      <c r="J135" s="18"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8"/>
     </row>
     <row r="136" spans="9:10">
-      <c r="I136" s="18"/>
-      <c r="J136" s="18"/>
+      <c r="I136" s="8"/>
+      <c r="J136" s="8"/>
     </row>
     <row r="137" spans="9:10">
-      <c r="I137" s="18"/>
-      <c r="J137" s="18"/>
+      <c r="I137" s="8"/>
+      <c r="J137" s="8"/>
     </row>
     <row r="138" spans="9:10">
-      <c r="I138" s="18"/>
-      <c r="J138" s="18"/>
+      <c r="I138" s="8"/>
+      <c r="J138" s="8"/>
     </row>
     <row r="139" spans="9:10">
-      <c r="I139" s="18"/>
-      <c r="J139" s="18"/>
+      <c r="I139" s="8"/>
+      <c r="J139" s="8"/>
     </row>
     <row r="140" spans="9:10">
-      <c r="I140" s="18"/>
-      <c r="J140" s="18"/>
+      <c r="I140" s="8"/>
+      <c r="J140" s="8"/>
     </row>
     <row r="141" spans="9:10">
-      <c r="I141" s="18"/>
-      <c r="J141" s="18"/>
+      <c r="I141" s="8"/>
+      <c r="J141" s="8"/>
     </row>
     <row r="142" spans="9:10">
-      <c r="I142" s="18"/>
-      <c r="J142" s="18"/>
+      <c r="I142" s="8"/>
+      <c r="J142" s="8"/>
     </row>
     <row r="143" spans="9:10">
-      <c r="I143" s="18"/>
-      <c r="J143" s="18"/>
+      <c r="I143" s="8"/>
+      <c r="J143" s="8"/>
     </row>
     <row r="144" spans="9:10">
-      <c r="I144" s="18"/>
-      <c r="J144" s="18"/>
+      <c r="I144" s="8"/>
+      <c r="J144" s="8"/>
     </row>
     <row r="145" spans="9:10">
-      <c r="I145" s="18"/>
-      <c r="J145" s="18"/>
+      <c r="I145" s="8"/>
+      <c r="J145" s="8"/>
     </row>
     <row r="146" spans="9:10">
-      <c r="I146" s="18"/>
-      <c r="J146" s="18"/>
+      <c r="I146" s="8"/>
+      <c r="J146" s="8"/>
     </row>
     <row r="147" spans="9:10">
-      <c r="I147" s="18"/>
-      <c r="J147" s="18"/>
+      <c r="I147" s="8"/>
+      <c r="J147" s="8"/>
     </row>
     <row r="148" spans="9:10">
-      <c r="I148" s="18"/>
-      <c r="J148" s="18"/>
+      <c r="I148" s="8"/>
+      <c r="J148" s="8"/>
     </row>
     <row r="149" spans="9:10">
-      <c r="I149" s="18"/>
-      <c r="J149" s="18"/>
+      <c r="I149" s="8"/>
+      <c r="J149" s="8"/>
     </row>
     <row r="150" spans="9:10">
-      <c r="I150" s="18"/>
-      <c r="J150" s="18"/>
+      <c r="I150" s="8"/>
+      <c r="J150" s="8"/>
     </row>
     <row r="151" spans="9:10">
-      <c r="I151" s="18"/>
-      <c r="J151" s="18"/>
+      <c r="I151" s="8"/>
+      <c r="J151" s="8"/>
     </row>
     <row r="152" spans="9:10">
-      <c r="I152" s="18"/>
-      <c r="J152" s="18"/>
+      <c r="I152" s="8"/>
+      <c r="J152" s="8"/>
     </row>
     <row r="153" spans="9:10">
-      <c r="I153" s="18"/>
-      <c r="J153" s="18"/>
+      <c r="I153" s="8"/>
+      <c r="J153" s="8"/>
     </row>
     <row r="154" spans="9:10">
-      <c r="I154" s="18"/>
-      <c r="J154" s="18"/>
+      <c r="I154" s="8"/>
+      <c r="J154" s="8"/>
     </row>
     <row r="155" spans="9:10">
-      <c r="I155" s="18"/>
-      <c r="J155" s="18"/>
+      <c r="I155" s="8"/>
+      <c r="J155" s="8"/>
     </row>
     <row r="156" spans="9:10">
-      <c r="I156" s="18"/>
-      <c r="J156" s="18"/>
+      <c r="I156" s="8"/>
+      <c r="J156" s="8"/>
     </row>
     <row r="157" spans="9:10">
-      <c r="I157" s="18"/>
-      <c r="J157" s="18"/>
+      <c r="I157" s="8"/>
+      <c r="J157" s="8"/>
     </row>
     <row r="158" spans="9:10">
-      <c r="I158" s="18"/>
-      <c r="J158" s="18"/>
+      <c r="I158" s="8"/>
+      <c r="J158" s="8"/>
     </row>
     <row r="159" spans="9:10">
-      <c r="I159" s="18"/>
-      <c r="J159" s="18"/>
+      <c r="I159" s="8"/>
+      <c r="J159" s="8"/>
     </row>
     <row r="160" spans="9:10">
-      <c r="I160" s="18"/>
-      <c r="J160" s="18"/>
+      <c r="I160" s="8"/>
+      <c r="J160" s="8"/>
     </row>
     <row r="161" spans="9:10">
-      <c r="I161" s="18"/>
-      <c r="J161" s="18"/>
+      <c r="I161" s="8"/>
+      <c r="J161" s="8"/>
     </row>
     <row r="162" spans="9:10">
-      <c r="I162" s="18"/>
-      <c r="J162" s="18"/>
+      <c r="I162" s="8"/>
+      <c r="J162" s="8"/>
     </row>
     <row r="163" spans="9:10">
-      <c r="I163" s="18"/>
-      <c r="J163" s="18"/>
+      <c r="I163" s="8"/>
+      <c r="J163" s="8"/>
     </row>
     <row r="164" spans="9:10">
-      <c r="I164" s="18"/>
-      <c r="J164" s="18"/>
+      <c r="I164" s="8"/>
+      <c r="J164" s="8"/>
     </row>
     <row r="165" spans="9:10">
-      <c r="I165" s="18"/>
-      <c r="J165" s="18"/>
+      <c r="I165" s="8"/>
+      <c r="J165" s="8"/>
     </row>
     <row r="166" spans="9:10">
-      <c r="I166" s="18"/>
-      <c r="J166" s="18"/>
+      <c r="I166" s="8"/>
+      <c r="J166" s="8"/>
     </row>
     <row r="167" spans="9:10">
-      <c r="I167" s="18"/>
-      <c r="J167" s="18"/>
+      <c r="I167" s="8"/>
+      <c r="J167" s="8"/>
     </row>
     <row r="168" spans="9:10">
-      <c r="I168" s="18"/>
-      <c r="J168" s="18"/>
+      <c r="I168" s="8"/>
+      <c r="J168" s="8"/>
     </row>
     <row r="169" spans="9:10">
-      <c r="I169" s="18"/>
-      <c r="J169" s="18"/>
+      <c r="I169" s="8"/>
+      <c r="J169" s="8"/>
     </row>
     <row r="170" spans="9:10">
-      <c r="I170" s="18"/>
-      <c r="J170" s="18"/>
+      <c r="I170" s="8"/>
+      <c r="J170" s="8"/>
     </row>
     <row r="171" spans="9:10">
-      <c r="I171" s="18"/>
-      <c r="J171" s="18"/>
+      <c r="I171" s="8"/>
+      <c r="J171" s="8"/>
     </row>
     <row r="172" spans="9:10">
-      <c r="I172" s="18"/>
-      <c r="J172" s="18"/>
+      <c r="I172" s="8"/>
+      <c r="J172" s="8"/>
     </row>
     <row r="173" spans="9:10">
-      <c r="I173" s="18"/>
-      <c r="J173" s="18"/>
+      <c r="I173" s="8"/>
+      <c r="J173" s="8"/>
     </row>
     <row r="174" spans="9:10">
-      <c r="I174" s="18"/>
-      <c r="J174" s="18"/>
+      <c r="I174" s="8"/>
+      <c r="J174" s="8"/>
     </row>
     <row r="175" spans="9:10">
-      <c r="I175" s="18"/>
-      <c r="J175" s="18"/>
+      <c r="I175" s="8"/>
+      <c r="J175" s="8"/>
     </row>
     <row r="176" spans="9:10">
-      <c r="I176" s="18"/>
-      <c r="J176" s="18"/>
+      <c r="I176" s="8"/>
+      <c r="J176" s="8"/>
     </row>
     <row r="177" spans="9:10">
-      <c r="I177" s="18"/>
-      <c r="J177" s="18"/>
+      <c r="I177" s="8"/>
+      <c r="J177" s="8"/>
     </row>
     <row r="178" spans="9:10">
-      <c r="I178" s="18"/>
-      <c r="J178" s="18"/>
+      <c r="I178" s="8"/>
+      <c r="J178" s="8"/>
     </row>
     <row r="179" spans="9:10">
-      <c r="I179" s="18"/>
-      <c r="J179" s="18"/>
+      <c r="I179" s="8"/>
+      <c r="J179" s="8"/>
     </row>
     <row r="180" spans="9:10">
-      <c r="I180" s="18"/>
-      <c r="J180" s="18"/>
+      <c r="I180" s="8"/>
+      <c r="J180" s="8"/>
     </row>
     <row r="181" spans="9:10">
-      <c r="I181" s="18"/>
-      <c r="J181" s="18"/>
+      <c r="I181" s="8"/>
+      <c r="J181" s="8"/>
     </row>
     <row r="182" spans="9:10">
-      <c r="I182" s="18"/>
-      <c r="J182" s="18"/>
+      <c r="I182" s="8"/>
+      <c r="J182" s="8"/>
     </row>
     <row r="183" spans="9:10">
-      <c r="I183" s="18"/>
-      <c r="J183" s="18"/>
+      <c r="I183" s="8"/>
+      <c r="J183" s="8"/>
     </row>
     <row r="184" spans="9:10">
-      <c r="I184" s="18"/>
-      <c r="J184" s="18"/>
+      <c r="I184" s="8"/>
+      <c r="J184" s="8"/>
     </row>
     <row r="185" spans="9:10">
-      <c r="I185" s="18"/>
-      <c r="J185" s="18"/>
+      <c r="I185" s="8"/>
+      <c r="J185" s="8"/>
     </row>
     <row r="186" spans="9:10">
-      <c r="I186" s="18"/>
-      <c r="J186" s="18"/>
+      <c r="I186" s="8"/>
+      <c r="J186" s="8"/>
     </row>
     <row r="187" spans="9:10">
-      <c r="I187" s="18"/>
-      <c r="J187" s="18"/>
+      <c r="I187" s="8"/>
+      <c r="J187" s="8"/>
     </row>
     <row r="188" spans="9:10">
-      <c r="I188" s="18"/>
-      <c r="J188" s="18"/>
+      <c r="I188" s="8"/>
+      <c r="J188" s="8"/>
     </row>
     <row r="189" spans="9:10">
-      <c r="I189" s="18"/>
-      <c r="J189" s="18"/>
+      <c r="I189" s="8"/>
+      <c r="J189" s="8"/>
     </row>
     <row r="190" spans="9:10">
-      <c r="I190" s="18"/>
-      <c r="J190" s="18"/>
+      <c r="I190" s="8"/>
+      <c r="J190" s="8"/>
     </row>
     <row r="191" spans="9:10">
-      <c r="I191" s="18"/>
-      <c r="J191" s="18"/>
+      <c r="I191" s="8"/>
+      <c r="J191" s="8"/>
     </row>
     <row r="192" spans="9:10">
-      <c r="I192" s="18"/>
-      <c r="J192" s="18"/>
+      <c r="I192" s="8"/>
+      <c r="J192" s="8"/>
     </row>
     <row r="193" spans="9:10">
-      <c r="I193" s="18"/>
-      <c r="J193" s="18"/>
+      <c r="I193" s="8"/>
+      <c r="J193" s="8"/>
     </row>
     <row r="194" spans="9:10">
-      <c r="I194" s="18"/>
-      <c r="J194" s="18"/>
+      <c r="I194" s="8"/>
+      <c r="J194" s="8"/>
     </row>
     <row r="195" spans="9:10">
-      <c r="I195" s="18"/>
-      <c r="J195" s="18"/>
+      <c r="I195" s="8"/>
+      <c r="J195" s="8"/>
     </row>
     <row r="196" spans="9:10">
-      <c r="I196" s="18"/>
-      <c r="J196" s="18"/>
+      <c r="I196" s="8"/>
+      <c r="J196" s="8"/>
     </row>
     <row r="197" spans="9:10">
-      <c r="I197" s="18"/>
-      <c r="J197" s="18"/>
+      <c r="I197" s="8"/>
+      <c r="J197" s="8"/>
     </row>
     <row r="198" spans="9:10">
-      <c r="I198" s="18"/>
-      <c r="J198" s="18"/>
+      <c r="I198" s="8"/>
+      <c r="J198" s="8"/>
     </row>
     <row r="199" spans="9:10">
-      <c r="I199" s="18"/>
-      <c r="J199" s="18"/>
+      <c r="I199" s="8"/>
+      <c r="J199" s="8"/>
     </row>
     <row r="200" spans="9:10">
-      <c r="I200" s="18"/>
-      <c r="J200" s="18"/>
+      <c r="I200" s="8"/>
+      <c r="J200" s="8"/>
     </row>
     <row r="201" spans="9:10">
-      <c r="I201" s="18"/>
-      <c r="J201" s="18"/>
+      <c r="I201" s="8"/>
+      <c r="J201" s="8"/>
     </row>
     <row r="202" spans="9:10">
-      <c r="I202" s="18"/>
-      <c r="J202" s="18"/>
+      <c r="I202" s="8"/>
+      <c r="J202" s="8"/>
     </row>
     <row r="203" spans="9:10">
-      <c r="I203" s="18"/>
-      <c r="J203" s="18"/>
+      <c r="I203" s="8"/>
+      <c r="J203" s="8"/>
     </row>
     <row r="204" spans="9:10">
-      <c r="I204" s="18"/>
-      <c r="J204" s="18"/>
+      <c r="I204" s="8"/>
+      <c r="J204" s="8"/>
     </row>
     <row r="205" spans="9:10">
-      <c r="I205" s="18"/>
-      <c r="J205" s="18"/>
+      <c r="I205" s="8"/>
+      <c r="J205" s="8"/>
     </row>
     <row r="206" spans="9:10">
-      <c r="I206" s="18"/>
-      <c r="J206" s="18"/>
+      <c r="I206" s="8"/>
+      <c r="J206" s="8"/>
     </row>
     <row r="207" spans="9:10">
-      <c r="I207" s="18"/>
-      <c r="J207" s="18"/>
+      <c r="I207" s="8"/>
+      <c r="J207" s="8"/>
     </row>
     <row r="208" spans="9:10">
-      <c r="I208" s="18"/>
-      <c r="J208" s="18"/>
+      <c r="I208" s="8"/>
+      <c r="J208" s="8"/>
     </row>
     <row r="209" spans="9:10">
-      <c r="I209" s="18"/>
-      <c r="J209" s="18"/>
+      <c r="I209" s="8"/>
+      <c r="J209" s="8"/>
     </row>
     <row r="210" spans="9:10">
-      <c r="I210" s="18"/>
-      <c r="J210" s="18"/>
+      <c r="I210" s="8"/>
+      <c r="J210" s="8"/>
     </row>
     <row r="211" spans="9:10">
-      <c r="I211" s="18"/>
-      <c r="J211" s="18"/>
+      <c r="I211" s="8"/>
+      <c r="J211" s="8"/>
     </row>
     <row r="212" spans="9:10">
-      <c r="I212" s="18"/>
-      <c r="J212" s="18"/>
+      <c r="I212" s="8"/>
+      <c r="J212" s="8"/>
     </row>
     <row r="213" spans="9:10">
-      <c r="I213" s="18"/>
-      <c r="J213" s="18"/>
+      <c r="I213" s="8"/>
+      <c r="J213" s="8"/>
     </row>
     <row r="214" spans="9:10">
-      <c r="I214" s="18"/>
-      <c r="J214" s="18"/>
+      <c r="I214" s="8"/>
+      <c r="J214" s="8"/>
     </row>
     <row r="215" spans="9:10">
-      <c r="I215" s="18"/>
-      <c r="J215" s="18"/>
+      <c r="I215" s="8"/>
+      <c r="J215" s="8"/>
     </row>
     <row r="216" spans="9:10">
-      <c r="I216" s="18"/>
-      <c r="J216" s="18"/>
+      <c r="I216" s="8"/>
+      <c r="J216" s="8"/>
     </row>
     <row r="217" spans="9:10">
-      <c r="I217" s="18"/>
-      <c r="J217" s="18"/>
+      <c r="I217" s="8"/>
+      <c r="J217" s="8"/>
     </row>
     <row r="218" spans="9:10">
-      <c r="I218" s="18"/>
-      <c r="J218" s="18"/>
+      <c r="I218" s="8"/>
+      <c r="J218" s="8"/>
     </row>
     <row r="219" spans="9:10">
-      <c r="I219" s="18"/>
-      <c r="J219" s="18"/>
+      <c r="I219" s="8"/>
+      <c r="J219" s="8"/>
     </row>
     <row r="220" spans="9:10">
-      <c r="I220" s="18"/>
-      <c r="J220" s="18"/>
+      <c r="I220" s="8"/>
+      <c r="J220" s="8"/>
     </row>
     <row r="221" spans="9:10">
-      <c r="I221" s="18"/>
-      <c r="J221" s="18"/>
+      <c r="I221" s="8"/>
+      <c r="J221" s="8"/>
     </row>
     <row r="222" spans="9:10">
-      <c r="I222" s="18"/>
-      <c r="J222" s="18"/>
+      <c r="I222" s="8"/>
+      <c r="J222" s="8"/>
     </row>
     <row r="223" spans="9:10">
-      <c r="I223" s="18"/>
-      <c r="J223" s="18"/>
+      <c r="I223" s="8"/>
+      <c r="J223" s="8"/>
     </row>
     <row r="224" spans="9:10">
-      <c r="I224" s="18"/>
-      <c r="J224" s="18"/>
+      <c r="I224" s="8"/>
+      <c r="J224" s="8"/>
     </row>
     <row r="225" spans="9:10">
-      <c r="I225" s="18"/>
-      <c r="J225" s="18"/>
+      <c r="I225" s="8"/>
+      <c r="J225" s="8"/>
     </row>
     <row r="226" spans="9:10">
-      <c r="I226" s="18"/>
-      <c r="J226" s="18"/>
+      <c r="I226" s="8"/>
+      <c r="J226" s="8"/>
     </row>
     <row r="227" spans="9:10">
-      <c r="I227" s="18"/>
-      <c r="J227" s="18"/>
+      <c r="I227" s="8"/>
+      <c r="J227" s="8"/>
     </row>
     <row r="228" spans="9:10">
-      <c r="I228" s="18"/>
-      <c r="J228" s="18"/>
+      <c r="I228" s="8"/>
+      <c r="J228" s="8"/>
     </row>
     <row r="229" spans="9:10">
-      <c r="I229" s="18"/>
-      <c r="J229" s="18"/>
+      <c r="I229" s="8"/>
+      <c r="J229" s="8"/>
     </row>
     <row r="230" spans="9:10">
-      <c r="I230" s="18"/>
-      <c r="J230" s="18"/>
+      <c r="I230" s="8"/>
+      <c r="J230" s="8"/>
     </row>
     <row r="231" spans="9:10">
-      <c r="I231" s="18"/>
-      <c r="J231" s="18"/>
+      <c r="I231" s="8"/>
+      <c r="J231" s="8"/>
     </row>
     <row r="232" spans="9:10">
-      <c r="I232" s="18"/>
-      <c r="J232" s="18"/>
+      <c r="I232" s="8"/>
+      <c r="J232" s="8"/>
     </row>
     <row r="233" spans="9:10">
-      <c r="I233" s="18"/>
-      <c r="J233" s="18"/>
+      <c r="I233" s="8"/>
+      <c r="J233" s="8"/>
     </row>
     <row r="234" spans="9:10">
-      <c r="I234" s="18"/>
-      <c r="J234" s="18"/>
+      <c r="I234" s="8"/>
+      <c r="J234" s="8"/>
     </row>
     <row r="235" spans="9:10">
-      <c r="I235" s="18"/>
-      <c r="J235" s="18"/>
+      <c r="I235" s="8"/>
+      <c r="J235" s="8"/>
     </row>
     <row r="236" spans="9:10">
-      <c r="I236" s="18"/>
-      <c r="J236" s="18"/>
+      <c r="I236" s="8"/>
+      <c r="J236" s="8"/>
     </row>
     <row r="237" spans="9:10">
-      <c r="I237" s="18"/>
-      <c r="J237" s="18"/>
+      <c r="I237" s="8"/>
+      <c r="J237" s="8"/>
     </row>
     <row r="238" spans="9:10">
-      <c r="I238" s="18"/>
-      <c r="J238" s="18"/>
+      <c r="I238" s="8"/>
+      <c r="J238" s="8"/>
     </row>
     <row r="239" spans="9:10">
-      <c r="I239" s="18"/>
-      <c r="J239" s="18"/>
+      <c r="I239" s="8"/>
+      <c r="J239" s="8"/>
     </row>
     <row r="240" spans="9:10">
-      <c r="I240" s="18"/>
-      <c r="J240" s="18"/>
+      <c r="I240" s="8"/>
+      <c r="J240" s="8"/>
     </row>
     <row r="241" spans="9:10">
-      <c r="I241" s="18"/>
-      <c r="J241" s="18"/>
+      <c r="I241" s="8"/>
+      <c r="J241" s="8"/>
     </row>
     <row r="242" spans="9:10">
-      <c r="I242" s="18"/>
-      <c r="J242" s="18"/>
+      <c r="I242" s="8"/>
+      <c r="J242" s="8"/>
     </row>
     <row r="243" spans="9:10">
-      <c r="I243" s="18"/>
-      <c r="J243" s="18"/>
+      <c r="I243" s="8"/>
+      <c r="J243" s="8"/>
     </row>
     <row r="244" spans="9:10">
-      <c r="I244" s="18"/>
-      <c r="J244" s="18"/>
+      <c r="I244" s="8"/>
+      <c r="J244" s="8"/>
     </row>
     <row r="245" spans="9:10">
-      <c r="I245" s="18"/>
-      <c r="J245" s="18"/>
+      <c r="I245" s="8"/>
+      <c r="J245" s="8"/>
     </row>
     <row r="246" spans="9:10">
-      <c r="I246" s="18"/>
-      <c r="J246" s="18"/>
+      <c r="I246" s="8"/>
+      <c r="J246" s="8"/>
     </row>
     <row r="247" spans="9:10">
-      <c r="I247" s="18"/>
-      <c r="J247" s="18"/>
+      <c r="I247" s="8"/>
+      <c r="J247" s="8"/>
     </row>
     <row r="248" spans="9:10">
-      <c r="I248" s="18"/>
-      <c r="J248" s="18"/>
+      <c r="I248" s="8"/>
+      <c r="J248" s="8"/>
     </row>
     <row r="249" spans="9:10">
-      <c r="I249" s="18"/>
-      <c r="J249" s="18"/>
+      <c r="I249" s="8"/>
+      <c r="J249" s="8"/>
     </row>
     <row r="250" spans="9:10">
-      <c r="I250" s="18"/>
-      <c r="J250" s="18"/>
+      <c r="I250" s="8"/>
+      <c r="J250" s="8"/>
     </row>
     <row r="251" spans="9:10">
-      <c r="I251" s="18"/>
-      <c r="J251" s="18"/>
+      <c r="I251" s="8"/>
+      <c r="J251" s="8"/>
     </row>
     <row r="252" spans="9:10">
-      <c r="I252" s="18"/>
-      <c r="J252" s="18"/>
+      <c r="I252" s="8"/>
+      <c r="J252" s="8"/>
     </row>
     <row r="253" spans="9:10">
-      <c r="I253" s="18"/>
-      <c r="J253" s="18"/>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
     </row>
     <row r="254" spans="9:10">
-      <c r="I254" s="18"/>
-      <c r="J254" s="18"/>
+      <c r="I254" s="8"/>
+      <c r="J254" s="8"/>
     </row>
     <row r="255" spans="9:10">
-      <c r="I255" s="18"/>
-      <c r="J255" s="18"/>
+      <c r="I255" s="8"/>
+      <c r="J255" s="8"/>
     </row>
     <row r="256" spans="9:10">
-      <c r="I256" s="18"/>
-      <c r="J256" s="18"/>
+      <c r="I256" s="8"/>
+      <c r="J256" s="8"/>
     </row>
     <row r="257" spans="9:10">
-      <c r="I257" s="18"/>
-      <c r="J257" s="18"/>
+      <c r="I257" s="8"/>
+      <c r="J257" s="8"/>
     </row>
     <row r="258" spans="9:10">
-      <c r="I258" s="18"/>
-      <c r="J258" s="18"/>
+      <c r="I258" s="8"/>
+      <c r="J258" s="8"/>
     </row>
     <row r="259" spans="9:10">
-      <c r="I259" s="18"/>
-      <c r="J259" s="18"/>
+      <c r="I259" s="8"/>
+      <c r="J259" s="8"/>
     </row>
     <row r="260" spans="9:10">
-      <c r="I260" s="18"/>
-      <c r="J260" s="18"/>
+      <c r="I260" s="8"/>
+      <c r="J260" s="8"/>
     </row>
     <row r="261" spans="9:10">
-      <c r="I261" s="18"/>
-      <c r="J261" s="18"/>
+      <c r="I261" s="8"/>
+      <c r="J261" s="8"/>
     </row>
     <row r="262" spans="9:10">
-      <c r="I262" s="18"/>
-      <c r="J262" s="18"/>
+      <c r="I262" s="8"/>
+      <c r="J262" s="8"/>
     </row>
     <row r="263" spans="9:10">
-      <c r="I263" s="18"/>
-      <c r="J263" s="18"/>
+      <c r="I263" s="8"/>
+      <c r="J263" s="8"/>
     </row>
     <row r="264" spans="9:10">
-      <c r="I264" s="18"/>
-      <c r="J264" s="18"/>
+      <c r="I264" s="8"/>
+      <c r="J264" s="8"/>
     </row>
     <row r="265" spans="9:10">
-      <c r="I265" s="18"/>
-      <c r="J265" s="18"/>
+      <c r="I265" s="8"/>
+      <c r="J265" s="8"/>
     </row>
     <row r="266" spans="9:10">
-      <c r="I266" s="18"/>
-      <c r="J266" s="18"/>
+      <c r="I266" s="8"/>
+      <c r="J266" s="8"/>
     </row>
     <row r="267" spans="9:10">
-      <c r="I267" s="18"/>
-      <c r="J267" s="18"/>
+      <c r="I267" s="8"/>
+      <c r="J267" s="8"/>
     </row>
     <row r="268" spans="9:10">
-      <c r="I268" s="18"/>
-      <c r="J268" s="18"/>
+      <c r="I268" s="8"/>
+      <c r="J268" s="8"/>
     </row>
     <row r="269" spans="9:10">
-      <c r="I269" s="18"/>
-      <c r="J269" s="18"/>
+      <c r="I269" s="8"/>
+      <c r="J269" s="8"/>
     </row>
     <row r="270" spans="9:10">
-      <c r="I270" s="18"/>
-      <c r="J270" s="18"/>
+      <c r="I270" s="8"/>
+      <c r="J270" s="8"/>
     </row>
     <row r="271" spans="9:10">
-      <c r="I271" s="18"/>
-      <c r="J271" s="18"/>
+      <c r="I271" s="8"/>
+      <c r="J271" s="8"/>
     </row>
     <row r="272" spans="9:10">
-      <c r="I272" s="18"/>
-      <c r="J272" s="18"/>
+      <c r="I272" s="8"/>
+      <c r="J272" s="8"/>
     </row>
     <row r="273" spans="9:10">
-      <c r="I273" s="18"/>
-      <c r="J273" s="18"/>
+      <c r="I273" s="8"/>
+      <c r="J273" s="8"/>
     </row>
     <row r="274" spans="9:10">
-      <c r="I274" s="18"/>
-      <c r="J274" s="18"/>
+      <c r="I274" s="8"/>
+      <c r="J274" s="8"/>
     </row>
     <row r="275" spans="9:10">
-      <c r="I275" s="18"/>
-      <c r="J275" s="18"/>
+      <c r="I275" s="8"/>
+      <c r="J275" s="8"/>
     </row>
     <row r="276" spans="9:10">
-      <c r="I276" s="18"/>
-      <c r="J276" s="18"/>
+      <c r="I276" s="8"/>
+      <c r="J276" s="8"/>
     </row>
     <row r="277" spans="9:10">
-      <c r="I277" s="18"/>
-      <c r="J277" s="18"/>
+      <c r="I277" s="8"/>
+      <c r="J277" s="8"/>
     </row>
     <row r="278" spans="9:10">
-      <c r="I278" s="18"/>
-      <c r="J278" s="18"/>
+      <c r="I278" s="8"/>
+      <c r="J278" s="8"/>
     </row>
     <row r="279" spans="9:10">
-      <c r="I279" s="18"/>
-      <c r="J279" s="18"/>
+      <c r="I279" s="8"/>
+      <c r="J279" s="8"/>
     </row>
     <row r="280" spans="9:10">
-      <c r="I280" s="18"/>
-      <c r="J280" s="18"/>
+      <c r="I280" s="8"/>
+      <c r="J280" s="8"/>
     </row>
     <row r="281" spans="9:10">
-      <c r="I281" s="18"/>
-      <c r="J281" s="18"/>
+      <c r="I281" s="8"/>
+      <c r="J281" s="8"/>
     </row>
     <row r="282" spans="9:10">
-      <c r="I282" s="18"/>
-      <c r="J282" s="18"/>
+      <c r="I282" s="8"/>
+      <c r="J282" s="8"/>
     </row>
     <row r="283" spans="9:10">
-      <c r="I283" s="18"/>
-      <c r="J283" s="18"/>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
     </row>
     <row r="284" spans="9:10">
-      <c r="I284" s="18"/>
-      <c r="J284" s="18"/>
+      <c r="I284" s="8"/>
+      <c r="J284" s="8"/>
     </row>
     <row r="285" spans="9:10">
-      <c r="I285" s="18"/>
-      <c r="J285" s="18"/>
+      <c r="I285" s="8"/>
+      <c r="J285" s="8"/>
     </row>
     <row r="286" spans="9:10">
-      <c r="I286" s="18"/>
-      <c r="J286" s="18"/>
+      <c r="I286" s="8"/>
+      <c r="J286" s="8"/>
     </row>
     <row r="287" spans="9:10">
-      <c r="I287" s="18"/>
-      <c r="J287" s="18"/>
+      <c r="I287" s="8"/>
+      <c r="J287" s="8"/>
     </row>
     <row r="288" spans="9:10">
-      <c r="I288" s="18"/>
-      <c r="J288" s="18"/>
+      <c r="I288" s="8"/>
+      <c r="J288" s="8"/>
     </row>
     <row r="289" spans="9:10">
-      <c r="I289" s="18"/>
-      <c r="J289" s="18"/>
+      <c r="I289" s="8"/>
+      <c r="J289" s="8"/>
     </row>
     <row r="290" spans="9:10">
-      <c r="I290" s="18"/>
-      <c r="J290" s="18"/>
+      <c r="I290" s="8"/>
+      <c r="J290" s="8"/>
     </row>
     <row r="291" spans="9:10">
-      <c r="I291" s="18"/>
-      <c r="J291" s="18"/>
+      <c r="I291" s="8"/>
+      <c r="J291" s="8"/>
     </row>
     <row r="292" spans="9:10">
-      <c r="I292" s="18"/>
-      <c r="J292" s="18"/>
+      <c r="I292" s="8"/>
+      <c r="J292" s="8"/>
     </row>
     <row r="293" spans="9:10">
-      <c r="I293" s="18"/>
-      <c r="J293" s="18"/>
+      <c r="I293" s="8"/>
+      <c r="J293" s="8"/>
     </row>
     <row r="294" spans="9:10">
-      <c r="I294" s="18"/>
-      <c r="J294" s="18"/>
+      <c r="I294" s="8"/>
+      <c r="J294" s="8"/>
     </row>
     <row r="295" spans="9:10">
-      <c r="I295" s="18"/>
-      <c r="J295" s="18"/>
+      <c r="I295" s="8"/>
+      <c r="J295" s="8"/>
     </row>
     <row r="296" spans="9:10">
-      <c r="I296" s="18"/>
-      <c r="J296" s="18"/>
+      <c r="I296" s="8"/>
+      <c r="J296" s="8"/>
     </row>
     <row r="297" spans="9:10">
-      <c r="I297" s="18"/>
-      <c r="J297" s="18"/>
+      <c r="I297" s="8"/>
+      <c r="J297" s="8"/>
     </row>
     <row r="298" spans="9:10">
-      <c r="I298" s="18"/>
-      <c r="J298" s="18"/>
+      <c r="I298" s="8"/>
+      <c r="J298" s="8"/>
     </row>
     <row r="299" spans="9:10">
-      <c r="I299" s="18"/>
-      <c r="J299" s="18"/>
+      <c r="I299" s="8"/>
+      <c r="J299" s="8"/>
     </row>
     <row r="300" spans="9:10">
-      <c r="I300" s="18"/>
-      <c r="J300" s="18"/>
+      <c r="I300" s="8"/>
+      <c r="J300" s="8"/>
     </row>
     <row r="301" spans="9:10">
-      <c r="I301" s="18"/>
-      <c r="J301" s="18"/>
+      <c r="I301" s="8"/>
+      <c r="J301" s="8"/>
     </row>
     <row r="302" spans="9:10">
-      <c r="I302" s="18"/>
-      <c r="J302" s="18"/>
+      <c r="I302" s="8"/>
+      <c r="J302" s="8"/>
     </row>
     <row r="303" spans="9:10">
-      <c r="I303" s="18"/>
-      <c r="J303" s="18"/>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
     </row>
     <row r="304" spans="9:10">
-      <c r="I304" s="18"/>
-      <c r="J304" s="18"/>
+      <c r="I304" s="8"/>
+      <c r="J304" s="8"/>
     </row>
     <row r="305" spans="9:10">
-      <c r="I305" s="18"/>
-      <c r="J305" s="18"/>
+      <c r="I305" s="8"/>
+      <c r="J305" s="8"/>
     </row>
     <row r="306" spans="9:10">
-      <c r="I306" s="18"/>
-      <c r="J306" s="18"/>
+      <c r="I306" s="8"/>
+      <c r="J306" s="8"/>
     </row>
     <row r="307" spans="9:10">
-      <c r="I307" s="18"/>
-      <c r="J307" s="18"/>
+      <c r="I307" s="8"/>
+      <c r="J307" s="8"/>
     </row>
     <row r="308" spans="9:10">
-      <c r="I308" s="18"/>
-      <c r="J308" s="18"/>
+      <c r="I308" s="8"/>
+      <c r="J308" s="8"/>
     </row>
     <row r="309" spans="9:10">
-      <c r="I309" s="18"/>
-      <c r="J309" s="18"/>
+      <c r="I309" s="8"/>
+      <c r="J309" s="8"/>
     </row>
     <row r="310" spans="9:10">
-      <c r="I310" s="18"/>
-      <c r="J310" s="18"/>
+      <c r="I310" s="8"/>
+      <c r="J310" s="8"/>
     </row>
     <row r="311" spans="9:10">
-      <c r="I311" s="18"/>
-      <c r="J311" s="18"/>
+      <c r="I311" s="8"/>
+      <c r="J311" s="8"/>
     </row>
     <row r="312" spans="9:10">
-      <c r="I312" s="18"/>
-      <c r="J312" s="18"/>
+      <c r="I312" s="8"/>
+      <c r="J312" s="8"/>
     </row>
     <row r="313" spans="9:10">
-      <c r="I313" s="18"/>
-      <c r="J313" s="18"/>
+      <c r="I313" s="8"/>
+      <c r="J313" s="8"/>
     </row>
     <row r="314" spans="9:10">
-      <c r="I314" s="18"/>
-      <c r="J314" s="18"/>
+      <c r="I314" s="8"/>
+      <c r="J314" s="8"/>
     </row>
     <row r="315" spans="9:10">
-      <c r="I315" s="18"/>
-      <c r="J315" s="18"/>
+      <c r="I315" s="8"/>
+      <c r="J315" s="8"/>
     </row>
     <row r="316" spans="9:10">
-      <c r="I316" s="18"/>
-      <c r="J316" s="18"/>
+      <c r="I316" s="8"/>
+      <c r="J316" s="8"/>
     </row>
     <row r="317" spans="9:10">
-      <c r="I317" s="18"/>
-      <c r="J317" s="18"/>
+      <c r="I317" s="8"/>
+      <c r="J317" s="8"/>
     </row>
     <row r="318" spans="9:10">
-      <c r="I318" s="18"/>
-      <c r="J318" s="18"/>
+      <c r="I318" s="8"/>
+      <c r="J318" s="8"/>
     </row>
     <row r="319" spans="9:10">
-      <c r="I319" s="18"/>
-      <c r="J319" s="18"/>
+      <c r="I319" s="8"/>
+      <c r="J319" s="8"/>
     </row>
     <row r="320" spans="9:10">
-      <c r="I320" s="18"/>
-      <c r="J320" s="18"/>
+      <c r="I320" s="8"/>
+      <c r="J320" s="8"/>
     </row>
     <row r="321" spans="9:10">
-      <c r="I321" s="18"/>
-      <c r="J321" s="18"/>
+      <c r="I321" s="8"/>
+      <c r="J321" s="8"/>
     </row>
     <row r="322" spans="9:10">
-      <c r="I322" s="18"/>
-      <c r="J322" s="18"/>
+      <c r="I322" s="8"/>
+      <c r="J322" s="8"/>
     </row>
     <row r="323" spans="9:10">
-      <c r="I323" s="18"/>
-      <c r="J323" s="18"/>
+      <c r="I323" s="8"/>
+      <c r="J323" s="8"/>
     </row>
     <row r="324" spans="9:10">
-      <c r="I324" s="18"/>
-      <c r="J324" s="18"/>
+      <c r="I324" s="8"/>
+      <c r="J324" s="8"/>
     </row>
     <row r="325" spans="9:10">
-      <c r="I325" s="18"/>
-      <c r="J325" s="18"/>
+      <c r="I325" s="8"/>
+      <c r="J325" s="8"/>
     </row>
     <row r="326" spans="9:10">
-      <c r="I326" s="18"/>
-      <c r="J326" s="18"/>
+      <c r="I326" s="8"/>
+      <c r="J326" s="8"/>
     </row>
     <row r="327" spans="9:10">
-      <c r="I327" s="18"/>
-      <c r="J327" s="18"/>
+      <c r="I327" s="8"/>
+      <c r="J327" s="8"/>
     </row>
     <row r="328" spans="9:10">
-      <c r="I328" s="18"/>
-      <c r="J328" s="18"/>
+      <c r="I328" s="8"/>
+      <c r="J328" s="8"/>
     </row>
     <row r="329" spans="9:10">
-      <c r="I329" s="18"/>
-      <c r="J329" s="18"/>
+      <c r="I329" s="8"/>
+      <c r="J329" s="8"/>
     </row>
     <row r="330" spans="9:10">
-      <c r="I330" s="18"/>
-      <c r="J330" s="18"/>
+      <c r="I330" s="8"/>
+      <c r="J330" s="8"/>
     </row>
     <row r="331" spans="9:10">
-      <c r="I331" s="18"/>
-      <c r="J331" s="18"/>
+      <c r="I331" s="8"/>
+      <c r="J331" s="8"/>
     </row>
     <row r="332" spans="9:10">
-      <c r="I332" s="18"/>
-      <c r="J332" s="18"/>
+      <c r="I332" s="8"/>
+      <c r="J332" s="8"/>
     </row>
     <row r="333" spans="9:10">
-      <c r="I333" s="18"/>
-      <c r="J333" s="18"/>
+      <c r="I333" s="8"/>
+      <c r="J333" s="8"/>
     </row>
     <row r="334" spans="9:10">
-      <c r="I334" s="18"/>
-      <c r="J334" s="18"/>
+      <c r="I334" s="8"/>
+      <c r="J334" s="8"/>
     </row>
     <row r="335" spans="9:10">
-      <c r="I335" s="18"/>
-      <c r="J335" s="18"/>
+      <c r="I335" s="8"/>
+      <c r="J335" s="8"/>
     </row>
     <row r="336" spans="9:10">
-      <c r="I336" s="18"/>
-      <c r="J336" s="18"/>
+      <c r="I336" s="8"/>
+      <c r="J336" s="8"/>
     </row>
     <row r="337" spans="9:10">
-      <c r="I337" s="18"/>
-      <c r="J337" s="18"/>
+      <c r="I337" s="8"/>
+      <c r="J337" s="8"/>
     </row>
     <row r="338" spans="9:10">
-      <c r="I338" s="18"/>
-      <c r="J338" s="18"/>
+      <c r="I338" s="8"/>
+      <c r="J338" s="8"/>
     </row>
     <row r="339" spans="9:10">
-      <c r="I339" s="18"/>
-      <c r="J339" s="18"/>
+      <c r="I339" s="8"/>
+      <c r="J339" s="8"/>
     </row>
     <row r="340" spans="9:10">
-      <c r="I340" s="18"/>
-      <c r="J340" s="18"/>
+      <c r="I340" s="8"/>
+      <c r="J340" s="8"/>
     </row>
     <row r="341" spans="9:10">
-      <c r="I341" s="18"/>
-      <c r="J341" s="18"/>
+      <c r="I341" s="8"/>
+      <c r="J341" s="8"/>
     </row>
     <row r="342" spans="9:10">
-      <c r="I342" s="18"/>
-      <c r="J342" s="18"/>
+      <c r="I342" s="8"/>
+      <c r="J342" s="8"/>
     </row>
     <row r="343" spans="9:10">
-      <c r="I343" s="18"/>
-      <c r="J343" s="18"/>
+      <c r="I343" s="8"/>
+      <c r="J343" s="8"/>
     </row>
     <row r="344" spans="9:10">
-      <c r="I344" s="18"/>
-      <c r="J344" s="18"/>
+      <c r="I344" s="8"/>
+      <c r="J344" s="8"/>
     </row>
     <row r="345" spans="9:10">
-      <c r="I345" s="18"/>
-      <c r="J345" s="18"/>
+      <c r="I345" s="8"/>
+      <c r="J345" s="8"/>
     </row>
     <row r="346" spans="9:10">
-      <c r="I346" s="18"/>
-      <c r="J346" s="18"/>
+      <c r="I346" s="8"/>
+      <c r="J346" s="8"/>
     </row>
     <row r="347" spans="9:10">
-      <c r="I347" s="18"/>
-      <c r="J347" s="18"/>
+      <c r="I347" s="8"/>
+      <c r="J347" s="8"/>
     </row>
     <row r="348" spans="9:10">
-      <c r="I348" s="18"/>
-      <c r="J348" s="18"/>
+      <c r="I348" s="8"/>
+      <c r="J348" s="8"/>
     </row>
     <row r="349" spans="9:10">
-      <c r="I349" s="18"/>
-      <c r="J349" s="18"/>
+      <c r="I349" s="8"/>
+      <c r="J349" s="8"/>
     </row>
     <row r="350" spans="9:10">
-      <c r="I350" s="18"/>
-      <c r="J350" s="18"/>
+      <c r="I350" s="8"/>
+      <c r="J350" s="8"/>
     </row>
     <row r="351" spans="9:10">
-      <c r="I351" s="18"/>
-      <c r="J351" s="18"/>
+      <c r="I351" s="8"/>
+      <c r="J351" s="8"/>
     </row>
     <row r="352" spans="9:10">
-      <c r="I352" s="18"/>
-      <c r="J352" s="18"/>
+      <c r="I352" s="8"/>
+      <c r="J352" s="8"/>
     </row>
     <row r="353" spans="9:10">
-      <c r="I353" s="18"/>
-      <c r="J353" s="18"/>
+      <c r="I353" s="8"/>
+      <c r="J353" s="8"/>
     </row>
     <row r="354" spans="9:10">
-      <c r="I354" s="18"/>
-      <c r="J354" s="18"/>
+      <c r="I354" s="8"/>
+      <c r="J354" s="8"/>
     </row>
     <row r="355" spans="9:10">
-      <c r="I355" s="18"/>
-      <c r="J355" s="18"/>
+      <c r="I355" s="8"/>
+      <c r="J355" s="8"/>
     </row>
     <row r="356" spans="9:10">
-      <c r="I356" s="18"/>
-      <c r="J356" s="18"/>
+      <c r="I356" s="8"/>
+      <c r="J356" s="8"/>
     </row>
     <row r="357" spans="9:10">
-      <c r="I357" s="18"/>
-      <c r="J357" s="18"/>
+      <c r="I357" s="8"/>
+      <c r="J357" s="8"/>
     </row>
     <row r="358" spans="9:10">
-      <c r="I358" s="18"/>
-      <c r="J358" s="18"/>
+      <c r="I358" s="8"/>
+      <c r="J358" s="8"/>
     </row>
     <row r="359" spans="9:10">
-      <c r="I359" s="18"/>
-      <c r="J359" s="18"/>
+      <c r="I359" s="8"/>
+      <c r="J359" s="8"/>
     </row>
     <row r="360" spans="9:10">
-      <c r="I360" s="18"/>
-      <c r="J360" s="18"/>
+      <c r="I360" s="8"/>
+      <c r="J360" s="8"/>
     </row>
     <row r="361" spans="9:10">
-      <c r="I361" s="18"/>
-      <c r="J361" s="18"/>
+      <c r="I361" s="8"/>
+      <c r="J361" s="8"/>
     </row>
     <row r="362" spans="9:10">
-      <c r="I362" s="18"/>
-      <c r="J362" s="18"/>
+      <c r="I362" s="8"/>
+      <c r="J362" s="8"/>
     </row>
     <row r="363" spans="9:10">
-      <c r="I363" s="18"/>
-      <c r="J363" s="18"/>
+      <c r="I363" s="8"/>
+      <c r="J363" s="8"/>
     </row>
     <row r="364" spans="9:10">
-      <c r="I364" s="18"/>
-      <c r="J364" s="18"/>
+      <c r="I364" s="8"/>
+      <c r="J364" s="8"/>
     </row>
     <row r="365" spans="9:10">
-      <c r="I365" s="18"/>
-      <c r="J365" s="18"/>
+      <c r="I365" s="8"/>
+      <c r="J365" s="8"/>
     </row>
     <row r="366" spans="9:10">
-      <c r="I366" s="18"/>
-      <c r="J366" s="18"/>
+      <c r="I366" s="8"/>
+      <c r="J366" s="8"/>
     </row>
     <row r="367" spans="9:10">
-      <c r="I367" s="18"/>
-      <c r="J367" s="18"/>
+      <c r="I367" s="8"/>
+      <c r="J367" s="8"/>
     </row>
     <row r="368" spans="9:10">
-      <c r="I368" s="18"/>
-      <c r="J368" s="18"/>
+      <c r="I368" s="8"/>
+      <c r="J368" s="8"/>
     </row>
     <row r="369" spans="9:10">
-      <c r="I369" s="18"/>
-      <c r="J369" s="18"/>
+      <c r="I369" s="8"/>
+      <c r="J369" s="8"/>
     </row>
     <row r="370" spans="9:10">
-      <c r="I370" s="18"/>
-      <c r="J370" s="18"/>
+      <c r="I370" s="8"/>
+      <c r="J370" s="8"/>
     </row>
     <row r="371" spans="9:10">
-      <c r="I371" s="18"/>
-      <c r="J371" s="18"/>
+      <c r="I371" s="8"/>
+      <c r="J371" s="8"/>
     </row>
     <row r="372" spans="9:10">
-      <c r="I372" s="18"/>
-      <c r="J372" s="18"/>
+      <c r="I372" s="8"/>
+      <c r="J372" s="8"/>
     </row>
     <row r="373" spans="9:10">
-      <c r="I373" s="18"/>
-      <c r="J373" s="18"/>
+      <c r="I373" s="8"/>
+      <c r="J373" s="8"/>
     </row>
     <row r="374" spans="9:10">
-      <c r="I374" s="18"/>
-      <c r="J374" s="18"/>
+      <c r="I374" s="8"/>
+      <c r="J374" s="8"/>
     </row>
     <row r="375" spans="9:10">
-      <c r="I375" s="18"/>
-      <c r="J375" s="18"/>
+      <c r="I375" s="8"/>
+      <c r="J375" s="8"/>
     </row>
     <row r="376" spans="9:10">
-      <c r="I376" s="18"/>
-      <c r="J376" s="18"/>
+      <c r="I376" s="8"/>
+      <c r="J376" s="8"/>
     </row>
     <row r="377" spans="9:10">
-      <c r="I377" s="18"/>
-      <c r="J377" s="18"/>
+      <c r="I377" s="8"/>
+      <c r="J377" s="8"/>
     </row>
     <row r="378" spans="9:10">
-      <c r="I378" s="18"/>
-      <c r="J378" s="18"/>
+      <c r="I378" s="8"/>
+      <c r="J378" s="8"/>
     </row>
     <row r="379" spans="9:10">
-      <c r="I379" s="18"/>
-      <c r="J379" s="18"/>
+      <c r="I379" s="8"/>
+      <c r="J379" s="8"/>
     </row>
     <row r="380" spans="9:10">
-      <c r="I380" s="18"/>
-      <c r="J380" s="18"/>
+      <c r="I380" s="8"/>
+      <c r="J380" s="8"/>
     </row>
     <row r="381" spans="9:10">
-      <c r="I381" s="18"/>
-      <c r="J381" s="18"/>
+      <c r="I381" s="8"/>
+      <c r="J381" s="8"/>
     </row>
     <row r="382" spans="9:10">
-      <c r="I382" s="18"/>
-      <c r="J382" s="18"/>
+      <c r="I382" s="8"/>
+      <c r="J382" s="8"/>
     </row>
     <row r="383" spans="9:10">
-      <c r="I383" s="18"/>
-      <c r="J383" s="18"/>
+      <c r="I383" s="8"/>
+      <c r="J383" s="8"/>
     </row>
     <row r="384" spans="9:10">
-      <c r="I384" s="18"/>
-      <c r="J384" s="18"/>
+      <c r="I384" s="8"/>
+      <c r="J384" s="8"/>
     </row>
     <row r="385" spans="9:10">
-      <c r="I385" s="18"/>
-      <c r="J385" s="18"/>
+      <c r="I385" s="8"/>
+      <c r="J385" s="8"/>
     </row>
     <row r="386" spans="9:10">
-      <c r="I386" s="18"/>
-      <c r="J386" s="18"/>
+      <c r="I386" s="8"/>
+      <c r="J386" s="8"/>
     </row>
     <row r="387" spans="9:10">
-      <c r="I387" s="18"/>
-      <c r="J387" s="18"/>
+      <c r="I387" s="8"/>
+      <c r="J387" s="8"/>
     </row>
     <row r="388" spans="9:10">
-      <c r="I388" s="18"/>
-      <c r="J388" s="18"/>
+      <c r="I388" s="8"/>
+      <c r="J388" s="8"/>
     </row>
     <row r="389" spans="9:10">
-      <c r="I389" s="18"/>
-      <c r="J389" s="18"/>
+      <c r="I389" s="8"/>
+      <c r="J389" s="8"/>
     </row>
     <row r="390" spans="9:10">
-      <c r="I390" s="18"/>
-      <c r="J390" s="18"/>
+      <c r="I390" s="8"/>
+      <c r="J390" s="8"/>
     </row>
     <row r="391" spans="9:10">
-      <c r="I391" s="18"/>
-      <c r="J391" s="18"/>
+      <c r="I391" s="8"/>
+      <c r="J391" s="8"/>
     </row>
     <row r="392" spans="9:10">
-      <c r="I392" s="18"/>
-      <c r="J392" s="18"/>
+      <c r="I392" s="8"/>
+      <c r="J392" s="8"/>
     </row>
     <row r="393" spans="9:10">
-      <c r="I393" s="18"/>
-      <c r="J393" s="18"/>
+      <c r="I393" s="8"/>
+      <c r="J393" s="8"/>
     </row>
     <row r="394" spans="9:10">
-      <c r="I394" s="18"/>
-      <c r="J394" s="18"/>
+      <c r="I394" s="8"/>
+      <c r="J394" s="8"/>
     </row>
     <row r="395" spans="9:10">
-      <c r="I395" s="18"/>
-      <c r="J395" s="18"/>
+      <c r="I395" s="8"/>
+      <c r="J395" s="8"/>
     </row>
     <row r="396" spans="9:10">
-      <c r="I396" s="18"/>
-      <c r="J396" s="18"/>
+      <c r="I396" s="8"/>
+      <c r="J396" s="8"/>
     </row>
     <row r="397" spans="9:10">
-      <c r="I397" s="18"/>
-      <c r="J397" s="18"/>
+      <c r="I397" s="8"/>
+      <c r="J397" s="8"/>
     </row>
     <row r="398" spans="9:10">
-      <c r="I398" s="18"/>
-      <c r="J398" s="18"/>
+      <c r="I398" s="8"/>
+      <c r="J398" s="8"/>
     </row>
     <row r="399" spans="9:10">
-      <c r="I399" s="18"/>
-      <c r="J399" s="18"/>
+      <c r="I399" s="8"/>
+      <c r="J399" s="8"/>
     </row>
     <row r="400" spans="9:10">
-      <c r="I400" s="18"/>
-      <c r="J400" s="18"/>
+      <c r="I400" s="8"/>
+      <c r="J400" s="8"/>
     </row>
     <row r="401" spans="9:10">
-      <c r="I401" s="18"/>
-      <c r="J401" s="18"/>
+      <c r="I401" s="8"/>
+      <c r="J401" s="8"/>
     </row>
     <row r="402" spans="9:10">
-      <c r="I402" s="18"/>
-      <c r="J402" s="18"/>
+      <c r="I402" s="8"/>
+      <c r="J402" s="8"/>
     </row>
     <row r="403" spans="9:10">
-      <c r="I403" s="18"/>
-      <c r="J403" s="18"/>
+      <c r="I403" s="8"/>
+      <c r="J403" s="8"/>
     </row>
     <row r="404" spans="9:10">
-      <c r="I404" s="18"/>
-      <c r="J404" s="18"/>
+      <c r="I404" s="8"/>
+      <c r="J404" s="8"/>
     </row>
     <row r="405" spans="9:10">
-      <c r="I405" s="18"/>
-      <c r="J405" s="18"/>
+      <c r="I405" s="8"/>
+      <c r="J405" s="8"/>
     </row>
     <row r="406" spans="9:10">
-      <c r="I406" s="18"/>
-      <c r="J406" s="18"/>
+      <c r="I406" s="8"/>
+      <c r="J406" s="8"/>
     </row>
     <row r="407" spans="9:10">
-      <c r="I407" s="18"/>
-      <c r="J407" s="18"/>
+      <c r="I407" s="8"/>
+      <c r="J407" s="8"/>
     </row>
     <row r="408" spans="9:10">
-      <c r="I408" s="18"/>
-      <c r="J408" s="18"/>
+      <c r="I408" s="8"/>
+      <c r="J408" s="8"/>
     </row>
     <row r="409" spans="9:10">
-      <c r="I409" s="18"/>
-      <c r="J409" s="18"/>
+      <c r="I409" s="8"/>
+      <c r="J409" s="8"/>
     </row>
     <row r="410" spans="9:10">
-      <c r="I410" s="18"/>
-      <c r="J410" s="18"/>
+      <c r="I410" s="8"/>
+      <c r="J410" s="8"/>
     </row>
     <row r="411" spans="9:10">
-      <c r="I411" s="18"/>
-      <c r="J411" s="18"/>
+      <c r="I411" s="8"/>
+      <c r="J411" s="8"/>
     </row>
     <row r="412" spans="9:10">
-      <c r="I412" s="18"/>
-      <c r="J412" s="18"/>
+      <c r="I412" s="8"/>
+      <c r="J412" s="8"/>
     </row>
     <row r="413" spans="9:10">
-      <c r="I413" s="18"/>
-      <c r="J413" s="18"/>
+      <c r="I413" s="8"/>
+      <c r="J413" s="8"/>
     </row>
     <row r="414" spans="9:10">
-      <c r="I414" s="18"/>
-      <c r="J414" s="18"/>
+      <c r="I414" s="8"/>
+      <c r="J414" s="8"/>
     </row>
     <row r="415" spans="9:10">
-      <c r="I415" s="18"/>
-      <c r="J415" s="18"/>
+      <c r="I415" s="8"/>
+      <c r="J415" s="8"/>
     </row>
     <row r="416" spans="9:10">
-      <c r="I416" s="18"/>
-      <c r="J416" s="18"/>
+      <c r="I416" s="8"/>
+      <c r="J416" s="8"/>
     </row>
     <row r="417" spans="9:10">
-      <c r="I417" s="18"/>
-      <c r="J417" s="18"/>
+      <c r="I417" s="8"/>
+      <c r="J417" s="8"/>
     </row>
     <row r="418" spans="9:10">
-      <c r="I418" s="18"/>
-      <c r="J418" s="18"/>
+      <c r="I418" s="8"/>
+      <c r="J418" s="8"/>
     </row>
     <row r="419" spans="9:10">
-      <c r="I419" s="18"/>
-      <c r="J419" s="18"/>
+      <c r="I419" s="8"/>
+      <c r="J419" s="8"/>
     </row>
     <row r="420" spans="9:10">
-      <c r="I420" s="18"/>
-      <c r="J420" s="18"/>
+      <c r="I420" s="8"/>
+      <c r="J420" s="8"/>
     </row>
     <row r="421" spans="9:10">
-      <c r="I421" s="18"/>
-      <c r="J421" s="18"/>
+      <c r="I421" s="8"/>
+      <c r="J421" s="8"/>
     </row>
     <row r="422" spans="9:10">
-      <c r="I422" s="18"/>
-      <c r="J422" s="18"/>
+      <c r="I422" s="8"/>
+      <c r="J422" s="8"/>
     </row>
     <row r="423" spans="9:10">
-      <c r="I423" s="18"/>
-      <c r="J423" s="18"/>
+      <c r="I423" s="8"/>
+      <c r="J423" s="8"/>
     </row>
     <row r="424" spans="9:10">
-      <c r="I424" s="18"/>
-      <c r="J424" s="18"/>
+      <c r="I424" s="8"/>
+      <c r="J424" s="8"/>
     </row>
     <row r="425" spans="9:10">
-      <c r="I425" s="18"/>
-      <c r="J425" s="18"/>
+      <c r="I425" s="8"/>
+      <c r="J425" s="8"/>
     </row>
     <row r="426" spans="9:10">
-      <c r="I426" s="18"/>
-      <c r="J426" s="18"/>
+      <c r="I426" s="8"/>
+      <c r="J426" s="8"/>
     </row>
     <row r="427" spans="9:10">
-      <c r="I427" s="18"/>
-      <c r="J427" s="18"/>
+      <c r="I427" s="8"/>
+      <c r="J427" s="8"/>
     </row>
     <row r="428" spans="9:10">
-      <c r="I428" s="18"/>
-      <c r="J428" s="18"/>
+      <c r="I428" s="8"/>
+      <c r="J428" s="8"/>
     </row>
     <row r="429" spans="9:10">
-      <c r="I429" s="18"/>
-      <c r="J429" s="18"/>
+      <c r="I429" s="8"/>
+      <c r="J429" s="8"/>
     </row>
     <row r="430" spans="9:10">
-      <c r="I430" s="18"/>
-      <c r="J430" s="18"/>
+      <c r="I430" s="8"/>
+      <c r="J430" s="8"/>
     </row>
     <row r="431" spans="9:10">
-      <c r="I431" s="18"/>
-      <c r="J431" s="18"/>
+      <c r="I431" s="8"/>
+      <c r="J431" s="8"/>
     </row>
     <row r="432" spans="9:10">
-      <c r="I432" s="18"/>
-      <c r="J432" s="18"/>
+      <c r="I432" s="8"/>
+      <c r="J432" s="8"/>
     </row>
     <row r="433" spans="9:10">
-      <c r="I433" s="18"/>
-      <c r="J433" s="18"/>
+      <c r="I433" s="8"/>
+      <c r="J433" s="8"/>
     </row>
     <row r="434" spans="9:10">
-      <c r="I434" s="18"/>
-      <c r="J434" s="18"/>
+      <c r="I434" s="8"/>
+      <c r="J434" s="8"/>
     </row>
     <row r="435" spans="9:10">
-      <c r="I435" s="18"/>
-      <c r="J435" s="18"/>
+      <c r="I435" s="8"/>
+      <c r="J435" s="8"/>
     </row>
     <row r="436" spans="9:10">
-      <c r="I436" s="18"/>
-      <c r="J436" s="18"/>
+      <c r="I436" s="8"/>
+      <c r="J436" s="8"/>
     </row>
     <row r="437" spans="9:10">
-      <c r="I437" s="18"/>
-      <c r="J437" s="18"/>
+      <c r="I437" s="8"/>
+      <c r="J437" s="8"/>
     </row>
     <row r="438" spans="9:10">
-      <c r="I438" s="18"/>
-      <c r="J438" s="18"/>
+      <c r="I438" s="8"/>
+      <c r="J438" s="8"/>
     </row>
     <row r="439" spans="9:10">
-      <c r="I439" s="18"/>
-      <c r="J439" s="18"/>
+      <c r="I439" s="8"/>
+      <c r="J439" s="8"/>
     </row>
     <row r="440" spans="9:10">
-      <c r="I440" s="18"/>
-      <c r="J440" s="18"/>
+      <c r="I440" s="8"/>
+      <c r="J440" s="8"/>
     </row>
     <row r="441" spans="9:10">
-      <c r="I441" s="18"/>
-      <c r="J441" s="18"/>
+      <c r="I441" s="8"/>
+      <c r="J441" s="8"/>
     </row>
     <row r="442" spans="9:10">
-      <c r="I442" s="18"/>
-      <c r="J442" s="18"/>
+      <c r="I442" s="8"/>
+      <c r="J442" s="8"/>
     </row>
     <row r="443" spans="9:10">
-      <c r="I443" s="18"/>
-      <c r="J443" s="18"/>
+      <c r="I443" s="8"/>
+      <c r="J443" s="8"/>
     </row>
     <row r="444" spans="9:10">
-      <c r="I444" s="18"/>
-      <c r="J444" s="18"/>
+      <c r="I444" s="8"/>
+      <c r="J444" s="8"/>
     </row>
     <row r="445" spans="9:10">
-      <c r="I445" s="18"/>
-      <c r="J445" s="18"/>
+      <c r="I445" s="8"/>
+      <c r="J445" s="8"/>
     </row>
     <row r="446" spans="9:10">
-      <c r="I446" s="18"/>
-      <c r="J446" s="18"/>
+      <c r="I446" s="8"/>
+      <c r="J446" s="8"/>
     </row>
     <row r="447" spans="9:10">
-      <c r="I447" s="18"/>
-      <c r="J447" s="18"/>
+      <c r="I447" s="8"/>
+      <c r="J447" s="8"/>
     </row>
     <row r="448" spans="9:10">
-      <c r="I448" s="18"/>
-      <c r="J448" s="18"/>
+      <c r="I448" s="8"/>
+      <c r="J448" s="8"/>
     </row>
     <row r="449" spans="9:10">
-      <c r="I449" s="18"/>
-      <c r="J449" s="18"/>
+      <c r="I449" s="8"/>
+      <c r="J449" s="8"/>
     </row>
     <row r="450" spans="9:10">
-      <c r="I450" s="18"/>
-      <c r="J450" s="18"/>
+      <c r="I450" s="8"/>
+      <c r="J450" s="8"/>
     </row>
     <row r="451" spans="9:10">
-      <c r="I451" s="18"/>
-      <c r="J451" s="18"/>
+      <c r="I451" s="8"/>
+      <c r="J451" s="8"/>
     </row>
     <row r="452" spans="9:10">
-      <c r="I452" s="18"/>
-      <c r="J452" s="18"/>
+      <c r="I452" s="8"/>
+      <c r="J452" s="8"/>
     </row>
     <row r="453" spans="9:10">
-      <c r="I453" s="18"/>
-      <c r="J453" s="18"/>
+      <c r="I453" s="8"/>
+      <c r="J453" s="8"/>
     </row>
     <row r="454" spans="9:10">
-      <c r="I454" s="18"/>
-      <c r="J454" s="18"/>
+      <c r="I454" s="8"/>
+      <c r="J454" s="8"/>
     </row>
     <row r="455" spans="9:10">
-      <c r="I455" s="18"/>
-      <c r="J455" s="18"/>
+      <c r="I455" s="8"/>
+      <c r="J455" s="8"/>
     </row>
     <row r="456" spans="9:10">
-      <c r="I456" s="18"/>
-      <c r="J456" s="18"/>
+      <c r="I456" s="8"/>
+      <c r="J456" s="8"/>
     </row>
     <row r="457" spans="9:10">
-      <c r="I457" s="18"/>
-      <c r="J457" s="18"/>
+      <c r="I457" s="8"/>
+      <c r="J457" s="8"/>
     </row>
     <row r="458" spans="9:10">
-      <c r="I458" s="18"/>
-      <c r="J458" s="18"/>
+      <c r="I458" s="8"/>
+      <c r="J458" s="8"/>
     </row>
     <row r="459" spans="9:10">
-      <c r="I459" s="18"/>
-      <c r="J459" s="18"/>
+      <c r="I459" s="8"/>
+      <c r="J459" s="8"/>
     </row>
     <row r="460" spans="9:10">
-      <c r="I460" s="18"/>
-      <c r="J460" s="18"/>
+      <c r="I460" s="8"/>
+      <c r="J460" s="8"/>
     </row>
     <row r="461" spans="9:10">
-      <c r="I461" s="18"/>
-      <c r="J461" s="18"/>
+      <c r="I461" s="8"/>
+      <c r="J461" s="8"/>
     </row>
     <row r="462" spans="9:10">
-      <c r="I462" s="18"/>
-      <c r="J462" s="18"/>
+      <c r="I462" s="8"/>
+      <c r="J462" s="8"/>
     </row>
     <row r="463" spans="9:10">
-      <c r="I463" s="18"/>
-      <c r="J463" s="18"/>
+      <c r="I463" s="8"/>
+      <c r="J463" s="8"/>
     </row>
     <row r="464" spans="9:10">
-      <c r="I464" s="18"/>
-      <c r="J464" s="18"/>
+      <c r="I464" s="8"/>
+      <c r="J464" s="8"/>
     </row>
     <row r="465" spans="9:10">
-      <c r="I465" s="18"/>
-      <c r="J465" s="18"/>
+      <c r="I465" s="8"/>
+      <c r="J465" s="8"/>
     </row>
     <row r="466" spans="9:10">
-      <c r="I466" s="18"/>
-      <c r="J466" s="18"/>
+      <c r="I466" s="8"/>
+      <c r="J466" s="8"/>
     </row>
     <row r="467" spans="9:10">
-      <c r="I467" s="18"/>
-      <c r="J467" s="18"/>
+      <c r="I467" s="8"/>
+      <c r="J467" s="8"/>
     </row>
     <row r="468" spans="9:10">
-      <c r="I468" s="18"/>
-      <c r="J468" s="18"/>
+      <c r="I468" s="8"/>
+      <c r="J468" s="8"/>
     </row>
     <row r="469" spans="9:10">
-      <c r="I469" s="18"/>
-      <c r="J469" s="18"/>
+      <c r="I469" s="8"/>
+      <c r="J469" s="8"/>
     </row>
     <row r="470" spans="9:10">
-      <c r="I470" s="18"/>
-      <c r="J470" s="18"/>
+      <c r="I470" s="8"/>
+      <c r="J470" s="8"/>
     </row>
     <row r="471" spans="9:10">
-      <c r="I471" s="18"/>
-      <c r="J471" s="18"/>
+      <c r="I471" s="8"/>
+      <c r="J471" s="8"/>
     </row>
     <row r="472" spans="9:10">
-      <c r="I472" s="18"/>
-      <c r="J472" s="18"/>
+      <c r="I472" s="8"/>
+      <c r="J472" s="8"/>
     </row>
     <row r="473" spans="9:10">
-      <c r="I473" s="18"/>
-      <c r="J473" s="18"/>
+      <c r="I473" s="8"/>
+      <c r="J473" s="8"/>
     </row>
     <row r="474" spans="9:10">
-      <c r="I474" s="18"/>
-      <c r="J474" s="18"/>
+      <c r="I474" s="8"/>
+      <c r="J474" s="8"/>
     </row>
     <row r="475" spans="9:10">
-      <c r="I475" s="18"/>
-      <c r="J475" s="18"/>
+      <c r="I475" s="8"/>
+      <c r="J475" s="8"/>
     </row>
     <row r="476" spans="9:10">
-      <c r="I476" s="18"/>
-      <c r="J476" s="18"/>
+      <c r="I476" s="8"/>
+      <c r="J476" s="8"/>
     </row>
     <row r="477" spans="9:10">
-      <c r="I477" s="18"/>
-      <c r="J477" s="18"/>
+      <c r="I477" s="8"/>
+      <c r="J477" s="8"/>
     </row>
     <row r="478" spans="9:10">
-      <c r="I478" s="18"/>
-      <c r="J478" s="18"/>
+      <c r="I478" s="8"/>
+      <c r="J478" s="8"/>
     </row>
     <row r="479" spans="9:10">
-      <c r="I479" s="18"/>
-      <c r="J479" s="18"/>
+      <c r="I479" s="8"/>
+      <c r="J479" s="8"/>
     </row>
     <row r="480" spans="9:10">
-      <c r="I480" s="18"/>
-      <c r="J480" s="18"/>
+      <c r="I480" s="8"/>
+      <c r="J480" s="8"/>
     </row>
     <row r="481" spans="9:10">
-      <c r="I481" s="18"/>
-      <c r="J481" s="18"/>
+      <c r="I481" s="8"/>
+      <c r="J481" s="8"/>
     </row>
     <row r="482" spans="9:10">
-      <c r="I482" s="18"/>
-      <c r="J482" s="18"/>
+      <c r="I482" s="8"/>
+      <c r="J482" s="8"/>
     </row>
     <row r="483" spans="9:10">
-      <c r="I483" s="18"/>
-      <c r="J483" s="18"/>
+      <c r="I483" s="8"/>
+      <c r="J483" s="8"/>
     </row>
     <row r="484" spans="9:10">
-      <c r="I484" s="18"/>
-      <c r="J484" s="18"/>
+      <c r="I484" s="8"/>
+      <c r="J484" s="8"/>
     </row>
     <row r="485" spans="9:10">
-      <c r="I485" s="18"/>
-      <c r="J485" s="18"/>
+      <c r="I485" s="8"/>
+      <c r="J485" s="8"/>
     </row>
     <row r="486" spans="9:10">
-      <c r="I486" s="18"/>
-      <c r="J486" s="18"/>
+      <c r="I486" s="8"/>
+      <c r="J486" s="8"/>
     </row>
     <row r="487" spans="9:10">
-      <c r="I487" s="18"/>
-      <c r="J487" s="18"/>
+      <c r="I487" s="8"/>
+      <c r="J487" s="8"/>
     </row>
     <row r="488" spans="9:10">
-      <c r="I488" s="18"/>
-      <c r="J488" s="18"/>
+      <c r="I488" s="8"/>
+      <c r="J488" s="8"/>
     </row>
     <row r="489" spans="9:10">
-      <c r="I489" s="18"/>
-      <c r="J489" s="18"/>
+      <c r="I489" s="8"/>
+      <c r="J489" s="8"/>
     </row>
     <row r="490" spans="9:10">
-      <c r="I490" s="18"/>
-      <c r="J490" s="18"/>
+      <c r="I490" s="8"/>
+      <c r="J490" s="8"/>
     </row>
     <row r="491" spans="9:10">
-      <c r="I491" s="18"/>
-      <c r="J491" s="18"/>
+      <c r="I491" s="8"/>
+      <c r="J491" s="8"/>
     </row>
     <row r="492" spans="9:10">
-      <c r="I492" s="18"/>
-      <c r="J492" s="18"/>
+      <c r="I492" s="8"/>
+      <c r="J492" s="8"/>
     </row>
     <row r="493" spans="9:10">
-      <c r="I493" s="18"/>
-      <c r="J493" s="18"/>
+      <c r="I493" s="8"/>
+      <c r="J493" s="8"/>
     </row>
     <row r="494" spans="9:10">
-      <c r="I494" s="18"/>
-      <c r="J494" s="18"/>
+      <c r="I494" s="8"/>
+      <c r="J494" s="8"/>
     </row>
     <row r="495" spans="9:10">
-      <c r="I495" s="18"/>
-      <c r="J495" s="18"/>
+      <c r="I495" s="8"/>
+      <c r="J495" s="8"/>
     </row>
     <row r="496" spans="9:10">
-      <c r="I496" s="18"/>
-      <c r="J496" s="18"/>
+      <c r="I496" s="8"/>
+      <c r="J496" s="8"/>
     </row>
     <row r="497" spans="9:10">
-      <c r="I497" s="18"/>
-      <c r="J497" s="18"/>
+      <c r="I497" s="8"/>
+      <c r="J497" s="8"/>
     </row>
     <row r="498" spans="9:10">
-      <c r="I498" s="18"/>
-      <c r="J498" s="18"/>
+      <c r="I498" s="8"/>
+      <c r="J498" s="8"/>
     </row>
     <row r="499" spans="9:10">
-      <c r="I499" s="18"/>
-      <c r="J499" s="18"/>
+      <c r="I499" s="8"/>
+      <c r="J499" s="8"/>
     </row>
     <row r="500" spans="9:10">
-      <c r="I500" s="18"/>
-      <c r="J500" s="18"/>
+      <c r="I500" s="8"/>
+      <c r="J500" s="8"/>
     </row>
     <row r="501" spans="9:10">
-      <c r="I501" s="18"/>
-      <c r="J501" s="18"/>
+      <c r="I501" s="8"/>
+      <c r="J501" s="8"/>
     </row>
     <row r="502" spans="9:10">
-      <c r="I502" s="18"/>
-      <c r="J502" s="18"/>
+      <c r="I502" s="8"/>
+      <c r="J502" s="8"/>
     </row>
     <row r="503" spans="9:10">
-      <c r="I503" s="18"/>
-      <c r="J503" s="18"/>
+      <c r="I503" s="8"/>
+      <c r="J503" s="8"/>
     </row>
     <row r="504" spans="9:10">
-      <c r="I504" s="18"/>
-      <c r="J504" s="18"/>
+      <c r="I504" s="8"/>
+      <c r="J504" s="8"/>
     </row>
     <row r="505" spans="9:10">
-      <c r="I505" s="18"/>
-      <c r="J505" s="18"/>
+      <c r="I505" s="8"/>
+      <c r="J505" s="8"/>
     </row>
     <row r="506" spans="9:10">
-      <c r="I506" s="18"/>
-      <c r="J506" s="18"/>
+      <c r="I506" s="8"/>
+      <c r="J506" s="8"/>
     </row>
     <row r="507" spans="9:10">
-      <c r="I507" s="18"/>
-      <c r="J507" s="18"/>
+      <c r="I507" s="8"/>
+      <c r="J507" s="8"/>
     </row>
     <row r="508" spans="9:10">
-      <c r="I508" s="18"/>
-      <c r="J508" s="18"/>
+      <c r="I508" s="8"/>
+      <c r="J508" s="8"/>
     </row>
     <row r="509" spans="9:10">
-      <c r="I509" s="18"/>
-      <c r="J509" s="18"/>
+      <c r="I509" s="8"/>
+      <c r="J509" s="8"/>
     </row>
     <row r="510" spans="9:10">
-      <c r="I510" s="18"/>
-      <c r="J510" s="18"/>
+      <c r="I510" s="8"/>
+      <c r="J510" s="8"/>
     </row>
     <row r="511" spans="9:10">
-      <c r="I511" s="18"/>
-      <c r="J511" s="18"/>
+      <c r="I511" s="8"/>
+      <c r="J511" s="8"/>
     </row>
     <row r="512" spans="9:10">
-      <c r="I512" s="18"/>
-      <c r="J512" s="18"/>
+      <c r="I512" s="8"/>
+      <c r="J512" s="8"/>
     </row>
     <row r="513" spans="9:10">
-      <c r="I513" s="18"/>
-      <c r="J513" s="18"/>
+      <c r="I513" s="8"/>
+      <c r="J513" s="8"/>
     </row>
     <row r="514" spans="9:10">
-      <c r="I514" s="18"/>
-      <c r="J514" s="18"/>
+      <c r="I514" s="8"/>
+      <c r="J514" s="8"/>
     </row>
     <row r="515" spans="9:10">
-      <c r="I515" s="18"/>
-      <c r="J515" s="18"/>
+      <c r="I515" s="8"/>
+      <c r="J515" s="8"/>
     </row>
     <row r="516" spans="9:10">
-      <c r="I516" s="18"/>
-      <c r="J516" s="18"/>
+      <c r="I516" s="8"/>
+      <c r="J516" s="8"/>
     </row>
     <row r="517" spans="9:10">
-      <c r="I517" s="18"/>
-      <c r="J517" s="18"/>
+      <c r="I517" s="8"/>
+      <c r="J517" s="8"/>
     </row>
     <row r="518" spans="9:10">
-      <c r="I518" s="18"/>
-      <c r="J518" s="18"/>
+      <c r="I518" s="8"/>
+      <c r="J518" s="8"/>
     </row>
     <row r="519" spans="9:10">
-      <c r="I519" s="18"/>
-      <c r="J519" s="18"/>
+      <c r="I519" s="8"/>
+      <c r="J519" s="8"/>
     </row>
     <row r="520" spans="9:10">
-      <c r="I520" s="18"/>
-      <c r="J520" s="18"/>
+      <c r="I520" s="8"/>
+      <c r="J520" s="8"/>
     </row>
     <row r="521" spans="9:10">
-      <c r="I521" s="18"/>
-      <c r="J521" s="18"/>
+      <c r="I521" s="8"/>
+      <c r="J521" s="8"/>
     </row>
     <row r="522" spans="9:10">
-      <c r="I522" s="18"/>
-      <c r="J522" s="18"/>
+      <c r="I522" s="8"/>
+      <c r="J522" s="8"/>
     </row>
     <row r="523" spans="9:10">
-      <c r="I523" s="18"/>
-      <c r="J523" s="18"/>
+      <c r="I523" s="8"/>
+      <c r="J523" s="8"/>
     </row>
     <row r="524" spans="9:10">
-      <c r="I524" s="18"/>
-      <c r="J524" s="18"/>
+      <c r="I524" s="8"/>
+      <c r="J524" s="8"/>
     </row>
     <row r="525" spans="9:10">
-      <c r="I525" s="18"/>
-      <c r="J525" s="18"/>
+      <c r="I525" s="8"/>
+      <c r="J525" s="8"/>
     </row>
     <row r="526" spans="9:10">
-      <c r="I526" s="18"/>
-      <c r="J526" s="18"/>
+      <c r="I526" s="8"/>
+      <c r="J526" s="8"/>
     </row>
     <row r="527" spans="9:10">
-      <c r="I527" s="18"/>
-      <c r="J527" s="18"/>
+      <c r="I527" s="8"/>
+      <c r="J527" s="8"/>
     </row>
     <row r="528" spans="9:10">
-      <c r="I528" s="18"/>
-      <c r="J528" s="18"/>
+      <c r="I528" s="8"/>
+      <c r="J528" s="8"/>
     </row>
     <row r="529" spans="9:10">
-      <c r="I529" s="18"/>
-      <c r="J529" s="18"/>
+      <c r="I529" s="8"/>
+      <c r="J529" s="8"/>
     </row>
     <row r="530" spans="9:10">
-      <c r="I530" s="18"/>
-      <c r="J530" s="18"/>
+      <c r="I530" s="8"/>
+      <c r="J530" s="8"/>
     </row>
     <row r="531" spans="9:10">
-      <c r="I531" s="18"/>
-      <c r="J531" s="18"/>
+      <c r="I531" s="8"/>
+      <c r="J531" s="8"/>
     </row>
     <row r="532" spans="9:10">
-      <c r="I532" s="18"/>
-      <c r="J532" s="18"/>
+      <c r="I532" s="8"/>
+      <c r="J532" s="8"/>
     </row>
     <row r="533" spans="9:10">
-      <c r="I533" s="18"/>
-      <c r="J533" s="18"/>
+      <c r="I533" s="8"/>
+      <c r="J533" s="8"/>
     </row>
     <row r="534" spans="9:10">
-      <c r="I534" s="18"/>
-      <c r="J534" s="18"/>
+      <c r="I534" s="8"/>
+      <c r="J534" s="8"/>
     </row>
     <row r="535" spans="9:10">
-      <c r="I535" s="18"/>
-      <c r="J535" s="18"/>
+      <c r="I535" s="8"/>
+      <c r="J535" s="8"/>
     </row>
     <row r="536" spans="9:10">
-      <c r="I536" s="18"/>
-      <c r="J536" s="18"/>
+      <c r="I536" s="8"/>
+      <c r="J536" s="8"/>
     </row>
     <row r="537" spans="9:10">
-      <c r="I537" s="18"/>
-      <c r="J537" s="18"/>
+      <c r="I537" s="8"/>
+      <c r="J537" s="8"/>
     </row>
     <row r="538" spans="9:10">
-      <c r="I538" s="18"/>
-      <c r="J538" s="18"/>
+      <c r="I538" s="8"/>
+      <c r="J538" s="8"/>
     </row>
     <row r="539" spans="9:10">
-      <c r="I539" s="18"/>
-      <c r="J539" s="18"/>
+      <c r="I539" s="8"/>
+      <c r="J539" s="8"/>
     </row>
     <row r="540" spans="9:10">
-      <c r="I540" s="18"/>
-      <c r="J540" s="18"/>
+      <c r="I540" s="8"/>
+      <c r="J540" s="8"/>
     </row>
     <row r="541" spans="9:10">
-      <c r="I541" s="18"/>
-      <c r="J541" s="18"/>
+      <c r="I541" s="8"/>
+      <c r="J541" s="8"/>
     </row>
     <row r="542" spans="9:10">
-      <c r="I542" s="18"/>
-      <c r="J542" s="18"/>
+      <c r="I542" s="8"/>
+      <c r="J542" s="8"/>
     </row>
     <row r="543" spans="9:10">
-      <c r="I543" s="18"/>
-      <c r="J543" s="18"/>
+      <c r="I543" s="8"/>
+      <c r="J543" s="8"/>
     </row>
     <row r="544" spans="9:10">
-      <c r="I544" s="18"/>
-      <c r="J544" s="18"/>
+      <c r="I544" s="8"/>
+      <c r="J544" s="8"/>
     </row>
     <row r="545" spans="9:10">
-      <c r="I545" s="18"/>
-      <c r="J545" s="18"/>
+      <c r="I545" s="8"/>
+      <c r="J545" s="8"/>
     </row>
     <row r="546" spans="9:10">
-      <c r="I546" s="18"/>
-      <c r="J546" s="18"/>
+      <c r="I546" s="8"/>
+      <c r="J546" s="8"/>
     </row>
     <row r="547" spans="9:10">
-      <c r="I547" s="18"/>
-      <c r="J547" s="18"/>
+      <c r="I547" s="8"/>
+      <c r="J547" s="8"/>
     </row>
     <row r="548" spans="9:10">
-      <c r="I548" s="18"/>
-      <c r="J548" s="18"/>
+      <c r="I548" s="8"/>
+      <c r="J548" s="8"/>
     </row>
     <row r="549" spans="9:10">
-      <c r="I549" s="18"/>
-      <c r="J549" s="18"/>
+      <c r="I549" s="8"/>
+      <c r="J549" s="8"/>
     </row>
     <row r="550" spans="9:10">
-      <c r="I550" s="18"/>
-      <c r="J550" s="18"/>
+      <c r="I550" s="8"/>
+      <c r="J550" s="8"/>
     </row>
     <row r="551" spans="9:10">
-      <c r="I551" s="18"/>
-      <c r="J551" s="18"/>
+      <c r="I551" s="8"/>
+      <c r="J551" s="8"/>
     </row>
     <row r="552" spans="9:10">
-      <c r="I552" s="18"/>
-      <c r="J552" s="18"/>
+      <c r="I552" s="8"/>
+      <c r="J552" s="8"/>
     </row>
     <row r="553" spans="9:10">
-      <c r="I553" s="18"/>
-      <c r="J553" s="18"/>
+      <c r="I553" s="8"/>
+      <c r="J553" s="8"/>
     </row>
     <row r="554" spans="9:10">
-      <c r="I554" s="18"/>
-      <c r="J554" s="18"/>
+      <c r="I554" s="8"/>
+      <c r="J554" s="8"/>
     </row>
     <row r="555" spans="9:10">
-      <c r="I555" s="18"/>
-      <c r="J555" s="18"/>
+      <c r="I555" s="8"/>
+      <c r="J555" s="8"/>
     </row>
     <row r="556" spans="9:10">
-      <c r="I556" s="18"/>
-      <c r="J556" s="18"/>
+      <c r="I556" s="8"/>
+      <c r="J556" s="8"/>
     </row>
     <row r="557" spans="9:10">
-      <c r="I557" s="18"/>
-      <c r="J557" s="18"/>
+      <c r="I557" s="8"/>
+      <c r="J557" s="8"/>
     </row>
     <row r="558" spans="9:10">
-      <c r="I558" s="18"/>
-      <c r="J558" s="18"/>
+      <c r="I558" s="8"/>
+      <c r="J558" s="8"/>
     </row>
     <row r="559" spans="9:10">
-      <c r="I559" s="18"/>
-      <c r="J559" s="18"/>
+      <c r="I559" s="8"/>
+      <c r="J559" s="8"/>
     </row>
     <row r="560" spans="9:10">
-      <c r="I560" s="18"/>
-      <c r="J560" s="18"/>
+      <c r="I560" s="8"/>
+      <c r="J560" s="8"/>
     </row>
     <row r="561" spans="9:10">
-      <c r="I561" s="18"/>
-      <c r="J561" s="18"/>
+      <c r="I561" s="8"/>
+      <c r="J561" s="8"/>
     </row>
     <row r="562" spans="9:10">
-      <c r="I562" s="18"/>
-      <c r="J562" s="18"/>
+      <c r="I562" s="8"/>
+      <c r="J562" s="8"/>
     </row>
     <row r="563" spans="9:10">
-      <c r="I563" s="18"/>
-      <c r="J563" s="18"/>
+      <c r="I563" s="8"/>
+      <c r="J563" s="8"/>
     </row>
     <row r="564" spans="9:10">
-      <c r="I564" s="18"/>
-      <c r="J564" s="18"/>
+      <c r="I564" s="8"/>
+      <c r="J564" s="8"/>
     </row>
     <row r="565" spans="9:10">
-      <c r="I565" s="18"/>
-      <c r="J565" s="18"/>
+      <c r="I565" s="8"/>
+      <c r="J565" s="8"/>
     </row>
     <row r="566" spans="9:10">
-      <c r="I566" s="18"/>
-      <c r="J566" s="18"/>
+      <c r="I566" s="8"/>
+      <c r="J566" s="8"/>
     </row>
     <row r="567" spans="9:10">
-      <c r="I567" s="18"/>
-      <c r="J567" s="18"/>
+      <c r="I567" s="8"/>
+      <c r="J567" s="8"/>
     </row>
     <row r="568" spans="9:10">
-      <c r="I568" s="18"/>
-      <c r="J568" s="18"/>
+      <c r="I568" s="8"/>
+      <c r="J568" s="8"/>
     </row>
     <row r="569" spans="9:10">
-      <c r="I569" s="18"/>
-      <c r="J569" s="18"/>
+      <c r="I569" s="8"/>
+      <c r="J569" s="8"/>
     </row>
     <row r="570" spans="9:10">
-      <c r="I570" s="18"/>
-      <c r="J570" s="18"/>
+      <c r="I570" s="8"/>
+      <c r="J570" s="8"/>
     </row>
     <row r="571" spans="9:10">
-      <c r="I571" s="18"/>
-      <c r="J571" s="18"/>
+      <c r="I571" s="8"/>
+      <c r="J571" s="8"/>
     </row>
     <row r="572" spans="9:10">
-      <c r="I572" s="18"/>
-      <c r="J572" s="18"/>
+      <c r="I572" s="8"/>
+      <c r="J572" s="8"/>
     </row>
     <row r="573" spans="9:10">
-      <c r="I573" s="18"/>
-      <c r="J573" s="18"/>
+      <c r="I573" s="8"/>
+      <c r="J573" s="8"/>
     </row>
     <row r="574" spans="9:10">
-      <c r="I574" s="18"/>
-      <c r="J574" s="18"/>
+      <c r="I574" s="8"/>
+      <c r="J574" s="8"/>
     </row>
     <row r="575" spans="9:10">
-      <c r="I575" s="18"/>
-      <c r="J575" s="18"/>
+      <c r="I575" s="8"/>
+      <c r="J575" s="8"/>
     </row>
     <row r="576" spans="9:10">
-      <c r="I576" s="18"/>
-      <c r="J576" s="18"/>
+      <c r="I576" s="8"/>
+      <c r="J576" s="8"/>
     </row>
     <row r="577" spans="9:10">
-      <c r="I577" s="18"/>
-      <c r="J577" s="18"/>
+      <c r="I577" s="8"/>
+      <c r="J577" s="8"/>
     </row>
     <row r="578" spans="9:10">
-      <c r="I578" s="18"/>
-      <c r="J578" s="18"/>
+      <c r="I578" s="8"/>
+      <c r="J578" s="8"/>
     </row>
     <row r="579" spans="9:10">
-      <c r="I579" s="18"/>
-      <c r="J579" s="18"/>
+      <c r="I579" s="8"/>
+      <c r="J579" s="8"/>
     </row>
     <row r="580" spans="9:10">
-      <c r="I580" s="18"/>
-      <c r="J580" s="18"/>
+      <c r="I580" s="8"/>
+      <c r="J580" s="8"/>
     </row>
     <row r="581" spans="9:10">
-      <c r="I581" s="18"/>
-      <c r="J581" s="18"/>
+      <c r="I581" s="8"/>
+      <c r="J581" s="8"/>
     </row>
     <row r="582" spans="9:10">
-      <c r="I582" s="18"/>
-      <c r="J582" s="18"/>
+      <c r="I582" s="8"/>
+      <c r="J582" s="8"/>
     </row>
     <row r="583" spans="9:10">
-      <c r="I583" s="18"/>
-      <c r="J583" s="18"/>
+      <c r="I583" s="8"/>
+      <c r="J583" s="8"/>
     </row>
     <row r="584" spans="9:10">
-      <c r="I584" s="18"/>
-      <c r="J584" s="18"/>
+      <c r="I584" s="8"/>
+      <c r="J584" s="8"/>
     </row>
     <row r="585" spans="9:10">
-      <c r="I585" s="18"/>
-      <c r="J585" s="18"/>
+      <c r="I585" s="8"/>
+      <c r="J585" s="8"/>
     </row>
     <row r="586" spans="9:10">
-      <c r="I586" s="18"/>
-      <c r="J586" s="18"/>
+      <c r="I586" s="8"/>
+      <c r="J586" s="8"/>
     </row>
     <row r="587" spans="9:10">
-      <c r="I587" s="18"/>
-      <c r="J587" s="18"/>
+      <c r="I587" s="8"/>
+      <c r="J587" s="8"/>
     </row>
     <row r="588" spans="9:10">
-      <c r="I588" s="18"/>
-      <c r="J588" s="18"/>
+      <c r="I588" s="8"/>
+      <c r="J588" s="8"/>
     </row>
     <row r="589" spans="9:10">
-      <c r="I589" s="18"/>
-      <c r="J589" s="18"/>
+      <c r="I589" s="8"/>
+      <c r="J589" s="8"/>
     </row>
     <row r="590" spans="9:10">
-      <c r="I590" s="18"/>
-      <c r="J590" s="18"/>
+      <c r="I590" s="8"/>
+      <c r="J590" s="8"/>
     </row>
     <row r="591" spans="9:10">
-      <c r="I591" s="18"/>
-      <c r="J591" s="18"/>
+      <c r="I591" s="8"/>
+      <c r="J591" s="8"/>
     </row>
     <row r="592" spans="9:10">
-      <c r="I592" s="18"/>
-      <c r="J592" s="18"/>
+      <c r="I592" s="8"/>
+      <c r="J592" s="8"/>
     </row>
     <row r="593" spans="9:10">
-      <c r="I593" s="18"/>
-      <c r="J593" s="18"/>
+      <c r="I593" s="8"/>
+      <c r="J593" s="8"/>
     </row>
     <row r="594" spans="9:10">
-      <c r="I594" s="18"/>
-      <c r="J594" s="18"/>
+      <c r="I594" s="8"/>
+      <c r="J594" s="8"/>
     </row>
     <row r="595" spans="9:10">
-      <c r="I595" s="18"/>
-      <c r="J595" s="18"/>
+      <c r="I595" s="8"/>
+      <c r="J595" s="8"/>
     </row>
     <row r="596" spans="9:10">
-      <c r="I596" s="18"/>
-      <c r="J596" s="18"/>
+      <c r="I596" s="8"/>
+      <c r="J596" s="8"/>
     </row>
     <row r="597" spans="9:10">
-      <c r="I597" s="18"/>
-      <c r="J597" s="18"/>
+      <c r="I597" s="8"/>
+      <c r="J597" s="8"/>
     </row>
     <row r="598" spans="9:10">
-      <c r="I598" s="18"/>
-      <c r="J598" s="18"/>
+      <c r="I598" s="8"/>
+      <c r="J598" s="8"/>
     </row>
     <row r="599" spans="9:10">
-      <c r="I599" s="18"/>
-      <c r="J599" s="18"/>
+      <c r="I599" s="8"/>
+      <c r="J599" s="8"/>
     </row>
     <row r="600" spans="9:10">
-      <c r="I600" s="18"/>
-      <c r="J600" s="18"/>
+      <c r="I600" s="8"/>
+      <c r="J600" s="8"/>
     </row>
     <row r="601" spans="9:10">
-      <c r="I601" s="18"/>
-      <c r="J601" s="18"/>
+      <c r="I601" s="8"/>
+      <c r="J601" s="8"/>
     </row>
     <row r="602" spans="9:10">
-      <c r="I602" s="18"/>
-      <c r="J602" s="18"/>
+      <c r="I602" s="8"/>
+      <c r="J602" s="8"/>
     </row>
     <row r="603" spans="9:10">
-      <c r="I603" s="18"/>
-      <c r="J603" s="18"/>
+      <c r="I603" s="8"/>
+      <c r="J603" s="8"/>
     </row>
     <row r="604" spans="9:10">
-      <c r="I604" s="18"/>
-      <c r="J604" s="18"/>
+      <c r="I604" s="8"/>
+      <c r="J604" s="8"/>
     </row>
     <row r="605" spans="9:10">
-      <c r="I605" s="18"/>
-      <c r="J605" s="18"/>
+      <c r="I605" s="8"/>
+      <c r="J605" s="8"/>
     </row>
     <row r="606" spans="9:10">
-      <c r="I606" s="18"/>
-      <c r="J606" s="18"/>
+      <c r="I606" s="8"/>
+      <c r="J606" s="8"/>
     </row>
     <row r="607" spans="9:10">
-      <c r="I607" s="18"/>
-      <c r="J607" s="18"/>
+      <c r="I607" s="8"/>
+      <c r="J607" s="8"/>
     </row>
     <row r="608" spans="9:10">
-      <c r="I608" s="18"/>
-      <c r="J608" s="18"/>
+      <c r="I608" s="8"/>
+      <c r="J608" s="8"/>
     </row>
     <row r="609" spans="9:10">
-      <c r="I609" s="18"/>
-      <c r="J609" s="18"/>
+      <c r="I609" s="8"/>
+      <c r="J609" s="8"/>
     </row>
     <row r="610" spans="9:10">
-      <c r="I610" s="18"/>
-      <c r="J610" s="18"/>
+      <c r="I610" s="8"/>
+      <c r="J610" s="8"/>
     </row>
     <row r="611" spans="9:10">
-      <c r="I611" s="18"/>
-      <c r="J611" s="18"/>
+      <c r="I611" s="8"/>
+      <c r="J611" s="8"/>
     </row>
     <row r="612" spans="9:10">
-      <c r="I612" s="18"/>
-      <c r="J612" s="18"/>
+      <c r="I612" s="8"/>
+      <c r="J612" s="8"/>
     </row>
     <row r="613" spans="9:10">
-      <c r="I613" s="18"/>
-      <c r="J613" s="18"/>
+      <c r="I613" s="8"/>
+      <c r="J613" s="8"/>
     </row>
     <row r="614" spans="9:10">
-      <c r="I614" s="18"/>
-      <c r="J614" s="18"/>
+      <c r="I614" s="8"/>
+      <c r="J614" s="8"/>
     </row>
     <row r="615" spans="9:10">
-      <c r="I615" s="18"/>
-      <c r="J615" s="18"/>
+      <c r="I615" s="8"/>
+      <c r="J615" s="8"/>
     </row>
     <row r="616" spans="9:10">
-      <c r="I616" s="18"/>
-      <c r="J616" s="18"/>
+      <c r="I616" s="8"/>
+      <c r="J616" s="8"/>
     </row>
     <row r="617" spans="9:10">
-      <c r="I617" s="18"/>
-      <c r="J617" s="18"/>
+      <c r="I617" s="8"/>
+      <c r="J617" s="8"/>
     </row>
     <row r="618" spans="9:10">
-      <c r="I618" s="18"/>
-      <c r="J618" s="18"/>
+      <c r="I618" s="8"/>
+      <c r="J618" s="8"/>
     </row>
     <row r="619" spans="9:10">
-      <c r="I619" s="18"/>
-      <c r="J619" s="18"/>
+      <c r="I619" s="8"/>
+      <c r="J619" s="8"/>
     </row>
     <row r="620" spans="9:10">
-      <c r="I620" s="18"/>
-      <c r="J620" s="18"/>
+      <c r="I620" s="8"/>
+      <c r="J620" s="8"/>
     </row>
     <row r="621" spans="9:10">
-      <c r="I621" s="18"/>
-      <c r="J621" s="18"/>
+      <c r="I621" s="8"/>
+      <c r="J621" s="8"/>
     </row>
     <row r="622" spans="9:10">
-      <c r="I622" s="18"/>
-      <c r="J622" s="18"/>
+      <c r="I622" s="8"/>
+      <c r="J622" s="8"/>
     </row>
     <row r="623" spans="9:10">
-      <c r="I623" s="18"/>
-      <c r="J623" s="18"/>
+      <c r="I623" s="8"/>
+      <c r="J623" s="8"/>
     </row>
     <row r="624" spans="9:10">
-      <c r="I624" s="18"/>
-      <c r="J624" s="18"/>
+      <c r="I624" s="8"/>
+      <c r="J624" s="8"/>
     </row>
     <row r="625" spans="9:10">
-      <c r="I625" s="18"/>
-      <c r="J625" s="18"/>
+      <c r="I625" s="8"/>
+      <c r="J625" s="8"/>
     </row>
     <row r="626" spans="9:10">
-      <c r="I626" s="18"/>
-      <c r="J626" s="18"/>
+      <c r="I626" s="8"/>
+      <c r="J626" s="8"/>
     </row>
     <row r="627" spans="9:10">
-      <c r="I627" s="18"/>
-      <c r="J627" s="18"/>
+      <c r="I627" s="8"/>
+      <c r="J627" s="8"/>
     </row>
     <row r="628" spans="9:10">
-      <c r="I628" s="18"/>
-      <c r="J628" s="18"/>
+      <c r="I628" s="8"/>
+      <c r="J628" s="8"/>
     </row>
     <row r="629" spans="9:10">
-      <c r="I629" s="18"/>
-      <c r="J629" s="18"/>
+      <c r="I629" s="8"/>
+      <c r="J629" s="8"/>
     </row>
     <row r="630" spans="9:10">
-      <c r="I630" s="18"/>
-      <c r="J630" s="18"/>
+      <c r="I630" s="8"/>
+      <c r="J630" s="8"/>
     </row>
     <row r="631" spans="9:10">
-      <c r="I631" s="18"/>
-      <c r="J631" s="18"/>
+      <c r="I631" s="8"/>
+      <c r="J631" s="8"/>
     </row>
     <row r="632" spans="9:10">
-      <c r="I632" s="18"/>
-      <c r="J632" s="18"/>
+      <c r="I632" s="8"/>
+      <c r="J632" s="8"/>
     </row>
     <row r="633" spans="9:10">
-      <c r="I633" s="18"/>
-      <c r="J633" s="18"/>
+      <c r="I633" s="8"/>
+      <c r="J633" s="8"/>
     </row>
     <row r="634" spans="9:10">
-      <c r="I634" s="18"/>
-      <c r="J634" s="18"/>
+      <c r="I634" s="8"/>
+      <c r="J634" s="8"/>
     </row>
     <row r="635" spans="9:10">
-      <c r="I635" s="18"/>
-      <c r="J635" s="18"/>
+      <c r="I635" s="8"/>
+      <c r="J635" s="8"/>
     </row>
     <row r="636" spans="9:10">
-      <c r="I636" s="18"/>
-      <c r="J636" s="18"/>
+      <c r="I636" s="8"/>
+      <c r="J636" s="8"/>
     </row>
     <row r="637" spans="9:10">
-      <c r="I637" s="18"/>
-      <c r="J637" s="18"/>
+      <c r="I637" s="8"/>
+      <c r="J637" s="8"/>
     </row>
     <row r="638" spans="9:10">
-      <c r="I638" s="18"/>
-      <c r="J638" s="18"/>
+      <c r="I638" s="8"/>
+      <c r="J638" s="8"/>
     </row>
     <row r="639" spans="9:10">
-      <c r="I639" s="18"/>
-      <c r="J639" s="18"/>
+      <c r="I639" s="8"/>
+      <c r="J639" s="8"/>
     </row>
     <row r="640" spans="9:10">
-      <c r="I640" s="18"/>
-      <c r="J640" s="18"/>
+      <c r="I640" s="8"/>
+      <c r="J640" s="8"/>
     </row>
     <row r="641" spans="9:10">
-      <c r="I641" s="18"/>
-      <c r="J641" s="18"/>
+      <c r="I641" s="8"/>
+      <c r="J641" s="8"/>
     </row>
     <row r="642" spans="9:10">
-      <c r="I642" s="18"/>
-      <c r="J642" s="18"/>
+      <c r="I642" s="8"/>
+      <c r="J642" s="8"/>
     </row>
     <row r="643" spans="9:10">
-      <c r="I643" s="18"/>
-      <c r="J643" s="18"/>
+      <c r="I643" s="8"/>
+      <c r="J643" s="8"/>
     </row>
     <row r="644" spans="9:10">
-      <c r="I644" s="18"/>
-      <c r="J644" s="18"/>
+      <c r="I644" s="8"/>
+      <c r="J644" s="8"/>
     </row>
     <row r="645" spans="9:10">
-      <c r="I645" s="18"/>
-      <c r="J645" s="18"/>
+      <c r="I645" s="8"/>
+      <c r="J645" s="8"/>
     </row>
     <row r="646" spans="9:10">
-      <c r="I646" s="18"/>
-      <c r="J646" s="18"/>
+      <c r="I646" s="8"/>
+      <c r="J646" s="8"/>
     </row>
     <row r="647" spans="9:10">
-      <c r="I647" s="18"/>
-      <c r="J647" s="18"/>
+      <c r="I647" s="8"/>
+      <c r="J647" s="8"/>
     </row>
     <row r="648" spans="9:10">
-      <c r="I648" s="18"/>
-      <c r="J648" s="18"/>
+      <c r="I648" s="8"/>
+      <c r="J648" s="8"/>
     </row>
     <row r="649" spans="9:10">
-      <c r="I649" s="18"/>
-      <c r="J649" s="18"/>
+      <c r="I649" s="8"/>
+      <c r="J649" s="8"/>
     </row>
     <row r="650" spans="9:10">
-      <c r="I650" s="18"/>
-      <c r="J650" s="18"/>
+      <c r="I650" s="8"/>
+      <c r="J650" s="8"/>
     </row>
     <row r="651" spans="9:10">
-      <c r="I651" s="18"/>
-      <c r="J651" s="18"/>
+      <c r="I651" s="8"/>
+      <c r="J651" s="8"/>
     </row>
     <row r="652" spans="9:10">
-      <c r="I652" s="18"/>
-      <c r="J652" s="18"/>
+      <c r="I652" s="8"/>
+      <c r="J652" s="8"/>
     </row>
     <row r="653" spans="9:10">
-      <c r="I653" s="18"/>
-      <c r="J653" s="18"/>
+      <c r="I653" s="8"/>
+      <c r="J653" s="8"/>
     </row>
     <row r="654" spans="9:10">
-      <c r="I654" s="18"/>
-      <c r="J654" s="18"/>
+      <c r="I654" s="8"/>
+      <c r="J654" s="8"/>
     </row>
     <row r="655" spans="9:10">
-      <c r="I655" s="18"/>
-      <c r="J655" s="18"/>
+      <c r="I655" s="8"/>
+      <c r="J655" s="8"/>
     </row>
     <row r="656" spans="9:10">
-      <c r="I656" s="18"/>
-      <c r="J656" s="18"/>
+      <c r="I656" s="8"/>
+      <c r="J656" s="8"/>
     </row>
     <row r="657" spans="9:10">
-      <c r="I657" s="18"/>
-      <c r="J657" s="18"/>
+      <c r="I657" s="8"/>
+      <c r="J657" s="8"/>
     </row>
     <row r="658" spans="9:10">
-      <c r="I658" s="18"/>
-      <c r="J658" s="18"/>
+      <c r="I658" s="8"/>
+      <c r="J658" s="8"/>
     </row>
     <row r="659" spans="9:10">
-      <c r="I659" s="18"/>
-      <c r="J659" s="18"/>
+      <c r="I659" s="8"/>
+      <c r="J659" s="8"/>
     </row>
     <row r="660" spans="9:10">
-      <c r="I660" s="18"/>
-      <c r="J660" s="18"/>
+      <c r="I660" s="8"/>
+      <c r="J660" s="8"/>
     </row>
     <row r="661" spans="9:10">
-      <c r="I661" s="18"/>
-      <c r="J661" s="18"/>
+      <c r="I661" s="8"/>
+      <c r="J661" s="8"/>
     </row>
     <row r="662" spans="9:10">
-      <c r="I662" s="18"/>
-      <c r="J662" s="18"/>
+      <c r="I662" s="8"/>
+      <c r="J662" s="8"/>
     </row>
     <row r="663" spans="9:10">
-      <c r="I663" s="18"/>
-      <c r="J663" s="18"/>
+      <c r="I663" s="8"/>
+      <c r="J663" s="8"/>
     </row>
     <row r="664" spans="9:10">
-      <c r="I664" s="18"/>
-      <c r="J664" s="18"/>
+      <c r="I664" s="8"/>
+      <c r="J664" s="8"/>
     </row>
     <row r="665" spans="9:10">
-      <c r="I665" s="18"/>
-      <c r="J665" s="18"/>
+      <c r="I665" s="8"/>
+      <c r="J665" s="8"/>
     </row>
     <row r="666" spans="9:10">
-      <c r="I666" s="18"/>
-      <c r="J666" s="18"/>
+      <c r="I666" s="8"/>
+      <c r="J666" s="8"/>
     </row>
     <row r="667" spans="9:10">
-      <c r="I667" s="18"/>
-      <c r="J667" s="18"/>
+      <c r="I667" s="8"/>
+      <c r="J667" s="8"/>
     </row>
     <row r="668" spans="9:10">
-      <c r="I668" s="18"/>
-      <c r="J668" s="18"/>
+      <c r="I668" s="8"/>
+      <c r="J668" s="8"/>
     </row>
     <row r="669" spans="9:10">
-      <c r="I669" s="18"/>
-      <c r="J669" s="18"/>
+      <c r="I669" s="8"/>
+      <c r="J669" s="8"/>
     </row>
     <row r="670" spans="9:10">
-      <c r="I670" s="18"/>
-      <c r="J670" s="18"/>
+      <c r="I670" s="8"/>
+      <c r="J670" s="8"/>
     </row>
     <row r="671" spans="9:10">
-      <c r="I671" s="18"/>
-      <c r="J671" s="18"/>
+      <c r="I671" s="8"/>
+      <c r="J671" s="8"/>
     </row>
     <row r="672" spans="9:10">
-      <c r="I672" s="18"/>
-      <c r="J672" s="18"/>
+      <c r="I672" s="8"/>
+      <c r="J672" s="8"/>
     </row>
     <row r="673" spans="9:10">
-      <c r="I673" s="18"/>
-      <c r="J673" s="18"/>
+      <c r="I673" s="8"/>
+      <c r="J673" s="8"/>
     </row>
     <row r="674" spans="9:10">
-      <c r="I674" s="18"/>
-      <c r="J674" s="18"/>
+      <c r="I674" s="8"/>
+      <c r="J674" s="8"/>
     </row>
     <row r="675" spans="9:10">
-      <c r="I675" s="18"/>
-      <c r="J675" s="18"/>
+      <c r="I675" s="8"/>
+      <c r="J675" s="8"/>
     </row>
     <row r="676" spans="9:10">
-      <c r="I676" s="18"/>
-      <c r="J676" s="18"/>
+      <c r="I676" s="8"/>
+      <c r="J676" s="8"/>
     </row>
     <row r="677" spans="9:10">
-      <c r="I677" s="18"/>
-      <c r="J677" s="18"/>
+      <c r="I677" s="8"/>
+      <c r="J677" s="8"/>
     </row>
     <row r="678" spans="9:10">
-      <c r="I678" s="18"/>
-      <c r="J678" s="18"/>
+      <c r="I678" s="8"/>
+      <c r="J678" s="8"/>
     </row>
     <row r="679" spans="9:10">
-      <c r="I679" s="18"/>
-      <c r="J679" s="18"/>
+      <c r="I679" s="8"/>
+      <c r="J679" s="8"/>
     </row>
     <row r="680" spans="9:10">
-      <c r="I680" s="18"/>
-      <c r="J680" s="18"/>
+      <c r="I680" s="8"/>
+      <c r="J680" s="8"/>
     </row>
     <row r="681" spans="9:10">
-      <c r="I681" s="18"/>
-      <c r="J681" s="18"/>
+      <c r="I681" s="8"/>
+      <c r="J681" s="8"/>
     </row>
     <row r="682" spans="9:10">
-      <c r="I682" s="18"/>
-      <c r="J682" s="18"/>
+      <c r="I682" s="8"/>
+      <c r="J682" s="8"/>
     </row>
     <row r="683" spans="9:10">
-      <c r="I683" s="18"/>
-      <c r="J683" s="18"/>
+      <c r="I683" s="8"/>
+      <c r="J683" s="8"/>
     </row>
     <row r="684" spans="9:10">
-      <c r="I684" s="18"/>
-      <c r="J684" s="18"/>
+      <c r="I684" s="8"/>
+      <c r="J684" s="8"/>
     </row>
     <row r="685" spans="9:10">
-      <c r="I685" s="18"/>
-      <c r="J685" s="18"/>
+      <c r="I685" s="8"/>
+      <c r="J685" s="8"/>
     </row>
     <row r="686" spans="9:10">
-      <c r="I686" s="18"/>
-      <c r="J686" s="18"/>
+      <c r="I686" s="8"/>
+      <c r="J686" s="8"/>
     </row>
     <row r="687" spans="9:10">
-      <c r="I687" s="18"/>
-      <c r="J687" s="18"/>
+      <c r="I687" s="8"/>
+      <c r="J687" s="8"/>
     </row>
     <row r="688" spans="9:10">
-      <c r="I688" s="18"/>
-      <c r="J688" s="18"/>
+      <c r="I688" s="8"/>
+      <c r="J688" s="8"/>
     </row>
     <row r="689" spans="9:10">
-      <c r="I689" s="18"/>
-      <c r="J689" s="18"/>
+      <c r="I689" s="8"/>
+      <c r="J689" s="8"/>
     </row>
     <row r="690" spans="9:10">
-      <c r="I690" s="18"/>
-      <c r="J690" s="18"/>
+      <c r="I690" s="8"/>
+      <c r="J690" s="8"/>
     </row>
     <row r="691" spans="9:10">
-      <c r="I691" s="18"/>
-      <c r="J691" s="18"/>
+      <c r="I691" s="8"/>
+      <c r="J691" s="8"/>
     </row>
     <row r="692" spans="9:10">
-      <c r="I692" s="18"/>
-      <c r="J692" s="18"/>
+      <c r="I692" s="8"/>
+      <c r="J692" s="8"/>
     </row>
     <row r="693" spans="9:10">
-      <c r="I693" s="18"/>
-      <c r="J693" s="18"/>
+      <c r="I693" s="8"/>
+      <c r="J693" s="8"/>
     </row>
     <row r="694" spans="9:10">
-      <c r="I694" s="18"/>
-      <c r="J694" s="18"/>
+      <c r="I694" s="8"/>
+      <c r="J694" s="8"/>
     </row>
     <row r="695" spans="9:10">
-      <c r="I695" s="18"/>
-      <c r="J695" s="18"/>
+      <c r="I695" s="8"/>
+      <c r="J695" s="8"/>
     </row>
     <row r="696" spans="9:10">
-      <c r="I696" s="18"/>
-      <c r="J696" s="18"/>
+      <c r="I696" s="8"/>
+      <c r="J696" s="8"/>
     </row>
     <row r="697" spans="9:10">
-      <c r="I697" s="18"/>
-      <c r="J697" s="18"/>
+      <c r="I697" s="8"/>
+      <c r="J697" s="8"/>
     </row>
     <row r="698" spans="9:10">
-      <c r="I698" s="18"/>
-      <c r="J698" s="18"/>
+      <c r="I698" s="8"/>
+      <c r="J698" s="8"/>
     </row>
     <row r="699" spans="9:10">
-      <c r="I699" s="18"/>
-      <c r="J699" s="18"/>
+      <c r="I699" s="8"/>
+      <c r="J699" s="8"/>
     </row>
     <row r="700" spans="9:10">
-      <c r="I700" s="18"/>
-      <c r="J700" s="18"/>
+      <c r="I700" s="8"/>
+      <c r="J700" s="8"/>
     </row>
     <row r="701" spans="9:10">
-      <c r="I701" s="18"/>
-      <c r="J701" s="18"/>
+      <c r="I701" s="8"/>
+      <c r="J701" s="8"/>
     </row>
     <row r="702" spans="9:10">
-      <c r="I702" s="18"/>
-      <c r="J702" s="18"/>
+      <c r="I702" s="8"/>
+      <c r="J702" s="8"/>
     </row>
     <row r="703" spans="9:10">
-      <c r="I703" s="18"/>
-      <c r="J703" s="18"/>
+      <c r="I703" s="8"/>
+      <c r="J703" s="8"/>
     </row>
     <row r="704" spans="9:10">
-      <c r="I704" s="18"/>
-      <c r="J704" s="18"/>
+      <c r="I704" s="8"/>
+      <c r="J704" s="8"/>
     </row>
     <row r="705" spans="9:10">
-      <c r="I705" s="18"/>
-      <c r="J705" s="18"/>
+      <c r="I705" s="8"/>
+      <c r="J705" s="8"/>
     </row>
     <row r="706" spans="9:10">
-      <c r="I706" s="18"/>
-      <c r="J706" s="18"/>
+      <c r="I706" s="8"/>
+      <c r="J706" s="8"/>
     </row>
     <row r="707" spans="9:10">
-      <c r="I707" s="18"/>
-      <c r="J707" s="18"/>
+      <c r="I707" s="8"/>
+      <c r="J707" s="8"/>
     </row>
     <row r="708" spans="9:10">
-      <c r="I708" s="18"/>
-      <c r="J708" s="18"/>
+      <c r="I708" s="8"/>
+      <c r="J708" s="8"/>
     </row>
     <row r="709" spans="9:10">
-      <c r="I709" s="18"/>
-      <c r="J709" s="18"/>
+      <c r="I709" s="8"/>
+      <c r="J709" s="8"/>
     </row>
     <row r="710" spans="9:10">
-      <c r="I710" s="18"/>
-      <c r="J710" s="18"/>
+      <c r="I710" s="8"/>
+      <c r="J710" s="8"/>
     </row>
     <row r="711" spans="9:10">
-      <c r="I711" s="18"/>
-      <c r="J711" s="18"/>
+      <c r="I711" s="8"/>
+      <c r="J711" s="8"/>
     </row>
     <row r="712" spans="9:10">
-      <c r="I712" s="18"/>
-      <c r="J712" s="18"/>
+      <c r="I712" s="8"/>
+      <c r="J712" s="8"/>
     </row>
     <row r="713" spans="9:10">
-      <c r="I713" s="18"/>
-      <c r="J713" s="18"/>
+      <c r="I713" s="8"/>
+      <c r="J713" s="8"/>
     </row>
     <row r="714" spans="9:10">
-      <c r="I714" s="18"/>
-      <c r="J714" s="18"/>
+      <c r="I714" s="8"/>
+      <c r="J714" s="8"/>
     </row>
     <row r="715" spans="9:10">
-      <c r="I715" s="18"/>
-      <c r="J715" s="18"/>
+      <c r="I715" s="8"/>
+      <c r="J715" s="8"/>
     </row>
     <row r="716" spans="9:10">
-      <c r="I716" s="18"/>
-      <c r="J716" s="18"/>
+      <c r="I716" s="8"/>
+      <c r="J716" s="8"/>
     </row>
     <row r="717" spans="9:10">
-      <c r="I717" s="18"/>
-      <c r="J717" s="18"/>
+      <c r="I717" s="8"/>
+      <c r="J717" s="8"/>
     </row>
     <row r="718" spans="9:10">
-      <c r="I718" s="18"/>
-      <c r="J718" s="18"/>
+      <c r="I718" s="8"/>
+      <c r="J718" s="8"/>
     </row>
     <row r="719" spans="9:10">
-      <c r="I719" s="18"/>
-      <c r="J719" s="18"/>
+      <c r="I719" s="8"/>
+      <c r="J719" s="8"/>
     </row>
     <row r="720" spans="9:10">
-      <c r="I720" s="18"/>
-      <c r="J720" s="18"/>
+      <c r="I720" s="8"/>
+      <c r="J720" s="8"/>
     </row>
     <row r="721" spans="9:10">
-      <c r="I721" s="18"/>
-      <c r="J721" s="18"/>
+      <c r="I721" s="8"/>
+      <c r="J721" s="8"/>
     </row>
     <row r="722" spans="9:10">
-      <c r="I722" s="18"/>
-      <c r="J722" s="18"/>
+      <c r="I722" s="8"/>
+      <c r="J722" s="8"/>
     </row>
     <row r="723" spans="9:10">
-      <c r="I723" s="18"/>
-      <c r="J723" s="18"/>
+      <c r="I723" s="8"/>
+      <c r="J723" s="8"/>
     </row>
     <row r="724" spans="9:10">
-      <c r="I724" s="18"/>
-      <c r="J724" s="18"/>
+      <c r="I724" s="8"/>
+      <c r="J724" s="8"/>
     </row>
     <row r="725" spans="9:10">
-      <c r="I725" s="18"/>
-      <c r="J725" s="18"/>
+      <c r="I725" s="8"/>
+      <c r="J725" s="8"/>
     </row>
     <row r="726" spans="9:10">
-      <c r="I726" s="18"/>
-      <c r="J726" s="18"/>
+      <c r="I726" s="8"/>
+      <c r="J726" s="8"/>
     </row>
     <row r="727" spans="9:10">
-      <c r="I727" s="18"/>
-      <c r="J727" s="18"/>
+      <c r="I727" s="8"/>
+      <c r="J727" s="8"/>
     </row>
     <row r="728" spans="9:10">
-      <c r="I728" s="18"/>
-      <c r="J728" s="18"/>
+      <c r="I728" s="8"/>
+      <c r="J728" s="8"/>
     </row>
     <row r="729" spans="9:10">
-      <c r="I729" s="18"/>
-      <c r="J729" s="18"/>
+      <c r="I729" s="8"/>
+      <c r="J729" s="8"/>
     </row>
     <row r="730" spans="9:10">
-      <c r="I730" s="18"/>
-      <c r="J730" s="18"/>
+      <c r="I730" s="8"/>
+      <c r="J730" s="8"/>
     </row>
     <row r="731" spans="9:10">
-      <c r="I731" s="18"/>
-      <c r="J731" s="18"/>
+      <c r="I731" s="8"/>
+      <c r="J731" s="8"/>
     </row>
     <row r="732" spans="9:10">
-      <c r="I732" s="18"/>
-      <c r="J732" s="18"/>
+      <c r="I732" s="8"/>
+      <c r="J732" s="8"/>
     </row>
     <row r="733" spans="9:10">
-      <c r="I733" s="18"/>
-      <c r="J733" s="18"/>
+      <c r="I733" s="8"/>
+      <c r="J733" s="8"/>
     </row>
     <row r="734" spans="9:10">
-      <c r="I734" s="18"/>
-      <c r="J734" s="18"/>
+      <c r="I734" s="8"/>
+      <c r="J734" s="8"/>
     </row>
     <row r="735" spans="9:10">
-      <c r="I735" s="18"/>
-      <c r="J735" s="18"/>
+      <c r="I735" s="8"/>
+      <c r="J735" s="8"/>
     </row>
     <row r="736" spans="9:10">
-      <c r="I736" s="18"/>
-      <c r="J736" s="18"/>
+      <c r="I736" s="8"/>
+      <c r="J736" s="8"/>
     </row>
     <row r="737" spans="9:10">
-      <c r="I737" s="18"/>
-      <c r="J737" s="18"/>
+      <c r="I737" s="8"/>
+      <c r="J737" s="8"/>
     </row>
     <row r="738" spans="9:10">
-      <c r="I738" s="18"/>
-      <c r="J738" s="18"/>
+      <c r="I738" s="8"/>
+      <c r="J738" s="8"/>
     </row>
     <row r="739" spans="9:10">
-      <c r="I739" s="18"/>
-      <c r="J739" s="18"/>
+      <c r="I739" s="8"/>
+      <c r="J739" s="8"/>
     </row>
     <row r="740" spans="9:10">
-      <c r="I740" s="18"/>
-      <c r="J740" s="18"/>
+      <c r="I740" s="8"/>
+      <c r="J740" s="8"/>
     </row>
     <row r="741" spans="9:10">
-      <c r="I741" s="18"/>
-      <c r="J741" s="18"/>
+      <c r="I741" s="8"/>
+      <c r="J741" s="8"/>
     </row>
     <row r="742" spans="9:10">
-      <c r="I742" s="18"/>
-      <c r="J742" s="18"/>
+      <c r="I742" s="8"/>
+      <c r="J742" s="8"/>
     </row>
     <row r="743" spans="9:10">
-      <c r="I743" s="18"/>
-      <c r="J743" s="18"/>
+      <c r="I743" s="8"/>
+      <c r="J743" s="8"/>
     </row>
     <row r="744" spans="9:10">
-      <c r="I744" s="18"/>
-      <c r="J744" s="18"/>
+      <c r="I744" s="8"/>
+      <c r="J744" s="8"/>
     </row>
     <row r="745" spans="9:10">
-      <c r="I745" s="18"/>
-      <c r="J745" s="18"/>
+      <c r="I745" s="8"/>
+      <c r="J745" s="8"/>
     </row>
     <row r="746" spans="9:10">
-      <c r="I746" s="18"/>
-      <c r="J746" s="18"/>
+      <c r="I746" s="8"/>
+      <c r="J746" s="8"/>
     </row>
     <row r="747" spans="9:10">
-      <c r="I747" s="18"/>
-      <c r="J747" s="18"/>
+      <c r="I747" s="8"/>
+      <c r="J747" s="8"/>
     </row>
     <row r="748" spans="9:10">
-      <c r="I748" s="18"/>
-      <c r="J748" s="18"/>
+      <c r="I748" s="8"/>
+      <c r="J748" s="8"/>
     </row>
     <row r="749" spans="9:10">
-      <c r="I749" s="18"/>
-      <c r="J749" s="18"/>
+      <c r="I749" s="8"/>
+      <c r="J749" s="8"/>
     </row>
     <row r="750" spans="9:10">
-      <c r="I750" s="18"/>
-      <c r="J750" s="18"/>
+      <c r="I750" s="8"/>
+      <c r="J750" s="8"/>
     </row>
     <row r="751" spans="9:10">
-      <c r="I751" s="18"/>
-      <c r="J751" s="18"/>
+      <c r="I751" s="8"/>
+      <c r="J751" s="8"/>
     </row>
     <row r="752" spans="9:10">
-      <c r="I752" s="18"/>
-      <c r="J752" s="18"/>
+      <c r="I752" s="8"/>
+      <c r="J752" s="8"/>
     </row>
     <row r="753" spans="9:10">
-      <c r="I753" s="18"/>
-      <c r="J753" s="18"/>
+      <c r="I753" s="8"/>
+      <c r="J753" s="8"/>
     </row>
     <row r="754" spans="9:10">
-      <c r="I754" s="18"/>
-      <c r="J754" s="18"/>
+      <c r="I754" s="8"/>
+      <c r="J754" s="8"/>
     </row>
     <row r="755" spans="9:10">
-      <c r="I755" s="18"/>
-      <c r="J755" s="18"/>
+      <c r="I755" s="8"/>
+      <c r="J755" s="8"/>
     </row>
     <row r="756" spans="9:10">
-      <c r="I756" s="18"/>
-      <c r="J756" s="18"/>
+      <c r="I756" s="8"/>
+      <c r="J756" s="8"/>
     </row>
     <row r="757" spans="9:10">
-      <c r="I757" s="18"/>
-      <c r="J757" s="18"/>
+      <c r="I757" s="8"/>
+      <c r="J757" s="8"/>
     </row>
     <row r="758" spans="9:10">
-      <c r="I758" s="18"/>
-      <c r="J758" s="18"/>
+      <c r="I758" s="8"/>
+      <c r="J758" s="8"/>
     </row>
     <row r="759" spans="9:10">
-      <c r="I759" s="18"/>
-      <c r="J759" s="18"/>
+      <c r="I759" s="8"/>
+      <c r="J759" s="8"/>
     </row>
     <row r="760" spans="9:10">
-      <c r="I760" s="18"/>
-      <c r="J760" s="18"/>
+      <c r="I760" s="8"/>
+      <c r="J760" s="8"/>
     </row>
     <row r="761" spans="9:10">
-      <c r="I761" s="18"/>
-      <c r="J761" s="18"/>
+      <c r="I761" s="8"/>
+      <c r="J761" s="8"/>
     </row>
     <row r="762" spans="9:10">
-      <c r="I762" s="18"/>
-      <c r="J762" s="18"/>
+      <c r="I762" s="8"/>
+      <c r="J762" s="8"/>
     </row>
     <row r="763" spans="9:10">
-      <c r="I763" s="18"/>
-      <c r="J763" s="18"/>
+      <c r="I763" s="8"/>
+      <c r="J763" s="8"/>
     </row>
     <row r="764" spans="9:10">
-      <c r="I764" s="18"/>
-      <c r="J764" s="18"/>
+      <c r="I764" s="8"/>
+      <c r="J764" s="8"/>
     </row>
     <row r="765" spans="9:10">
-      <c r="I765" s="18"/>
-      <c r="J765" s="18"/>
+      <c r="I765" s="8"/>
+      <c r="J765" s="8"/>
     </row>
     <row r="766" spans="9:10">
-      <c r="I766" s="18"/>
-      <c r="J766" s="18"/>
+      <c r="I766" s="8"/>
+      <c r="J766" s="8"/>
     </row>
     <row r="767" spans="9:10">
-      <c r="I767" s="18"/>
-      <c r="J767" s="18"/>
+      <c r="I767" s="8"/>
+      <c r="J767" s="8"/>
     </row>
     <row r="768" spans="9:10">
-      <c r="I768" s="18"/>
-      <c r="J768" s="18"/>
+      <c r="I768" s="8"/>
+      <c r="J768" s="8"/>
     </row>
     <row r="769" spans="9:10">
-      <c r="I769" s="18"/>
-      <c r="J769" s="18"/>
+      <c r="I769" s="8"/>
+      <c r="J769" s="8"/>
     </row>
     <row r="770" spans="9:10">
-      <c r="I770" s="18"/>
-      <c r="J770" s="18"/>
+      <c r="I770" s="8"/>
+      <c r="J770" s="8"/>
     </row>
     <row r="771" spans="9:10">
-      <c r="I771" s="18"/>
-      <c r="J771" s="18"/>
+      <c r="I771" s="8"/>
+      <c r="J771" s="8"/>
     </row>
     <row r="772" spans="9:10">
-      <c r="I772" s="18"/>
-      <c r="J772" s="18"/>
+      <c r="I772" s="8"/>
+      <c r="J772" s="8"/>
     </row>
     <row r="773" spans="9:10">
-      <c r="I773" s="18"/>
-      <c r="J773" s="18"/>
+      <c r="I773" s="8"/>
+      <c r="J773" s="8"/>
     </row>
     <row r="774" spans="9:10">
-      <c r="I774" s="18"/>
-      <c r="J774" s="18"/>
+      <c r="I774" s="8"/>
+      <c r="J774" s="8"/>
     </row>
     <row r="775" spans="9:10">
-      <c r="I775" s="18"/>
-      <c r="J775" s="18"/>
+      <c r="I775" s="8"/>
+      <c r="J775" s="8"/>
     </row>
     <row r="776" spans="9:10">
-      <c r="I776" s="18"/>
-      <c r="J776" s="18"/>
+      <c r="I776" s="8"/>
+      <c r="J776" s="8"/>
     </row>
     <row r="777" spans="9:10">
-      <c r="I777" s="18"/>
-      <c r="J777" s="18"/>
+      <c r="I777" s="8"/>
+      <c r="J777" s="8"/>
     </row>
     <row r="778" spans="9:10">
-      <c r="I778" s="18"/>
-      <c r="J778" s="18"/>
+      <c r="I778" s="8"/>
+      <c r="J778" s="8"/>
     </row>
     <row r="779" spans="9:10">
-      <c r="I779" s="18"/>
-      <c r="J779" s="18"/>
+      <c r="I779" s="8"/>
+      <c r="J779" s="8"/>
     </row>
     <row r="780" spans="9:10">
-      <c r="I780" s="18"/>
-      <c r="J780" s="18"/>
+      <c r="I780" s="8"/>
+      <c r="J780" s="8"/>
     </row>
     <row r="781" spans="9:10">
-      <c r="I781" s="18"/>
-      <c r="J781" s="18"/>
+      <c r="I781" s="8"/>
+      <c r="J781" s="8"/>
     </row>
     <row r="782" spans="9:10">
-      <c r="I782" s="18"/>
-      <c r="J782" s="18"/>
+      <c r="I782" s="8"/>
+      <c r="J782" s="8"/>
     </row>
     <row r="783" spans="9:10">
-      <c r="I783" s="18"/>
-      <c r="J783" s="18"/>
+      <c r="I783" s="8"/>
+      <c r="J783" s="8"/>
     </row>
     <row r="784" spans="9:10">
-      <c r="I784" s="18"/>
-      <c r="J784" s="18"/>
+      <c r="I784" s="8"/>
+      <c r="J784" s="8"/>
     </row>
     <row r="785" spans="9:10">
-      <c r="I785" s="18"/>
-      <c r="J785" s="18"/>
+      <c r="I785" s="8"/>
+      <c r="J785" s="8"/>
     </row>
     <row r="786" spans="9:10">
-      <c r="I786" s="18"/>
-      <c r="J786" s="18"/>
+      <c r="I786" s="8"/>
+      <c r="J786" s="8"/>
     </row>
     <row r="787" spans="9:10">
-      <c r="I787" s="18"/>
-      <c r="J787" s="18"/>
+      <c r="I787" s="8"/>
+      <c r="J787" s="8"/>
     </row>
     <row r="788" spans="9:10">
-      <c r="I788" s="18"/>
-      <c r="J788" s="18"/>
+      <c r="I788" s="8"/>
+      <c r="J788" s="8"/>
     </row>
     <row r="789" spans="9:10">
-      <c r="I789" s="18"/>
-      <c r="J789" s="18"/>
+      <c r="I789" s="8"/>
+      <c r="J789" s="8"/>
     </row>
     <row r="790" spans="9:10">
-      <c r="I790" s="18"/>
-      <c r="J790" s="18"/>
+      <c r="I790" s="8"/>
+      <c r="J790" s="8"/>
     </row>
     <row r="791" spans="9:10">
-      <c r="I791" s="18"/>
-      <c r="J791" s="18"/>
+      <c r="I791" s="8"/>
+      <c r="J791" s="8"/>
     </row>
     <row r="792" spans="9:10">
-      <c r="I792" s="18"/>
-      <c r="J792" s="18"/>
+      <c r="I792" s="8"/>
+      <c r="J792" s="8"/>
     </row>
     <row r="793" spans="9:10">
-      <c r="I793" s="18"/>
-      <c r="J793" s="18"/>
+      <c r="I793" s="8"/>
+      <c r="J793" s="8"/>
     </row>
     <row r="794" spans="9:10">
-      <c r="I794" s="18"/>
-      <c r="J794" s="18"/>
+      <c r="I794" s="8"/>
+      <c r="J794" s="8"/>
     </row>
     <row r="795" spans="9:10">
-      <c r="I795" s="18"/>
-      <c r="J795" s="18"/>
+      <c r="I795" s="8"/>
+      <c r="J795" s="8"/>
     </row>
     <row r="796" spans="9:10">
-      <c r="I796" s="18"/>
-      <c r="J796" s="18"/>
+      <c r="I796" s="8"/>
+      <c r="J796" s="8"/>
     </row>
     <row r="797" spans="9:10">
-      <c r="I797" s="18"/>
-      <c r="J797" s="18"/>
+      <c r="I797" s="8"/>
+      <c r="J797" s="8"/>
     </row>
     <row r="798" spans="9:10">
-      <c r="I798" s="18"/>
-      <c r="J798" s="18"/>
+      <c r="I798" s="8"/>
+      <c r="J798" s="8"/>
     </row>
     <row r="799" spans="9:10">
-      <c r="I799" s="18"/>
-      <c r="J799" s="18"/>
+      <c r="I799" s="8"/>
+      <c r="J799" s="8"/>
     </row>
     <row r="800" spans="9:10">
-      <c r="I800" s="18"/>
-      <c r="J800" s="18"/>
+      <c r="I800" s="8"/>
+      <c r="J800" s="8"/>
     </row>
     <row r="801" spans="9:10">
-      <c r="I801" s="18"/>
-      <c r="J801" s="18"/>
+      <c r="I801" s="8"/>
+      <c r="J801" s="8"/>
     </row>
     <row r="802" spans="9:10">
-      <c r="I802" s="18"/>
-      <c r="J802" s="18"/>
+      <c r="I802" s="8"/>
+      <c r="J802" s="8"/>
     </row>
     <row r="803" spans="9:10">
-      <c r="I803" s="18"/>
-      <c r="J803" s="18"/>
+      <c r="I803" s="8"/>
+      <c r="J803" s="8"/>
     </row>
     <row r="804" spans="9:10">
-      <c r="I804" s="18"/>
-      <c r="J804" s="18"/>
+      <c r="I804" s="8"/>
+      <c r="J804" s="8"/>
     </row>
     <row r="805" spans="9:10">
-      <c r="I805" s="18"/>
-      <c r="J805" s="18"/>
+      <c r="I805" s="8"/>
+      <c r="J805" s="8"/>
     </row>
     <row r="806" spans="9:10">
-      <c r="I806" s="18"/>
-      <c r="J806" s="18"/>
+      <c r="I806" s="8"/>
+      <c r="J806" s="8"/>
     </row>
     <row r="807" spans="9:10">
-      <c r="I807" s="18"/>
-      <c r="J807" s="18"/>
+      <c r="I807" s="8"/>
+      <c r="J807" s="8"/>
     </row>
     <row r="808" spans="9:10">
-      <c r="I808" s="18"/>
-      <c r="J808" s="18"/>
+      <c r="I808" s="8"/>
+      <c r="J808" s="8"/>
     </row>
     <row r="809" spans="9:10">
-      <c r="I809" s="18"/>
-      <c r="J809" s="18"/>
+      <c r="I809" s="8"/>
+      <c r="J809" s="8"/>
     </row>
     <row r="810" spans="9:10">
-      <c r="I810" s="18"/>
-      <c r="J810" s="18"/>
+      <c r="I810" s="8"/>
+      <c r="J810" s="8"/>
     </row>
     <row r="811" spans="9:10">
-      <c r="I811" s="18"/>
-      <c r="J811" s="18"/>
+      <c r="I811" s="8"/>
+      <c r="J811" s="8"/>
     </row>
     <row r="812" spans="9:10">
-      <c r="I812" s="18"/>
-      <c r="J812" s="18"/>
+      <c r="I812" s="8"/>
+      <c r="J812" s="8"/>
     </row>
     <row r="813" spans="9:10">
-      <c r="I813" s="18"/>
-      <c r="J813" s="18"/>
+      <c r="I813" s="8"/>
+      <c r="J813" s="8"/>
     </row>
     <row r="814" spans="9:10">
-      <c r="I814" s="18"/>
-      <c r="J814" s="18"/>
+      <c r="I814" s="8"/>
+      <c r="J814" s="8"/>
     </row>
     <row r="815" spans="9:10">
-      <c r="I815" s="18"/>
-      <c r="J815" s="18"/>
+      <c r="I815" s="8"/>
+      <c r="J815" s="8"/>
     </row>
     <row r="816" spans="9:10">
-      <c r="I816" s="18"/>
-      <c r="J816" s="18"/>
+      <c r="I816" s="8"/>
+      <c r="J816" s="8"/>
     </row>
     <row r="817" spans="9:10">
-      <c r="I817" s="18"/>
-      <c r="J817" s="18"/>
+      <c r="I817" s="8"/>
+      <c r="J817" s="8"/>
     </row>
     <row r="818" spans="9:10">
-      <c r="I818" s="18"/>
-      <c r="J818" s="18"/>
+      <c r="I818" s="8"/>
+      <c r="J818" s="8"/>
     </row>
     <row r="819" spans="9:10">
-      <c r="I819" s="18"/>
-      <c r="J819" s="18"/>
+      <c r="I819" s="8"/>
+      <c r="J819" s="8"/>
     </row>
     <row r="820" spans="9:10">
-      <c r="I820" s="18"/>
-      <c r="J820" s="18"/>
+      <c r="I820" s="8"/>
+      <c r="J820" s="8"/>
     </row>
     <row r="821" spans="9:10">
-      <c r="I821" s="18"/>
-      <c r="J821" s="18"/>
+      <c r="I821" s="8"/>
+      <c r="J821" s="8"/>
     </row>
     <row r="822" spans="9:10">
-      <c r="I822" s="18"/>
-      <c r="J822" s="18"/>
+      <c r="I822" s="8"/>
+      <c r="J822" s="8"/>
     </row>
     <row r="823" spans="9:10">
-      <c r="I823" s="18"/>
-      <c r="J823" s="18"/>
+      <c r="I823" s="8"/>
+      <c r="J823" s="8"/>
     </row>
     <row r="824" spans="9:10">
-      <c r="I824" s="18"/>
-      <c r="J824" s="18"/>
+      <c r="I824" s="8"/>
+      <c r="J824" s="8"/>
     </row>
     <row r="825" spans="9:10">
-      <c r="I825" s="18"/>
-      <c r="J825" s="18"/>
+      <c r="I825" s="8"/>
+      <c r="J825" s="8"/>
     </row>
     <row r="826" spans="9:10">
-      <c r="I826" s="18"/>
-      <c r="J826" s="18"/>
+      <c r="I826" s="8"/>
+      <c r="J826" s="8"/>
     </row>
     <row r="827" spans="9:10">
-      <c r="I827" s="18"/>
-      <c r="J827" s="18"/>
+      <c r="I827" s="8"/>
+      <c r="J827" s="8"/>
     </row>
     <row r="828" spans="9:10">
-      <c r="I828" s="18"/>
-      <c r="J828" s="18"/>
+      <c r="I828" s="8"/>
+      <c r="J828" s="8"/>
     </row>
     <row r="829" spans="9:10">
-      <c r="I829" s="18"/>
-      <c r="J829" s="18"/>
+      <c r="I829" s="8"/>
+      <c r="J829" s="8"/>
     </row>
     <row r="830" spans="9:10">
-      <c r="I830" s="18"/>
-      <c r="J830" s="18"/>
+      <c r="I830" s="8"/>
+      <c r="J830" s="8"/>
     </row>
     <row r="831" spans="9:10">
-      <c r="I831" s="18"/>
-      <c r="J831" s="18"/>
+      <c r="I831" s="8"/>
+      <c r="J831" s="8"/>
     </row>
     <row r="832" spans="9:10">
-      <c r="I832" s="18"/>
-      <c r="J832" s="18"/>
+      <c r="I832" s="8"/>
+      <c r="J832" s="8"/>
     </row>
     <row r="833" spans="9:10">
-      <c r="I833" s="18"/>
-      <c r="J833" s="18"/>
+      <c r="I833" s="8"/>
+      <c r="J833" s="8"/>
     </row>
     <row r="834" spans="9:10">
-      <c r="I834" s="18"/>
-      <c r="J834" s="18"/>
+      <c r="I834" s="8"/>
+      <c r="J834" s="8"/>
     </row>
     <row r="835" spans="9:10">
-      <c r="I835" s="18"/>
-      <c r="J835" s="18"/>
+      <c r="I835" s="8"/>
+      <c r="J835" s="8"/>
     </row>
     <row r="836" spans="9:10">
-      <c r="I836" s="18"/>
-      <c r="J836" s="18"/>
+      <c r="I836" s="8"/>
+      <c r="J836" s="8"/>
     </row>
     <row r="837" spans="9:10">
-      <c r="I837" s="18"/>
-      <c r="J837" s="18"/>
+      <c r="I837" s="8"/>
+      <c r="J837" s="8"/>
     </row>
     <row r="838" spans="9:10">
-      <c r="I838" s="18"/>
-      <c r="J838" s="18"/>
+      <c r="I838" s="8"/>
+      <c r="J838" s="8"/>
     </row>
     <row r="839" spans="9:10">
-      <c r="I839" s="18"/>
-      <c r="J839" s="18"/>
+      <c r="I839" s="8"/>
+      <c r="J839" s="8"/>
     </row>
     <row r="840" spans="9:10">
-      <c r="I840" s="18"/>
-      <c r="J840" s="18"/>
+      <c r="I840" s="8"/>
+      <c r="J840" s="8"/>
     </row>
     <row r="841" spans="9:10">
-      <c r="I841" s="18"/>
-      <c r="J841" s="18"/>
+      <c r="I841" s="8"/>
+      <c r="J841" s="8"/>
     </row>
     <row r="842" spans="9:10">
-      <c r="I842" s="18"/>
-      <c r="J842" s="18"/>
+      <c r="I842" s="8"/>
+      <c r="J842" s="8"/>
     </row>
     <row r="843" spans="9:10">
-      <c r="I843" s="18"/>
-      <c r="J843" s="18"/>
+      <c r="I843" s="8"/>
+      <c r="J843" s="8"/>
     </row>
     <row r="844" spans="9:10">
-      <c r="I844" s="18"/>
-      <c r="J844" s="18"/>
+      <c r="I844" s="8"/>
+      <c r="J844" s="8"/>
     </row>
     <row r="845" spans="9:10">
-      <c r="I845" s="18"/>
-      <c r="J845" s="18"/>
+      <c r="I845" s="8"/>
+      <c r="J845" s="8"/>
     </row>
     <row r="846" spans="9:10">
-      <c r="I846" s="18"/>
-      <c r="J846" s="18"/>
+      <c r="I846" s="8"/>
+      <c r="J846" s="8"/>
     </row>
     <row r="847" spans="9:10">
-      <c r="I847" s="18"/>
-      <c r="J847" s="18"/>
+      <c r="I847" s="8"/>
+      <c r="J847" s="8"/>
     </row>
     <row r="848" spans="9:10">
-      <c r="I848" s="18"/>
-      <c r="J848" s="18"/>
+      <c r="I848" s="8"/>
+      <c r="J848" s="8"/>
     </row>
     <row r="849" spans="9:10">
-      <c r="I849" s="18"/>
-      <c r="J849" s="18"/>
+      <c r="I849" s="8"/>
+      <c r="J849" s="8"/>
     </row>
     <row r="850" spans="9:10">
-      <c r="I850" s="18"/>
-      <c r="J850" s="18"/>
+      <c r="I850" s="8"/>
+      <c r="J850" s="8"/>
     </row>
     <row r="851" spans="9:10">
-      <c r="I851" s="18"/>
-      <c r="J851" s="18"/>
+      <c r="I851" s="8"/>
+      <c r="J851" s="8"/>
     </row>
     <row r="852" spans="9:10">
-      <c r="I852" s="18"/>
-      <c r="J852" s="18"/>
+      <c r="I852" s="8"/>
+      <c r="J852" s="8"/>
     </row>
     <row r="853" spans="9:10">
-      <c r="I853" s="18"/>
-      <c r="J853" s="18"/>
+      <c r="I853" s="8"/>
+      <c r="J853" s="8"/>
     </row>
     <row r="854" spans="9:10">
-      <c r="I854" s="18"/>
-      <c r="J854" s="18"/>
+      <c r="I854" s="8"/>
+      <c r="J854" s="8"/>
     </row>
     <row r="855" spans="9:10">
-      <c r="I855" s="18"/>
-      <c r="J855" s="18"/>
+      <c r="I855" s="8"/>
+      <c r="J855" s="8"/>
     </row>
     <row r="856" spans="9:10">
-      <c r="I856" s="18"/>
-      <c r="J856" s="18"/>
+      <c r="I856" s="8"/>
+      <c r="J856" s="8"/>
     </row>
     <row r="857" spans="9:10">
-      <c r="I857" s="18"/>
-      <c r="J857" s="18"/>
+      <c r="I857" s="8"/>
+      <c r="J857" s="8"/>
     </row>
     <row r="858" spans="9:10">
-      <c r="I858" s="18"/>
-      <c r="J858" s="18"/>
+      <c r="I858" s="8"/>
+      <c r="J858" s="8"/>
     </row>
     <row r="859" spans="9:10">
-      <c r="I859" s="18"/>
-      <c r="J859" s="18"/>
+      <c r="I859" s="8"/>
+      <c r="J859" s="8"/>
     </row>
     <row r="860" spans="9:10">
-      <c r="I860" s="18"/>
-      <c r="J860" s="18"/>
+      <c r="I860" s="8"/>
+      <c r="J860" s="8"/>
     </row>
     <row r="861" spans="9:10">
-      <c r="I861" s="18"/>
-      <c r="J861" s="18"/>
+      <c r="I861" s="8"/>
+      <c r="J861" s="8"/>
     </row>
     <row r="862" spans="9:10">
-      <c r="I862" s="18"/>
-      <c r="J862" s="18"/>
+      <c r="I862" s="8"/>
+      <c r="J862" s="8"/>
     </row>
     <row r="863" spans="9:10">
-      <c r="I863" s="18"/>
-      <c r="J863" s="18"/>
+      <c r="I863" s="8"/>
+      <c r="J863" s="8"/>
     </row>
     <row r="864" spans="9:10">
-      <c r="I864" s="18"/>
-      <c r="J864" s="18"/>
+      <c r="I864" s="8"/>
+      <c r="J864" s="8"/>
     </row>
     <row r="865" spans="9:10">
-      <c r="I865" s="18"/>
-      <c r="J865" s="18"/>
+      <c r="I865" s="8"/>
+      <c r="J865" s="8"/>
     </row>
     <row r="866" spans="9:10">
-      <c r="I866" s="18"/>
-      <c r="J866" s="18"/>
+      <c r="I866" s="8"/>
+      <c r="J866" s="8"/>
     </row>
     <row r="867" spans="9:10">
-      <c r="I867" s="18"/>
-      <c r="J867" s="18"/>
+      <c r="I867" s="8"/>
+      <c r="J867" s="8"/>
     </row>
     <row r="868" spans="9:10">
-      <c r="I868" s="18"/>
-      <c r="J868" s="18"/>
+      <c r="I868" s="8"/>
+      <c r="J868" s="8"/>
     </row>
     <row r="869" spans="9:10">
-      <c r="I869" s="18"/>
-      <c r="J869" s="18"/>
+      <c r="I869" s="8"/>
+      <c r="J869" s="8"/>
     </row>
     <row r="870" spans="9:10">
-      <c r="I870" s="18"/>
-      <c r="J870" s="18"/>
+      <c r="I870" s="8"/>
+      <c r="J870" s="8"/>
     </row>
     <row r="871" spans="9:10">
-      <c r="I871" s="18"/>
-      <c r="J871" s="18"/>
+      <c r="I871" s="8"/>
+      <c r="J871" s="8"/>
     </row>
     <row r="872" spans="9:10">
-      <c r="I872" s="18"/>
-      <c r="J872" s="18"/>
+      <c r="I872" s="8"/>
+      <c r="J872" s="8"/>
     </row>
     <row r="873" spans="9:10">
-      <c r="I873" s="18"/>
-      <c r="J873" s="18"/>
+      <c r="I873" s="8"/>
+      <c r="J873" s="8"/>
     </row>
     <row r="874" spans="9:10">
-      <c r="I874" s="18"/>
-      <c r="J874" s="18"/>
+      <c r="I874" s="8"/>
+      <c r="J874" s="8"/>
     </row>
     <row r="875" spans="9:10">
-      <c r="I875" s="18"/>
-      <c r="J875" s="18"/>
+      <c r="I875" s="8"/>
+      <c r="J875" s="8"/>
     </row>
     <row r="876" spans="9:10">
-      <c r="I876" s="18"/>
-      <c r="J876" s="18"/>
+      <c r="I876" s="8"/>
+      <c r="J876" s="8"/>
     </row>
     <row r="877" spans="9:10">
-      <c r="I877" s="18"/>
-      <c r="J877" s="18"/>
+      <c r="I877" s="8"/>
+      <c r="J877" s="8"/>
     </row>
     <row r="878" spans="9:10">
-      <c r="I878" s="18"/>
-      <c r="J878" s="18"/>
+      <c r="I878" s="8"/>
+      <c r="J878" s="8"/>
     </row>
     <row r="879" spans="9:10">
-      <c r="I879" s="18"/>
-      <c r="J879" s="18"/>
+      <c r="I879" s="8"/>
+      <c r="J879" s="8"/>
     </row>
     <row r="880" spans="9:10">
-      <c r="I880" s="18"/>
-      <c r="J880" s="18"/>
+      <c r="I880" s="8"/>
+      <c r="J880" s="8"/>
     </row>
     <row r="881" spans="9:10">
-      <c r="I881" s="18"/>
-      <c r="J881" s="18"/>
+      <c r="I881" s="8"/>
+      <c r="J881" s="8"/>
     </row>
     <row r="882" spans="9:10">
-      <c r="I882" s="18"/>
-      <c r="J882" s="18"/>
+      <c r="I882" s="8"/>
+      <c r="J882" s="8"/>
     </row>
     <row r="883" spans="9:10">
-      <c r="I883" s="18"/>
-      <c r="J883" s="18"/>
+      <c r="I883" s="8"/>
+      <c r="J883" s="8"/>
     </row>
     <row r="884" spans="9:10">
-      <c r="I884" s="18"/>
-      <c r="J884" s="18"/>
+      <c r="I884" s="8"/>
+      <c r="J884" s="8"/>
     </row>
     <row r="885" spans="9:10">
-      <c r="I885" s="18"/>
-      <c r="J885" s="18"/>
+      <c r="I885" s="8"/>
+      <c r="J885" s="8"/>
     </row>
     <row r="886" spans="9:10">
-      <c r="I886" s="18"/>
-      <c r="J886" s="18"/>
+      <c r="I886" s="8"/>
+      <c r="J886" s="8"/>
     </row>
     <row r="887" spans="9:10">
-      <c r="I887" s="18"/>
-      <c r="J887" s="18"/>
+      <c r="I887" s="8"/>
+      <c r="J887" s="8"/>
     </row>
     <row r="888" spans="9:10">
-      <c r="I888" s="18"/>
-      <c r="J888" s="18"/>
+      <c r="I888" s="8"/>
+      <c r="J888" s="8"/>
     </row>
     <row r="889" spans="9:10">
-      <c r="I889" s="18"/>
-      <c r="J889" s="18"/>
+      <c r="I889" s="8"/>
+      <c r="J889" s="8"/>
     </row>
     <row r="890" spans="9:10">
-      <c r="I890" s="18"/>
-      <c r="J890" s="18"/>
+      <c r="I890" s="8"/>
+      <c r="J890" s="8"/>
     </row>
     <row r="891" spans="9:10">
-      <c r="I891" s="18"/>
-      <c r="J891" s="18"/>
+      <c r="I891" s="8"/>
+      <c r="J891" s="8"/>
     </row>
     <row r="892" spans="9:10">
-      <c r="I892" s="18"/>
-      <c r="J892" s="18"/>
+      <c r="I892" s="8"/>
+      <c r="J892" s="8"/>
     </row>
     <row r="893" spans="9:10">
-      <c r="I893" s="18"/>
-      <c r="J893" s="18"/>
+      <c r="I893" s="8"/>
+      <c r="J893" s="8"/>
     </row>
     <row r="894" spans="9:10">
-      <c r="I894" s="18"/>
-      <c r="J894" s="18"/>
+      <c r="I894" s="8"/>
+      <c r="J894" s="8"/>
     </row>
     <row r="895" spans="9:10">
-      <c r="I895" s="18"/>
-      <c r="J895" s="18"/>
+      <c r="I895" s="8"/>
+      <c r="J895" s="8"/>
     </row>
     <row r="896" spans="9:10">
-      <c r="I896" s="18"/>
-      <c r="J896" s="18"/>
+      <c r="I896" s="8"/>
+      <c r="J896" s="8"/>
     </row>
     <row r="897" spans="9:10">
-      <c r="I897" s="18"/>
-      <c r="J897" s="18"/>
+      <c r="I897" s="8"/>
+      <c r="J897" s="8"/>
     </row>
     <row r="898" spans="9:10">
-      <c r="I898" s="18"/>
-      <c r="J898" s="18"/>
+      <c r="I898" s="8"/>
+      <c r="J898" s="8"/>
     </row>
     <row r="899" spans="9:10">
-      <c r="I899" s="18"/>
-      <c r="J899" s="18"/>
+      <c r="I899" s="8"/>
+      <c r="J899" s="8"/>
     </row>
     <row r="900" spans="9:10">
-      <c r="I900" s="18"/>
-      <c r="J900" s="18"/>
+      <c r="I900" s="8"/>
+      <c r="J900" s="8"/>
     </row>
     <row r="901" spans="9:10">
-      <c r="I901" s="18"/>
-      <c r="J901" s="18"/>
+      <c r="I901" s="8"/>
+      <c r="J901" s="8"/>
     </row>
     <row r="902" spans="9:10">
-      <c r="I902" s="18"/>
-      <c r="J902" s="18"/>
+      <c r="I902" s="8"/>
+      <c r="J902" s="8"/>
     </row>
     <row r="903" spans="9:10">
-      <c r="I903" s="18"/>
-      <c r="J903" s="18"/>
+      <c r="I903" s="8"/>
+      <c r="J903" s="8"/>
     </row>
     <row r="904" spans="9:10">
-      <c r="I904" s="18"/>
-      <c r="J904" s="18"/>
+      <c r="I904" s="8"/>
+      <c r="J904" s="8"/>
     </row>
     <row r="905" spans="9:10">
-      <c r="I905" s="18"/>
-      <c r="J905" s="18"/>
+      <c r="I905" s="8"/>
+      <c r="J905" s="8"/>
     </row>
     <row r="906" spans="9:10">
-      <c r="I906" s="18"/>
-      <c r="J906" s="18"/>
+      <c r="I906" s="8"/>
+      <c r="J906" s="8"/>
     </row>
     <row r="907" spans="9:10">
-      <c r="I907" s="18"/>
-      <c r="J907" s="18"/>
+      <c r="I907" s="8"/>
+      <c r="J907" s="8"/>
     </row>
     <row r="908" spans="9:10">
-      <c r="I908" s="18"/>
-      <c r="J908" s="18"/>
+      <c r="I908" s="8"/>
+      <c r="J908" s="8"/>
     </row>
     <row r="909" spans="9:10">
-      <c r="I909" s="18"/>
-      <c r="J909" s="18"/>
+      <c r="I909" s="8"/>
+      <c r="J909" s="8"/>
     </row>
     <row r="910" spans="9:10">
-      <c r="I910" s="18"/>
-      <c r="J910" s="18"/>
+      <c r="I910" s="8"/>
+      <c r="J910" s="8"/>
     </row>
     <row r="911" spans="9:10">
-      <c r="I911" s="18"/>
-      <c r="J911" s="18"/>
+      <c r="I911" s="8"/>
+      <c r="J911" s="8"/>
     </row>
     <row r="912" spans="9:10">
-      <c r="I912" s="18"/>
-      <c r="J912" s="18"/>
+      <c r="I912" s="8"/>
+      <c r="J912" s="8"/>
     </row>
     <row r="913" spans="9:10">
-      <c r="I913" s="18"/>
-      <c r="J913" s="18"/>
+      <c r="I913" s="8"/>
+      <c r="J913" s="8"/>
     </row>
     <row r="914" spans="9:10">
-      <c r="I914" s="18"/>
-      <c r="J914" s="18"/>
+      <c r="I914" s="8"/>
+      <c r="J914" s="8"/>
     </row>
     <row r="915" spans="9:10">
-      <c r="I915" s="18"/>
-      <c r="J915" s="18"/>
+      <c r="I915" s="8"/>
+      <c r="J915" s="8"/>
     </row>
     <row r="916" spans="9:10">
-      <c r="I916" s="18"/>
-      <c r="J916" s="18"/>
+      <c r="I916" s="8"/>
+      <c r="J916" s="8"/>
     </row>
     <row r="917" spans="9:10">
-      <c r="I917" s="18"/>
-      <c r="J917" s="18"/>
+      <c r="I917" s="8"/>
+      <c r="J917" s="8"/>
     </row>
     <row r="918" spans="9:10">
-      <c r="I918" s="18"/>
-      <c r="J918" s="18"/>
+      <c r="I918" s="8"/>
+      <c r="J918" s="8"/>
     </row>
     <row r="919" spans="9:10">
-      <c r="I919" s="18"/>
-      <c r="J919" s="18"/>
+      <c r="I919" s="8"/>
+      <c r="J919" s="8"/>
     </row>
     <row r="920" spans="9:10">
-      <c r="I920" s="18"/>
-      <c r="J920" s="18"/>
+      <c r="I920" s="8"/>
+      <c r="J920" s="8"/>
     </row>
     <row r="921" spans="9:10">
-      <c r="I921" s="18"/>
-      <c r="J921" s="18"/>
+      <c r="I921" s="8"/>
+      <c r="J921" s="8"/>
     </row>
     <row r="922" spans="9:10">
-      <c r="I922" s="18"/>
-      <c r="J922" s="18"/>
+      <c r="I922" s="8"/>
+      <c r="J922" s="8"/>
     </row>
     <row r="923" spans="9:10">
-      <c r="I923" s="18"/>
-      <c r="J923" s="18"/>
+      <c r="I923" s="8"/>
+      <c r="J923" s="8"/>
     </row>
     <row r="924" spans="9:10">
-      <c r="I924" s="18"/>
-      <c r="J924" s="18"/>
+      <c r="I924" s="8"/>
+      <c r="J924" s="8"/>
     </row>
     <row r="925" spans="9:10">
-      <c r="I925" s="18"/>
-      <c r="J925" s="18"/>
+      <c r="I925" s="8"/>
+      <c r="J925" s="8"/>
     </row>
     <row r="926" spans="9:10">
-      <c r="I926" s="18"/>
-      <c r="J926" s="18"/>
+      <c r="I926" s="8"/>
+      <c r="J926" s="8"/>
     </row>
     <row r="927" spans="9:10">
-      <c r="I927" s="18"/>
-      <c r="J927" s="18"/>
+      <c r="I927" s="8"/>
+      <c r="J927" s="8"/>
     </row>
     <row r="928" spans="9:10">
-      <c r="I928" s="18"/>
-      <c r="J928" s="18"/>
+      <c r="I928" s="8"/>
+      <c r="J928" s="8"/>
     </row>
     <row r="929" spans="9:10">
-      <c r="I929" s="18"/>
-      <c r="J929" s="18"/>
+      <c r="I929" s="8"/>
+      <c r="J929" s="8"/>
     </row>
     <row r="930" spans="9:10">
-      <c r="I930" s="18"/>
-      <c r="J930" s="18"/>
+      <c r="I930" s="8"/>
+      <c r="J930" s="8"/>
     </row>
     <row r="931" spans="9:10">
-      <c r="I931" s="18"/>
-      <c r="J931" s="18"/>
+      <c r="I931" s="8"/>
+      <c r="J931" s="8"/>
     </row>
     <row r="932" spans="9:10">
-      <c r="I932" s="18"/>
-      <c r="J932" s="18"/>
+      <c r="I932" s="8"/>
+      <c r="J932" s="8"/>
     </row>
     <row r="933" spans="9:10">
-      <c r="I933" s="18"/>
-      <c r="J933" s="18"/>
+      <c r="I933" s="8"/>
+      <c r="J933" s="8"/>
     </row>
     <row r="934" spans="9:10">
-      <c r="I934" s="18"/>
-      <c r="J934" s="18"/>
+      <c r="I934" s="8"/>
+      <c r="J934" s="8"/>
     </row>
     <row r="935" spans="9:10">
-      <c r="I935" s="18"/>
-      <c r="J935" s="18"/>
+      <c r="I935" s="8"/>
+      <c r="J935" s="8"/>
     </row>
     <row r="936" spans="9:10">
-      <c r="I936" s="18"/>
-      <c r="J936" s="18"/>
+      <c r="I936" s="8"/>
+      <c r="J936" s="8"/>
     </row>
     <row r="937" spans="9:10">
-      <c r="I937" s="18"/>
-      <c r="J937" s="18"/>
+      <c r="I937" s="8"/>
+      <c r="J937" s="8"/>
     </row>
     <row r="938" spans="9:10">
-      <c r="I938" s="18"/>
-      <c r="J938" s="18"/>
+      <c r="I938" s="8"/>
+      <c r="J938" s="8"/>
     </row>
     <row r="939" spans="9:10">
-      <c r="I939" s="18"/>
-      <c r="J939" s="18"/>
+      <c r="I939" s="8"/>
+      <c r="J939" s="8"/>
     </row>
     <row r="940" spans="9:10">
-      <c r="I940" s="18"/>
-      <c r="J940" s="18"/>
+      <c r="I940" s="8"/>
+      <c r="J940" s="8"/>
     </row>
     <row r="941" spans="9:10">
-      <c r="I941" s="18"/>
-      <c r="J941" s="18"/>
+      <c r="I941" s="8"/>
+      <c r="J941" s="8"/>
     </row>
     <row r="942" spans="9:10">
-      <c r="I942" s="18"/>
-      <c r="J942" s="18"/>
+      <c r="I942" s="8"/>
+      <c r="J942" s="8"/>
     </row>
     <row r="943" spans="9:10">
-      <c r="I943" s="18"/>
-      <c r="J943" s="18"/>
+      <c r="I943" s="8"/>
+      <c r="J943" s="8"/>
     </row>
     <row r="944" spans="9:10">
-      <c r="I944" s="18"/>
-      <c r="J944" s="18"/>
+      <c r="I944" s="8"/>
+      <c r="J944" s="8"/>
     </row>
     <row r="945" spans="9:10">
-      <c r="I945" s="18"/>
-      <c r="J945" s="18"/>
+      <c r="I945" s="8"/>
+      <c r="J945" s="8"/>
     </row>
     <row r="946" spans="9:10">
-      <c r="I946" s="18"/>
-      <c r="J946" s="18"/>
+      <c r="I946" s="8"/>
+      <c r="J946" s="8"/>
     </row>
     <row r="947" spans="9:10">
-      <c r="I947" s="18"/>
-      <c r="J947" s="18"/>
+      <c r="I947" s="8"/>
+      <c r="J947" s="8"/>
     </row>
     <row r="948" spans="9:10">
-      <c r="I948" s="18"/>
-      <c r="J948" s="18"/>
+      <c r="I948" s="8"/>
+      <c r="J948" s="8"/>
     </row>
     <row r="949" spans="9:10">
-      <c r="I949" s="18"/>
-      <c r="J949" s="18"/>
+      <c r="I949" s="8"/>
+      <c r="J949" s="8"/>
     </row>
     <row r="950" spans="9:10">
-      <c r="I950" s="18"/>
-      <c r="J950" s="18"/>
+      <c r="I950" s="8"/>
+      <c r="J950" s="8"/>
     </row>
     <row r="951" spans="9:10">
-      <c r="I951" s="18"/>
-      <c r="J951" s="18"/>
+      <c r="I951" s="8"/>
+      <c r="J951" s="8"/>
     </row>
     <row r="952" spans="9:10">
-      <c r="I952" s="18"/>
-      <c r="J952" s="18"/>
+      <c r="I952" s="8"/>
+      <c r="J952" s="8"/>
     </row>
     <row r="953" spans="9:10">
-      <c r="I953" s="18"/>
-      <c r="J953" s="18"/>
+      <c r="I953" s="8"/>
+      <c r="J953" s="8"/>
     </row>
     <row r="954" spans="9:10">
-      <c r="I954" s="18"/>
-      <c r="J954" s="18"/>
+      <c r="I954" s="8"/>
+      <c r="J954" s="8"/>
     </row>
     <row r="955" spans="9:10">
-      <c r="I955" s="18"/>
-      <c r="J955" s="18"/>
+      <c r="I955" s="8"/>
+      <c r="J955" s="8"/>
     </row>
     <row r="956" spans="9:10">
-      <c r="I956" s="18"/>
-      <c r="J956" s="18"/>
+      <c r="I956" s="8"/>
+      <c r="J956" s="8"/>
     </row>
     <row r="957" spans="9:10">
-      <c r="I957" s="18"/>
-      <c r="J957" s="18"/>
+      <c r="I957" s="8"/>
+      <c r="J957" s="8"/>
     </row>
     <row r="958" spans="9:10">
-      <c r="I958" s="18"/>
-      <c r="J958" s="18"/>
+      <c r="I958" s="8"/>
+      <c r="J958" s="8"/>
     </row>
     <row r="959" spans="9:10">
-      <c r="I959" s="18"/>
-      <c r="J959" s="18"/>
+      <c r="I959" s="8"/>
+      <c r="J959" s="8"/>
     </row>
     <row r="960" spans="9:10">
-      <c r="I960" s="18"/>
-      <c r="J960" s="18"/>
+      <c r="I960" s="8"/>
+      <c r="J960" s="8"/>
     </row>
     <row r="961" spans="9:10">
-      <c r="I961" s="18"/>
-      <c r="J961" s="18"/>
+      <c r="I961" s="8"/>
+      <c r="J961" s="8"/>
     </row>
     <row r="962" spans="9:10">
-      <c r="I962" s="18"/>
-      <c r="J962" s="18"/>
+      <c r="I962" s="8"/>
+      <c r="J962" s="8"/>
     </row>
     <row r="963" spans="9:10">
-      <c r="I963" s="18"/>
-      <c r="J963" s="18"/>
+      <c r="I963" s="8"/>
+      <c r="J963" s="8"/>
     </row>
     <row r="964" spans="9:10">
-      <c r="I964" s="18"/>
-      <c r="J964" s="18"/>
+      <c r="I964" s="8"/>
+      <c r="J964" s="8"/>
     </row>
     <row r="965" spans="9:10">
-      <c r="I965" s="18"/>
-      <c r="J965" s="18"/>
+      <c r="I965" s="8"/>
+      <c r="J965" s="8"/>
     </row>
     <row r="966" spans="9:10">
-      <c r="I966" s="18"/>
-      <c r="J966" s="18"/>
+      <c r="I966" s="8"/>
+      <c r="J966" s="8"/>
     </row>
     <row r="967" spans="9:10">
-      <c r="I967" s="18"/>
-      <c r="J967" s="18"/>
+      <c r="I967" s="8"/>
+      <c r="J967" s="8"/>
     </row>
     <row r="968" spans="9:10">
-      <c r="I968" s="18"/>
-      <c r="J968" s="18"/>
+      <c r="I968" s="8"/>
+      <c r="J968" s="8"/>
     </row>
     <row r="969" spans="9:10">
-      <c r="I969" s="18"/>
-      <c r="J969" s="18"/>
+      <c r="I969" s="8"/>
+      <c r="J969" s="8"/>
     </row>
     <row r="970" spans="9:10">
-      <c r="I970" s="18"/>
-      <c r="J970" s="18"/>
+      <c r="I970" s="8"/>
+      <c r="J970" s="8"/>
     </row>
     <row r="971" spans="9:10">
-      <c r="I971" s="18"/>
-      <c r="J971" s="18"/>
+      <c r="I971" s="8"/>
+      <c r="J971" s="8"/>
     </row>
     <row r="972" spans="9:10">
-      <c r="I972" s="18"/>
-      <c r="J972" s="18"/>
+      <c r="I972" s="8"/>
+      <c r="J972" s="8"/>
     </row>
     <row r="973" spans="9:10">
-      <c r="I973" s="18"/>
-      <c r="J973" s="18"/>
+      <c r="I973" s="8"/>
+      <c r="J973" s="8"/>
     </row>
     <row r="974" spans="9:10">
-      <c r="I974" s="18"/>
-      <c r="J974" s="18"/>
+      <c r="I974" s="8"/>
+      <c r="J974" s="8"/>
     </row>
     <row r="975" spans="9:10">
-      <c r="I975" s="18"/>
-      <c r="J975" s="18"/>
+      <c r="I975" s="8"/>
+      <c r="J975" s="8"/>
     </row>
     <row r="976" spans="9:10">
-      <c r="I976" s="18"/>
-      <c r="J976" s="18"/>
+      <c r="I976" s="8"/>
+      <c r="J976" s="8"/>
     </row>
     <row r="977" spans="9:10">
-      <c r="I977" s="18"/>
-      <c r="J977" s="18"/>
+      <c r="I977" s="8"/>
+      <c r="J977" s="8"/>
     </row>
     <row r="978" spans="9:10">
-      <c r="I978" s="18"/>
-      <c r="J978" s="18"/>
+      <c r="I978" s="8"/>
+      <c r="J978" s="8"/>
     </row>
     <row r="979" spans="9:10">
-      <c r="I979" s="18"/>
-      <c r="J979" s="18"/>
+      <c r="I979" s="8"/>
+      <c r="J979" s="8"/>
     </row>
     <row r="980" spans="9:10">
-      <c r="I980" s="18"/>
-      <c r="J980" s="18"/>
+      <c r="I980" s="8"/>
+      <c r="J980" s="8"/>
     </row>
     <row r="981" spans="9:10">
-      <c r="I981" s="18"/>
-      <c r="J981" s="18"/>
+      <c r="I981" s="8"/>
+      <c r="J981" s="8"/>
     </row>
     <row r="982" spans="9:10">
-      <c r="I982" s="18"/>
-      <c r="J982" s="18"/>
+      <c r="I982" s="8"/>
+      <c r="J982" s="8"/>
     </row>
     <row r="983" spans="9:10">
-      <c r="I983" s="18"/>
-      <c r="J983" s="18"/>
+      <c r="I983" s="8"/>
+      <c r="J983" s="8"/>
     </row>
     <row r="984" spans="9:10">
-      <c r="I984" s="18"/>
-      <c r="J984" s="18"/>
+      <c r="I984" s="8"/>
+      <c r="J984" s="8"/>
     </row>
     <row r="985" spans="9:10">
-      <c r="I985" s="18"/>
-      <c r="J985" s="18"/>
+      <c r="I985" s="8"/>
+      <c r="J985" s="8"/>
     </row>
     <row r="986" spans="9:10">
-      <c r="I986" s="18"/>
-      <c r="J986" s="18"/>
+      <c r="I986" s="8"/>
+      <c r="J986" s="8"/>
     </row>
     <row r="987" spans="9:10">
-      <c r="I987" s="18"/>
-      <c r="J987" s="18"/>
+      <c r="I987" s="8"/>
+      <c r="J987" s="8"/>
     </row>
     <row r="988" spans="9:10">
-      <c r="I988" s="18"/>
-      <c r="J988" s="18"/>
+      <c r="I988" s="8"/>
+      <c r="J988" s="8"/>
     </row>
     <row r="989" spans="9:10">
-      <c r="I989" s="18"/>
-      <c r="J989" s="18"/>
+      <c r="I989" s="8"/>
+      <c r="J989" s="8"/>
     </row>
     <row r="990" spans="9:10">
-      <c r="I990" s="18"/>
-      <c r="J990" s="18"/>
+      <c r="I990" s="8"/>
+      <c r="J990" s="8"/>
     </row>
     <row r="991" spans="9:10">
-      <c r="I991" s="18"/>
-      <c r="J991" s="18"/>
+      <c r="I991" s="8"/>
+      <c r="J991" s="8"/>
     </row>
     <row r="992" spans="9:10">
-      <c r="I992" s="18"/>
-      <c r="J992" s="18"/>
+      <c r="I992" s="8"/>
+      <c r="J992" s="8"/>
     </row>
     <row r="993" spans="9:10">
-      <c r="I993" s="18"/>
-      <c r="J993" s="18"/>
+      <c r="I993" s="8"/>
+      <c r="J993" s="8"/>
     </row>
     <row r="994" spans="9:10">
-      <c r="I994" s="18"/>
-      <c r="J994" s="18"/>
+      <c r="I994" s="8"/>
+      <c r="J994" s="8"/>
     </row>
     <row r="995" spans="9:10">
-      <c r="I995" s="18"/>
-      <c r="J995" s="18"/>
+      <c r="I995" s="8"/>
+      <c r="J995" s="8"/>
     </row>
     <row r="996" spans="9:10">
-      <c r="I996" s="18"/>
-      <c r="J996" s="18"/>
+      <c r="I996" s="8"/>
+      <c r="J996" s="8"/>
     </row>
     <row r="997" spans="9:10">
-      <c r="I997" s="18"/>
-      <c r="J997" s="18"/>
+      <c r="I997" s="8"/>
+      <c r="J997" s="8"/>
     </row>
     <row r="998" spans="9:10">
-      <c r="I998" s="18"/>
-      <c r="J998" s="18"/>
+      <c r="I998" s="8"/>
+      <c r="J998" s="8"/>
     </row>
     <row r="999" spans="9:10">
-      <c r="I999" s="18"/>
-      <c r="J999" s="18"/>
+      <c r="I999" s="8"/>
+      <c r="J999" s="8"/>
     </row>
     <row r="1000" spans="9:10">
-      <c r="I1000" s="18"/>
-      <c r="J1000" s="18"/>
+      <c r="I1000" s="8"/>
+      <c r="J1000" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M1" xr:uid="{724E297C-E4EA-4AA3-B0EF-D35314885408}"/>
@@ -7472,17 +7606,17 @@
     <col min="4" max="4" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="5" customFormat="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:4" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>65</v>
       </c>
     </row>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEB13C5-6C27-4EAE-BF18-4AE00ED47291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209BC7C-0638-4D8C-82D3-DAFFD3C6DCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -334,7 +334,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
   <si>
     <t>id</t>
   </si>
@@ -1069,6 +1069,9 @@
   </si>
   <si>
     <t>https://m.media-amazon.com/images/I/51h95iRUqrL._SL1080_.jpg</t>
+  </si>
+  <si>
+    <t>https://static.srpcdigital.com/styles/1037xauto/public/2024-03/563741.jpeg</t>
   </si>
 </sst>
 </file>
@@ -3026,8 +3029,8 @@
       <c r="F2" s="4">
         <v>0.46505787037037039</v>
       </c>
-      <c r="G2" t="s">
-        <v>9</v>
+      <c r="G2" s="3" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -3122,10 +3125,11 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" xr:uid="{68493181-F98E-438B-88DD-7AEA2299D695}"/>
+    <hyperlink ref="G2" r:id="rId2" xr:uid="{5AC46D5E-0BA7-46FD-B56D-A7B9C80580C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 G3:G5 E2 G2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 G3:G5 E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209BC7C-0638-4D8C-82D3-DAFFD3C6DCEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10F21A7-F865-4E84-B6F5-763BA96EFACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="Popups" sheetId="9" r:id="rId7"/>
     <sheet name="Statuses" sheetId="6" r:id="rId8"/>
     <sheet name="Notifications" sheetId="7" r:id="rId9"/>
+    <sheet name="Codes" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Popups!$A$1:$M$1</definedName>
@@ -334,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="238">
   <si>
     <t>id</t>
   </si>
@@ -1072,6 +1073,12 @@
   </si>
   <si>
     <t>https://static.srpcdigital.com/styles/1037xauto/public/2024-03/563741.jpeg</t>
+  </si>
+  <si>
+    <t>https://img.youm7.com/xlarge/202503220235503550.jpg</t>
+  </si>
+  <si>
+    <t>مدة الصلاحية (يوم)</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1088,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$EGP]_-;\-* #,##0\ [$EGP]_-;_-* &quot;-&quot;\ [$EGP]_-;_-@_-"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1207,6 +1214,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1235,7 +1248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1294,6 +1307,10 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1733,6 +1750,1548 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAA67635-66B8-4F03-B727-D55B5356AEF5}">
+  <dimension ref="A1:C500"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="2" width="24.625" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="17.25">
+      <c r="A2">
+        <v>3212</v>
+      </c>
+      <c r="B2" s="27">
+        <v>10</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="B3" s="27"/>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="B4" s="27"/>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" s="27"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="27"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" s="27"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" s="27"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" s="27"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" s="27"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" s="27"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" s="27"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" s="27"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" s="27"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" s="27"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="B16" s="27"/>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" s="27"/>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" s="27"/>
+    </row>
+    <row r="19" spans="2:2">
+      <c r="B19" s="27"/>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" s="27"/>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="27"/>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" s="27"/>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" s="27"/>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" s="27"/>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="27"/>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" s="27"/>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" s="27"/>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" s="27"/>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="27"/>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" s="27"/>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="27"/>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" s="27"/>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="27"/>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" s="27"/>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" s="27"/>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" s="27"/>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" s="27"/>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="27"/>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="27"/>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" s="27"/>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="27"/>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" s="27"/>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="27"/>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" s="27"/>
+    </row>
+    <row r="45" spans="2:2">
+      <c r="B45" s="27"/>
+    </row>
+    <row r="46" spans="2:2">
+      <c r="B46" s="27"/>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="27"/>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" s="27"/>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="27"/>
+    </row>
+    <row r="50" spans="2:2">
+      <c r="B50" s="27"/>
+    </row>
+    <row r="51" spans="2:2">
+      <c r="B51" s="27"/>
+    </row>
+    <row r="52" spans="2:2">
+      <c r="B52" s="27"/>
+    </row>
+    <row r="53" spans="2:2">
+      <c r="B53" s="27"/>
+    </row>
+    <row r="54" spans="2:2">
+      <c r="B54" s="27"/>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" s="27"/>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" s="27"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="27"/>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" s="27"/>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" s="27"/>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" s="27"/>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" s="27"/>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" s="27"/>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" s="27"/>
+    </row>
+    <row r="64" spans="2:2">
+      <c r="B64" s="27"/>
+    </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="27"/>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" s="27"/>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="27"/>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" s="27"/>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="27"/>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" s="27"/>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="27"/>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" s="27"/>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="27"/>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" s="27"/>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="27"/>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" s="27"/>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="27"/>
+    </row>
+    <row r="78" spans="2:2">
+      <c r="B78" s="27"/>
+    </row>
+    <row r="79" spans="2:2">
+      <c r="B79" s="27"/>
+    </row>
+    <row r="80" spans="2:2">
+      <c r="B80" s="27"/>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="27"/>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" s="27"/>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="27"/>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" s="27"/>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="27"/>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" s="27"/>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="27"/>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" s="27"/>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="27"/>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" s="27"/>
+    </row>
+    <row r="91" spans="2:2">
+      <c r="B91" s="27"/>
+    </row>
+    <row r="92" spans="2:2">
+      <c r="B92" s="27"/>
+    </row>
+    <row r="93" spans="2:2">
+      <c r="B93" s="27"/>
+    </row>
+    <row r="94" spans="2:2">
+      <c r="B94" s="27"/>
+    </row>
+    <row r="95" spans="2:2">
+      <c r="B95" s="27"/>
+    </row>
+    <row r="96" spans="2:2">
+      <c r="B96" s="27"/>
+    </row>
+    <row r="97" spans="2:2">
+      <c r="B97" s="27"/>
+    </row>
+    <row r="98" spans="2:2">
+      <c r="B98" s="27"/>
+    </row>
+    <row r="99" spans="2:2">
+      <c r="B99" s="27"/>
+    </row>
+    <row r="100" spans="2:2">
+      <c r="B100" s="27"/>
+    </row>
+    <row r="101" spans="2:2">
+      <c r="B101" s="27"/>
+    </row>
+    <row r="102" spans="2:2">
+      <c r="B102" s="27"/>
+    </row>
+    <row r="103" spans="2:2">
+      <c r="B103" s="27"/>
+    </row>
+    <row r="104" spans="2:2">
+      <c r="B104" s="27"/>
+    </row>
+    <row r="105" spans="2:2">
+      <c r="B105" s="27"/>
+    </row>
+    <row r="106" spans="2:2">
+      <c r="B106" s="27"/>
+    </row>
+    <row r="107" spans="2:2">
+      <c r="B107" s="27"/>
+    </row>
+    <row r="108" spans="2:2">
+      <c r="B108" s="27"/>
+    </row>
+    <row r="109" spans="2:2">
+      <c r="B109" s="27"/>
+    </row>
+    <row r="110" spans="2:2">
+      <c r="B110" s="27"/>
+    </row>
+    <row r="111" spans="2:2">
+      <c r="B111" s="27"/>
+    </row>
+    <row r="112" spans="2:2">
+      <c r="B112" s="27"/>
+    </row>
+    <row r="113" spans="2:2">
+      <c r="B113" s="27"/>
+    </row>
+    <row r="114" spans="2:2">
+      <c r="B114" s="27"/>
+    </row>
+    <row r="115" spans="2:2">
+      <c r="B115" s="27"/>
+    </row>
+    <row r="116" spans="2:2">
+      <c r="B116" s="27"/>
+    </row>
+    <row r="117" spans="2:2">
+      <c r="B117" s="27"/>
+    </row>
+    <row r="118" spans="2:2">
+      <c r="B118" s="27"/>
+    </row>
+    <row r="119" spans="2:2">
+      <c r="B119" s="27"/>
+    </row>
+    <row r="120" spans="2:2">
+      <c r="B120" s="27"/>
+    </row>
+    <row r="121" spans="2:2">
+      <c r="B121" s="27"/>
+    </row>
+    <row r="122" spans="2:2">
+      <c r="B122" s="27"/>
+    </row>
+    <row r="123" spans="2:2">
+      <c r="B123" s="27"/>
+    </row>
+    <row r="124" spans="2:2">
+      <c r="B124" s="27"/>
+    </row>
+    <row r="125" spans="2:2">
+      <c r="B125" s="27"/>
+    </row>
+    <row r="126" spans="2:2">
+      <c r="B126" s="27"/>
+    </row>
+    <row r="127" spans="2:2">
+      <c r="B127" s="27"/>
+    </row>
+    <row r="128" spans="2:2">
+      <c r="B128" s="27"/>
+    </row>
+    <row r="129" spans="2:2">
+      <c r="B129" s="27"/>
+    </row>
+    <row r="130" spans="2:2">
+      <c r="B130" s="27"/>
+    </row>
+    <row r="131" spans="2:2">
+      <c r="B131" s="27"/>
+    </row>
+    <row r="132" spans="2:2">
+      <c r="B132" s="27"/>
+    </row>
+    <row r="133" spans="2:2">
+      <c r="B133" s="27"/>
+    </row>
+    <row r="134" spans="2:2">
+      <c r="B134" s="27"/>
+    </row>
+    <row r="135" spans="2:2">
+      <c r="B135" s="27"/>
+    </row>
+    <row r="136" spans="2:2">
+      <c r="B136" s="27"/>
+    </row>
+    <row r="137" spans="2:2">
+      <c r="B137" s="27"/>
+    </row>
+    <row r="138" spans="2:2">
+      <c r="B138" s="27"/>
+    </row>
+    <row r="139" spans="2:2">
+      <c r="B139" s="27"/>
+    </row>
+    <row r="140" spans="2:2">
+      <c r="B140" s="27"/>
+    </row>
+    <row r="141" spans="2:2">
+      <c r="B141" s="27"/>
+    </row>
+    <row r="142" spans="2:2">
+      <c r="B142" s="27"/>
+    </row>
+    <row r="143" spans="2:2">
+      <c r="B143" s="27"/>
+    </row>
+    <row r="144" spans="2:2">
+      <c r="B144" s="27"/>
+    </row>
+    <row r="145" spans="2:2">
+      <c r="B145" s="27"/>
+    </row>
+    <row r="146" spans="2:2">
+      <c r="B146" s="27"/>
+    </row>
+    <row r="147" spans="2:2">
+      <c r="B147" s="27"/>
+    </row>
+    <row r="148" spans="2:2">
+      <c r="B148" s="27"/>
+    </row>
+    <row r="149" spans="2:2">
+      <c r="B149" s="27"/>
+    </row>
+    <row r="150" spans="2:2">
+      <c r="B150" s="27"/>
+    </row>
+    <row r="151" spans="2:2">
+      <c r="B151" s="27"/>
+    </row>
+    <row r="152" spans="2:2">
+      <c r="B152" s="27"/>
+    </row>
+    <row r="153" spans="2:2">
+      <c r="B153" s="27"/>
+    </row>
+    <row r="154" spans="2:2">
+      <c r="B154" s="27"/>
+    </row>
+    <row r="155" spans="2:2">
+      <c r="B155" s="27"/>
+    </row>
+    <row r="156" spans="2:2">
+      <c r="B156" s="27"/>
+    </row>
+    <row r="157" spans="2:2">
+      <c r="B157" s="27"/>
+    </row>
+    <row r="158" spans="2:2">
+      <c r="B158" s="27"/>
+    </row>
+    <row r="159" spans="2:2">
+      <c r="B159" s="27"/>
+    </row>
+    <row r="160" spans="2:2">
+      <c r="B160" s="27"/>
+    </row>
+    <row r="161" spans="2:2">
+      <c r="B161" s="27"/>
+    </row>
+    <row r="162" spans="2:2">
+      <c r="B162" s="27"/>
+    </row>
+    <row r="163" spans="2:2">
+      <c r="B163" s="27"/>
+    </row>
+    <row r="164" spans="2:2">
+      <c r="B164" s="27"/>
+    </row>
+    <row r="165" spans="2:2">
+      <c r="B165" s="27"/>
+    </row>
+    <row r="166" spans="2:2">
+      <c r="B166" s="27"/>
+    </row>
+    <row r="167" spans="2:2">
+      <c r="B167" s="27"/>
+    </row>
+    <row r="168" spans="2:2">
+      <c r="B168" s="27"/>
+    </row>
+    <row r="169" spans="2:2">
+      <c r="B169" s="27"/>
+    </row>
+    <row r="170" spans="2:2">
+      <c r="B170" s="27"/>
+    </row>
+    <row r="171" spans="2:2">
+      <c r="B171" s="27"/>
+    </row>
+    <row r="172" spans="2:2">
+      <c r="B172" s="27"/>
+    </row>
+    <row r="173" spans="2:2">
+      <c r="B173" s="27"/>
+    </row>
+    <row r="174" spans="2:2">
+      <c r="B174" s="27"/>
+    </row>
+    <row r="175" spans="2:2">
+      <c r="B175" s="27"/>
+    </row>
+    <row r="176" spans="2:2">
+      <c r="B176" s="27"/>
+    </row>
+    <row r="177" spans="2:2">
+      <c r="B177" s="27"/>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="27"/>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="27"/>
+    </row>
+    <row r="180" spans="2:2">
+      <c r="B180" s="27"/>
+    </row>
+    <row r="181" spans="2:2">
+      <c r="B181" s="27"/>
+    </row>
+    <row r="182" spans="2:2">
+      <c r="B182" s="27"/>
+    </row>
+    <row r="183" spans="2:2">
+      <c r="B183" s="27"/>
+    </row>
+    <row r="184" spans="2:2">
+      <c r="B184" s="27"/>
+    </row>
+    <row r="185" spans="2:2">
+      <c r="B185" s="27"/>
+    </row>
+    <row r="186" spans="2:2">
+      <c r="B186" s="27"/>
+    </row>
+    <row r="187" spans="2:2">
+      <c r="B187" s="27"/>
+    </row>
+    <row r="188" spans="2:2">
+      <c r="B188" s="27"/>
+    </row>
+    <row r="189" spans="2:2">
+      <c r="B189" s="27"/>
+    </row>
+    <row r="190" spans="2:2">
+      <c r="B190" s="27"/>
+    </row>
+    <row r="191" spans="2:2">
+      <c r="B191" s="27"/>
+    </row>
+    <row r="192" spans="2:2">
+      <c r="B192" s="27"/>
+    </row>
+    <row r="193" spans="2:2">
+      <c r="B193" s="27"/>
+    </row>
+    <row r="194" spans="2:2">
+      <c r="B194" s="27"/>
+    </row>
+    <row r="195" spans="2:2">
+      <c r="B195" s="27"/>
+    </row>
+    <row r="196" spans="2:2">
+      <c r="B196" s="27"/>
+    </row>
+    <row r="197" spans="2:2">
+      <c r="B197" s="27"/>
+    </row>
+    <row r="198" spans="2:2">
+      <c r="B198" s="27"/>
+    </row>
+    <row r="199" spans="2:2">
+      <c r="B199" s="27"/>
+    </row>
+    <row r="200" spans="2:2">
+      <c r="B200" s="27"/>
+    </row>
+    <row r="201" spans="2:2">
+      <c r="B201" s="27"/>
+    </row>
+    <row r="202" spans="2:2">
+      <c r="B202" s="27"/>
+    </row>
+    <row r="203" spans="2:2">
+      <c r="B203" s="27"/>
+    </row>
+    <row r="204" spans="2:2">
+      <c r="B204" s="27"/>
+    </row>
+    <row r="205" spans="2:2">
+      <c r="B205" s="27"/>
+    </row>
+    <row r="206" spans="2:2">
+      <c r="B206" s="27"/>
+    </row>
+    <row r="207" spans="2:2">
+      <c r="B207" s="27"/>
+    </row>
+    <row r="208" spans="2:2">
+      <c r="B208" s="27"/>
+    </row>
+    <row r="209" spans="2:2">
+      <c r="B209" s="27"/>
+    </row>
+    <row r="210" spans="2:2">
+      <c r="B210" s="27"/>
+    </row>
+    <row r="211" spans="2:2">
+      <c r="B211" s="27"/>
+    </row>
+    <row r="212" spans="2:2">
+      <c r="B212" s="27"/>
+    </row>
+    <row r="213" spans="2:2">
+      <c r="B213" s="27"/>
+    </row>
+    <row r="214" spans="2:2">
+      <c r="B214" s="27"/>
+    </row>
+    <row r="215" spans="2:2">
+      <c r="B215" s="27"/>
+    </row>
+    <row r="216" spans="2:2">
+      <c r="B216" s="27"/>
+    </row>
+    <row r="217" spans="2:2">
+      <c r="B217" s="27"/>
+    </row>
+    <row r="218" spans="2:2">
+      <c r="B218" s="27"/>
+    </row>
+    <row r="219" spans="2:2">
+      <c r="B219" s="27"/>
+    </row>
+    <row r="220" spans="2:2">
+      <c r="B220" s="27"/>
+    </row>
+    <row r="221" spans="2:2">
+      <c r="B221" s="27"/>
+    </row>
+    <row r="222" spans="2:2">
+      <c r="B222" s="27"/>
+    </row>
+    <row r="223" spans="2:2">
+      <c r="B223" s="27"/>
+    </row>
+    <row r="224" spans="2:2">
+      <c r="B224" s="27"/>
+    </row>
+    <row r="225" spans="2:2">
+      <c r="B225" s="27"/>
+    </row>
+    <row r="226" spans="2:2">
+      <c r="B226" s="27"/>
+    </row>
+    <row r="227" spans="2:2">
+      <c r="B227" s="27"/>
+    </row>
+    <row r="228" spans="2:2">
+      <c r="B228" s="27"/>
+    </row>
+    <row r="229" spans="2:2">
+      <c r="B229" s="27"/>
+    </row>
+    <row r="230" spans="2:2">
+      <c r="B230" s="27"/>
+    </row>
+    <row r="231" spans="2:2">
+      <c r="B231" s="27"/>
+    </row>
+    <row r="232" spans="2:2">
+      <c r="B232" s="27"/>
+    </row>
+    <row r="233" spans="2:2">
+      <c r="B233" s="27"/>
+    </row>
+    <row r="234" spans="2:2">
+      <c r="B234" s="27"/>
+    </row>
+    <row r="235" spans="2:2">
+      <c r="B235" s="27"/>
+    </row>
+    <row r="236" spans="2:2">
+      <c r="B236" s="27"/>
+    </row>
+    <row r="237" spans="2:2">
+      <c r="B237" s="27"/>
+    </row>
+    <row r="238" spans="2:2">
+      <c r="B238" s="27"/>
+    </row>
+    <row r="239" spans="2:2">
+      <c r="B239" s="27"/>
+    </row>
+    <row r="240" spans="2:2">
+      <c r="B240" s="27"/>
+    </row>
+    <row r="241" spans="2:2">
+      <c r="B241" s="27"/>
+    </row>
+    <row r="242" spans="2:2">
+      <c r="B242" s="27"/>
+    </row>
+    <row r="243" spans="2:2">
+      <c r="B243" s="27"/>
+    </row>
+    <row r="244" spans="2:2">
+      <c r="B244" s="27"/>
+    </row>
+    <row r="245" spans="2:2">
+      <c r="B245" s="27"/>
+    </row>
+    <row r="246" spans="2:2">
+      <c r="B246" s="27"/>
+    </row>
+    <row r="247" spans="2:2">
+      <c r="B247" s="27"/>
+    </row>
+    <row r="248" spans="2:2">
+      <c r="B248" s="27"/>
+    </row>
+    <row r="249" spans="2:2">
+      <c r="B249" s="27"/>
+    </row>
+    <row r="250" spans="2:2">
+      <c r="B250" s="27"/>
+    </row>
+    <row r="251" spans="2:2">
+      <c r="B251" s="27"/>
+    </row>
+    <row r="252" spans="2:2">
+      <c r="B252" s="27"/>
+    </row>
+    <row r="253" spans="2:2">
+      <c r="B253" s="27"/>
+    </row>
+    <row r="254" spans="2:2">
+      <c r="B254" s="27"/>
+    </row>
+    <row r="255" spans="2:2">
+      <c r="B255" s="27"/>
+    </row>
+    <row r="256" spans="2:2">
+      <c r="B256" s="27"/>
+    </row>
+    <row r="257" spans="2:2">
+      <c r="B257" s="27"/>
+    </row>
+    <row r="258" spans="2:2">
+      <c r="B258" s="27"/>
+    </row>
+    <row r="259" spans="2:2">
+      <c r="B259" s="27"/>
+    </row>
+    <row r="260" spans="2:2">
+      <c r="B260" s="27"/>
+    </row>
+    <row r="261" spans="2:2">
+      <c r="B261" s="27"/>
+    </row>
+    <row r="262" spans="2:2">
+      <c r="B262" s="27"/>
+    </row>
+    <row r="263" spans="2:2">
+      <c r="B263" s="27"/>
+    </row>
+    <row r="264" spans="2:2">
+      <c r="B264" s="27"/>
+    </row>
+    <row r="265" spans="2:2">
+      <c r="B265" s="27"/>
+    </row>
+    <row r="266" spans="2:2">
+      <c r="B266" s="27"/>
+    </row>
+    <row r="267" spans="2:2">
+      <c r="B267" s="27"/>
+    </row>
+    <row r="268" spans="2:2">
+      <c r="B268" s="27"/>
+    </row>
+    <row r="269" spans="2:2">
+      <c r="B269" s="27"/>
+    </row>
+    <row r="270" spans="2:2">
+      <c r="B270" s="27"/>
+    </row>
+    <row r="271" spans="2:2">
+      <c r="B271" s="27"/>
+    </row>
+    <row r="272" spans="2:2">
+      <c r="B272" s="27"/>
+    </row>
+    <row r="273" spans="2:2">
+      <c r="B273" s="27"/>
+    </row>
+    <row r="274" spans="2:2">
+      <c r="B274" s="27"/>
+    </row>
+    <row r="275" spans="2:2">
+      <c r="B275" s="27"/>
+    </row>
+    <row r="276" spans="2:2">
+      <c r="B276" s="27"/>
+    </row>
+    <row r="277" spans="2:2">
+      <c r="B277" s="27"/>
+    </row>
+    <row r="278" spans="2:2">
+      <c r="B278" s="27"/>
+    </row>
+    <row r="279" spans="2:2">
+      <c r="B279" s="27"/>
+    </row>
+    <row r="280" spans="2:2">
+      <c r="B280" s="27"/>
+    </row>
+    <row r="281" spans="2:2">
+      <c r="B281" s="27"/>
+    </row>
+    <row r="282" spans="2:2">
+      <c r="B282" s="27"/>
+    </row>
+    <row r="283" spans="2:2">
+      <c r="B283" s="27"/>
+    </row>
+    <row r="284" spans="2:2">
+      <c r="B284" s="27"/>
+    </row>
+    <row r="285" spans="2:2">
+      <c r="B285" s="27"/>
+    </row>
+    <row r="286" spans="2:2">
+      <c r="B286" s="27"/>
+    </row>
+    <row r="287" spans="2:2">
+      <c r="B287" s="27"/>
+    </row>
+    <row r="288" spans="2:2">
+      <c r="B288" s="27"/>
+    </row>
+    <row r="289" spans="2:2">
+      <c r="B289" s="27"/>
+    </row>
+    <row r="290" spans="2:2">
+      <c r="B290" s="27"/>
+    </row>
+    <row r="291" spans="2:2">
+      <c r="B291" s="27"/>
+    </row>
+    <row r="292" spans="2:2">
+      <c r="B292" s="27"/>
+    </row>
+    <row r="293" spans="2:2">
+      <c r="B293" s="27"/>
+    </row>
+    <row r="294" spans="2:2">
+      <c r="B294" s="27"/>
+    </row>
+    <row r="295" spans="2:2">
+      <c r="B295" s="27"/>
+    </row>
+    <row r="296" spans="2:2">
+      <c r="B296" s="27"/>
+    </row>
+    <row r="297" spans="2:2">
+      <c r="B297" s="27"/>
+    </row>
+    <row r="298" spans="2:2">
+      <c r="B298" s="27"/>
+    </row>
+    <row r="299" spans="2:2">
+      <c r="B299" s="27"/>
+    </row>
+    <row r="300" spans="2:2">
+      <c r="B300" s="27"/>
+    </row>
+    <row r="301" spans="2:2">
+      <c r="B301" s="27"/>
+    </row>
+    <row r="302" spans="2:2">
+      <c r="B302" s="27"/>
+    </row>
+    <row r="303" spans="2:2">
+      <c r="B303" s="27"/>
+    </row>
+    <row r="304" spans="2:2">
+      <c r="B304" s="27"/>
+    </row>
+    <row r="305" spans="2:2">
+      <c r="B305" s="27"/>
+    </row>
+    <row r="306" spans="2:2">
+      <c r="B306" s="27"/>
+    </row>
+    <row r="307" spans="2:2">
+      <c r="B307" s="27"/>
+    </row>
+    <row r="308" spans="2:2">
+      <c r="B308" s="27"/>
+    </row>
+    <row r="309" spans="2:2">
+      <c r="B309" s="27"/>
+    </row>
+    <row r="310" spans="2:2">
+      <c r="B310" s="27"/>
+    </row>
+    <row r="311" spans="2:2">
+      <c r="B311" s="27"/>
+    </row>
+    <row r="312" spans="2:2">
+      <c r="B312" s="27"/>
+    </row>
+    <row r="313" spans="2:2">
+      <c r="B313" s="27"/>
+    </row>
+    <row r="314" spans="2:2">
+      <c r="B314" s="27"/>
+    </row>
+    <row r="315" spans="2:2">
+      <c r="B315" s="27"/>
+    </row>
+    <row r="316" spans="2:2">
+      <c r="B316" s="27"/>
+    </row>
+    <row r="317" spans="2:2">
+      <c r="B317" s="27"/>
+    </row>
+    <row r="318" spans="2:2">
+      <c r="B318" s="27"/>
+    </row>
+    <row r="319" spans="2:2">
+      <c r="B319" s="27"/>
+    </row>
+    <row r="320" spans="2:2">
+      <c r="B320" s="27"/>
+    </row>
+    <row r="321" spans="2:2">
+      <c r="B321" s="27"/>
+    </row>
+    <row r="322" spans="2:2">
+      <c r="B322" s="27"/>
+    </row>
+    <row r="323" spans="2:2">
+      <c r="B323" s="27"/>
+    </row>
+    <row r="324" spans="2:2">
+      <c r="B324" s="27"/>
+    </row>
+    <row r="325" spans="2:2">
+      <c r="B325" s="27"/>
+    </row>
+    <row r="326" spans="2:2">
+      <c r="B326" s="27"/>
+    </row>
+    <row r="327" spans="2:2">
+      <c r="B327" s="27"/>
+    </row>
+    <row r="328" spans="2:2">
+      <c r="B328" s="27"/>
+    </row>
+    <row r="329" spans="2:2">
+      <c r="B329" s="27"/>
+    </row>
+    <row r="330" spans="2:2">
+      <c r="B330" s="27"/>
+    </row>
+    <row r="331" spans="2:2">
+      <c r="B331" s="27"/>
+    </row>
+    <row r="332" spans="2:2">
+      <c r="B332" s="27"/>
+    </row>
+    <row r="333" spans="2:2">
+      <c r="B333" s="27"/>
+    </row>
+    <row r="334" spans="2:2">
+      <c r="B334" s="27"/>
+    </row>
+    <row r="335" spans="2:2">
+      <c r="B335" s="27"/>
+    </row>
+    <row r="336" spans="2:2">
+      <c r="B336" s="27"/>
+    </row>
+    <row r="337" spans="2:2">
+      <c r="B337" s="27"/>
+    </row>
+    <row r="338" spans="2:2">
+      <c r="B338" s="27"/>
+    </row>
+    <row r="339" spans="2:2">
+      <c r="B339" s="27"/>
+    </row>
+    <row r="340" spans="2:2">
+      <c r="B340" s="27"/>
+    </row>
+    <row r="341" spans="2:2">
+      <c r="B341" s="27"/>
+    </row>
+    <row r="342" spans="2:2">
+      <c r="B342" s="27"/>
+    </row>
+    <row r="343" spans="2:2">
+      <c r="B343" s="27"/>
+    </row>
+    <row r="344" spans="2:2">
+      <c r="B344" s="27"/>
+    </row>
+    <row r="345" spans="2:2">
+      <c r="B345" s="27"/>
+    </row>
+    <row r="346" spans="2:2">
+      <c r="B346" s="27"/>
+    </row>
+    <row r="347" spans="2:2">
+      <c r="B347" s="27"/>
+    </row>
+    <row r="348" spans="2:2">
+      <c r="B348" s="27"/>
+    </row>
+    <row r="349" spans="2:2">
+      <c r="B349" s="27"/>
+    </row>
+    <row r="350" spans="2:2">
+      <c r="B350" s="27"/>
+    </row>
+    <row r="351" spans="2:2">
+      <c r="B351" s="27"/>
+    </row>
+    <row r="352" spans="2:2">
+      <c r="B352" s="27"/>
+    </row>
+    <row r="353" spans="2:2">
+      <c r="B353" s="27"/>
+    </row>
+    <row r="354" spans="2:2">
+      <c r="B354" s="27"/>
+    </row>
+    <row r="355" spans="2:2">
+      <c r="B355" s="27"/>
+    </row>
+    <row r="356" spans="2:2">
+      <c r="B356" s="27"/>
+    </row>
+    <row r="357" spans="2:2">
+      <c r="B357" s="27"/>
+    </row>
+    <row r="358" spans="2:2">
+      <c r="B358" s="27"/>
+    </row>
+    <row r="359" spans="2:2">
+      <c r="B359" s="27"/>
+    </row>
+    <row r="360" spans="2:2">
+      <c r="B360" s="27"/>
+    </row>
+    <row r="361" spans="2:2">
+      <c r="B361" s="27"/>
+    </row>
+    <row r="362" spans="2:2">
+      <c r="B362" s="27"/>
+    </row>
+    <row r="363" spans="2:2">
+      <c r="B363" s="27"/>
+    </row>
+    <row r="364" spans="2:2">
+      <c r="B364" s="27"/>
+    </row>
+    <row r="365" spans="2:2">
+      <c r="B365" s="27"/>
+    </row>
+    <row r="366" spans="2:2">
+      <c r="B366" s="27"/>
+    </row>
+    <row r="367" spans="2:2">
+      <c r="B367" s="27"/>
+    </row>
+    <row r="368" spans="2:2">
+      <c r="B368" s="27"/>
+    </row>
+    <row r="369" spans="2:2">
+      <c r="B369" s="27"/>
+    </row>
+    <row r="370" spans="2:2">
+      <c r="B370" s="27"/>
+    </row>
+    <row r="371" spans="2:2">
+      <c r="B371" s="27"/>
+    </row>
+    <row r="372" spans="2:2">
+      <c r="B372" s="27"/>
+    </row>
+    <row r="373" spans="2:2">
+      <c r="B373" s="27"/>
+    </row>
+    <row r="374" spans="2:2">
+      <c r="B374" s="27"/>
+    </row>
+    <row r="375" spans="2:2">
+      <c r="B375" s="27"/>
+    </row>
+    <row r="376" spans="2:2">
+      <c r="B376" s="27"/>
+    </row>
+    <row r="377" spans="2:2">
+      <c r="B377" s="27"/>
+    </row>
+    <row r="378" spans="2:2">
+      <c r="B378" s="27"/>
+    </row>
+    <row r="379" spans="2:2">
+      <c r="B379" s="27"/>
+    </row>
+    <row r="380" spans="2:2">
+      <c r="B380" s="27"/>
+    </row>
+    <row r="381" spans="2:2">
+      <c r="B381" s="27"/>
+    </row>
+    <row r="382" spans="2:2">
+      <c r="B382" s="27"/>
+    </row>
+    <row r="383" spans="2:2">
+      <c r="B383" s="27"/>
+    </row>
+    <row r="384" spans="2:2">
+      <c r="B384" s="27"/>
+    </row>
+    <row r="385" spans="2:2">
+      <c r="B385" s="27"/>
+    </row>
+    <row r="386" spans="2:2">
+      <c r="B386" s="27"/>
+    </row>
+    <row r="387" spans="2:2">
+      <c r="B387" s="27"/>
+    </row>
+    <row r="388" spans="2:2">
+      <c r="B388" s="27"/>
+    </row>
+    <row r="389" spans="2:2">
+      <c r="B389" s="27"/>
+    </row>
+    <row r="390" spans="2:2">
+      <c r="B390" s="27"/>
+    </row>
+    <row r="391" spans="2:2">
+      <c r="B391" s="27"/>
+    </row>
+    <row r="392" spans="2:2">
+      <c r="B392" s="27"/>
+    </row>
+    <row r="393" spans="2:2">
+      <c r="B393" s="27"/>
+    </row>
+    <row r="394" spans="2:2">
+      <c r="B394" s="27"/>
+    </row>
+    <row r="395" spans="2:2">
+      <c r="B395" s="27"/>
+    </row>
+    <row r="396" spans="2:2">
+      <c r="B396" s="27"/>
+    </row>
+    <row r="397" spans="2:2">
+      <c r="B397" s="27"/>
+    </row>
+    <row r="398" spans="2:2">
+      <c r="B398" s="27"/>
+    </row>
+    <row r="399" spans="2:2">
+      <c r="B399" s="27"/>
+    </row>
+    <row r="400" spans="2:2">
+      <c r="B400" s="27"/>
+    </row>
+    <row r="401" spans="2:2">
+      <c r="B401" s="27"/>
+    </row>
+    <row r="402" spans="2:2">
+      <c r="B402" s="27"/>
+    </row>
+    <row r="403" spans="2:2">
+      <c r="B403" s="27"/>
+    </row>
+    <row r="404" spans="2:2">
+      <c r="B404" s="27"/>
+    </row>
+    <row r="405" spans="2:2">
+      <c r="B405" s="27"/>
+    </row>
+    <row r="406" spans="2:2">
+      <c r="B406" s="27"/>
+    </row>
+    <row r="407" spans="2:2">
+      <c r="B407" s="27"/>
+    </row>
+    <row r="408" spans="2:2">
+      <c r="B408" s="27"/>
+    </row>
+    <row r="409" spans="2:2">
+      <c r="B409" s="27"/>
+    </row>
+    <row r="410" spans="2:2">
+      <c r="B410" s="27"/>
+    </row>
+    <row r="411" spans="2:2">
+      <c r="B411" s="27"/>
+    </row>
+    <row r="412" spans="2:2">
+      <c r="B412" s="27"/>
+    </row>
+    <row r="413" spans="2:2">
+      <c r="B413" s="27"/>
+    </row>
+    <row r="414" spans="2:2">
+      <c r="B414" s="27"/>
+    </row>
+    <row r="415" spans="2:2">
+      <c r="B415" s="27"/>
+    </row>
+    <row r="416" spans="2:2">
+      <c r="B416" s="27"/>
+    </row>
+    <row r="417" spans="2:2">
+      <c r="B417" s="27"/>
+    </row>
+    <row r="418" spans="2:2">
+      <c r="B418" s="27"/>
+    </row>
+    <row r="419" spans="2:2">
+      <c r="B419" s="27"/>
+    </row>
+    <row r="420" spans="2:2">
+      <c r="B420" s="27"/>
+    </row>
+    <row r="421" spans="2:2">
+      <c r="B421" s="27"/>
+    </row>
+    <row r="422" spans="2:2">
+      <c r="B422" s="27"/>
+    </row>
+    <row r="423" spans="2:2">
+      <c r="B423" s="27"/>
+    </row>
+    <row r="424" spans="2:2">
+      <c r="B424" s="27"/>
+    </row>
+    <row r="425" spans="2:2">
+      <c r="B425" s="27"/>
+    </row>
+    <row r="426" spans="2:2">
+      <c r="B426" s="27"/>
+    </row>
+    <row r="427" spans="2:2">
+      <c r="B427" s="27"/>
+    </row>
+    <row r="428" spans="2:2">
+      <c r="B428" s="27"/>
+    </row>
+    <row r="429" spans="2:2">
+      <c r="B429" s="27"/>
+    </row>
+    <row r="430" spans="2:2">
+      <c r="B430" s="27"/>
+    </row>
+    <row r="431" spans="2:2">
+      <c r="B431" s="27"/>
+    </row>
+    <row r="432" spans="2:2">
+      <c r="B432" s="27"/>
+    </row>
+    <row r="433" spans="2:2">
+      <c r="B433" s="27"/>
+    </row>
+    <row r="434" spans="2:2">
+      <c r="B434" s="27"/>
+    </row>
+    <row r="435" spans="2:2">
+      <c r="B435" s="27"/>
+    </row>
+    <row r="436" spans="2:2">
+      <c r="B436" s="27"/>
+    </row>
+    <row r="437" spans="2:2">
+      <c r="B437" s="27"/>
+    </row>
+    <row r="438" spans="2:2">
+      <c r="B438" s="27"/>
+    </row>
+    <row r="439" spans="2:2">
+      <c r="B439" s="27"/>
+    </row>
+    <row r="440" spans="2:2">
+      <c r="B440" s="27"/>
+    </row>
+    <row r="441" spans="2:2">
+      <c r="B441" s="27"/>
+    </row>
+    <row r="442" spans="2:2">
+      <c r="B442" s="27"/>
+    </row>
+    <row r="443" spans="2:2">
+      <c r="B443" s="27"/>
+    </row>
+    <row r="444" spans="2:2">
+      <c r="B444" s="27"/>
+    </row>
+    <row r="445" spans="2:2">
+      <c r="B445" s="27"/>
+    </row>
+    <row r="446" spans="2:2">
+      <c r="B446" s="27"/>
+    </row>
+    <row r="447" spans="2:2">
+      <c r="B447" s="27"/>
+    </row>
+    <row r="448" spans="2:2">
+      <c r="B448" s="27"/>
+    </row>
+    <row r="449" spans="2:2">
+      <c r="B449" s="27"/>
+    </row>
+    <row r="450" spans="2:2">
+      <c r="B450" s="27"/>
+    </row>
+    <row r="451" spans="2:2">
+      <c r="B451" s="27"/>
+    </row>
+    <row r="452" spans="2:2">
+      <c r="B452" s="27"/>
+    </row>
+    <row r="453" spans="2:2">
+      <c r="B453" s="27"/>
+    </row>
+    <row r="454" spans="2:2">
+      <c r="B454" s="27"/>
+    </row>
+    <row r="455" spans="2:2">
+      <c r="B455" s="27"/>
+    </row>
+    <row r="456" spans="2:2">
+      <c r="B456" s="27"/>
+    </row>
+    <row r="457" spans="2:2">
+      <c r="B457" s="27"/>
+    </row>
+    <row r="458" spans="2:2">
+      <c r="B458" s="27"/>
+    </row>
+    <row r="459" spans="2:2">
+      <c r="B459" s="27"/>
+    </row>
+    <row r="460" spans="2:2">
+      <c r="B460" s="27"/>
+    </row>
+    <row r="461" spans="2:2">
+      <c r="B461" s="27"/>
+    </row>
+    <row r="462" spans="2:2">
+      <c r="B462" s="27"/>
+    </row>
+    <row r="463" spans="2:2">
+      <c r="B463" s="27"/>
+    </row>
+    <row r="464" spans="2:2">
+      <c r="B464" s="27"/>
+    </row>
+    <row r="465" spans="2:2">
+      <c r="B465" s="27"/>
+    </row>
+    <row r="466" spans="2:2">
+      <c r="B466" s="27"/>
+    </row>
+    <row r="467" spans="2:2">
+      <c r="B467" s="27"/>
+    </row>
+    <row r="468" spans="2:2">
+      <c r="B468" s="27"/>
+    </row>
+    <row r="469" spans="2:2">
+      <c r="B469" s="27"/>
+    </row>
+    <row r="470" spans="2:2">
+      <c r="B470" s="27"/>
+    </row>
+    <row r="471" spans="2:2">
+      <c r="B471" s="27"/>
+    </row>
+    <row r="472" spans="2:2">
+      <c r="B472" s="27"/>
+    </row>
+    <row r="473" spans="2:2">
+      <c r="B473" s="27"/>
+    </row>
+    <row r="474" spans="2:2">
+      <c r="B474" s="27"/>
+    </row>
+    <row r="475" spans="2:2">
+      <c r="B475" s="27"/>
+    </row>
+    <row r="476" spans="2:2">
+      <c r="B476" s="27"/>
+    </row>
+    <row r="477" spans="2:2">
+      <c r="B477" s="27"/>
+    </row>
+    <row r="478" spans="2:2">
+      <c r="B478" s="27"/>
+    </row>
+    <row r="479" spans="2:2">
+      <c r="B479" s="27"/>
+    </row>
+    <row r="480" spans="2:2">
+      <c r="B480" s="27"/>
+    </row>
+    <row r="481" spans="2:2">
+      <c r="B481" s="27"/>
+    </row>
+    <row r="482" spans="2:2">
+      <c r="B482" s="27"/>
+    </row>
+    <row r="483" spans="2:2">
+      <c r="B483" s="27"/>
+    </row>
+    <row r="484" spans="2:2">
+      <c r="B484" s="27"/>
+    </row>
+    <row r="485" spans="2:2">
+      <c r="B485" s="27"/>
+    </row>
+    <row r="486" spans="2:2">
+      <c r="B486" s="27"/>
+    </row>
+    <row r="487" spans="2:2">
+      <c r="B487" s="27"/>
+    </row>
+    <row r="488" spans="2:2">
+      <c r="B488" s="27"/>
+    </row>
+    <row r="489" spans="2:2">
+      <c r="B489" s="27"/>
+    </row>
+    <row r="490" spans="2:2">
+      <c r="B490" s="27"/>
+    </row>
+    <row r="491" spans="2:2">
+      <c r="B491" s="27"/>
+    </row>
+    <row r="492" spans="2:2">
+      <c r="B492" s="27"/>
+    </row>
+    <row r="493" spans="2:2">
+      <c r="B493" s="27"/>
+    </row>
+    <row r="494" spans="2:2">
+      <c r="B494" s="27"/>
+    </row>
+    <row r="495" spans="2:2">
+      <c r="B495" s="27"/>
+    </row>
+    <row r="496" spans="2:2">
+      <c r="B496" s="27"/>
+    </row>
+    <row r="497" spans="2:2">
+      <c r="B497" s="27"/>
+    </row>
+    <row r="498" spans="2:2">
+      <c r="B498" s="27"/>
+    </row>
+    <row r="499" spans="2:2">
+      <c r="B499" s="27"/>
+    </row>
+    <row r="500" spans="2:2">
+      <c r="B500" s="27"/>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3:C500" xr:uid="{A099AD98-63D4-4C40-92C5-B423444552BC}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>"نعم,لا"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"نعم,لا"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q25"/>
@@ -3047,13 +4606,13 @@
         <v>22</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F3" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -3129,7 +4688,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1 G3:G5 E2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 G4:G5 E2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -4796,7 +4796,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -4973,11 +4973,231 @@
       <c r="A16" t="s">
         <v>129</v>
       </c>
-      <c r="B16" t="s">
-        <v>130</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>#f7f9f8</t>
+        </is>
       </c>
       <c r="C16" t="s">
         <v>131</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">academy_logo_image</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>academy-video-icon.svg</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>مسار صورة رمز فيديو الأكاديمية بجوار الاسم</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">academy_description_color</t>
+        </is>
+      </c>
+      <c r="B18"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لون وصف الأكاديمية بصيغة HEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">academy_description_size</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حجم خط وصف الأكاديمية بالبكسل</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_kicker</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">أهلاً بك في متجر مشالى</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">عبارة الترحيب أعلى مقدمة المتجر</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_title</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">اختياراتك التقنية</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">العنوان الرئيسي لمقدمة المتجر</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_highlight</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">بخطوات أسهل</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">السطر المميز أسفل عنوان مقدمة المتجر</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_description</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">تصفّح المنتجات والأقسام، قارن التفاصيل والأسعار، ثم أرسل طلبك مباشرة عبر واتساب.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">النص التعريفي أسفل عنوان المتجر</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_kicker_color</t>
+        </is>
+      </c>
+      <c r="B24"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لون عبارة الترحيب بصيغة HEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_title_color</t>
+        </is>
+      </c>
+      <c r="B25"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لون عنوان المتجر بصيغة HEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_highlight_color</t>
+        </is>
+      </c>
+      <c r="B26"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لون السطر المميز بصيغة HEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_description_color</t>
+        </is>
+      </c>
+      <c r="B27"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">لون النص التعريفي بصيغة HEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_kicker_size</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حجم عبارة الترحيب بالبكسل</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_title_size</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حجم عنوان المتجر بالبكسل (من 12 إلى 64)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">store_hero_description_size</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">حجم النص التعريفي بالبكسل</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5080,7 +5300,7 @@
         <v>200</v>
       </c>
       <c r="K2" s="1">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>66</v>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -4796,7 +4796,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -4973,231 +4973,11 @@
       <c r="A16" t="s">
         <v>129</v>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>#f7f9f8</t>
-        </is>
+      <c r="B16" t="s">
+        <v>130</v>
       </c>
       <c r="C16" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_logo_image</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>academy-video-icon.svg</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>مسار صورة رمز فيديو الأكاديمية بجوار الاسم</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_description_color</t>
-        </is>
-      </c>
-      <c r="B18"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون وصف الأكاديمية بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_description_size</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم خط وصف الأكاديمية بالبكسل</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">أهلاً بك في متجر مشالى</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">عبارة الترحيب أعلى مقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اختياراتك التقنية</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">العنوان الرئيسي لمقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_highlight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بخطوات أسهل</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">السطر المميز أسفل عنوان مقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تصفّح المنتجات والأقسام، قارن التفاصيل والأسعار، ثم أرسل طلبك مباشرة عبر واتساب.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">النص التعريفي أسفل عنوان المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker_color</t>
-        </is>
-      </c>
-      <c r="B24"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون عبارة الترحيب بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title_color</t>
-        </is>
-      </c>
-      <c r="B25"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون عنوان المتجر بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_highlight_color</t>
-        </is>
-      </c>
-      <c r="B26"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون السطر المميز بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description_color</t>
-        </is>
-      </c>
-      <c r="B27"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون النص التعريفي بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker_size</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم عبارة الترحيب بالبكسل</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title_size</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم عنوان المتجر بالبكسل (من 12 إلى 64)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description_size</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم النص التعريفي بالبكسل</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -5300,7 +5080,7 @@
         <v>200</v>
       </c>
       <c r="K2" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>66</v>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -4796,7 +4796,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -4951,8 +4951,10 @@
       <c r="A14" t="s">
         <v>123</v>
       </c>
-      <c r="B14" t="s">
-        <v>124</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>أكاديمية مشالى للالكترونيات</t>
+        </is>
       </c>
       <c r="C14" t="s">
         <v>125</v>
@@ -5197,6 +5199,40 @@
       <c r="C30" t="inlineStr">
         <is>
           <t xml:space="preserve">حجم النص التعريفي بالبكسل</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>academy_logo_image</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>video.png</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>مسار صورة الأكاديمية؛ استبدل video.png أو اكتب مسار صورة أخرى لتحديثها بالموقع</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>brand_logo_image</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>logo.png</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>مسار صورة شعار المتجر؛ اكتب اسم الملف أو رابطه وارفع ملف الصورة إلى GitHub</t>
         </is>
       </c>
     </row>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -4796,7 +4796,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -5233,6 +5233,57 @@
       <c r="C32" t="inlineStr">
         <is>
           <t>مسار صورة شعار المتجر؛ اكتب اسم الملف أو رابطه وارفع ملف الصورة إلى GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>app_icon_192</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>icon-192.png</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>مسار أيقونة التطبيق المربعة بحجم 192×192؛ حدّث الصورة وارفعها للمستودع</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>app_icon_512</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>icon-512.png</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>مسار أيقونة التطبيق المربعة بحجم 512×512؛ تستخدم أيضاً لشاشة بدء Android</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>app_splash_image</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>logo.png</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>مسار الصورة التي تظهر أثناء تحميل التطبيق؛ ارفع الصورة إلى المستودع</t>
         </is>
       </c>
     </row>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\11-10-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10F21A7-F865-4E84-B6F5-763BA96EFACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD8B1CB-5D50-4E30-B918-B9784FFF3A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="285">
   <si>
     <t>id</t>
   </si>
@@ -376,9 +376,6 @@
     <t>🔥 الأكثر مبيعاً</t>
   </si>
   <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
     <t>الأيقونة</t>
   </si>
   <si>
@@ -463,13 +460,7 @@
     <t>الحد الأدنى</t>
   </si>
   <si>
-    <t>3212</t>
-  </si>
-  <si>
     <t>percent</t>
-  </si>
-  <si>
-    <t>SAVE10</t>
   </si>
   <si>
     <t>fixed</t>
@@ -722,9 +713,6 @@
     <t>academy_name</t>
   </si>
   <si>
-    <t>أكاديمية مشالى التعليمية</t>
-  </si>
-  <si>
     <t>اسم صفحة الأكاديمية</t>
   </si>
   <si>
@@ -738,9 +726,6 @@
   </si>
   <si>
     <t>theme_color</t>
-  </si>
-  <si>
-    <t>#2e8b57</t>
   </si>
   <si>
     <t>لون شريط المتصفح والتطبيق بصيغة HEX</t>
@@ -1079,6 +1064,162 @@
   </si>
   <si>
     <t>مدة الصلاحية (يوم)</t>
+  </si>
+  <si>
+    <t>#f7f9f8</t>
+  </si>
+  <si>
+    <t>academy_logo_image</t>
+  </si>
+  <si>
+    <t>academy-video-icon.svg</t>
+  </si>
+  <si>
+    <t>مسار صورة رمز فيديو الأكاديمية بجوار الاسم</t>
+  </si>
+  <si>
+    <t>academy_description_color</t>
+  </si>
+  <si>
+    <t>لون وصف الأكاديمية بصيغة HEX</t>
+  </si>
+  <si>
+    <t>academy_description_size</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>حجم خط وصف الأكاديمية بالبكسل</t>
+  </si>
+  <si>
+    <t>store_hero_kicker</t>
+  </si>
+  <si>
+    <t>أهلاً بك في متجر مشالى</t>
+  </si>
+  <si>
+    <t>عبارة الترحيب أعلى مقدمة المتجر</t>
+  </si>
+  <si>
+    <t>store_hero_title</t>
+  </si>
+  <si>
+    <t>اختياراتك التقنية</t>
+  </si>
+  <si>
+    <t>العنوان الرئيسي لمقدمة المتجر</t>
+  </si>
+  <si>
+    <t>store_hero_highlight</t>
+  </si>
+  <si>
+    <t>بخطوات أسهل</t>
+  </si>
+  <si>
+    <t>السطر المميز أسفل عنوان مقدمة المتجر</t>
+  </si>
+  <si>
+    <t>store_hero_description</t>
+  </si>
+  <si>
+    <t>تصفّح المنتجات والأقسام، قارن التفاصيل والأسعار، ثم أرسل طلبك مباشرة عبر واتساب.</t>
+  </si>
+  <si>
+    <t>النص التعريفي أسفل عنوان المتجر</t>
+  </si>
+  <si>
+    <t>store_hero_kicker_color</t>
+  </si>
+  <si>
+    <t>لون عبارة الترحيب بصيغة HEX</t>
+  </si>
+  <si>
+    <t>store_hero_title_color</t>
+  </si>
+  <si>
+    <t>لون عنوان المتجر بصيغة HEX</t>
+  </si>
+  <si>
+    <t>store_hero_highlight_color</t>
+  </si>
+  <si>
+    <t>لون السطر المميز بصيغة HEX</t>
+  </si>
+  <si>
+    <t>store_hero_description_color</t>
+  </si>
+  <si>
+    <t>لون النص التعريفي بصيغة HEX</t>
+  </si>
+  <si>
+    <t>store_hero_kicker_size</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>حجم عبارة الترحيب بالبكسل</t>
+  </si>
+  <si>
+    <t>store_hero_title_size</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>حجم عنوان المتجر بالبكسل (من 12 إلى 64)</t>
+  </si>
+  <si>
+    <t>store_hero_description_size</t>
+  </si>
+  <si>
+    <t>حجم النص التعريفي بالبكسل</t>
+  </si>
+  <si>
+    <t>video.png</t>
+  </si>
+  <si>
+    <t>مسار صورة الأكاديمية؛ استبدل video.png أو اكتب مسار صورة أخرى لتحديثها بالموقع</t>
+  </si>
+  <si>
+    <t>brand_logo_image</t>
+  </si>
+  <si>
+    <t>logo.png</t>
+  </si>
+  <si>
+    <t>مسار صورة شعار المتجر؛ اكتب اسم الملف أو رابطه وارفع ملف الصورة إلى GitHub</t>
+  </si>
+  <si>
+    <t>app_icon_192</t>
+  </si>
+  <si>
+    <t>icon-192.png</t>
+  </si>
+  <si>
+    <t>مسار أيقونة التطبيق المربعة بحجم 192×192؛ حدّث الصورة وارفعها للمستودع</t>
+  </si>
+  <si>
+    <t>app_icon_512</t>
+  </si>
+  <si>
+    <t>icon-512.png</t>
+  </si>
+  <si>
+    <t>مسار أيقونة التطبيق المربعة بحجم 512×512؛ تستخدم أيضاً لشاشة بدء Android</t>
+  </si>
+  <si>
+    <t>app_splash_image</t>
+  </si>
+  <si>
+    <t>مسار الصورة التي تظهر أثناء تحميل التطبيق؛ ارفع الصورة إلى المستودع</t>
+  </si>
+  <si>
+    <t>mashily</t>
+  </si>
+  <si>
+    <t>التعليمية</t>
   </si>
 </sst>
 </file>
@@ -1663,21 +1804,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1686,12 +1827,12 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>176</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>30</v>
@@ -1700,12 +1841,12 @@
         <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B4">
         <v>10</v>
@@ -1714,12 +1855,12 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>10</v>
@@ -1728,12 +1869,12 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B6">
         <v>50</v>
@@ -1742,7 +1883,7 @@
         <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1761,13 +1902,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="17.25">
@@ -1778,7 +1919,7 @@
         <v>10</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3320,40 +3461,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
+      <c r="K1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="L1" s="10" t="s">
-        <v>79</v>
-      </c>
       <c r="M1" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="N1" s="9" t="s">
         <v>4</v>
@@ -3365,7 +3506,7 @@
         <v>6</v>
       </c>
       <c r="Q1" s="11" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="48.75" customHeight="1">
@@ -3373,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C2" s="12">
         <v>110</v>
@@ -3382,28 +3523,28 @@
         <v>149</v>
       </c>
       <c r="E2" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>98</v>
-      </c>
       <c r="L2" s="14" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M2" s="9"/>
       <c r="N2" s="9" t="s">
@@ -3422,7 +3563,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C3" s="12">
         <v>125</v>
@@ -3431,28 +3572,28 @@
         <v>181</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="M3" s="9"/>
       <c r="N3" s="9" t="s">
@@ -3471,7 +3612,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C4" s="12">
         <v>100</v>
@@ -3480,28 +3621,28 @@
         <v>125</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="M4" s="9"/>
       <c r="N4" s="9" t="s">
@@ -3520,7 +3661,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C5" s="12">
         <v>125</v>
@@ -3529,28 +3670,28 @@
         <v>150</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="K5" s="9" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L5" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="M5" s="16">
         <v>46296</v>
@@ -3565,7 +3706,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C6" s="12">
         <v>25</v>
@@ -3574,24 +3715,24 @@
         <v>50</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="M6" s="9"/>
       <c r="N6" s="9"/>
@@ -3604,7 +3745,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C7" s="12">
         <v>25</v>
@@ -3613,24 +3754,24 @@
         <v>50</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
@@ -3643,7 +3784,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C8" s="12">
         <v>5</v>
@@ -3652,24 +3793,24 @@
         <v>20</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
@@ -3682,7 +3823,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C9" s="12">
         <v>10</v>
@@ -3691,24 +3832,24 @@
         <v>20</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
@@ -3721,7 +3862,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C10" s="12">
         <v>35</v>
@@ -3730,24 +3871,24 @@
         <v>50</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
@@ -3760,7 +3901,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C11" s="12">
         <v>50</v>
@@ -3769,26 +3910,26 @@
         <v>60</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
@@ -3801,7 +3942,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C12" s="18">
         <v>10</v>
@@ -3810,30 +3951,30 @@
         <v>15</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M12" s="20">
         <v>46300.999305555553</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O12" s="17">
         <v>4.5</v>
@@ -3850,7 +3991,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C13" s="18">
         <v>100</v>
@@ -3859,30 +4000,30 @@
         <v>150</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I13" s="21" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J13" s="9"/>
       <c r="K13" s="17"/>
       <c r="L13" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M13" s="20">
         <v>46300.999305555553</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O13" s="17">
         <v>4.5</v>
@@ -3899,7 +4040,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C14" s="12">
         <v>40</v>
@@ -3908,24 +4049,24 @@
         <v>55</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="22" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
@@ -3942,7 +4083,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C15" s="12">
         <v>80</v>
@@ -3951,24 +4092,24 @@
         <v>105</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
@@ -3985,7 +4126,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C16" s="12">
         <v>35</v>
@@ -3994,24 +4135,24 @@
         <v>50</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
@@ -4028,7 +4169,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C17" s="12">
         <v>50</v>
@@ -4037,24 +4178,24 @@
         <v>65</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M17" s="20">
         <v>46305.999305555553</v>
@@ -4073,7 +4214,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C18" s="12">
         <v>50</v>
@@ -4082,24 +4223,24 @@
         <v>75</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="15" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="M18" s="20">
         <v>46305.999305555553</v>
@@ -4118,7 +4259,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C19" s="12">
         <v>20</v>
@@ -4127,24 +4268,24 @@
         <v>35</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
@@ -4161,7 +4302,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C20" s="12">
         <v>20</v>
@@ -4170,24 +4311,24 @@
         <v>35</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="15" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
@@ -4204,7 +4345,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C21" s="12">
         <v>20</v>
@@ -4213,24 +4354,24 @@
         <v>35</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="14" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
@@ -4247,7 +4388,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C22" s="12">
         <v>30</v>
@@ -4256,24 +4397,24 @@
         <v>45</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="23" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
@@ -4290,7 +4431,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="C23" s="12">
         <v>35</v>
@@ -4299,24 +4440,24 @@
         <v>50</v>
       </c>
       <c r="E23" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="F23" s="9" t="s">
-        <v>234</v>
-      </c>
       <c r="G23" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="24" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
@@ -4333,7 +4474,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C24" s="12">
         <v>30</v>
@@ -4342,24 +4483,24 @@
         <v>45</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="24" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
@@ -4376,7 +4517,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C25" s="12">
         <v>50</v>
@@ -4385,24 +4526,24 @@
         <v>90</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="26" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="M25" s="20">
         <v>46305.999305555553</v>
@@ -4458,71 +4599,71 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -4544,6 +4685,7 @@
     <col min="4" max="4" width="11.625" customWidth="1"/>
     <col min="5" max="5" width="12.875" customWidth="1"/>
     <col min="6" max="6" width="11.375" customWidth="1"/>
+    <col min="7" max="7" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4551,22 +4693,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
         <v>15</v>
-      </c>
-      <c r="C1" t="s">
-        <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>18</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4574,22 +4716,22 @@
         <v>1770051311267</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="4">
         <v>0.46505787037037039</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4597,22 +4739,22 @@
         <v>1770051311268</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -4620,19 +4762,19 @@
         <v>1770051311269</v>
       </c>
       <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -4643,19 +4785,19 @@
         <v>1770051311270</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>32</v>
       </c>
       <c r="G5" t="s">
         <v>9</v>
@@ -4666,19 +4808,19 @@
         <v>1770051311271</v>
       </c>
       <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4695,7 +4837,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="4" max="4" width="19.25" customWidth="1"/>
@@ -4703,93 +4845,76 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
         <v>38</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>42</v>
+      <c r="A2" s="5">
+        <v>2032126</v>
       </c>
       <c r="B2">
         <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>44</v>
+      <c r="A3" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5">
-        <v>12345</v>
+        <v>32126</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
       </c>
       <c r="E4">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="5">
-        <v>14521</v>
-      </c>
-      <c r="B5">
-        <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5">
-        <v>500</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:E2 B4:C4 B3 D3:E3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:E1 B3:C3 B2:C2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4806,10 +4931,10 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -4817,474 +4942,361 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>أكاديمية مشالى للالكترونيات</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="B14" t="s">
+        <v>284</v>
       </c>
       <c r="C14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>129</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>#f7f9f8</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="B16" t="s">
+        <v>233</v>
       </c>
       <c r="C16" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_logo_image</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>academy-video-icon.svg</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>مسار صورة رمز فيديو الأكاديمية بجوار الاسم</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_description_color</t>
-        </is>
-      </c>
-      <c r="B18"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون وصف الأكاديمية بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">academy_description_size</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم خط وصف الأكاديمية بالبكسل</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">أهلاً بك في متجر مشالى</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">عبارة الترحيب أعلى مقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">اختياراتك التقنية</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">العنوان الرئيسي لمقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_highlight</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">بخطوات أسهل</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">السطر المميز أسفل عنوان مقدمة المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">تصفّح المنتجات والأقسام، قارن التفاصيل والأسعار، ثم أرسل طلبك مباشرة عبر واتساب.</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">النص التعريفي أسفل عنوان المتجر</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker_color</t>
-        </is>
-      </c>
-      <c r="B24"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون عبارة الترحيب بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title_color</t>
-        </is>
-      </c>
-      <c r="B25"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون عنوان المتجر بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_highlight_color</t>
-        </is>
-      </c>
-      <c r="B26"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون السطر المميز بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description_color</t>
-        </is>
-      </c>
-      <c r="B27"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">لون النص التعريفي بصيغة HEX</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_kicker_size</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم عبارة الترحيب بالبكسل</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_title_size</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم عنوان المتجر بالبكسل (من 12 إلى 64)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">store_hero_description_size</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">حجم النص التعريفي بالبكسل</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>academy_logo_image</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>video.png</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>مسار صورة الأكاديمية؛ استبدل video.png أو اكتب مسار صورة أخرى لتحديثها بالموقع</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>brand_logo_image</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>logo.png</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>مسار صورة شعار المتجر؛ اكتب اسم الملف أو رابطه وارفع ملف الصورة إلى GitHub</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>app_icon_192</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>icon-192.png</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>مسار أيقونة التطبيق المربعة بحجم 192×192؛ حدّث الصورة وارفعها للمستودع</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>app_icon_512</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>icon-512.png</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>مسار أيقونة التطبيق المربعة بحجم 512×512؛ تستخدم أيضاً لشاشة بدء Android</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>app_splash_image</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>logo.png</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>مسار الصورة التي تظهر أثناء تحميل التطبيق؛ ارفع الصورة إلى المستودع</t>
-        </is>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B17" t="s">
+        <v>235</v>
+      </c>
+      <c r="C17" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>248</v>
+      </c>
+      <c r="B22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B23" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="C27" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C28" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>265</v>
+      </c>
+      <c r="B29" t="s">
+        <v>266</v>
+      </c>
+      <c r="C29" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B30" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>234</v>
+      </c>
+      <c r="B31" t="s">
+        <v>270</v>
+      </c>
+      <c r="C31" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>272</v>
+      </c>
+      <c r="B32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C32" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>275</v>
+      </c>
+      <c r="B33" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>281</v>
+      </c>
+      <c r="B35" t="s">
+        <v>273</v>
+      </c>
+      <c r="C35" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -5316,87 +5328,87 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="A1" s="6" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="K1" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>189</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="48" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="K2" s="1">
         <v>6</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="M2" s="1">
         <v>3</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -9439,7 +9451,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -9454,7 +9466,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -9478,21 +9490,21 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -9501,12 +9513,12 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -9515,12 +9527,12 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -9529,12 +9541,12 @@
         <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -9543,12 +9555,12 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -9557,12 +9569,12 @@
         <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B7">
         <v>4</v>
@@ -9571,12 +9583,12 @@
         <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -9585,12 +9597,12 @@
         <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="B9">
         <v>4</v>
@@ -9599,12 +9611,12 @@
         <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B10">
         <v>10</v>
@@ -9613,7 +9625,7 @@
         <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/store-data.xlsx
+++ b/store-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\M@shily\WEPSITE\void\11-10-2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WEPSITE\2026\mashily-store-M-shily_Store\mashily-store-M-shily_Store\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD8B1CB-5D50-4E30-B918-B9784FFF3A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33222E8-94B8-4FDE-A835-4BB5669FF099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11160" tabRatio="766" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="766" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ticker" sheetId="8" r:id="rId1"/>
@@ -335,7 +335,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="293">
   <si>
     <t>id</t>
   </si>
@@ -1220,6 +1220,30 @@
   </si>
   <si>
     <t>التعليمية</t>
+  </si>
+  <si>
+    <t>cart_auto_close_seconds</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>عدد الثواني قبل إغلاق السلة تلقائياً بعد إضافة صنف؛ اكتب 0 لإيقاف الإغلاق التلقائي</t>
+  </si>
+  <si>
+    <t>bank_name</t>
+  </si>
+  <si>
+    <t>اسم البنك للتحويل البنكي</t>
+  </si>
+  <si>
+    <t>bank_account</t>
+  </si>
+  <si>
+    <t>رقم الحساب البنكي للتحويل</t>
+  </si>
+  <si>
+    <t>الأهلي</t>
   </si>
 </sst>
 </file>
@@ -4921,7 +4945,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="18.375" bestFit="1" customWidth="1"/>
@@ -5297,6 +5321,39 @@
       </c>
       <c r="C35" t="s">
         <v>282</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>285</v>
+      </c>
+      <c r="B36" t="s">
+        <v>286</v>
+      </c>
+      <c r="C36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>288</v>
+      </c>
+      <c r="B37" t="s">
+        <v>292</v>
+      </c>
+      <c r="C37" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>290</v>
+      </c>
+      <c r="B38">
+        <v>123456</v>
+      </c>
+      <c r="C38" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
